--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -1320,26 +1320,30 @@
       <c r="Q5" s="42" t="n"/>
     </row>
     <row r="6" hidden="1" ht="40" customHeight="1">
-      <c r="A6" s="78" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
+      <c r="A6" s="81" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="n"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Group HRIS Manager</t>
+          <t>People Operations and HRIS Lead</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>CLM Search (groupe industriel mondial)</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>euremotejobs.com</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -1349,40 +1353,33 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Worldwide</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Groupe industriel 40+ pays, 170K salariés, 30Mds€ — SF expertise non negotiable (Comp/Recruiting/Reporting) — évolution HRIS Director — FIT PARFAIT (L'Oréal 40+ pays)</t>
+          <t>Builder role HRIS + People Ops : talent management, performance, L&amp;D, succession, org design, compensation. AI company 11B USD, scale rapide. Pas de plateforme SAP mentionnee. Worldwide remote. Postulé le 04/08/2026 (formulaire : question mission ElevenLabs + hard problem).</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4415288591</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>95 K€</t>
-        </is>
-      </c>
+          <t>https://euremotejobs.com/job/people-operations-and-hris-lead/</t>
+        </is>
+      </c>
+      <c r="N6" s="40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
+        </is>
+      </c>
+      <c r="O6" s="40" t="n"/>
+      <c r="P6" s="40" t="n"/>
       <c r="Q6" s="42" t="n"/>
     </row>
     <row r="7" hidden="1" ht="40" customHeight="1">
@@ -1395,17 +1392,17 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Senior Manager Conseil Talent Management F/H</t>
+          <t>Group HRIS Manager</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>HRConseil</t>
+          <t>CLM Search (groupe industriel mondial)</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>SmartRecruiters</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1420,43 +1417,39 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Hybride (3j/sem)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>75 000 - 85 000 € + 8 000 € bonus</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil SIRH (Workday, SF, Oracle HCM). 15+ ans requis, maîtrise SF, face client, avant-vente, management consultants. Salaire dans la cible haute. Fit parfait avec le profil Gaëtan (15 ans, SAP/SF, L'Oréal, avant-vente).</t>
+          <t>Groupe industriel 40+ pays, 170K salariés, 30Mds€ — SF expertise non negotiable (Comp/Recruiting/Reporting) — évolution HRIS Director — FIT PARFAIT (L'Oréal 40+ pays)</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/HRConseil1/744000100293238-senior-manager-conseil-talent-management-f-h-cdi</t>
+          <t>https://fr.linkedin.com/jobs/view/4415288591</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>82 K€</t>
-        </is>
-      </c>
-      <c r="Q7" s="42" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
+          <t>95 K€</t>
+        </is>
+      </c>
+      <c r="Q7" s="42" t="n"/>
     </row>
     <row r="8" hidden="1" ht="40" customHeight="1">
-      <c r="A8" s="77" t="inlineStr">
+      <c r="A8" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1465,17 +1458,17 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Senior Principal Success Manager</t>
+          <t>Senior Manager Conseil Talent Management F/H</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>HRConseil</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Salesforce Careers</t>
+          <t>SmartRecruiters</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1490,29 +1483,38 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="n"/>
+          <t>Hybride (3j/sem)</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>75 000 - 85 000 € + 8 000 € bonus</t>
+        </is>
+      </c>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Niveau CSM le plus élevé chez Salesforce France, profil 15 ans exact, posté 23/03/2026</t>
+          <t>Cabinet conseil SIRH (Workday, SF, Oracle HCM). 15+ ans requis, maîtrise SF, face client, avant-vente, management consultants. Salaire dans la cible haute. Fit parfait avec le profil Gaëtan (15 ans, SAP/SF, L'Oréal, avant-vente).</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>https://careers.salesforce.com/en/jobs/jr330883/senior-principal-success-manager/</t>
+          <t>https://jobs.smartrecruiters.com/HRConseil1/744000100293238-senior-manager-conseil-talent-management-f-h-cdi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>82 K€</t>
         </is>
       </c>
       <c r="Q8" s="42" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -1526,17 +1528,17 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors H/F</t>
+          <t>Senior Principal Success Manager</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>HR Path</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>HR Path Careers</t>
+          <t>Salesforce Careers</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1546,7 +1548,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Paris La Défense</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1558,27 +1560,27 @@
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Cabinet SIRH majeur, projets SF internationaux, 2 ans mini SF — profil L'Oréal 40 pays en cible directe</t>
+          <t>Niveau CSM le plus élevé chez Salesforce France, profil 15 ans exact, posté 23/03/2026</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
+          <t>https://careers.salesforce.com/en/jobs/jr330883/senior-principal-success-manager/</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS.pdf</t>
         </is>
       </c>
       <c r="Q9" s="42" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="10" hidden="1" ht="40" customHeight="1">
-      <c r="A10" s="78" t="inlineStr">
+      <c r="A10" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1587,178 +1589,182 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
+          <t>Consultant SAP SuccessFactors H/F</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>HR Path</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>HR Path Careers</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Paris La Défense</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Cabinet SIRH majeur, projets SF internationaux, 2 ans mini SF — profil L'Oréal 40 pays en cible directe</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="Q10" s="42" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" hidden="1" ht="40" customHeight="1">
+      <c r="A11" s="78" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
           <t>Directeur de Programme SIRH Senior H/F</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>LeHibou (client grand groupe)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>650-780 €/j</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>18 mois (démarrage août 2026)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Pilotage transformation RH grand groupe international bout en bout. 15 ans requis, SAP SF/TalentSoft/Workday. TJM dans cible haute, durée longue. Profil parfait.</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
         </is>
       </c>
-      <c r="Q10" s="42" t="inlineStr">
+      <c r="Q11" s="42" t="inlineStr">
         <is>
           <t>17/06/2026</t>
         </is>
       </c>
     </row>
-    <row r="11" hidden="1" ht="40" customHeight="1">
-      <c r="A11" s="77" t="inlineStr">
+    <row r="12" hidden="1" ht="40" customHeight="1">
+      <c r="A12" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Consultant(e) SIRH – Audit SIRH Grand Groupe</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Client grand groupe (via Le Club des RH)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>leclubdesrh.fr</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Partiel (2j/sem)</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>900 €/j</t>
         </is>
       </c>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>TJM 900€/j. Audit SIRH grand groupe, 2j/sem Paris. Mission visible uniquement après inscription sur app.leclubdesrh.fr (rejoindre la communauté via airtable.com/appqNConNIfeCCjB8/shrhxbRraMvUqda2C).</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>https://app.leclubdesrh.fr/</t>
         </is>
       </c>
-      <c r="Q11" s="42" t="n"/>
-    </row>
-    <row r="12" hidden="1" ht="40" customHeight="1">
-      <c r="A12" s="78" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Directeur de Programme SIRH Senior H/F</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>LeHibou (client grand groupe)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>free-work.com</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>650-780 €/j</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>18 mois (démarrage août 2026)</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>Pilotage transformation RH grand groupe international bout en bout. 15 ans requis, SAP SF/Workday. TJM dans cible haute, durée longue.</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
-        </is>
-      </c>
-      <c r="Q12" s="42" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
+      <c r="N12" s="40" t="n"/>
+      <c r="O12" s="40" t="n"/>
+      <c r="P12" s="40" t="n"/>
+      <c r="Q12" s="42" t="n"/>
     </row>
     <row r="13" hidden="1" ht="40" customHeight="1">
-      <c r="A13" s="77" t="inlineStr">
+      <c r="A13" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1767,73 +1773,65 @@
       <c r="C13" s="40" t="n"/>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Data Migration SAP SuccessFactors Consultant (24 mois)</t>
+          <t>Directeur de Programme SIRH Senior H/F</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via Freelance-Informatique)</t>
+          <t>LeHibou (client grand groupe)</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Freelance-Informatique</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Clichy (92)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>650-780 €/j</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>24 mois (démarrage ASAP)</t>
+          <t>18 mois (démarrage août 2026)</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>Spécialité migration données SAP SuccessFactors. Profil Gaëtan : migration SAP HR → SF sur L'Oréal 40+ pays = différenciant majeur. Mission longue et très alignée.</t>
+          <t>Pilotage transformation RH grand groupe international bout en bout. 15 ans requis, SAP SF/Workday. TJM dans cible haute, durée longue.</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/cv-mission-consultant-sap-successfactors-freelance-f11256</t>
-        </is>
-      </c>
-      <c r="N13" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
-        </is>
-      </c>
-      <c r="O13" s="40" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
+        </is>
+      </c>
+      <c r="N13" s="40" t="n"/>
+      <c r="O13" s="40" t="n"/>
       <c r="P13" s="40" t="n"/>
       <c r="Q13" s="42" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="14" hidden="1" ht="40" customHeight="1">
-      <c r="A14" s="78" t="inlineStr">
+      <c r="A14" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1842,65 +1840,73 @@
       <c r="C14" s="40" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>HR Tech Run Lead</t>
+          <t>Data Migration SAP SuccessFactors Consultant (24 mois)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>L'Oréal</t>
+          <t>n.c. (via Freelance-Informatique)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Freelance-Informatique</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Clichy (92)</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Hybride (3j bureau / 2j remote)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>nc</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="n"/>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>24 mois (démarrage ASAP)</t>
+        </is>
+      </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>EXCEPTIONNEL : Biarritz + 10 ans L'Oréal SAP HCM/SF dans le profil — 10+ ans HRIS requis — posté il y a 5 jours</t>
+          <t>Spécialité migration données SAP SuccessFactors. Profil Gaëtan : migration SAP HR → SF sur L'Oréal 40+ pays = différenciant majeur. Mission longue et très alignée.</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/hr-tech-run-lead-at-l-or%C3%A9al-4435534808</t>
+          <t>https://www.freelance-informatique.fr/cv-mission-consultant-sap-successfactors-freelance-f11256</t>
         </is>
       </c>
       <c r="N14" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
         </is>
       </c>
       <c r="O14" s="40" t="inlineStr">
         <is>
-          <t>90-110K€</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P14" s="40" t="n"/>
-      <c r="Q14" s="42" t="n"/>
+      <c r="Q14" s="42" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="15" hidden="1" ht="40" customHeight="1">
-      <c r="A15" s="77" t="inlineStr">
+      <c r="A15" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1909,12 +1915,12 @@
       <c r="C15" s="40" t="n"/>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Senior AMOA Talent Consultant M/F</t>
+          <t>HR Tech Run Lead</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>MP People</t>
+          <t>L'Oréal</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1929,33 +1935,45 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="n"/>
+          <t>Hybride (3j bureau / 2j remote)</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>nc</t>
+        </is>
+      </c>
       <c r="K15" s="6" t="n"/>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>AMOA Talent senior = profil exact ; posté hier</t>
+          <t>EXCEPTIONNEL : Biarritz + 10 ans L'Oréal SAP HCM/SF dans le profil — 10+ ans HRIS requis — posté il y a 5 jours</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/senior-amoa-talent-consultant-m-f-at-mp-people-4437133991</t>
-        </is>
-      </c>
-      <c r="N15" s="40" t="n"/>
-      <c r="O15" s="40" t="n"/>
+          <t>https://fr.linkedin.com/jobs/view/hr-tech-run-lead-at-l-or%C3%A9al-4435534808</t>
+        </is>
+      </c>
+      <c r="N15" s="40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+        </is>
+      </c>
+      <c r="O15" s="40" t="inlineStr">
+        <is>
+          <t>90-110K€</t>
+        </is>
+      </c>
       <c r="P15" s="40" t="n"/>
       <c r="Q15" s="42" t="n"/>
     </row>
     <row r="16" hidden="1" ht="40" customHeight="1">
-      <c r="A16" s="78" t="inlineStr">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1964,7 +1982,7 @@
       <c r="C16" s="40" t="n"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Consultant Senior AMOA Talent H/F</t>
+          <t>Senior AMOA Talent Consultant M/F</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1996,18 +2014,18 @@
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>Variante Senior AMOA Talent ; posté hier</t>
+          <t>AMOA Talent senior = profil exact ; posté hier</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-senior-amoa-talent-h-f-at-mp-people-4437143555</t>
+          <t>https://fr.linkedin.com/jobs/view/senior-amoa-talent-consultant-m-f-at-mp-people-4437133991</t>
         </is>
       </c>
       <c r="N16" s="40" t="n"/>
       <c r="O16" s="40" t="n"/>
       <c r="P16" s="40" t="n"/>
-      <c r="Q16" s="40" t="n"/>
+      <c r="Q16" s="42" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="78" t="inlineStr">
@@ -2019,7 +2037,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Manager AMOA Talent M/F</t>
+          <t>Consultant Senior AMOA Talent H/F</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2051,12 +2069,12 @@
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Manager AMOA Talent ; 3 postes MP People simultanés = cabinet en forte croissance</t>
+          <t>Variante Senior AMOA Talent ; posté hier</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/manager-amoa-talent-m-f-at-mp-people-4437146495</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-senior-amoa-talent-h-f-at-mp-people-4437143555</t>
         </is>
       </c>
       <c r="N17" s="40" t="n"/>
@@ -2065,75 +2083,59 @@
       <c r="Q17" s="40" t="n"/>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="83" t="inlineStr">
+      <c r="A18" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B18" s="40" t="n"/>
       <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="inlineStr">
-        <is>
-          <t>Directeur de Programme SIRH Senior H/F</t>
-        </is>
-      </c>
-      <c r="E18" s="40" t="inlineStr">
-        <is>
-          <t>LeHibou</t>
-        </is>
-      </c>
-      <c r="F18" s="40" t="inlineStr">
-        <is>
-          <t>free-work</t>
-        </is>
-      </c>
-      <c r="G18" s="40" t="inlineStr">
-        <is>
-          <t>Mission freelance</t>
-        </is>
-      </c>
-      <c r="H18" s="40" t="inlineStr">
-        <is>
-          <t>Paris (75)</t>
-        </is>
-      </c>
-      <c r="I18" s="40" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="J18" s="40" t="inlineStr">
-        <is>
-          <t>650-780€/j</t>
-        </is>
-      </c>
-      <c r="K18" s="40" t="inlineStr">
-        <is>
-          <t>18 mois</t>
-        </is>
-      </c>
-      <c r="L18" s="40" t="inlineStr">
-        <is>
-          <t>Programme RH grand groupe, SAP SF + PowerBI, fort fit ; 17/06/2026</t>
-        </is>
-      </c>
-      <c r="M18" s="40" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Manager AMOA Talent M/F</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>MP People</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Manager AMOA Talent ; 3 postes MP People simultanés = cabinet en forte croissance</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/manager-amoa-talent-m-f-at-mp-people-4437146495</t>
         </is>
       </c>
       <c r="N18" s="40" t="n"/>
       <c r="O18" s="40" t="n"/>
-      <c r="P18" s="40" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="Q18" s="40" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
+      <c r="P18" s="40" t="n"/>
+      <c r="Q18" s="40" t="n"/>
     </row>
     <row r="19" hidden="1" ht="40" customHeight="1">
       <c r="A19" s="83" t="inlineStr">
@@ -2145,52 +2147,52 @@
       <c r="C19" s="40" t="n"/>
       <c r="D19" s="40" t="inlineStr">
         <is>
-          <t>SAP Project Manager / Trainer</t>
+          <t>Directeur de Programme SIRH Senior H/F</t>
         </is>
       </c>
       <c r="E19" s="40" t="inlineStr">
         <is>
-          <t>N/C (via eursap.eu)</t>
+          <t>LeHibou</t>
         </is>
       </c>
       <c r="F19" s="40" t="inlineStr">
         <is>
-          <t>eursap.eu</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G19" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H19" s="40" t="inlineStr">
         <is>
-          <t>100% Remote</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I19" s="40" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="J19" s="40" t="inlineStr">
         <is>
-          <t>80-156k€/an + equity</t>
+          <t>650-780€/j</t>
         </is>
       </c>
       <c r="K19" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>18 mois</t>
         </is>
       </c>
       <c r="L19" s="40" t="inlineStr">
         <is>
-          <t>SAP PM + formateur, full remote, fourchette haute, démarrage août 2026 ; ref 34811</t>
+          <t>Programme RH grand groupe, SAP SF + PowerBI, fort fit ; 17/06/2026</t>
         </is>
       </c>
       <c r="M19" s="40" t="inlineStr">
         <is>
-          <t>https://eursap.eu/sap-jobs/france/</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
         </is>
       </c>
       <c r="N19" s="40" t="n"/>
@@ -2202,7 +2204,7 @@
       </c>
       <c r="Q19" s="40" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2216,27 +2218,27 @@
       <c r="C20" s="40" t="n"/>
       <c r="D20" s="40" t="inlineStr">
         <is>
-          <t>Chef de Projet Fonctionnel SIRH 100% Remote</t>
+          <t>SAP Project Manager / Trainer</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>N/C (via eursap.eu)</t>
         </is>
       </c>
       <c r="F20" s="40" t="inlineStr">
         <is>
-          <t>freelance-informatique.fr</t>
+          <t>eursap.eu</t>
         </is>
       </c>
       <c r="G20" s="40" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H20" s="40" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>100% Remote</t>
         </is>
       </c>
       <c r="I20" s="40" t="inlineStr">
@@ -2246,34 +2248,34 @@
       </c>
       <c r="J20" s="40" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>80-156k€/an + equity</t>
         </is>
       </c>
       <c r="K20" s="40" t="inlineStr">
         <is>
-          <t>6 mois</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="L20" s="40" t="inlineStr">
         <is>
-          <t>Full remote, ASAP ; freelance-info ; 10/07/2026</t>
+          <t>SAP PM + formateur, full remote, fourchette haute, démarrage août 2026 ; ref 34811</t>
         </is>
       </c>
       <c r="M20" s="40" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/chef-de-projet-sirh-freelance-n112</t>
+          <t>https://eursap.eu/sap-jobs/france/</t>
         </is>
       </c>
       <c r="N20" s="40" t="n"/>
       <c r="O20" s="40" t="n"/>
       <c r="P20" s="40" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="Q20" s="40" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2287,32 +2289,32 @@
       <c r="C21" s="40" t="n"/>
       <c r="D21" s="40" t="inlineStr">
         <is>
-          <t>HRIS Project Manager</t>
+          <t>Chef de Projet Fonctionnel SIRH 100% Remote</t>
         </is>
       </c>
       <c r="E21" s="40" t="inlineStr">
         <is>
-          <t>Next Ventures</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="F21" s="40" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>freelance-informatique.fr</t>
         </is>
       </c>
       <c r="G21" s="40" t="inlineStr">
         <is>
-          <t>Contrat 6 mois</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H21" s="40" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I21" s="40" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J21" s="40" t="inlineStr">
@@ -2327,12 +2329,12 @@
       </c>
       <c r="L21" s="40" t="inlineStr">
         <is>
-          <t>SAP SF + ServiceNow, secteur financier, fort fit ; 03/07/2026</t>
-        </is>
-      </c>
-      <c r="M21" s="91" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/jobs/view/hris-sirh-project-manager-at-next-ventures-4433811211</t>
+          <t>Full remote, ASAP ; freelance-info ; 10/07/2026</t>
+        </is>
+      </c>
+      <c r="M21" s="40" t="inlineStr">
+        <is>
+          <t>https://www.freelance-informatique.fr/chef-de-projet-sirh-freelance-n112</t>
         </is>
       </c>
       <c r="N21" s="40" t="n"/>
@@ -2344,87 +2346,83 @@
       </c>
       <c r="Q21" s="40" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="77" t="inlineStr">
+      <c r="A22" s="83" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B22" s="40" t="n"/>
       <c r="C22" s="40" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Global Tech HR Domain Manager F/M/X</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Sephora</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Indeed</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Neuilly-sur-Seine</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>À clarifier</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>À négocier (viser 90-110K€)</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Supervision déploiement RH/SAP, coordination équipes internes + partenaires ext = profil DPO exact. LVMH group. Publié 13/07/2026. Proche profil L'Oréal HR Domain.</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>https://fr.indeed.com/q-consultant-sap-successfactors-emplois.html</t>
-        </is>
-      </c>
-      <c r="N22" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O22" s="40" t="inlineStr">
-        <is>
-          <t>90-110K€</t>
-        </is>
-      </c>
-      <c r="P22" s="40" t="n"/>
-      <c r="Q22" s="42" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
+      <c r="D22" s="40" t="inlineStr">
+        <is>
+          <t>HRIS Project Manager</t>
+        </is>
+      </c>
+      <c r="E22" s="40" t="inlineStr">
+        <is>
+          <t>Next Ventures</t>
+        </is>
+      </c>
+      <c r="F22" s="40" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G22" s="40" t="inlineStr">
+        <is>
+          <t>Contrat 6 mois</t>
+        </is>
+      </c>
+      <c r="H22" s="40" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I22" s="40" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J22" s="40" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K22" s="40" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
+      <c r="L22" s="40" t="inlineStr">
+        <is>
+          <t>SAP SF + ServiceNow, secteur financier, fort fit ; 03/07/2026</t>
+        </is>
+      </c>
+      <c r="M22" s="91" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/hris-sirh-project-manager-at-next-ventures-4433811211</t>
+        </is>
+      </c>
+      <c r="N22" s="40" t="n"/>
+      <c r="O22" s="40" t="n"/>
+      <c r="P22" s="40" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="Q22" s="40" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="23" hidden="1" ht="40" customHeight="1">
-      <c r="A23" s="78" t="inlineStr">
+      <c r="A23" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -2433,134 +2431,140 @@
       <c r="C23" s="40" t="n"/>
       <c r="D23" s="5" t="inlineStr">
         <is>
+          <t>Global Tech HR Domain Manager F/M/X</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Sephora</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Neuilly-sur-Seine</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>À clarifier</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>À négocier (viser 90-110K€)</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Supervision déploiement RH/SAP, coordination équipes internes + partenaires ext = profil DPO exact. LVMH group. Publié 13/07/2026. Proche profil L'Oréal HR Domain.</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.indeed.com/q-consultant-sap-successfactors-emplois.html</t>
+        </is>
+      </c>
+      <c r="N23" s="40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O23" s="40" t="inlineStr">
+        <is>
+          <t>90-110K€</t>
+        </is>
+      </c>
+      <c r="P23" s="40" t="n"/>
+      <c r="Q23" s="42" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" hidden="1" ht="40" customHeight="1">
+      <c r="A24" s="78" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B24" s="40" t="n"/>
+      <c r="C24" s="40" t="n"/>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
           <t>HR Domain Manager</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Parfums Christian Dior</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Indeed</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>À clarifier</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>À négocier (viser 90-110K€)</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>LVMH. Coordination équipes internes, consultants externes et équipes dev Finance &amp; HR. Fit direct 10 ans L'Oréal = same environment. Publié 13/07/2026.</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>https://fr.indeed.com/q-consultant-sap-successfactors-emplois.html</t>
         </is>
       </c>
-      <c r="N23" s="40" t="inlineStr">
+      <c r="N24" s="40" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O23" s="40" t="inlineStr">
+      <c r="O24" s="40" t="inlineStr">
         <is>
           <t>90-110K€</t>
         </is>
       </c>
-      <c r="P23" s="40" t="n"/>
-      <c r="Q23" s="42" t="n"/>
-    </row>
-    <row r="24" hidden="1" ht="40" customHeight="1">
-      <c r="A24" s="50" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Senior Manager, SAP SuccessFactors Employee Central &amp; Platform</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Foundever</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>UK (remote)</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>£75-90K (~87-105K€)</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Lead équipe globale SF EC 40+ pays ; gouvernance, stratégie, config EC, RBP, intégrations HR/Payroll/Finance — calque L'Oréal 40+ pays parfait</t>
-        </is>
-      </c>
-      <c r="M24" s="69" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4429527206/</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>95K€</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+      <c r="P24" s="40" t="n"/>
       <c r="Q24" s="42" t="n"/>
     </row>
     <row r="25" hidden="1" ht="40" customHeight="1">
@@ -2569,11 +2573,12 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
         <is>
           <t>À postuler</t>
         </is>
       </c>
+      <c r="C25" s="40" t="n"/>
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Responsable SIRH F/H</t>
@@ -2620,11 +2625,13 @@
           <t>https://www.welcometothejungle.com/fr/companies/kpmg-france/jobs/responsable-sirh-f-h_courbevoie</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="N25" s="40" t="n"/>
+      <c r="O25" s="40" t="inlineStr">
         <is>
           <t>90-110K€</t>
         </is>
       </c>
+      <c r="P25" s="40" t="n"/>
       <c r="Q25" s="42" t="inlineStr">
         <is>
           <t>18/06/2026</t>
@@ -2637,11 +2644,12 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="40" t="inlineStr">
         <is>
           <t>À postuler</t>
         </is>
       </c>
+      <c r="C26" s="40" t="n"/>
       <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Consultant Manager SIRH - HR Transformation</t>
@@ -2688,11 +2696,13 @@
           <t>https://careers.soprasteria.com/job/consultant-manager-sirh-hr-transformation-ile-de-france-in-courbevoie-france-jid-792</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="N26" s="40" t="n"/>
+      <c r="O26" s="40" t="inlineStr">
         <is>
           <t>70-85K€</t>
         </is>
       </c>
+      <c r="P26" s="40" t="n"/>
       <c r="Q26" s="42" t="inlineStr">
         <is>
           <t>18/06/2026</t>
@@ -3921,6 +3931,8 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
+      <c r="B46" s="40" t="n"/>
+      <c r="C46" s="40" t="n"/>
       <c r="D46" s="5" t="inlineStr">
         <is>
           <t>HRIS &amp; AI Tech Pre-Sales Specialist</t>
@@ -3963,16 +3975,17 @@
           <t>https://jobs.smartrecruiters.com/Arago/744000139094386-hris-ai-tech-pre-sales-specialist</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="40" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O46" s="40" t="inlineStr">
         <is>
           <t>90-110K€</t>
         </is>
       </c>
+      <c r="P46" s="40" t="n"/>
       <c r="Q46" s="42" t="inlineStr">
         <is>
           <t>06/07/2026</t>
@@ -3985,6 +3998,8 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
+      <c r="B47" s="40" t="n"/>
+      <c r="C47" s="40" t="n"/>
       <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Consultant(e) AMOA SAP SuccessFactors (H/F)</t>
@@ -4027,16 +4042,17 @@
           <t>https://www.convictionsrh.com/job/consultante-amoa-sap-successfactors-h-f/</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="40" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O47" s="40" t="inlineStr">
         <is>
           <t>75-85K€</t>
         </is>
       </c>
+      <c r="P47" s="40" t="n"/>
       <c r="Q47" s="42" t="inlineStr">
         <is>
           <t>06/07/2026</t>
@@ -7044,6 +7060,8 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
+      <c r="B93" s="40" t="n"/>
+      <c r="C93" s="40" t="n"/>
       <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Manager / Senior Manager SIRH</t>
@@ -7090,17 +7108,17 @@
           <t>https://fr.linkedin.com/jobs/view/4433103113</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="N93" s="40" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="O93" s="40" t="inlineStr">
         <is>
           <t>90K€</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="P93" s="40" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
@@ -7113,6 +7131,8 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
+      <c r="B94" s="40" t="n"/>
+      <c r="C94" s="40" t="n"/>
       <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Consultant SAP SuccessFactors Senior (Freelance)</t>
@@ -7159,12 +7179,13 @@
           <t>https://fr.linkedin.com/jobs/view/4430968714</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="N94" s="40" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="O94" s="40" t="n"/>
+      <c r="P94" s="40" t="inlineStr">
         <is>
           <t>14/07/2026</t>
         </is>
@@ -7177,12 +7198,12 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="40" t="inlineStr">
         <is>
           <t>Consultant Senior SIRH SAP SF Performance &amp; Goals H/F</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="40" t="inlineStr">
         <is>
           <t>Grand groupe international</t>
         </is>
@@ -7237,6 +7258,9 @@
           <t>11/07/2026</t>
         </is>
       </c>
+      <c r="N95" s="40" t="n"/>
+      <c r="O95" s="40" t="n"/>
+      <c r="P95" s="40" t="n"/>
       <c r="Q95" s="42" t="n"/>
     </row>
     <row r="96" hidden="1" ht="16" customHeight="1">
@@ -10193,6 +10217,8 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
+      <c r="B141" s="40" t="n"/>
+      <c r="C141" s="40" t="n"/>
       <c r="D141" s="5" t="inlineStr">
         <is>
           <t>Consultant Senior SAP SuccessFactors</t>
@@ -10235,12 +10261,12 @@
           <t>https://fr.linkedin.com/jobs/view/consultant-senior-sap-successfactors-at-dxc-technology-4438231698</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr">
+      <c r="N141" s="40" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O141" t="inlineStr">
+      <c r="O141" s="40" t="inlineStr">
         <is>
           <t>70-85K€</t>
         </is>
@@ -10253,6 +10279,8 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
+      <c r="B142" s="40" t="n"/>
+      <c r="C142" s="40" t="n"/>
       <c r="D142" s="5" t="inlineStr">
         <is>
           <t>Consultant SAP SuccessFactors expérimenté (H/F)</t>
@@ -10295,12 +10323,12 @@
           <t>https://fr.linkedin.com/jobs/view/consultant-sap-successfactors-exp%C3%A9riment%C3%A9-h-f-at-sqorus-4396619283</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr">
+      <c r="N142" s="40" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr">
+      <c r="O142" s="40" t="inlineStr">
         <is>
           <t>70-85K€</t>
         </is>
@@ -10367,6 +10395,7 @@
           <t>70-85K€</t>
         </is>
       </c>
+      <c r="P143" s="40" t="n"/>
       <c r="Q143" s="42" t="inlineStr">
         <is>
           <t>07/05/2025</t>
@@ -10441,6 +10470,7 @@
           <t>650-750€/j</t>
         </is>
       </c>
+      <c r="P144" s="40" t="n"/>
       <c r="Q144" s="42" t="n"/>
     </row>
     <row r="145" hidden="1" ht="32" customHeight="1">
@@ -21967,17 +21997,17 @@
       <c r="C315" s="40" t="n"/>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>People Operations and HRIS Lead</t>
+          <t>Consultant SIRH (F/H)</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>Onepoint</t>
         </is>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
-          <t>euremotejobs.com</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G315" s="6" t="inlineStr">
@@ -21987,34 +22017,42 @@
       </c>
       <c r="H315" s="6" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I315" s="6" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J315" s="6" t="n"/>
       <c r="K315" s="6" t="n"/>
       <c r="L315" s="5" t="inlineStr">
         <is>
-          <t>Builder role HRIS + People Ops : talent management, performance, L&amp;D, succession, org design, compensation. AI company 11B USD, scale rapide. Pas de plateforme SAP mentionnee. Worldwide remote.</t>
+          <t>Publié il y a 1 jour (30/07/2026). Onepoint cabinet conseil digital. Missions AMOA, audit SIRH, déploiements SAP/Oracle/Workday/ADP, conduite du changement. 2-8 ans expérience. 200+ candidatures — très concurrentiel. Grande école requise.</t>
         </is>
       </c>
       <c r="M315" s="5" t="inlineStr">
         <is>
-          <t>https://euremotejobs.com/job/people-operations-and-hris-lead/</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-sirh-%E2%80%93-f-h-at-onepoint-4329056727</t>
         </is>
       </c>
       <c r="N315" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
-        </is>
-      </c>
-      <c r="O315" s="40" t="n"/>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O315" s="40" t="inlineStr">
+        <is>
+          <t>70-85K€</t>
+        </is>
+      </c>
       <c r="P315" s="40" t="n"/>
-      <c r="Q315" s="42" t="n"/>
+      <c r="Q315" s="42" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="316" hidden="1" ht="32" customHeight="1">
       <c r="A316" s="81" t="inlineStr">
@@ -22024,46 +22062,46 @@
       </c>
       <c r="B316" s="40" t="n"/>
       <c r="C316" s="40" t="n"/>
-      <c r="D316" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SIRH (F/H)</t>
-        </is>
-      </c>
-      <c r="E316" s="5" t="inlineStr">
-        <is>
-          <t>Onepoint</t>
-        </is>
-      </c>
-      <c r="F316" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G316" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H316" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I316" s="6" t="inlineStr">
+      <c r="D316" s="40" t="inlineStr">
+        <is>
+          <t>Consultant Senior AMOA GA/Paie (H/F)</t>
+        </is>
+      </c>
+      <c r="E316" s="40" t="inlineStr">
+        <is>
+          <t>HR Path</t>
+        </is>
+      </c>
+      <c r="F316" s="40" t="inlineStr">
+        <is>
+          <t>jobs.hr-path.com</t>
+        </is>
+      </c>
+      <c r="G316" s="40" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H316" s="40" t="inlineStr">
+        <is>
+          <t>Paris La Défense</t>
+        </is>
+      </c>
+      <c r="I316" s="40" t="inlineStr">
         <is>
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J316" s="6" t="n"/>
-      <c r="K316" s="6" t="n"/>
-      <c r="L316" s="5" t="inlineStr">
-        <is>
-          <t>Publié il y a 1 jour (30/07/2026). Onepoint cabinet conseil digital. Missions AMOA, audit SIRH, déploiements SAP/Oracle/Workday/ADP, conduite du changement. 2-8 ans expérience. 200+ candidatures — très concurrentiel. Grande école requise.</t>
-        </is>
-      </c>
-      <c r="M316" s="5" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-sirh-%E2%80%93-f-h-at-onepoint-4329056727</t>
+      <c r="J316" s="40" t="n"/>
+      <c r="K316" s="40" t="n"/>
+      <c r="L316" s="40" t="inlineStr">
+        <is>
+          <t>Publié 28/07/2026. AMOA RH, GA/Paie, expertise Cegid/Cegedim/ADP/HR Access. Fit partiel — Gaëtan fort sur SAP HR mais pas spécialiste paie pure sur ces outils. À postuler si SAP HCM Paie France accepté.</t>
+        </is>
+      </c>
+      <c r="M316" s="40" t="inlineStr">
+        <is>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-Senior-AMOA-GAPaie-%28HF%29-75-92042/1419635633/</t>
         </is>
       </c>
       <c r="N316" s="40" t="inlineStr">
@@ -22093,17 +22131,17 @@
       <c r="C317" s="40" t="n"/>
       <c r="D317" s="40" t="inlineStr">
         <is>
-          <t>Consultant Senior AMOA GA/Paie (H/F)</t>
+          <t>Consultant fonctionnel SIRH (F/H)</t>
         </is>
       </c>
       <c r="E317" s="40" t="inlineStr">
         <is>
-          <t>HR Path</t>
+          <t>CGI</t>
         </is>
       </c>
       <c r="F317" s="40" t="inlineStr">
         <is>
-          <t>jobs.hr-path.com</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G317" s="40" t="inlineStr">
@@ -22113,7 +22151,7 @@
       </c>
       <c r="H317" s="40" t="inlineStr">
         <is>
-          <t>Paris La Défense</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I317" s="40" t="inlineStr">
@@ -22125,12 +22163,12 @@
       <c r="K317" s="40" t="n"/>
       <c r="L317" s="40" t="inlineStr">
         <is>
-          <t>Publié 28/07/2026. AMOA RH, GA/Paie, expertise Cegid/Cegedim/ADP/HR Access. Fit partiel — Gaëtan fort sur SAP HR mais pas spécialiste paie pure sur ces outils. À postuler si SAP HCM Paie France accepté.</t>
+          <t>CGI groupe IT services. SAP-HR / SuccessFactors, secteurs transport + secteur public + RH. Fit partiel (secteur public moins dans la cible mais compétences SAP HR directement applicables).</t>
         </is>
       </c>
       <c r="M317" s="40" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-Senior-AMOA-GAPaie-%28HF%29-75-92042/1419635633/</t>
+          <t>https://www.welcometothejungle.com/fr/companies/cgi/jobs/consultant-sirh-f-h-transport-secteur-public-et-hr_paris</t>
         </is>
       </c>
       <c r="N317" s="40" t="inlineStr">
@@ -22146,12 +22184,12 @@
       <c r="P317" s="40" t="n"/>
       <c r="Q317" s="42" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="318" hidden="1" ht="16" customHeight="1">
-      <c r="A318" s="81" t="inlineStr">
+      <c r="A318" s="74" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
@@ -22160,17 +22198,17 @@
       <c r="C318" s="40" t="n"/>
       <c r="D318" s="40" t="inlineStr">
         <is>
-          <t>Consultant fonctionnel SIRH (F/H)</t>
+          <t>Responsable SIRH et Data RH F/H</t>
         </is>
       </c>
       <c r="E318" s="40" t="inlineStr">
         <is>
-          <t>CGI</t>
+          <t>Mindquest (télécom)</t>
         </is>
       </c>
       <c r="F318" s="40" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G318" s="40" t="inlineStr">
@@ -22180,7 +22218,7 @@
       </c>
       <c r="H318" s="40" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Montrouge (92)</t>
         </is>
       </c>
       <c r="I318" s="40" t="inlineStr">
@@ -22188,34 +22226,30 @@
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J318" s="40" t="n"/>
-      <c r="K318" s="40" t="n"/>
+      <c r="J318" s="40" t="inlineStr">
+        <is>
+          <t>42-69k€/an</t>
+        </is>
+      </c>
+      <c r="K318" s="40" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="L318" s="40" t="inlineStr">
         <is>
-          <t>CGI groupe IT services. SAP-HR / SuccessFactors, secteurs transport + secteur public + RH. Fit partiel (secteur public moins dans la cible mais compétences SAP HR directement applicables).</t>
+          <t>7+ ans SIRH ; Workday/ADP (pas SAP SF) ; 25/06/2026</t>
         </is>
       </c>
       <c r="M318" s="40" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/cgi/jobs/consultant-sirh-f-h-transport-secteur-public-et-hr_paris</t>
-        </is>
-      </c>
-      <c r="N318" s="40" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O318" s="40" t="inlineStr">
-        <is>
-          <t>70-85K€</t>
-        </is>
-      </c>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/responsable-sirh-et-data-rh-f-h</t>
+        </is>
+      </c>
+      <c r="N318" s="40" t="n"/>
+      <c r="O318" s="40" t="n"/>
       <c r="P318" s="40" t="n"/>
-      <c r="Q318" s="42" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
+      <c r="Q318" s="42" t="n"/>
     </row>
     <row r="319" hidden="1" ht="32" customHeight="1">
       <c r="A319" s="74" t="inlineStr">
@@ -22227,12 +22261,12 @@
       <c r="C319" s="40" t="n"/>
       <c r="D319" s="40" t="inlineStr">
         <is>
-          <t>Responsable SIRH et Data RH F/H</t>
+          <t>Chef de projet technique SIRH H/F</t>
         </is>
       </c>
       <c r="E319" s="40" t="inlineStr">
         <is>
-          <t>Mindquest (télécom)</t>
+          <t>Groupe SYD</t>
         </is>
       </c>
       <c r="F319" s="40" t="inlineStr">
@@ -22242,37 +22276,37 @@
       </c>
       <c r="G319" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>CDI/Freelance</t>
         </is>
       </c>
       <c r="H319" s="40" t="inlineStr">
         <is>
-          <t>Montrouge (92)</t>
+          <t>Niort (79)</t>
         </is>
       </c>
       <c r="I319" s="40" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride 2j</t>
         </is>
       </c>
       <c r="J319" s="40" t="inlineStr">
         <is>
-          <t>42-69k€/an</t>
+          <t>45-50k€ ou 500-580€/j</t>
         </is>
       </c>
       <c r="K319" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>12 mois</t>
         </is>
       </c>
       <c r="L319" s="40" t="inlineStr">
         <is>
-          <t>7+ ans SIRH ; Workday/ADP (pas SAP SF) ; 25/06/2026</t>
+          <t>Workday/SAP HR/Talentsoft ; Niort proche Anglet mais hybride ; 06/07/2026</t>
         </is>
       </c>
       <c r="M319" s="40" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/responsable-sirh-et-data-rh-f-h</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/chef-de-projet-technique-sirh-h-f</t>
         </is>
       </c>
       <c r="N319" s="40" t="n"/>
@@ -22290,12 +22324,12 @@
       <c r="C320" s="40" t="n"/>
       <c r="D320" s="40" t="inlineStr">
         <is>
-          <t>Chef de projet technique SIRH H/F</t>
+          <t>Directeur de programme SIRH (Monaco)</t>
         </is>
       </c>
       <c r="E320" s="40" t="inlineStr">
         <is>
-          <t>Groupe SYD</t>
+          <t>Synergie Technologies</t>
         </is>
       </c>
       <c r="F320" s="40" t="inlineStr">
@@ -22310,7 +22344,7 @@
       </c>
       <c r="H320" s="40" t="inlineStr">
         <is>
-          <t>Niort (79)</t>
+          <t>Nice/Monaco</t>
         </is>
       </c>
       <c r="I320" s="40" t="inlineStr">
@@ -22320,22 +22354,22 @@
       </c>
       <c r="J320" s="40" t="inlineStr">
         <is>
-          <t>45-50k€ ou 500-580€/j</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K320" s="40" t="inlineStr">
         <is>
-          <t>12 mois</t>
+          <t>2 ans</t>
         </is>
       </c>
       <c r="L320" s="40" t="inlineStr">
         <is>
-          <t>Workday/SAP HR/Talentsoft ; Niort proche Anglet mais hybride ; 06/07/2026</t>
+          <t>10+ ans SIRH ; Cegedim Teams RH ; Monaco/EU requis ; 05/07/2026</t>
         </is>
       </c>
       <c r="M320" s="40" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/chef-de-projet-technique-sirh-h-f</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/directeur-de-programme-sirh-monaco</t>
         </is>
       </c>
       <c r="N320" s="40" t="n"/>
@@ -22344,65 +22378,65 @@
       <c r="Q320" s="42" t="n"/>
     </row>
     <row r="321" hidden="1" ht="32" customHeight="1">
-      <c r="A321" s="74" t="inlineStr">
+      <c r="A321" s="81" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B321" s="40" t="n"/>
       <c r="C321" s="40" t="n"/>
-      <c r="D321" s="40" t="inlineStr">
-        <is>
-          <t>Directeur de programme SIRH (Monaco)</t>
-        </is>
-      </c>
-      <c r="E321" s="40" t="inlineStr">
-        <is>
-          <t>Synergie Technologies</t>
-        </is>
-      </c>
-      <c r="F321" s="40" t="inlineStr">
-        <is>
-          <t>free-work</t>
-        </is>
-      </c>
-      <c r="G321" s="40" t="inlineStr">
-        <is>
-          <t>CDI/Freelance</t>
-        </is>
-      </c>
-      <c r="H321" s="40" t="inlineStr">
-        <is>
-          <t>Nice/Monaco</t>
-        </is>
-      </c>
-      <c r="I321" s="40" t="inlineStr">
-        <is>
-          <t>Hybride 2j</t>
-        </is>
-      </c>
-      <c r="J321" s="40" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="K321" s="40" t="inlineStr">
-        <is>
-          <t>2 ans</t>
-        </is>
-      </c>
-      <c r="L321" s="40" t="inlineStr">
-        <is>
-          <t>10+ ans SIRH ; Cegedim Teams RH ; Monaco/EU requis ; 05/07/2026</t>
-        </is>
-      </c>
-      <c r="M321" s="40" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/directeur-de-programme-sirh-monaco</t>
-        </is>
-      </c>
-      <c r="N321" s="40" t="n"/>
-      <c r="O321" s="40" t="n"/>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>Consultant(e) SIRH SAP HCM SuccessFactors (H/F)</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>Inetum</t>
+        </is>
+      </c>
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>inetum.com / LinkedIn</t>
+        </is>
+      </c>
+      <c r="G321" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H321" s="6" t="inlineStr">
+        <is>
+          <t>Tunis, Tunisie</t>
+        </is>
+      </c>
+      <c r="I321" s="6" t="inlineStr">
+        <is>
+          <t>À confirmer (vérifier si remote France possible)</t>
+        </is>
+      </c>
+      <c r="J321" s="6" t="n"/>
+      <c r="K321" s="6" t="n"/>
+      <c r="L321" s="5" t="inlineStr">
+        <is>
+          <t>Inetum (acteur majeur SAP France/EMEA) recrute un consultant SAP SF avec 2+ ans exp. et certification SF. Poste basé en Tunisie — contacter pour confirmer si 100% remote depuis France accepté avant de postuler.</t>
+        </is>
+      </c>
+      <c r="M321" s="5" t="inlineStr">
+        <is>
+          <t>https://www.inetum.com/fr/accueil/carrieres/d726923c-1981-42ba-89d3-b4d0355b578d.html</t>
+        </is>
+      </c>
+      <c r="N321" s="40" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O321" s="40" t="inlineStr">
+        <is>
+          <t>À préciser selon conditions remote</t>
+        </is>
+      </c>
       <c r="P321" s="40" t="n"/>
       <c r="Q321" s="42" t="n"/>
     </row>
@@ -22416,17 +22450,17 @@
       <c r="C322" s="40" t="n"/>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) SIRH SAP HCM SuccessFactors (H/F)</t>
+          <t>HRIS Project Manager</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
         <is>
-          <t>Inetum</t>
+          <t>Sonepar</t>
         </is>
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
-          <t>inetum.com / LinkedIn</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G322" s="6" t="inlineStr">
@@ -22436,34 +22470,34 @@
       </c>
       <c r="H322" s="6" t="inlineStr">
         <is>
-          <t>Tunis, Tunisie</t>
+          <t>Paris (Ville)</t>
         </is>
       </c>
       <c r="I322" s="6" t="inlineStr">
         <is>
-          <t>À confirmer (vérifier si remote France possible)</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J322" s="6" t="n"/>
       <c r="K322" s="6" t="n"/>
       <c r="L322" s="5" t="inlineStr">
         <is>
-          <t>Inetum (acteur majeur SAP France/EMEA) recrute un consultant SAP SF avec 2+ ans exp. et certification SF. Poste basé en Tunisie — contacter pour confirmer si 100% remote depuis France accepté avant de postuler.</t>
+          <t>Sonepar (distributeur électrique mondial, 40 pays) recrute un PM SIRH orienté SAP SuccessFactors — poste interne grand groupe similaire à l'expérience L'Oréal. Publié il y a 3 semaines, encore probablement actif.</t>
         </is>
       </c>
       <c r="M322" s="5" t="inlineStr">
         <is>
-          <t>https://www.inetum.com/fr/accueil/carrieres/d726923c-1981-42ba-89d3-b4d0355b578d.html</t>
+          <t>https://fr.linkedin.com/jobs/view/hris-project-manager-at-sonepar</t>
         </is>
       </c>
       <c r="N322" s="40" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
+          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
       <c r="O322" s="40" t="inlineStr">
         <is>
-          <t>À préciser selon conditions remote</t>
+          <t>80-90K€</t>
         </is>
       </c>
       <c r="P322" s="40" t="n"/>
@@ -22479,17 +22513,17 @@
       <c r="C323" s="40" t="n"/>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>HRIS Project Manager</t>
+          <t>Consultant Senior RH People Strategy &amp; Transformation (F/H)</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>Sonepar</t>
+          <t>KPMG France</t>
         </is>
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G323" s="6" t="inlineStr">
@@ -22499,7 +22533,7 @@
       </c>
       <c r="H323" s="6" t="inlineStr">
         <is>
-          <t>Paris (Ville)</t>
+          <t>Courbevoie (La Défense)</t>
         </is>
       </c>
       <c r="I323" s="6" t="inlineStr">
@@ -22511,17 +22545,17 @@
       <c r="K323" s="6" t="n"/>
       <c r="L323" s="5" t="inlineStr">
         <is>
-          <t>Sonepar (distributeur électrique mondial, 40 pays) recrute un PM SIRH orienté SAP SuccessFactors — poste interne grand groupe similaire à l'expérience L'Oréal. Publié il y a 3 semaines, encore probablement actif.</t>
+          <t>KPMG recrute un consultant senior transformation RH avec exposition digitale/SIRH (SAP S/4, SF, Workday). Gaëtan peut valoriser sa double casquette SAP+conseil client grands comptes. Remote limité = contrainte depuis Anglet.</t>
         </is>
       </c>
       <c r="M323" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/hris-project-manager-at-sonepar</t>
+          <t>https://www.welcometothejungle.com/fr/companies/kpmg-france/jobs/consultant-senior-rh-people-strategy-transformation-f-h_courbevoie</t>
         </is>
       </c>
       <c r="N323" s="40" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
       <c r="O323" s="40" t="inlineStr">
@@ -22542,17 +22576,17 @@
       <c r="C324" s="40" t="n"/>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Consultant Senior RH People Strategy &amp; Transformation (F/H)</t>
+          <t>Lead Technique SIRH &amp; Intégration (H/F)</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
         <is>
-          <t>KPMG France</t>
+          <t>Eramet</t>
         </is>
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G324" s="6" t="inlineStr">
@@ -22562,7 +22596,7 @@
       </c>
       <c r="H324" s="6" t="inlineStr">
         <is>
-          <t>Courbevoie (La Défense)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I324" s="6" t="inlineStr">
@@ -22574,12 +22608,12 @@
       <c r="K324" s="6" t="n"/>
       <c r="L324" s="5" t="inlineStr">
         <is>
-          <t>KPMG recrute un consultant senior transformation RH avec exposition digitale/SIRH (SAP S/4, SF, Workday). Gaëtan peut valoriser sa double casquette SAP+conseil client grands comptes. Remote limité = contrainte depuis Anglet.</t>
+          <t>Eramet (groupe minier mondial) recrute un lead SIRH &amp; intégration côté client/utilisateur final. Profil technique intégration peut être au-delà de la zone confort de Gaëtan mais expérience L'Oréal côté client SAP HR est valorisable.</t>
         </is>
       </c>
       <c r="M324" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/kpmg-france/jobs/consultant-senior-rh-people-strategy-transformation-f-h_courbevoie</t>
+          <t>https://fr.linkedin.com/jobs/view/lead-technique-sirh-int%C3%A9gration-h-f-at-eramet</t>
         </is>
       </c>
       <c r="N324" s="40" t="inlineStr">
@@ -22589,11 +22623,11 @@
       </c>
       <c r="O324" s="40" t="inlineStr">
         <is>
-          <t>80-90K€</t>
+          <t>75-85K€</t>
         </is>
       </c>
       <c r="P324" s="40" t="n"/>
-      <c r="Q324" s="42" t="n"/>
+      <c r="Q324" s="40" t="n"/>
     </row>
     <row r="325" hidden="1" ht="16" customHeight="1">
       <c r="A325" s="81" t="inlineStr">
@@ -22605,12 +22639,12 @@
       <c r="C325" s="40" t="n"/>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>Lead Technique SIRH &amp; Intégration (H/F)</t>
+          <t>Consultant(e) MOA HR Access (F/H)</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>Eramet</t>
+          <t>ACT-ON HRIS</t>
         </is>
       </c>
       <c r="F325" s="5" t="inlineStr">
@@ -22625,7 +22659,7 @@
       </c>
       <c r="H325" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Neuilly-sur-Seine (92)</t>
         </is>
       </c>
       <c r="I325" s="6" t="inlineStr">
@@ -22637,12 +22671,12 @@
       <c r="K325" s="6" t="n"/>
       <c r="L325" s="5" t="inlineStr">
         <is>
-          <t>Eramet (groupe minier mondial) recrute un lead SIRH &amp; intégration côté client/utilisateur final. Profil technique intégration peut être au-delà de la zone confort de Gaëtan mais expérience L'Oréal côté client SAP HR est valorisable.</t>
+          <t>ACT-ON HRIS recrute aussi sur HR Access (MOE). Gaëtan n'a pas d'expérience directe HR Access mais profil SIRH global et SAP permet de se positionner. Moins prioritaire que le poste AMOA généraliste ACT-ON du même jour.</t>
         </is>
       </c>
       <c r="M325" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/lead-technique-sirh-int%C3%A9gration-h-f-at-eramet</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-e-moa-hr-access-at-act-on-hris</t>
         </is>
       </c>
       <c r="N325" s="40" t="inlineStr">
@@ -22652,7 +22686,7 @@
       </c>
       <c r="O325" s="40" t="inlineStr">
         <is>
-          <t>75-85K€</t>
+          <t>70-80K€</t>
         </is>
       </c>
       <c r="P325" s="40" t="n"/>
@@ -22668,17 +22702,17 @@
       <c r="C326" s="40" t="n"/>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) MOA HR Access (F/H)</t>
+          <t>Consultant AMOA GTA SIRH</t>
         </is>
       </c>
       <c r="E326" s="5" t="inlineStr">
         <is>
-          <t>ACT-ON HRIS</t>
+          <t>Tenth Revolution Group</t>
         </is>
       </c>
       <c r="F326" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G326" s="6" t="inlineStr">
@@ -22688,7 +22722,7 @@
       </c>
       <c r="H326" s="6" t="inlineStr">
         <is>
-          <t>Neuilly-sur-Seine (92)</t>
+          <t>Paris (75001) et Île-de-France</t>
         </is>
       </c>
       <c r="I326" s="6" t="inlineStr">
@@ -22700,12 +22734,12 @@
       <c r="K326" s="6" t="n"/>
       <c r="L326" s="5" t="inlineStr">
         <is>
-          <t>ACT-ON HRIS recrute aussi sur HR Access (MOE). Gaëtan n'a pas d'expérience directe HR Access mais profil SIRH global et SAP permet de se positionner. Moins prioritaire que le poste AMOA généraliste ACT-ON du même jour.</t>
+          <t>Tenth Revolution Group (ex-Frank Recruitment, spécialiste SAP/SIRH) recrute plusieurs consultants AMOA GTA SIRH 5+ ans. Gaëtan dépasse ce seuil. Utile aussi comme contact réseau cabinet recrutement SAP/SIRH.</t>
         </is>
       </c>
       <c r="M326" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-e-moa-hr-access-at-act-on-hris</t>
+          <t>https://www.free-work.com/fr/tech-it/consultant-moa-amoa/job-mission/consultant-amoa-gta-sirh-14</t>
         </is>
       </c>
       <c r="N326" s="40" t="inlineStr">
@@ -22722,7 +22756,7 @@
       <c r="Q326" s="40" t="n"/>
     </row>
     <row r="327" hidden="1" ht="32" customHeight="1">
-      <c r="A327" s="81" t="inlineStr">
+      <c r="A327" s="94" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
@@ -22731,12 +22765,12 @@
       <c r="C327" s="40" t="n"/>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>Consultant AMOA GTA SIRH</t>
+          <t>Manager SIRH</t>
         </is>
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>Tenth Revolution Group</t>
+          <t>TalHenT (via HR DNA)</t>
         </is>
       </c>
       <c r="F327" s="5" t="inlineStr">
@@ -22751,7 +22785,7 @@
       </c>
       <c r="H327" s="6" t="inlineStr">
         <is>
-          <t>Paris (75001) et Île-de-France</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I327" s="6" t="inlineStr">
@@ -22759,16 +22793,20 @@
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J327" s="6" t="n"/>
+      <c r="J327" s="6" t="inlineStr">
+        <is>
+          <t>60-110K€/an</t>
+        </is>
+      </c>
       <c r="K327" s="6" t="n"/>
       <c r="L327" s="5" t="inlineStr">
         <is>
-          <t>Tenth Revolution Group (ex-Frank Recruitment, spécialiste SAP/SIRH) recrute plusieurs consultants AMOA GTA SIRH 5+ ans. Gaëtan dépasse ce seuil. Utile aussi comme contact réseau cabinet recrutement SAP/SIRH.</t>
+          <t>Poste hybride management + business development, correspond à la cible "Account Manager HR Tech" ; fourchette salariale large, à clarifier le niveau exact du poste en entretien.</t>
         </is>
       </c>
       <c r="M327" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/consultant-moa-amoa/job-mission/consultant-amoa-gta-sirh-14</t>
+          <t>https://www.free-work.com/fr/tech-it/jobs/sirh</t>
         </is>
       </c>
       <c r="N327" s="40" t="inlineStr">
@@ -22778,11 +22816,11 @@
       </c>
       <c r="O327" s="40" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>90K€</t>
         </is>
       </c>
       <c r="P327" s="40" t="n"/>
-      <c r="Q327" s="40" t="n"/>
+      <c r="Q327" s="42" t="n"/>
     </row>
     <row r="328" hidden="1" ht="16" customHeight="1">
       <c r="A328" s="94" t="inlineStr">
@@ -22794,12 +22832,12 @@
       <c r="C328" s="40" t="n"/>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>Manager SIRH</t>
+          <t>SAP PMO SuccessFactors (H/F)</t>
         </is>
       </c>
       <c r="E328" s="5" t="inlineStr">
         <is>
-          <t>TalHenT (via HR DNA)</t>
+          <t>Mindquest</t>
         </is>
       </c>
       <c r="F328" s="5" t="inlineStr">
@@ -22809,7 +22847,7 @@
       </c>
       <c r="G328" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H328" s="6" t="inlineStr">
@@ -22822,15 +22860,15 @@
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J328" s="6" t="inlineStr">
-        <is>
-          <t>60-110K€/an</t>
-        </is>
-      </c>
-      <c r="K328" s="6" t="n"/>
+      <c r="J328" s="6" t="n"/>
+      <c r="K328" s="6" t="inlineStr">
+        <is>
+          <t>3 mois</t>
+        </is>
+      </c>
       <c r="L328" s="5" t="inlineStr">
         <is>
-          <t>Poste hybride management + business development, correspond à la cible "Account Manager HR Tech" ; fourchette salariale large, à clarifier le niveau exact du poste en entretien.</t>
+          <t>Mission courte PMO SuccessFactors, bon complément entre deux missions plus longues ; correspond à l'expérience de pilotage de projets SIRH multi-pays.</t>
         </is>
       </c>
       <c r="M328" s="5" t="inlineStr">
@@ -22845,11 +22883,15 @@
       </c>
       <c r="O328" s="40" t="inlineStr">
         <is>
-          <t>90K€</t>
+          <t>600€/j</t>
         </is>
       </c>
       <c r="P328" s="40" t="n"/>
-      <c r="Q328" s="42" t="n"/>
+      <c r="Q328" s="42" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="329" hidden="1" ht="16" customHeight="1">
       <c r="A329" s="94" t="inlineStr">
@@ -22861,12 +22903,12 @@
       <c r="C329" s="40" t="n"/>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>SAP PMO SuccessFactors (H/F)</t>
+          <t>Chef de projet SIRH (H/F)</t>
         </is>
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>Mindquest</t>
+          <t>Groupe Artemys</t>
         </is>
       </c>
       <c r="F329" s="5" t="inlineStr">
@@ -22881,7 +22923,7 @@
       </c>
       <c r="H329" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris 15e</t>
         </is>
       </c>
       <c r="I329" s="6" t="inlineStr">
@@ -22889,15 +22931,19 @@
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J329" s="6" t="n"/>
+      <c r="J329" s="6" t="inlineStr">
+        <is>
+          <t>550-650€/j</t>
+        </is>
+      </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>3 mois</t>
+          <t>9 mois</t>
         </is>
       </c>
       <c r="L329" s="5" t="inlineStr">
         <is>
-          <t>Mission courte PMO SuccessFactors, bon complément entre deux missions plus longues ; correspond à l'expérience de pilotage de projets SIRH multi-pays.</t>
+          <t>Mission longue (9 mois) de chef de projet SIRH, correspond bien au profil de pilotage de projets SIRH mondiaux de Gaëtan.</t>
         </is>
       </c>
       <c r="M329" s="5" t="inlineStr">
@@ -22918,7 +22964,7 @@
       <c r="P329" s="40" t="n"/>
       <c r="Q329" s="42" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -22932,52 +22978,44 @@
       <c r="C330" s="40" t="n"/>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>Chef de projet SIRH (H/F)</t>
+          <t>Consultant SIRH Grands Comptes F/H/NB</t>
         </is>
       </c>
       <c r="E330" s="5" t="inlineStr">
         <is>
-          <t>Groupe Artemys</t>
+          <t>Cegid</t>
         </is>
       </c>
       <c r="F330" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G330" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H330" s="6" t="inlineStr">
         <is>
-          <t>Paris 15e</t>
+          <t>Boulogne-Billancourt</t>
         </is>
       </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J330" s="6" t="inlineStr">
-        <is>
-          <t>550-650€/j</t>
-        </is>
-      </c>
-      <c r="K330" s="6" t="inlineStr">
-        <is>
-          <t>9 mois</t>
-        </is>
-      </c>
+          <t>Non précisé</t>
+        </is>
+      </c>
+      <c r="J330" s="6" t="n"/>
+      <c r="K330" s="6" t="n"/>
       <c r="L330" s="5" t="inlineStr">
         <is>
-          <t>Mission longue (9 mois) de chef de projet SIRH, correspond bien au profil de pilotage de projets SIRH mondiaux de Gaëtan.</t>
+          <t>Même type de poste que la version Lyon déjà identifiée, publié ici pour Boulogne-Billancourt ; grands comptes = profil senior avec expérience L'Oréal valorisable.</t>
         </is>
       </c>
       <c r="M330" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/sirh</t>
+          <t>https://www.welcometothejungle.com/fr/companies/cegid/jobs/consultant-sirh-grands-comptes-f-h-nb_boulogne-billancourt_CEGID_Kp678y8</t>
         </is>
       </c>
       <c r="N330" s="40" t="inlineStr">
@@ -22987,15 +23025,11 @@
       </c>
       <c r="O330" s="40" t="inlineStr">
         <is>
-          <t>600€/j</t>
+          <t>75K€</t>
         </is>
       </c>
       <c r="P330" s="40" t="n"/>
-      <c r="Q330" s="42" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
+      <c r="Q330" s="42" t="n"/>
     </row>
     <row r="331" hidden="1" ht="16" customHeight="1">
       <c r="A331" s="94" t="inlineStr">
@@ -23007,12 +23041,12 @@
       <c r="C331" s="40" t="n"/>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>Consultant SIRH Grands Comptes F/H/NB</t>
+          <t>Chef(fe) de projet SIRH F/H</t>
         </is>
       </c>
       <c r="E331" s="5" t="inlineStr">
         <is>
-          <t>Cegid</t>
+          <t>CGI</t>
         </is>
       </c>
       <c r="F331" s="5" t="inlineStr">
@@ -23027,24 +23061,24 @@
       </c>
       <c r="H331" s="6" t="inlineStr">
         <is>
-          <t>Boulogne-Billancourt</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I331" s="6" t="inlineStr">
         <is>
-          <t>Non précisé</t>
+          <t>Hybride (jusqu'à 3j télétravail/semaine)</t>
         </is>
       </c>
       <c r="J331" s="6" t="n"/>
       <c r="K331" s="6" t="n"/>
       <c r="L331" s="5" t="inlineStr">
         <is>
-          <t>Même type de poste que la version Lyon déjà identifiée, publié ici pour Boulogne-Billancourt ; grands comptes = profil senior avec expérience L'Oréal valorisable.</t>
+          <t>Poste équivalent à celui déjà identifié à Paris chez CGI, ouvert également à Nantes ; intégrateur SAP majeur, hybride mais flexible.</t>
         </is>
       </c>
       <c r="M331" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/cegid/jobs/consultant-sirh-grands-comptes-f-h-nb_boulogne-billancourt_CEGID_Kp678y8</t>
+          <t>https://www.welcometothejungle.com/fr/companies/cgi/jobs/chef-fe-de-projet-sirh-f-h_nantes</t>
         </is>
       </c>
       <c r="N331" s="40" t="inlineStr">
@@ -23054,11 +23088,15 @@
       </c>
       <c r="O331" s="40" t="inlineStr">
         <is>
-          <t>75K€</t>
+          <t>70-80K€</t>
         </is>
       </c>
       <c r="P331" s="40" t="n"/>
-      <c r="Q331" s="42" t="n"/>
+      <c r="Q331" s="42" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="332" hidden="1" ht="16" customHeight="1">
       <c r="A332" s="94" t="inlineStr">
@@ -23070,17 +23108,17 @@
       <c r="C332" s="40" t="n"/>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>Chef(fe) de projet SIRH F/H</t>
+          <t>Consultant digital RH - F/H</t>
         </is>
       </c>
       <c r="E332" s="5" t="inlineStr">
         <is>
-          <t>CGI</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="F332" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>accenture.com</t>
         </is>
       </c>
       <c r="G332" s="6" t="inlineStr">
@@ -23090,24 +23128,24 @@
       </c>
       <c r="H332" s="6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I332" s="6" t="inlineStr">
         <is>
-          <t>Hybride (jusqu'à 3j télétravail/semaine)</t>
+          <t>Non confirmé (une source mentionne remote)</t>
         </is>
       </c>
       <c r="J332" s="6" t="n"/>
       <c r="K332" s="6" t="n"/>
       <c r="L332" s="5" t="inlineStr">
         <is>
-          <t>Poste équivalent à celui déjà identifié à Paris chez CGI, ouvert également à Nantes ; intégrateur SAP majeur, hybride mais flexible.</t>
+          <t>Exige 5+ ans sur Workday/SuccessFactors/Oracle HCM et transformation digitale RH incluant IA ; correspond au profil SAP + acculturation IA de Gaëtan.</t>
         </is>
       </c>
       <c r="M332" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/cgi/jobs/chef-fe-de-projet-sirh-f-h_nantes</t>
+          <t>https://www.accenture.com/fr-fr/careers/jobdetails?id=R00270940_fr-fr</t>
         </is>
       </c>
       <c r="N332" s="40" t="inlineStr">
@@ -23117,15 +23155,11 @@
       </c>
       <c r="O332" s="40" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>75-85K€</t>
         </is>
       </c>
       <c r="P332" s="40" t="n"/>
-      <c r="Q332" s="42" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q332" s="42" t="n"/>
     </row>
     <row r="333" hidden="1" ht="16" customHeight="1">
       <c r="A333" s="94" t="inlineStr">
@@ -23137,54 +23171,54 @@
       <c r="C333" s="40" t="n"/>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>Consultant digital RH - F/H</t>
+          <t>HCM Solution Architect</t>
         </is>
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="F333" s="5" t="inlineStr">
         <is>
-          <t>accenture.com</t>
+          <t>jobgether.com</t>
         </is>
       </c>
       <c r="G333" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="H333" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Non précisée</t>
         </is>
       </c>
       <c r="I333" s="6" t="inlineStr">
         <is>
-          <t>Non confirmé (une source mentionne remote)</t>
+          <t>100% remote</t>
         </is>
       </c>
       <c r="J333" s="6" t="n"/>
       <c r="K333" s="6" t="n"/>
       <c r="L333" s="5" t="inlineStr">
         <is>
-          <t>Exige 5+ ans sur Workday/SuccessFactors/Oracle HCM et transformation digitale RH incluant IA ; correspond au profil SAP + acculturation IA de Gaëtan.</t>
+          <t>Poste HCM senior full remote, plutôt orienté Workday/Oracle HCM que SAP mais compétences largement transférables. Lien à vérifier manuellement (page bloquée en fetch automatisé).</t>
         </is>
       </c>
       <c r="M333" s="5" t="inlineStr">
         <is>
-          <t>https://www.accenture.com/fr-fr/careers/jobdetails?id=R00270940_fr-fr</t>
+          <t>https://jobgether.com/offer/69eab9adc646310ee39997f9-hcm-solution-architect</t>
         </is>
       </c>
       <c r="N333" s="40" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
+          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
       <c r="O333" s="40" t="inlineStr">
         <is>
-          <t>75-85K€</t>
+          <t>80-90K€</t>
         </is>
       </c>
       <c r="P333" s="40" t="n"/>
@@ -23200,44 +23234,44 @@
       <c r="C334" s="40" t="n"/>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>HCM Solution Architect</t>
+          <t>HR Implementation Consultant (Guided)</t>
         </is>
       </c>
       <c r="E334" s="5" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>Employment Hero</t>
         </is>
       </c>
       <c r="F334" s="5" t="inlineStr">
         <is>
-          <t>jobgether.com</t>
+          <t>himalayas.app</t>
         </is>
       </c>
       <c r="G334" s="6" t="inlineStr">
         <is>
-          <t>Non précisé</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H334" s="6" t="inlineStr">
         <is>
-          <t>Non précisée</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J334" s="6" t="n"/>
       <c r="K334" s="6" t="n"/>
       <c r="L334" s="5" t="inlineStr">
         <is>
-          <t>Poste HCM senior full remote, plutôt orienté Workday/Oracle HCM que SAP mais compétences largement transférables. Lien à vérifier manuellement (page bloquée en fetch automatisé).</t>
+          <t>Poste implementation consultant HRIS full remote, correspond bien au profil chef de projet SIRH/consultant en migration de données.</t>
         </is>
       </c>
       <c r="M334" s="5" t="inlineStr">
         <is>
-          <t>https://jobgether.com/offer/69eab9adc646310ee39997f9-hcm-solution-architect</t>
+          <t>https://himalayas.app/companies/employment-hero/jobs/hr-implementation-consultant-guided</t>
         </is>
       </c>
       <c r="N334" s="40" t="inlineStr">
@@ -23247,33 +23281,33 @@
       </c>
       <c r="O334" s="40" t="inlineStr">
         <is>
-          <t>80-90K€</t>
+          <t>75-85K€</t>
         </is>
       </c>
       <c r="P334" s="40" t="n"/>
       <c r="Q334" s="42" t="n"/>
     </row>
     <row r="335" hidden="1" ht="16" customHeight="1">
-      <c r="A335" s="94" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
+      <c r="A335" s="87" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="B335" s="40" t="n"/>
       <c r="C335" s="40" t="n"/>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>HR Implementation Consultant (Guided)</t>
+          <t>Senior Consultant HR Transformation Workday</t>
         </is>
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>Employment Hero</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="F335" s="5" t="inlineStr">
         <is>
-          <t>himalayas.app</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G335" s="6" t="inlineStr">
@@ -23283,34 +23317,38 @@
       </c>
       <c r="H335" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>La Défense</t>
         </is>
       </c>
       <c r="I335" s="6" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="J335" s="6" t="n"/>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J335" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
       <c r="K335" s="6" t="n"/>
       <c r="L335" s="5" t="inlineStr">
         <is>
-          <t>Poste implementation consultant HRIS full remote, correspond bien au profil chef de projet SIRH/consultant en migration de données.</t>
+          <t>Consulting RH ✓ — certification Workday requise, stack différent de SAP</t>
         </is>
       </c>
       <c r="M335" s="5" t="inlineStr">
         <is>
-          <t>https://himalayas.app/companies/employment-hero/jobs/hr-implementation-consultant-guided</t>
+          <t>https://www.linkedin.com/jobs/view/4416588225/</t>
         </is>
       </c>
       <c r="N335" s="40" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O335" s="40" t="inlineStr">
         <is>
-          <t>75-85K€</t>
+          <t>60 K€</t>
         </is>
       </c>
       <c r="P335" s="40" t="n"/>
@@ -23326,32 +23364,32 @@
       <c r="C336" s="40" t="n"/>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>Senior Consultant HR Transformation Workday</t>
+          <t>PMO SuccessFactors</t>
         </is>
       </c>
       <c r="E336" s="5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mindquest</t>
         </is>
       </c>
       <c r="F336" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G336" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H336" s="6" t="inlineStr">
         <is>
-          <t>La Défense</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>n.p.</t>
         </is>
       </c>
       <c r="J336" s="6" t="inlineStr">
@@ -23359,29 +23397,37 @@
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K336" s="6" t="n"/>
+      <c r="K336" s="6" t="inlineStr">
+        <is>
+          <t>3 mois</t>
+        </is>
+      </c>
       <c r="L336" s="5" t="inlineStr">
         <is>
-          <t>Consulting RH ✓ — certification Workday requise, stack différent de SAP</t>
+          <t>Coordination projets SF design/build/test, reporting, bilingue EN requis</t>
         </is>
       </c>
       <c r="M336" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4416588225/</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/project-management-officer/pmo-successfactors-h-f-75</t>
         </is>
       </c>
       <c r="N336" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O336" s="40" t="inlineStr">
         <is>
-          <t>60 K€</t>
+          <t>650 €/j</t>
         </is>
       </c>
       <c r="P336" s="40" t="n"/>
-      <c r="Q336" s="42" t="n"/>
+      <c r="Q336" s="42" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="337" hidden="1" ht="32" customHeight="1">
       <c r="A337" s="87" t="inlineStr">
@@ -23393,70 +23439,62 @@
       <c r="C337" s="40" t="n"/>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>PMO SuccessFactors</t>
+          <t>Global SAP HRIS Manager (SuccessFactors)</t>
         </is>
       </c>
       <c r="E337" s="5" t="inlineStr">
         <is>
-          <t>Mindquest</t>
+          <t>Via Eursap</t>
         </is>
       </c>
       <c r="F337" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>eursap.eu</t>
         </is>
       </c>
       <c r="G337" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H337" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Allemagne</t>
         </is>
       </c>
       <c r="I337" s="6" t="inlineStr">
         <is>
-          <t>n.p.</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="J337" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K337" s="6" t="inlineStr">
-        <is>
-          <t>3 mois</t>
-        </is>
-      </c>
+          <t>jusqu'à 145 K€</t>
+        </is>
+      </c>
+      <c r="K337" s="6" t="n"/>
       <c r="L337" s="5" t="inlineStr">
         <is>
-          <t>Coordination projets SF design/build/test, reporting, bilingue EN requis</t>
+          <t>Très bon salaire — poste en Allemagne, pas remote confirmé</t>
         </is>
       </c>
       <c r="M337" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/project-management-officer/pmo-successfactors-h-f-75</t>
+          <t>https://eursap.eu/jobs/global-sap-hris-manager-successfactors-34522-de</t>
         </is>
       </c>
       <c r="N337" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O337" s="40" t="inlineStr">
         <is>
-          <t>650 €/j</t>
+          <t>110 K€</t>
         </is>
       </c>
       <c r="P337" s="40" t="n"/>
-      <c r="Q337" s="42" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q337" s="42" t="n"/>
     </row>
     <row r="338" hidden="1" ht="64" customHeight="1">
       <c r="A338" s="87" t="inlineStr">
@@ -23468,58 +23506,62 @@
       <c r="C338" s="40" t="n"/>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>Global SAP HRIS Manager (SuccessFactors)</t>
+          <t>Consultant fonctionnel SAP HR/HCM</t>
         </is>
       </c>
       <c r="E338" s="5" t="inlineStr">
         <is>
-          <t>Via Eursap</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="F338" s="5" t="inlineStr">
         <is>
-          <t>eursap.eu</t>
+          <t>freelance-informatique.fr</t>
         </is>
       </c>
       <c r="G338" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H338" s="6" t="inlineStr">
         <is>
-          <t>Allemagne</t>
+          <t>Clermont-Ferrand (63)</t>
         </is>
       </c>
       <c r="I338" s="6" t="inlineStr">
         <is>
-          <t>Non précisé</t>
+          <t>n.p.</t>
         </is>
       </c>
       <c r="J338" s="6" t="inlineStr">
         <is>
-          <t>jusqu'à 145 K€</t>
-        </is>
-      </c>
-      <c r="K338" s="6" t="n"/>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K338" s="6" t="inlineStr">
+        <is>
+          <t>9 mois</t>
+        </is>
+      </c>
       <c r="L338" s="5" t="inlineStr">
         <is>
-          <t>Très bon salaire — poste en Allemagne, pas remote confirmé</t>
+          <t>Hors IDF — déplacement nécessaire</t>
         </is>
       </c>
       <c r="M338" s="5" t="inlineStr">
         <is>
-          <t>https://eursap.eu/jobs/global-sap-hris-manager-successfactors-34522-de</t>
+          <t>https://www.freelance-informatique.fr/mission-sap-hr-461</t>
         </is>
       </c>
       <c r="N338" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O338" s="40" t="inlineStr">
         <is>
-          <t>110 K€</t>
+          <t>700 €/j</t>
         </is>
       </c>
       <c r="P338" s="40" t="n"/>
@@ -23535,27 +23577,27 @@
       <c r="C339" s="40" t="n"/>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>Consultant fonctionnel SAP HR/HCM</t>
+          <t>Consultant(e) Senior SIRH</t>
         </is>
       </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>ALTHEA</t>
         </is>
       </c>
       <c r="F339" s="5" t="inlineStr">
         <is>
-          <t>freelance-informatique.fr</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G339" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H339" s="6" t="inlineStr">
         <is>
-          <t>Clermont-Ferrand (63)</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I339" s="6" t="inlineStr">
@@ -23565,22 +23607,18 @@
       </c>
       <c r="J339" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K339" s="6" t="inlineStr">
-        <is>
-          <t>9 mois</t>
-        </is>
-      </c>
+          <t>40-50 K€</t>
+        </is>
+      </c>
+      <c r="K339" s="6" t="n"/>
       <c r="L339" s="5" t="inlineStr">
         <is>
-          <t>Hors IDF — déplacement nécessaire</t>
+          <t>1-5 ans exp, profil junior/mid — salaire faible, Nantes loin de Biarritz</t>
         </is>
       </c>
       <c r="M339" s="5" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/mission-sap-hr-461</t>
+          <t>https://fr.linkedin.com/jobs/view/4316255713</t>
         </is>
       </c>
       <c r="N339" s="40" t="inlineStr">
@@ -23590,7 +23628,7 @@
       </c>
       <c r="O339" s="40" t="inlineStr">
         <is>
-          <t>700 €/j</t>
+          <t>55 K€</t>
         </is>
       </c>
       <c r="P339" s="40" t="n"/>
@@ -23606,12 +23644,12 @@
       <c r="C340" s="40" t="n"/>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) Senior SIRH</t>
+          <t>HRIS Specialist SAP SuccessFactors</t>
         </is>
       </c>
       <c r="E340" s="5" t="inlineStr">
         <is>
-          <t>ALTHEA</t>
+          <t>Ingenico</t>
         </is>
       </c>
       <c r="F340" s="5" t="inlineStr">
@@ -23626,28 +23664,28 @@
       </c>
       <c r="H340" s="6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="I340" s="6" t="inlineStr">
         <is>
-          <t>n.p.</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="J340" s="6" t="inlineStr">
         <is>
-          <t>40-50 K€</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K340" s="6" t="n"/>
       <c r="L340" s="5" t="inlineStr">
         <is>
-          <t>1-5 ans exp, profil junior/mid — salaire faible, Nantes loin de Biarritz</t>
+          <t>4+ ans admin SF Employee Central requis — profil trop technique/admin, pas full remote. Gaëtan connait SAP HCM mais pas admin SF.</t>
         </is>
       </c>
       <c r="M340" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4316255713</t>
+          <t>https://fr.linkedin.com/jobs/view/hris-specialist-at-ingenico-4427731807</t>
         </is>
       </c>
       <c r="N340" s="40" t="inlineStr">
@@ -23657,7 +23695,7 @@
       </c>
       <c r="O340" s="40" t="inlineStr">
         <is>
-          <t>55 K€</t>
+          <t>65 K€</t>
         </is>
       </c>
       <c r="P340" s="40" t="n"/>
@@ -23673,12 +23711,12 @@
       <c r="C341" s="40" t="n"/>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>HRIS Specialist SAP SuccessFactors</t>
+          <t>Consultant Senior HR Transformation SAP SuccessFactors F/H</t>
         </is>
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>Ingenico</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="F341" s="5" t="inlineStr">
@@ -23693,7 +23731,7 @@
       </c>
       <c r="H341" s="6" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>La Défense</t>
         </is>
       </c>
       <c r="I341" s="6" t="inlineStr">
@@ -23709,12 +23747,12 @@
       <c r="K341" s="6" t="n"/>
       <c r="L341" s="5" t="inlineStr">
         <is>
-          <t>4+ ans admin SF Employee Central requis — profil trop technique/admin, pas full remote. Gaëtan connait SAP HCM mais pas admin SF.</t>
+          <t>2+ ans consulting cabinet requis + expérience SF. Profil consultant Deloitte ≠ profil client-side Gaëtan. Différent du Workday Deloitte déjà en liste.</t>
         </is>
       </c>
       <c r="M341" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/hris-specialist-at-ingenico-4427731807</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-senior-hr-transformation-sap-successfactors-f-h-at-deloitte-4072908135</t>
         </is>
       </c>
       <c r="N341" s="40" t="inlineStr">
@@ -23740,27 +23778,27 @@
       <c r="C342" s="40" t="n"/>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>Consultant Senior HR Transformation SAP SuccessFactors F/H</t>
+          <t>Directeur de Projet SIRH (Freelance)</t>
         </is>
       </c>
       <c r="E342" s="5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EXteam</t>
         </is>
       </c>
       <c r="F342" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G342" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H342" s="6" t="inlineStr">
         <is>
-          <t>La Défense</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I342" s="6" t="inlineStr">
@@ -23770,18 +23808,22 @@
       </c>
       <c r="J342" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K342" s="6" t="n"/>
+          <t>630-730 €/j</t>
+        </is>
+      </c>
+      <c r="K342" s="6" t="inlineStr">
+        <is>
+          <t>3 ans</t>
+        </is>
+      </c>
       <c r="L342" s="5" t="inlineStr">
         <is>
-          <t>2+ ans consulting cabinet requis + expérience SF. Profil consultant Deloitte ≠ profil client-side Gaëtan. Différent du Workday Deloitte déjà en liste.</t>
+          <t>Pilotage projets SIRH, ateliers, conduite du changement. Requiert expertise Pléiades 4you — pas son outil. Secteur audiovisuel public.</t>
         </is>
       </c>
       <c r="M342" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-senior-hr-transformation-sap-successfactors-f-h-at-deloitte-4072908135</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/directeur-de-projet-sirh-7</t>
         </is>
       </c>
       <c r="N342" s="40" t="inlineStr">
@@ -23791,11 +23833,15 @@
       </c>
       <c r="O342" s="40" t="inlineStr">
         <is>
-          <t>65 K€</t>
+          <t>730 €/j</t>
         </is>
       </c>
       <c r="P342" s="40" t="n"/>
-      <c r="Q342" s="42" t="n"/>
+      <c r="Q342" s="42" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="343" hidden="1" ht="16" customHeight="1">
       <c r="A343" s="87" t="inlineStr">
@@ -23807,68 +23853,64 @@
       <c r="C343" s="40" t="n"/>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>Directeur de Projet SIRH (Freelance)</t>
+          <t>Solution Advisor Senior Manager</t>
         </is>
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>EXteam</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="F343" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>jobs.sap.com</t>
         </is>
       </c>
       <c r="G343" s="6" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H343" s="6" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Levallois-Perret</t>
         </is>
       </c>
       <c r="I343" s="6" t="inlineStr">
         <is>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J343" s="6" t="inlineStr">
+        <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="J343" s="6" t="inlineStr">
-        <is>
-          <t>630-730 €/j</t>
-        </is>
-      </c>
-      <c r="K343" s="6" t="inlineStr">
-        <is>
-          <t>3 ans</t>
-        </is>
-      </c>
+      <c r="K343" s="6" t="n"/>
       <c r="L343" s="5" t="inlineStr">
         <is>
-          <t>Pilotage projets SIRH, ateliers, conduite du changement. Requiert expertise Pléiades 4you — pas son outil. Secteur audiovisuel public.</t>
+          <t>Management équipe SAs — Supply Chain focus (pas HCM). Requiert expérience leadership SA/CS teams. Mauvais domaine pour Gaëtan.</t>
         </is>
       </c>
       <c r="M343" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/directeur-de-projet-sirh-7</t>
+          <t>https://jobs.sap.com/job/Levallois-Perret-Solution-Advisor-Senior-Manager-92300/1385712733/</t>
         </is>
       </c>
       <c r="N343" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O343" s="40" t="inlineStr">
         <is>
-          <t>730 €/j</t>
+          <t>100 K€</t>
         </is>
       </c>
       <c r="P343" s="40" t="n"/>
       <c r="Q343" s="42" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -23882,7 +23924,7 @@
       <c r="C344" s="40" t="n"/>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>Solution Advisor Senior Manager</t>
+          <t>Client Delivery Manager F/M</t>
         </is>
       </c>
       <c r="E344" s="5" t="inlineStr">
@@ -23918,12 +23960,12 @@
       <c r="K344" s="6" t="n"/>
       <c r="L344" s="5" t="inlineStr">
         <is>
-          <t>Management équipe SAs — Supply Chain focus (pas HCM). Requiert expérience leadership SA/CS teams. Mauvais domaine pour Gaëtan.</t>
+          <t>SAP Enterprise Cloud Services — gestion lifecycle client, escalades, renouvellements. Requiert SAP Basis/infra technique. Pas le profil fonctionnel RH de Gaëtan.</t>
         </is>
       </c>
       <c r="M344" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.sap.com/job/Levallois-Perret-Solution-Advisor-Senior-Manager-92300/1385712733/</t>
+          <t>https://jobs.sap.com/job/Levallois-Perret-Client-Delivery-Manager-FM-92300/1379856933/</t>
         </is>
       </c>
       <c r="N344" s="40" t="inlineStr">
@@ -23933,15 +23975,11 @@
       </c>
       <c r="O344" s="40" t="inlineStr">
         <is>
-          <t>100 K€</t>
+          <t>90 K€</t>
         </is>
       </c>
       <c r="P344" s="40" t="n"/>
-      <c r="Q344" s="42" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
+      <c r="Q344" s="42" t="n"/>
     </row>
     <row r="345" hidden="1" ht="32" customHeight="1">
       <c r="A345" s="87" t="inlineStr">
@@ -23953,7 +23991,7 @@
       <c r="C345" s="40" t="n"/>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>Client Delivery Manager F/M</t>
+          <t>Services Sr. Account Executive F/M</t>
         </is>
       </c>
       <c r="E345" s="5" t="inlineStr">
@@ -23989,12 +24027,12 @@
       <c r="K345" s="6" t="n"/>
       <c r="L345" s="5" t="inlineStr">
         <is>
-          <t>SAP Enterprise Cloud Services — gestion lifecycle client, escalades, renouvellements. Requiert SAP Basis/infra technique. Pas le profil fonctionnel RH de Gaëtan.</t>
+          <t>Vente complexe 10+ ans requise, contrats implémentation SAP. Profil hunter/sales pur. Gaëtan est CSM/account management, pas business development.</t>
         </is>
       </c>
       <c r="M345" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.sap.com/job/Levallois-Perret-Client-Delivery-Manager-FM-92300/1379856933/</t>
+          <t>https://jobs.sap.com/job/Levallois-Perret-Services-Sr_-Account-Executive-FM-92300/1382751433/</t>
         </is>
       </c>
       <c r="N345" s="40" t="inlineStr">
@@ -24004,11 +24042,15 @@
       </c>
       <c r="O345" s="40" t="inlineStr">
         <is>
-          <t>90 K€</t>
+          <t>95 K€</t>
         </is>
       </c>
       <c r="P345" s="40" t="n"/>
-      <c r="Q345" s="42" t="n"/>
+      <c r="Q345" s="42" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="346" hidden="1" ht="32" customHeight="1">
       <c r="A346" s="87" t="inlineStr">
@@ -24020,17 +24062,17 @@
       <c r="C346" s="40" t="n"/>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>Services Sr. Account Executive F/M</t>
+          <t>Managing Consultant - HR Transformation (SuccessFactors)</t>
         </is>
       </c>
       <c r="E346" s="5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Capgemini Invent</t>
         </is>
       </c>
       <c r="F346" s="5" t="inlineStr">
         <is>
-          <t>jobs.sap.com</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G346" s="6" t="inlineStr">
@@ -24040,7 +24082,7 @@
       </c>
       <c r="H346" s="6" t="inlineStr">
         <is>
-          <t>Levallois-Perret</t>
+          <t>London (UK)</t>
         </is>
       </c>
       <c r="I346" s="6" t="inlineStr">
@@ -24056,12 +24098,12 @@
       <c r="K346" s="6" t="n"/>
       <c r="L346" s="5" t="inlineStr">
         <is>
-          <t>Vente complexe 10+ ans requise, contrats implémentation SAP. Profil hunter/sales pur. Gaëtan est CSM/account management, pas business development.</t>
+          <t>Postée il y a 5 mois — peut être pourvue. 8+ ans HR tech consulting + 4+ ans SF requis. Profil consultant cabinet. London hybride.</t>
         </is>
       </c>
       <c r="M346" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.sap.com/job/Levallois-Perret-Services-Sr_-Account-Executive-FM-92300/1382751433/</t>
+          <t>https://www.linkedin.com/jobs/view/4343035769</t>
         </is>
       </c>
       <c r="N346" s="40" t="inlineStr">
@@ -24071,15 +24113,11 @@
       </c>
       <c r="O346" s="40" t="inlineStr">
         <is>
-          <t>95 K€</t>
+          <t>100 K€</t>
         </is>
       </c>
       <c r="P346" s="40" t="n"/>
-      <c r="Q346" s="42" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q346" s="42" t="n"/>
     </row>
     <row r="347" hidden="1" ht="32" customHeight="1">
       <c r="A347" s="87" t="inlineStr">
@@ -24091,12 +24129,12 @@
       <c r="C347" s="40" t="n"/>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>Managing Consultant - HR Transformation (SuccessFactors)</t>
+          <t>SAP SuccessFactors Talent Acquisition Consultant</t>
         </is>
       </c>
       <c r="E347" s="5" t="inlineStr">
         <is>
-          <t>Capgemini Invent</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="F347" s="5" t="inlineStr">
@@ -24111,7 +24149,7 @@
       </c>
       <c r="H347" s="6" t="inlineStr">
         <is>
-          <t>London (UK)</t>
+          <t>London / Birmingham / Manchester (UK)</t>
         </is>
       </c>
       <c r="I347" s="6" t="inlineStr">
@@ -24127,12 +24165,12 @@
       <c r="K347" s="6" t="n"/>
       <c r="L347" s="5" t="inlineStr">
         <is>
-          <t>Postée il y a 5 mois — peut être pourvue. 8+ ans HR tech consulting + 4+ ans SF requis. Profil consultant cabinet. London hybride.</t>
+          <t>Deadline 31/05/2026 dépassée — vérifier si toujours ouverte. SF Recruiting &amp; Onboarding, 2-3 implémentations full cycle requis. UK offices.</t>
         </is>
       </c>
       <c r="M347" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4343035769</t>
+          <t>https://www.linkedin.com/jobs/view/4369181135</t>
         </is>
       </c>
       <c r="N347" s="40" t="inlineStr">
@@ -24142,7 +24180,7 @@
       </c>
       <c r="O347" s="40" t="inlineStr">
         <is>
-          <t>100 K€</t>
+          <t>90 K€</t>
         </is>
       </c>
       <c r="P347" s="40" t="n"/>
@@ -24158,12 +24196,12 @@
       <c r="C348" s="40" t="n"/>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>SAP SuccessFactors Talent Acquisition Consultant</t>
+          <t>SAP SuccessFactors Consultant</t>
         </is>
       </c>
       <c r="E348" s="5" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>RED Global</t>
         </is>
       </c>
       <c r="F348" s="5" t="inlineStr">
@@ -24173,12 +24211,12 @@
       </c>
       <c r="G348" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H348" s="6" t="inlineStr">
         <is>
-          <t>London / Birmingham / Manchester (UK)</t>
+          <t>Vitry-le-François</t>
         </is>
       </c>
       <c r="I348" s="6" t="inlineStr">
@@ -24194,12 +24232,12 @@
       <c r="K348" s="6" t="n"/>
       <c r="L348" s="5" t="inlineStr">
         <is>
-          <t>Deadline 31/05/2026 dépassée — vérifier si toujours ouverte. SF Recruiting &amp; Onboarding, 2-3 implémentations full cycle requis. UK offices.</t>
+          <t>RED Global (ex-RED Commerce) = réseau SAP utile à activer. Mission Vitry-le-François peu pratique depuis Biarritz, mais RED Global est un contact pertinent pour missions SAP SF.</t>
         </is>
       </c>
       <c r="M348" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4369181135</t>
+          <t>https://www.redglobal.com/jobs/</t>
         </is>
       </c>
       <c r="N348" s="40" t="inlineStr">
@@ -24207,11 +24245,7 @@
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O348" s="40" t="inlineStr">
-        <is>
-          <t>90 K€</t>
-        </is>
-      </c>
+      <c r="O348" s="40" t="n"/>
       <c r="P348" s="40" t="n"/>
       <c r="Q348" s="42" t="n"/>
     </row>
@@ -24225,12 +24259,12 @@
       <c r="C349" s="40" t="n"/>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>SAP SuccessFactors Consultant</t>
+          <t>AMOA SIRH</t>
         </is>
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>RED Global</t>
+          <t>Qim info</t>
         </is>
       </c>
       <c r="F349" s="5" t="inlineStr">
@@ -24240,17 +24274,17 @@
       </c>
       <c r="G349" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="H349" s="6" t="inlineStr">
         <is>
-          <t>Vitry-le-François</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="I349" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="J349" s="6" t="inlineStr">
@@ -24261,17 +24295,17 @@
       <c r="K349" s="6" t="n"/>
       <c r="L349" s="5" t="inlineStr">
         <is>
-          <t>RED Global (ex-RED Commerce) = réseau SAP utile à activer. Mission Vitry-le-François peu pratique depuis Biarritz, mais RED Global est un contact pertinent pour missions SAP SF.</t>
+          <t>Qim info = ESN régionale France. AMOA SIRH Annecy, postée il y a 2 jours. Localisation contraignante depuis Biarritz. Fit fonctionnel correct.</t>
         </is>
       </c>
       <c r="M349" s="5" t="inlineStr">
         <is>
-          <t>https://www.redglobal.com/jobs/</t>
+          <t>https://fr.linkedin.com/jobs/hris-emplois</t>
         </is>
       </c>
       <c r="N349" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O349" s="40" t="n"/>
@@ -24288,12 +24322,12 @@
       <c r="C350" s="40" t="n"/>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>AMOA SIRH</t>
+          <t>Responsable SIRH &amp; Data F/H</t>
         </is>
       </c>
       <c r="E350" s="5" t="inlineStr">
         <is>
-          <t>Qim info</t>
+          <t>GLS France</t>
         </is>
       </c>
       <c r="F350" s="5" t="inlineStr">
@@ -24303,12 +24337,12 @@
       </c>
       <c r="G350" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H350" s="6" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I350" s="6" t="inlineStr">
@@ -24324,7 +24358,7 @@
       <c r="K350" s="6" t="n"/>
       <c r="L350" s="5" t="inlineStr">
         <is>
-          <t>Qim info = ESN régionale France. AMOA SIRH Annecy, postée il y a 2 jours. Localisation contraignante depuis Biarritz. Fit fonctionnel correct.</t>
+          <t>GLS France = logistique/colis. Toulouse = géographiquement plus proche de Biarritz. Poste Responsable SIRH opérationnel (pas pure consulting). Fit partiel.</t>
         </is>
       </c>
       <c r="M350" s="5" t="inlineStr">
@@ -24337,7 +24371,11 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O350" s="40" t="n"/>
+      <c r="O350" s="40" t="inlineStr">
+        <is>
+          <t>75 K€</t>
+        </is>
+      </c>
       <c r="P350" s="40" t="n"/>
       <c r="Q350" s="42" t="n"/>
     </row>
@@ -24351,12 +24389,12 @@
       <c r="C351" s="40" t="n"/>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>Responsable SIRH &amp; Data F/H</t>
+          <t>Chef de Projet SIRH H/F</t>
         </is>
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>GLS France</t>
+          <t>Groupe Blachère</t>
         </is>
       </c>
       <c r="F351" s="5" t="inlineStr">
@@ -24371,12 +24409,12 @@
       </c>
       <c r="H351" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Châteaurenard (13)</t>
         </is>
       </c>
       <c r="I351" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J351" s="6" t="inlineStr">
@@ -24387,12 +24425,12 @@
       <c r="K351" s="6" t="n"/>
       <c r="L351" s="5" t="inlineStr">
         <is>
-          <t>GLS France = logistique/colis. Toulouse = géographiquement plus proche de Biarritz. Poste Responsable SIRH opérationnel (pas pure consulting). Fit partiel.</t>
+          <t>Groupe Blachère (Marie Blachère). Chef de projet SIRH réseau franchises. Provence, géographiquement accessible depuis Biarritz. Secteur restauration, pas HR Tech. Postée il y a 1 semaine.</t>
         </is>
       </c>
       <c r="M351" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/hris-emplois</t>
+          <t>https://www.groupe-blachere.com/recrutement/</t>
         </is>
       </c>
       <c r="N351" s="40" t="inlineStr">
@@ -24402,7 +24440,7 @@
       </c>
       <c r="O351" s="40" t="inlineStr">
         <is>
-          <t>75 K€</t>
+          <t>70 K€</t>
         </is>
       </c>
       <c r="P351" s="40" t="n"/>
@@ -24423,7 +24461,7 @@
       </c>
       <c r="E352" s="5" t="inlineStr">
         <is>
-          <t>Groupe Blachère</t>
+          <t>Paragon France</t>
         </is>
       </c>
       <c r="F352" s="5" t="inlineStr">
@@ -24438,7 +24476,7 @@
       </c>
       <c r="H352" s="6" t="inlineStr">
         <is>
-          <t>Châteaurenard (13)</t>
+          <t>Nanterre (92)</t>
         </is>
       </c>
       <c r="I352" s="6" t="inlineStr">
@@ -24454,12 +24492,12 @@
       <c r="K352" s="6" t="n"/>
       <c r="L352" s="5" t="inlineStr">
         <is>
-          <t>Groupe Blachère (Marie Blachère). Chef de projet SIRH réseau franchises. Provence, géographiquement accessible depuis Biarritz. Secteur restauration, pas HR Tech. Postée il y a 1 semaine.</t>
+          <t>Paragon = groupe international services RH et gestion documentaire. Chef de projet SIRH Nanterre. Postée il y a 2 semaines. Présentiel probable = frein.</t>
         </is>
       </c>
       <c r="M352" s="5" t="inlineStr">
         <is>
-          <t>https://www.groupe-blachere.com/recrutement/</t>
+          <t>https://fr.linkedin.com/jobs/chef-de-projet-sirh-emplois-france</t>
         </is>
       </c>
       <c r="N352" s="40" t="inlineStr">
@@ -24469,11 +24507,11 @@
       </c>
       <c r="O352" s="40" t="inlineStr">
         <is>
-          <t>70 K€</t>
+          <t>72 K€</t>
         </is>
       </c>
       <c r="P352" s="40" t="n"/>
-      <c r="Q352" s="42" t="n"/>
+      <c r="Q352" s="40" t="n"/>
     </row>
     <row r="353" hidden="1" ht="32" customHeight="1">
       <c r="A353" s="87" t="inlineStr">
@@ -24485,27 +24523,27 @@
       <c r="C353" s="40" t="n"/>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>Chef de Projet SIRH H/F</t>
+          <t>Directeur de Projet Senior Data &amp; BI RH</t>
         </is>
       </c>
       <c r="E353" s="5" t="inlineStr">
         <is>
-          <t>Paragon France</t>
+          <t>Freelance.com</t>
         </is>
       </c>
       <c r="F353" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G353" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H353" s="6" t="inlineStr">
         <is>
-          <t>Nanterre (92)</t>
+          <t>Orly (94)</t>
         </is>
       </c>
       <c r="I353" s="6" t="inlineStr">
@@ -24515,18 +24553,18 @@
       </c>
       <c r="J353" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>400 - 650 €/jour</t>
         </is>
       </c>
       <c r="K353" s="6" t="n"/>
       <c r="L353" s="5" t="inlineStr">
         <is>
-          <t>Paragon = groupe international services RH et gestion documentaire. Chef de projet SIRH Nanterre. Postée il y a 2 semaines. Présentiel probable = frein.</t>
+          <t>Mission Data/BI RH, adjacente SIRH. TJM en dessous de la cible (400-650€ vs 650-750€). Localisation Orly contraignante. Freelance.com = plateforme recrutement IT.</t>
         </is>
       </c>
       <c r="M353" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/chef-de-projet-sirh-emplois-france</t>
+          <t>https://www.freelance.com/missions/sirh</t>
         </is>
       </c>
       <c r="N353" s="40" t="inlineStr">
@@ -24534,11 +24572,7 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O353" s="40" t="inlineStr">
-        <is>
-          <t>72 K€</t>
-        </is>
-      </c>
+      <c r="O353" s="40" t="n"/>
       <c r="P353" s="40" t="n"/>
       <c r="Q353" s="40" t="n"/>
     </row>
@@ -24552,27 +24586,27 @@
       <c r="C354" s="40" t="n"/>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>Directeur de Projet Senior Data &amp; BI RH</t>
+          <t>Chef de Projet SIRH</t>
         </is>
       </c>
       <c r="E354" s="5" t="inlineStr">
         <is>
-          <t>Freelance.com</t>
+          <t>Silae</t>
         </is>
       </c>
       <c r="F354" s="5" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G354" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H354" s="6" t="inlineStr">
         <is>
-          <t>Orly (94)</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I354" s="6" t="inlineStr">
@@ -24582,18 +24616,18 @@
       </c>
       <c r="J354" s="6" t="inlineStr">
         <is>
-          <t>400 - 650 €/jour</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K354" s="6" t="n"/>
       <c r="L354" s="5" t="inlineStr">
         <is>
-          <t>Mission Data/BI RH, adjacente SIRH. TJM en dessous de la cible (400-650€ vs 650-750€). Localisation Orly contraignante. Freelance.com = plateforme recrutement IT.</t>
+          <t>Silae = leader logiciels paie France (éditeur). Rôle Partner Success, onboarding partenaires déployant Silae. Pas full remote, Nantes. Silae adjacent au profil SAP HR (paie).</t>
         </is>
       </c>
       <c r="M354" s="5" t="inlineStr">
         <is>
-          <t>https://www.freelance.com/missions/sirh</t>
+          <t>https://www.welcometothejungle.com/fr/companies/silae/jobs/chef-de-projet-sirh_nantes</t>
         </is>
       </c>
       <c r="N354" s="40" t="inlineStr">
@@ -24601,7 +24635,11 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O354" s="40" t="n"/>
+      <c r="O354" s="40" t="inlineStr">
+        <is>
+          <t>70 K€</t>
+        </is>
+      </c>
       <c r="P354" s="40" t="n"/>
       <c r="Q354" s="40" t="n"/>
     </row>
@@ -24615,17 +24653,17 @@
       <c r="C355" s="40" t="n"/>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>Chef de Projet SIRH</t>
+          <t>SAP S/4HANA Project Manager PMO</t>
         </is>
       </c>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>Silae</t>
+          <t>Client fabricant industriel (via Eursap)</t>
         </is>
       </c>
       <c r="F355" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Eursap.eu</t>
         </is>
       </c>
       <c r="G355" s="6" t="inlineStr">
@@ -24635,38 +24673,38 @@
       </c>
       <c r="H355" s="6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris 8e</t>
         </is>
       </c>
       <c r="I355" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Hybride (50%)</t>
         </is>
       </c>
       <c r="J355" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>Jusqu'à 115 000 € + 14% bonus + 11K€ participation</t>
         </is>
       </c>
       <c r="K355" s="6" t="n"/>
       <c r="L355" s="5" t="inlineStr">
         <is>
-          <t>Silae = leader logiciels paie France (éditeur). Rôle Partner Success, onboarding partenaires déployant Silae. Pas full remote, Nantes. Silae adjacent au profil SAP HR (paie).</t>
+          <t>PMO chef de projet SAP S/4HANA pour fabricant industriel en transformation globale. 10 ans IT requis. Gaëtan a 15 ans SAP mais orienté RH/HCM. Gap S/4HANA non-HR. Salaire excellent. Démarrage sept 2026.</t>
         </is>
       </c>
       <c r="M355" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/silae/jobs/chef-de-projet-sirh_nantes</t>
+          <t>https://eursap.eu/jobs/sap-s-4hana-project-manager-pmo-FR-34951</t>
         </is>
       </c>
       <c r="N355" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O355" s="40" t="inlineStr">
         <is>
-          <t>70 K€</t>
+          <t>100 K€</t>
         </is>
       </c>
       <c r="P355" s="40" t="n"/>
@@ -24682,62 +24720,62 @@
       <c r="C356" s="40" t="n"/>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>SAP S/4HANA Project Manager PMO</t>
+          <t>AMOA RH</t>
         </is>
       </c>
       <c r="E356" s="5" t="inlineStr">
         <is>
-          <t>Client fabricant industriel (via Eursap)</t>
+          <t>CAT-AMANIA (client assurance)</t>
         </is>
       </c>
       <c r="F356" s="5" t="inlineStr">
         <is>
-          <t>Eursap.eu</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G356" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H356" s="6" t="inlineStr">
         <is>
-          <t>Paris 8e</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I356" s="6" t="inlineStr">
         <is>
-          <t>Hybride (50%)</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J356" s="6" t="inlineStr">
         <is>
-          <t>Jusqu'à 115 000 € + 14% bonus + 11K€ participation</t>
-        </is>
-      </c>
-      <c r="K356" s="6" t="n"/>
+          <t>440-490 €/j</t>
+        </is>
+      </c>
+      <c r="K356" s="6" t="inlineStr">
+        <is>
+          <t>1 an renouvelable</t>
+        </is>
+      </c>
       <c r="L356" s="5" t="inlineStr">
         <is>
-          <t>PMO chef de projet SAP S/4HANA pour fabricant industriel en transformation globale. 10 ans IT requis. Gaëtan a 15 ans SAP mais orienté RH/HCM. Gap S/4HANA non-HR. Salaire excellent. Démarrage sept 2026.</t>
+          <t>Grand compte assurance, transformation RH, recette, conduite du changement. Bon fit MOA mais TJM sous cible (440-490€/j).</t>
         </is>
       </c>
       <c r="M356" s="5" t="inlineStr">
         <is>
-          <t>https://eursap.eu/jobs/sap-s-4hana-project-manager-pmo-FR-34951</t>
-        </is>
-      </c>
-      <c r="N356" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O356" s="40" t="inlineStr">
-        <is>
-          <t>100 K€</t>
-        </is>
-      </c>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/amoa-rh-2</t>
+        </is>
+      </c>
+      <c r="N356" s="40" t="n"/>
+      <c r="O356" s="40" t="n"/>
       <c r="P356" s="40" t="n"/>
-      <c r="Q356" s="40" t="n"/>
+      <c r="Q356" s="42" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="357" hidden="1" ht="16" customHeight="1">
       <c r="A357" s="87" t="inlineStr">
@@ -24747,52 +24785,52 @@
       </c>
       <c r="B357" s="40" t="n"/>
       <c r="C357" s="40" t="n"/>
-      <c r="D357" s="5" t="inlineStr">
+      <c r="D357" s="40" t="inlineStr">
         <is>
           <t>AMOA RH</t>
         </is>
       </c>
-      <c r="E357" s="5" t="inlineStr">
+      <c r="E357" s="40" t="inlineStr">
         <is>
           <t>CAT-AMANIA (client assurance)</t>
         </is>
       </c>
-      <c r="F357" s="5" t="inlineStr">
+      <c r="F357" s="40" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G357" s="6" t="inlineStr">
+      <c r="G357" s="40" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H357" s="6" t="inlineStr">
+      <c r="H357" s="40" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I357" s="6" t="inlineStr">
+      <c r="I357" s="40" t="inlineStr">
         <is>
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J357" s="6" t="inlineStr">
+      <c r="J357" s="40" t="inlineStr">
         <is>
           <t>440-490 €/j</t>
         </is>
       </c>
-      <c r="K357" s="6" t="inlineStr">
+      <c r="K357" s="40" t="inlineStr">
         <is>
           <t>1 an renouvelable</t>
         </is>
       </c>
-      <c r="L357" s="5" t="inlineStr">
-        <is>
-          <t>Grand compte assurance, transformation RH, recette, conduite du changement. Bon fit MOA mais TJM sous cible (440-490€/j).</t>
-        </is>
-      </c>
-      <c r="M357" s="5" t="inlineStr">
+      <c r="L357" s="40" t="inlineStr">
+        <is>
+          <t>Grand compte assurance, transformation RH, recette, conduite du changement. Bon fit MOA mais TJM sous cible.</t>
+        </is>
+      </c>
+      <c r="M357" s="40" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/amoa-rh-2</t>
         </is>
@@ -24816,60 +24854,64 @@
       <c r="C358" s="40" t="n"/>
       <c r="D358" s="40" t="inlineStr">
         <is>
-          <t>AMOA RH</t>
+          <t>Consultant Senior SIRH Paie</t>
         </is>
       </c>
       <c r="E358" s="40" t="inlineStr">
         <is>
-          <t>CAT-AMANIA (client assurance)</t>
+          <t>n.c. (Washington Frank)</t>
         </is>
       </c>
       <c r="F358" s="40" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>Washington Frank</t>
         </is>
       </c>
       <c r="G358" s="40" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H358" s="40" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I358" s="40" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J358" s="40" t="inlineStr">
         <is>
-          <t>440-490 €/j</t>
-        </is>
-      </c>
-      <c r="K358" s="40" t="inlineStr">
-        <is>
-          <t>1 an renouvelable</t>
-        </is>
-      </c>
+          <t>50-60K€/an</t>
+        </is>
+      </c>
+      <c r="K358" s="40" t="n"/>
       <c r="L358" s="40" t="inlineStr">
         <is>
-          <t>Grand compte assurance, transformation RH, recette, conduite du changement. Bon fit MOA mais TJM sous cible.</t>
+          <t>Senior SIRH Paie Lyon CDI. Salaire et localisation sous les critères cibles. Spécialisation paie et compliance.</t>
         </is>
       </c>
       <c r="M358" s="40" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/amoa-rh-2</t>
-        </is>
-      </c>
-      <c r="N358" s="40" t="n"/>
-      <c r="O358" s="40" t="n"/>
+          <t>https://washingtonfrank.com/job/a0M1i00000JW62x.1/consultant-senior-sirh-paie</t>
+        </is>
+      </c>
+      <c r="N358" s="40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
+        </is>
+      </c>
+      <c r="O358" s="40" t="inlineStr">
+        <is>
+          <t>70-80K€</t>
+        </is>
+      </c>
       <c r="P358" s="40" t="n"/>
       <c r="Q358" s="42" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -24883,27 +24925,27 @@
       <c r="C359" s="40" t="n"/>
       <c r="D359" s="40" t="inlineStr">
         <is>
-          <t>Consultant Senior SIRH Paie</t>
+          <t>Chef de projet SIRH confirmé (longue durée)</t>
         </is>
       </c>
       <c r="E359" s="40" t="inlineStr">
         <is>
-          <t>n.c. (Washington Frank)</t>
+          <t>n.c. (via Freelance-Informatique)</t>
         </is>
       </c>
       <c r="F359" s="40" t="inlineStr">
         <is>
-          <t>Washington Frank</t>
+          <t>Freelance-Informatique</t>
         </is>
       </c>
       <c r="G359" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="H359" s="40" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Gonesse (95)</t>
         </is>
       </c>
       <c r="I359" s="40" t="inlineStr">
@@ -24913,18 +24955,18 @@
       </c>
       <c r="J359" s="40" t="inlineStr">
         <is>
-          <t>50-60K€/an</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K359" s="40" t="n"/>
       <c r="L359" s="40" t="inlineStr">
         <is>
-          <t>Senior SIRH Paie Lyon CDI. Salaire et localisation sous les critères cibles. Spécialisation paie et compliance.</t>
+          <t>Mission très longue durée, profil senior chef de projet SIRH. Peu de détails disponibles. Gonesse = déplacements réguliers.</t>
         </is>
       </c>
       <c r="M359" s="40" t="inlineStr">
         <is>
-          <t>https://washingtonfrank.com/job/a0M1i00000JW62x.1/consultant-senior-sirh-paie</t>
+          <t>https://www.freelance-informatique.fr/mission-sirh-2293</t>
         </is>
       </c>
       <c r="N359" s="40" t="inlineStr">
@@ -24934,13 +24976,13 @@
       </c>
       <c r="O359" s="40" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P359" s="40" t="n"/>
       <c r="Q359" s="42" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24996,7 @@
       <c r="C360" s="40" t="n"/>
       <c r="D360" s="40" t="inlineStr">
         <is>
-          <t>Chef de projet SIRH confirmé (longue durée)</t>
+          <t>Consultant SIRH (4 mois)</t>
         </is>
       </c>
       <c r="E360" s="40" t="inlineStr">
@@ -24974,7 +25016,7 @@
       </c>
       <c r="H360" s="40" t="inlineStr">
         <is>
-          <t>Gonesse (95)</t>
+          <t>Archamps (74, frontière Genève)</t>
         </is>
       </c>
       <c r="I360" s="40" t="inlineStr">
@@ -24987,10 +25029,14 @@
           <t>N/C</t>
         </is>
       </c>
-      <c r="K360" s="40" t="n"/>
+      <c r="K360" s="40" t="inlineStr">
+        <is>
+          <t>4 mois (démarrage 01/09/2026)</t>
+        </is>
+      </c>
       <c r="L360" s="40" t="inlineStr">
         <is>
-          <t>Mission très longue durée, profil senior chef de projet SIRH. Peu de détails disponibles. Gonesse = déplacements réguliers.</t>
+          <t>Démarrage 01/09/2026, Archamps (Haute-Savoie, frontière suisse). Possible si ouvert aux déplacements.</t>
         </is>
       </c>
       <c r="M360" s="40" t="inlineStr">
@@ -25025,52 +25071,48 @@
       <c r="C361" s="40" t="n"/>
       <c r="D361" s="40" t="inlineStr">
         <is>
-          <t>Consultant SIRH (4 mois)</t>
+          <t>Manager Technique SIRH H/F</t>
         </is>
       </c>
       <c r="E361" s="40" t="inlineStr">
         <is>
-          <t>n.c. (via Freelance-Informatique)</t>
+          <t>LCL (Crédit Agricole)</t>
         </is>
       </c>
       <c r="F361" s="40" t="inlineStr">
         <is>
-          <t>Freelance-Informatique</t>
+          <t>LCL Emploi</t>
         </is>
       </c>
       <c r="G361" s="40" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H361" s="40" t="inlineStr">
         <is>
-          <t>Archamps (74, frontière Genève)</t>
+          <t>Villejuif (94)</t>
         </is>
       </c>
       <c r="I361" s="40" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Présentiel</t>
         </is>
       </c>
       <c r="J361" s="40" t="inlineStr">
         <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="K361" s="40" t="inlineStr">
-        <is>
-          <t>4 mois (démarrage 01/09/2026)</t>
-        </is>
-      </c>
+          <t>+70K€ estimé</t>
+        </is>
+      </c>
+      <c r="K361" s="40" t="n"/>
       <c r="L361" s="40" t="inlineStr">
         <is>
-          <t>Démarrage 01/09/2026, Archamps (Haute-Savoie, frontière suisse). Possible si ouvert aux déplacements.</t>
+          <t>Profil très technique (architecture SIRH, PHP/Symfony, CI/CD, API/ETL). 10-15 ans exp. Secteur bancaire requis. Poste DSI/tech plutôt que consultant fonctionnel — frein pour Gaëtan.</t>
         </is>
       </c>
       <c r="M361" s="40" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/mission-sirh-2293</t>
+          <t>https://offres-emploi.lcl.com/offre-de-emploi/emploi-manager-technique-sirh-h-f_112081.aspx</t>
         </is>
       </c>
       <c r="N361" s="40" t="inlineStr">
@@ -25080,13 +25122,13 @@
       </c>
       <c r="O361" s="40" t="inlineStr">
         <is>
-          <t>650-750€/j</t>
+          <t>80-90K€</t>
         </is>
       </c>
       <c r="P361" s="40" t="n"/>
       <c r="Q361" s="42" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
     </row>
@@ -25100,17 +25142,17 @@
       <c r="C362" s="40" t="n"/>
       <c r="D362" s="40" t="inlineStr">
         <is>
-          <t>Manager Technique SIRH H/F</t>
+          <t>Chef de projet / Consultant SIRH H/F</t>
         </is>
       </c>
       <c r="E362" s="40" t="inlineStr">
         <is>
-          <t>LCL (Crédit Agricole)</t>
+          <t>Septeo (Septeo HR Solutions)</t>
         </is>
       </c>
       <c r="F362" s="40" t="inlineStr">
         <is>
-          <t>LCL Emploi</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G362" s="40" t="inlineStr">
@@ -25120,7 +25162,7 @@
       </c>
       <c r="H362" s="40" t="inlineStr">
         <is>
-          <t>Villejuif (94)</t>
+          <t>Dardilly (69)</t>
         </is>
       </c>
       <c r="I362" s="40" t="inlineStr">
@@ -25130,18 +25172,18 @@
       </c>
       <c r="J362" s="40" t="inlineStr">
         <is>
-          <t>+70K€ estimé</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K362" s="40" t="n"/>
       <c r="L362" s="40" t="inlineStr">
         <is>
-          <t>Profil très technique (architecture SIRH, PHP/Symfony, CI/CD, API/ETL). 10-15 ans exp. Secteur bancaire requis. Poste DSI/tech plutôt que consultant fonctionnel — frein pour Gaëtan.</t>
+          <t>Éditeur SIRH (10e éditeur logiciel FR), accompagnement clients end-to-end. 5 ans exp. min. Localisation Lyon uniquement, pas de remote mentionné. Intéressant si déplacement envisagé.</t>
         </is>
       </c>
       <c r="M362" s="40" t="inlineStr">
         <is>
-          <t>https://offres-emploi.lcl.com/offre-de-emploi/emploi-manager-technique-sirh-h-f_112081.aspx</t>
+          <t>https://www.welcometothejungle.com/fr/companies/septeo/jobs/chef-de-projet-consultant-sirh-h-f_lyon_SEPTE_XKL6GRl</t>
         </is>
       </c>
       <c r="N362" s="40" t="inlineStr">
@@ -25151,15 +25193,11 @@
       </c>
       <c r="O362" s="40" t="inlineStr">
         <is>
-          <t>80-90K€</t>
+          <t>65-75K€</t>
         </is>
       </c>
       <c r="P362" s="40" t="n"/>
-      <c r="Q362" s="42" t="inlineStr">
-        <is>
-          <t>04/07/2026</t>
-        </is>
-      </c>
+      <c r="Q362" s="40" t="n"/>
     </row>
     <row r="363" ht="32" customHeight="1">
       <c r="A363" s="87" t="inlineStr">
@@ -25171,7 +25209,7 @@
       <c r="C363" s="40" t="n"/>
       <c r="D363" s="40" t="inlineStr">
         <is>
-          <t>Chef de projet / Consultant SIRH H/F</t>
+          <t>Consultant SIRH Technico-Fonctionnel H/F</t>
         </is>
       </c>
       <c r="E363" s="40" t="inlineStr">
@@ -25207,12 +25245,12 @@
       <c r="K363" s="40" t="n"/>
       <c r="L363" s="40" t="inlineStr">
         <is>
-          <t>Éditeur SIRH (10e éditeur logiciel FR), accompagnement clients end-to-end. 5 ans exp. min. Localisation Lyon uniquement, pas de remote mentionné. Intéressant si déplacement envisagé.</t>
+          <t>Profil technico-fonctionnel, distinct du poste Chef de projet Septeo. Lyon uniquement, pas de remote.</t>
         </is>
       </c>
       <c r="M363" s="40" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/septeo/jobs/chef-de-projet-consultant-sirh-h-f_lyon_SEPTE_XKL6GRl</t>
+          <t>https://www.welcometothejungle.com/fr/companies/septeo/jobs/consultant-technico-fonctionnel-sirh-h-f_lyon</t>
         </is>
       </c>
       <c r="N363" s="40" t="inlineStr">
@@ -25222,7 +25260,7 @@
       </c>
       <c r="O363" s="40" t="inlineStr">
         <is>
-          <t>65-75K€</t>
+          <t>60-70K€</t>
         </is>
       </c>
       <c r="P363" s="40" t="n"/>
@@ -25238,12 +25276,12 @@
       <c r="C364" s="40" t="n"/>
       <c r="D364" s="40" t="inlineStr">
         <is>
-          <t>Consultant SIRH Technico-Fonctionnel H/F</t>
+          <t>Chef de projet SIRH F/H Workday</t>
         </is>
       </c>
       <c r="E364" s="40" t="inlineStr">
         <is>
-          <t>Septeo (Septeo HR Solutions)</t>
+          <t>IDEX</t>
         </is>
       </c>
       <c r="F364" s="40" t="inlineStr">
@@ -25258,28 +25296,28 @@
       </c>
       <c r="H364" s="40" t="inlineStr">
         <is>
-          <t>Dardilly (69)</t>
+          <t>Boulogne-Billancourt (92)</t>
         </is>
       </c>
       <c r="I364" s="40" t="inlineStr">
         <is>
-          <t>Présentiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J364" s="40" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>43 800 – 56 200 €/an</t>
         </is>
       </c>
       <c r="K364" s="40" t="n"/>
       <c r="L364" s="40" t="inlineStr">
         <is>
-          <t>Profil technico-fonctionnel, distinct du poste Chef de projet Septeo. Lyon uniquement, pas de remote.</t>
+          <t>Programme Workday Core HR + MDM. 4 ans exp. min. Fourchette salariale modeste (43-56K) pour le profil senior de Gaëtan. Option de repli.</t>
         </is>
       </c>
       <c r="M364" s="40" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/septeo/jobs/consultant-technico-fonctionnel-sirh-h-f_lyon</t>
+          <t>https://www.welcometothejungle.com/fr/companies/idex-1/jobs/chef-de-projet-sirh-f-h_boulogne-billancourt_IDEX_DlyydO0</t>
         </is>
       </c>
       <c r="N364" s="40" t="inlineStr">
@@ -25289,7 +25327,7 @@
       </c>
       <c r="O364" s="40" t="inlineStr">
         <is>
-          <t>60-70K€</t>
+          <t>70-80K€</t>
         </is>
       </c>
       <c r="P364" s="40" t="n"/>
@@ -25305,12 +25343,12 @@
       <c r="C365" s="40" t="n"/>
       <c r="D365" s="40" t="inlineStr">
         <is>
-          <t>Chef de projet SIRH F/H Workday</t>
+          <t>Chef de projet IT SIRH</t>
         </is>
       </c>
       <c r="E365" s="40" t="inlineStr">
         <is>
-          <t>IDEX</t>
+          <t>Objectware</t>
         </is>
       </c>
       <c r="F365" s="40" t="inlineStr">
@@ -25325,7 +25363,7 @@
       </c>
       <c r="H365" s="40" t="inlineStr">
         <is>
-          <t>Boulogne-Billancourt (92)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I365" s="40" t="inlineStr">
@@ -25335,18 +25373,18 @@
       </c>
       <c r="J365" s="40" t="inlineStr">
         <is>
-          <t>43 800 – 56 200 €/an</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K365" s="40" t="n"/>
       <c r="L365" s="40" t="inlineStr">
         <is>
-          <t>Programme Workday Core HR + MDM. 4 ans exp. min. Fourchette salariale modeste (43-56K) pour le profil senior de Gaëtan. Option de repli.</t>
+          <t>Cabinet de conseil IT. Détails non accessibles (WTJ bloqué). À investiguer directement.</t>
         </is>
       </c>
       <c r="M365" s="40" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/idex-1/jobs/chef-de-projet-sirh-f-h_boulogne-billancourt_IDEX_DlyydO0</t>
+          <t>https://www.welcometothejungle.com/fr/companies/objectware/jobs/chef-de-projet-it-sirh_paris</t>
         </is>
       </c>
       <c r="N365" s="40" t="inlineStr">
@@ -25372,12 +25410,12 @@
       <c r="C366" s="40" t="n"/>
       <c r="D366" s="40" t="inlineStr">
         <is>
-          <t>Chef de projet IT SIRH</t>
+          <t>Consultant SIRH Paie H/F</t>
         </is>
       </c>
       <c r="E366" s="40" t="inlineStr">
         <is>
-          <t>Objectware</t>
+          <t>Primexis</t>
         </is>
       </c>
       <c r="F366" s="40" t="inlineStr">
@@ -25392,7 +25430,7 @@
       </c>
       <c r="H366" s="40" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Puteaux (92)</t>
         </is>
       </c>
       <c r="I366" s="40" t="inlineStr">
@@ -25402,18 +25440,18 @@
       </c>
       <c r="J366" s="40" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>40 000 – 55 000 €/an</t>
         </is>
       </c>
       <c r="K366" s="40" t="n"/>
       <c r="L366" s="40" t="inlineStr">
         <is>
-          <t>Cabinet de conseil IT. Détails non accessibles (WTJ bloqué). À investiguer directement.</t>
+          <t>Spécialité paie/Silae (pas SAP SF). Cabinet 450 pers. Fourchette basse pour profil senior. Option de repli.</t>
         </is>
       </c>
       <c r="M366" s="40" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/objectware/jobs/chef-de-projet-it-sirh_paris</t>
+          <t>https://www.welcometothejungle.com/fr/companies/primexis/jobs/consultant-sirh-paie-h-f_puteaux_PRIME_5AyPM2D</t>
         </is>
       </c>
       <c r="N366" s="40" t="inlineStr">
@@ -25423,7 +25461,7 @@
       </c>
       <c r="O366" s="40" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>60-70K€</t>
         </is>
       </c>
       <c r="P366" s="40" t="n"/>
@@ -25439,17 +25477,17 @@
       <c r="C367" s="40" t="n"/>
       <c r="D367" s="40" t="inlineStr">
         <is>
-          <t>Consultant SIRH Paie H/F</t>
+          <t>Product Owner IT SIRH CDI F/H/NB</t>
         </is>
       </c>
       <c r="E367" s="40" t="inlineStr">
         <is>
-          <t>Primexis</t>
+          <t>Disneyland Paris (The Walt Disney Company)</t>
         </is>
       </c>
       <c r="F367" s="40" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Disney Careers</t>
         </is>
       </c>
       <c r="G367" s="40" t="inlineStr">
@@ -25459,7 +25497,7 @@
       </c>
       <c r="H367" s="40" t="inlineStr">
         <is>
-          <t>Puteaux (92)</t>
+          <t>Marne-la-Vallée</t>
         </is>
       </c>
       <c r="I367" s="40" t="inlineStr">
@@ -25469,18 +25507,18 @@
       </c>
       <c r="J367" s="40" t="inlineStr">
         <is>
-          <t>40 000 – 55 000 €/an</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K367" s="40" t="n"/>
       <c r="L367" s="40" t="inlineStr">
         <is>
-          <t>Spécialité paie/Silae (pas SAP SF). Cabinet 450 pers. Fourchette basse pour profil senior. Option de repli.</t>
+          <t>Publié 2025 — peut être clôturé. Roadmap RH applications globales Walt Disney Company. Contexte international prestigieux. Vérifier si encore actif avant de postuler.</t>
         </is>
       </c>
       <c r="M367" s="40" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/primexis/jobs/consultant-sirh-paie-h-f_puteaux_PRIME_5AyPM2D</t>
+          <t>https://emplois.disneycareers.com/emploi/marne-la-vallee/product-owner-it-sirh-cdi-f-h-nb/391/77875747712</t>
         </is>
       </c>
       <c r="N367" s="40" t="inlineStr">
@@ -25490,7 +25528,7 @@
       </c>
       <c r="O367" s="40" t="inlineStr">
         <is>
-          <t>60-70K€</t>
+          <t>75-85K€</t>
         </is>
       </c>
       <c r="P367" s="40" t="n"/>
@@ -25506,62 +25544,66 @@
       <c r="C368" s="40" t="n"/>
       <c r="D368" s="40" t="inlineStr">
         <is>
-          <t>Product Owner IT SIRH CDI F/H/NB</t>
+          <t>Chargé de missions SIRH N2 – Workday HCM H/F</t>
         </is>
       </c>
       <c r="E368" s="40" t="inlineStr">
         <is>
-          <t>Disneyland Paris (The Walt Disney Company)</t>
+          <t>HR DNA</t>
         </is>
       </c>
       <c r="F368" s="40" t="inlineStr">
         <is>
-          <t>Disney Careers</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G368" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H368" s="40" t="inlineStr">
         <is>
-          <t>Marne-la-Vallée</t>
+          <t>Neuilly-sur-Marne (93)</t>
         </is>
       </c>
       <c r="I368" s="40" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J368" s="40" t="inlineStr">
         <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="K368" s="40" t="n"/>
+          <t>250-500€/j</t>
+        </is>
+      </c>
+      <c r="K368" s="40" t="inlineStr">
+        <is>
+          <t>24 mois</t>
+        </is>
+      </c>
       <c r="L368" s="40" t="inlineStr">
         <is>
-          <t>Publié 2025 — peut être clôturé. Roadmap RH applications globales Walt Disney Company. Contexte international prestigieux. Vérifier si encore actif avant de postuler.</t>
+          <t>MOA SIRH Workday HCM (pas SAP), specs fonctionnelles, recette, TJM bas 250-500€/j, 24 mois — profil AMOA SIRH proche mais mauvais outil et TJM insuffisant</t>
         </is>
       </c>
       <c r="M368" s="40" t="inlineStr">
         <is>
-          <t>https://emplois.disneycareers.com/emploi/marne-la-vallee/product-owner-it-sirh-cdi-f-h-nb/391/77875747712</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/charge-de-missions-sirh-n2-workday-hcm-h-f-23</t>
         </is>
       </c>
       <c r="N368" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
-        </is>
-      </c>
-      <c r="O368" s="40" t="inlineStr">
-        <is>
-          <t>75-85K€</t>
-        </is>
-      </c>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O368" s="40" t="n"/>
       <c r="P368" s="40" t="n"/>
-      <c r="Q368" s="40" t="n"/>
+      <c r="Q368" s="42" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="369" hidden="1" ht="16" customHeight="1">
       <c r="A369" s="87" t="inlineStr">
@@ -25573,66 +25615,62 @@
       <c r="C369" s="40" t="n"/>
       <c r="D369" s="40" t="inlineStr">
         <is>
-          <t>Chargé de missions SIRH N2 – Workday HCM H/F</t>
+          <t>Consultant SAP SuccessFactors</t>
         </is>
       </c>
       <c r="E369" s="40" t="inlineStr">
         <is>
-          <t>HR DNA</t>
+          <t>CELAD</t>
         </is>
       </c>
       <c r="F369" s="40" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G369" s="40" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H369" s="40" t="inlineStr">
         <is>
-          <t>Neuilly-sur-Marne (93)</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I369" s="40" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="J369" s="40" t="inlineStr">
         <is>
-          <t>250-500€/j</t>
-        </is>
-      </c>
-      <c r="K369" s="40" t="inlineStr">
-        <is>
-          <t>24 mois</t>
-        </is>
-      </c>
+          <t>nc</t>
+        </is>
+      </c>
+      <c r="K369" s="40" t="n"/>
       <c r="L369" s="40" t="inlineStr">
         <is>
-          <t>MOA SIRH Workday HCM (pas SAP), specs fonctionnelles, recette, TJM bas 250-500€/j, 24 mois — profil AMOA SIRH proche mais mauvais outil et TJM insuffisant</t>
+          <t>SAP SF + SAP HR ECP</t>
         </is>
       </c>
       <c r="M369" s="40" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/charge-de-missions-sirh-n2-workday-hcm-h-f-23</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-sap-succesfactors-sap-hr-ecp-h-f-at-celad-3275307413</t>
         </is>
       </c>
       <c r="N369" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O369" s="40" t="n"/>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+        </is>
+      </c>
+      <c r="O369" s="40" t="inlineStr">
+        <is>
+          <t>70-85K€</t>
+        </is>
+      </c>
       <c r="P369" s="40" t="n"/>
-      <c r="Q369" s="42" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="Q369" s="40" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="87" t="inlineStr">
@@ -25644,17 +25682,17 @@
       <c r="C370" s="40" t="n"/>
       <c r="D370" s="40" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors</t>
+          <t>SIRH and Data RH Manager</t>
         </is>
       </c>
       <c r="E370" s="40" t="inlineStr">
         <is>
-          <t>CELAD</t>
+          <t>n.c. (Free-Work)</t>
         </is>
       </c>
       <c r="F370" s="40" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Free-Work</t>
         </is>
       </c>
       <c r="G370" s="40" t="inlineStr">
@@ -25664,7 +25702,7 @@
       </c>
       <c r="H370" s="40" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Montrouge</t>
         </is>
       </c>
       <c r="I370" s="40" t="inlineStr">
@@ -25674,18 +25712,18 @@
       </c>
       <c r="J370" s="40" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>42-69K€</t>
         </is>
       </c>
       <c r="K370" s="40" t="n"/>
       <c r="L370" s="40" t="inlineStr">
         <is>
-          <t>SAP SF + SAP HR ECP</t>
+          <t>Salaire bas — à vérifier</t>
         </is>
       </c>
       <c r="M370" s="40" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-sap-succesfactors-sap-hr-ecp-h-f-at-celad-3275307413</t>
+          <t>https://www.montrouge-emplois.fr/emplois/81020788.html</t>
         </is>
       </c>
       <c r="N370" s="40" t="inlineStr">
@@ -25695,11 +25733,15 @@
       </c>
       <c r="O370" s="40" t="inlineStr">
         <is>
-          <t>70-85K€</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="P370" s="40" t="n"/>
-      <c r="Q370" s="40" t="n"/>
+      <c r="Q370" s="42" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="87" t="inlineStr">
@@ -25711,7 +25753,7 @@
       <c r="C371" s="40" t="n"/>
       <c r="D371" s="40" t="inlineStr">
         <is>
-          <t>SIRH and Data RH Manager</t>
+          <t>AMOA RH Consultant</t>
         </is>
       </c>
       <c r="E371" s="40" t="inlineStr">
@@ -25731,7 +25773,7 @@
       </c>
       <c r="H371" s="40" t="inlineStr">
         <is>
-          <t>Montrouge</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I371" s="40" t="inlineStr">
@@ -25741,7 +25783,7 @@
       </c>
       <c r="J371" s="40" t="inlineStr">
         <is>
-          <t>42-69K€</t>
+          <t>53-55K€</t>
         </is>
       </c>
       <c r="K371" s="40" t="n"/>
@@ -25750,11 +25792,7 @@
           <t>Salaire bas — à vérifier</t>
         </is>
       </c>
-      <c r="M371" s="40" t="inlineStr">
-        <is>
-          <t>https://www.montrouge-emplois.fr/emplois/81020788.html</t>
-        </is>
-      </c>
+      <c r="M371" s="40" t="n"/>
       <c r="N371" s="40" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.html</t>
@@ -25782,17 +25820,17 @@
       <c r="C372" s="40" t="n"/>
       <c r="D372" s="40" t="inlineStr">
         <is>
-          <t>AMOA RH Consultant</t>
+          <t>Consultant junior IA</t>
         </is>
       </c>
       <c r="E372" s="40" t="inlineStr">
         <is>
-          <t>n.c. (Free-Work)</t>
+          <t>MISTER IA</t>
         </is>
       </c>
       <c r="F372" s="40" t="inlineStr">
         <is>
-          <t>Free-Work</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G372" s="40" t="inlineStr">
@@ -25812,32 +25850,32 @@
       </c>
       <c r="J372" s="40" t="inlineStr">
         <is>
-          <t>53-55K€</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="K372" s="40" t="n"/>
       <c r="L372" s="40" t="inlineStr">
         <is>
-          <t>Salaire bas — à vérifier</t>
-        </is>
-      </c>
-      <c r="M372" s="40" t="n"/>
+          <t>Intitulé "junior" — expérience Gaëtan peut repositionner en senior</t>
+        </is>
+      </c>
+      <c r="M372" s="40" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/mister-ia/jobs/consultant-junior-cdi-des-que-possible_paris</t>
+        </is>
+      </c>
       <c r="N372" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+          <t>Resume_GaetanFRANCOIS.pdf</t>
         </is>
       </c>
       <c r="O372" s="40" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>70-85K€</t>
         </is>
       </c>
       <c r="P372" s="40" t="n"/>
-      <c r="Q372" s="42" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q372" s="40" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="87" t="inlineStr">
@@ -25849,65 +25887,53 @@
       <c r="C373" s="40" t="n"/>
       <c r="D373" s="40" t="inlineStr">
         <is>
-          <t>Consultant junior IA</t>
+          <t>Group HRIS Specialist</t>
         </is>
       </c>
       <c r="E373" s="40" t="inlineStr">
         <is>
-          <t>MISTER IA</t>
+          <t>Lynxeo</t>
         </is>
       </c>
       <c r="F373" s="40" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G373" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>CDD 12 mois</t>
         </is>
       </c>
       <c r="H373" s="40" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Puteaux (La Défense)</t>
         </is>
       </c>
       <c r="I373" s="40" t="inlineStr">
         <is>
-          <t>nc</t>
-        </is>
-      </c>
-      <c r="J373" s="40" t="inlineStr">
-        <is>
-          <t>nc</t>
-        </is>
-      </c>
+          <t>Non précisé</t>
+        </is>
+      </c>
+      <c r="J373" s="40" t="n"/>
       <c r="K373" s="40" t="n"/>
       <c r="L373" s="40" t="inlineStr">
         <is>
-          <t>Intitulé "junior" — expérience Gaëtan peut repositionner en senior</t>
+          <t>SAP SF apprécié ; CDD 12 mois + Puteaux sur site = faible</t>
         </is>
       </c>
       <c r="M373" s="40" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/mister-ia/jobs/consultant-junior-cdi-des-que-possible_paris</t>
-        </is>
-      </c>
-      <c r="N373" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS.pdf</t>
-        </is>
-      </c>
-      <c r="O373" s="40" t="inlineStr">
-        <is>
-          <t>70-85K€</t>
-        </is>
-      </c>
+          <t>https://fr.linkedin.com/jobs/view/group-hris-specialist-at-lynxeo-4436222526</t>
+        </is>
+      </c>
+      <c r="N373" s="40" t="n"/>
+      <c r="O373" s="40" t="n"/>
       <c r="P373" s="40" t="n"/>
       <c r="Q373" s="40" t="n"/>
     </row>
     <row r="374">
-      <c r="A374" s="87" t="inlineStr">
+      <c r="A374" s="88" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -25916,49 +25942,57 @@
       <c r="C374" s="40" t="n"/>
       <c r="D374" s="40" t="inlineStr">
         <is>
-          <t>Group HRIS Specialist</t>
+          <t>Business Analyst TalentSoft / HR Access</t>
         </is>
       </c>
       <c r="E374" s="40" t="inlineStr">
         <is>
-          <t>Lynxeo</t>
+          <t>CELAD</t>
         </is>
       </c>
       <c r="F374" s="40" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G374" s="40" t="inlineStr">
         <is>
-          <t>CDD 12 mois</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H374" s="40" t="inlineStr">
         <is>
-          <t>Puteaux (La Défense)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I374" s="40" t="inlineStr">
         <is>
-          <t>Non précisé</t>
-        </is>
-      </c>
-      <c r="J374" s="40" t="n"/>
-      <c r="K374" s="40" t="n"/>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J374" s="40" t="inlineStr">
+        <is>
+          <t>450-500€/j</t>
+        </is>
+      </c>
+      <c r="K374" s="40" t="inlineStr">
+        <is>
+          <t>1 an</t>
+        </is>
+      </c>
       <c r="L374" s="40" t="inlineStr">
         <is>
-          <t>SAP SF apprécié ; CDD 12 mois + Puteaux sur site = faible</t>
-        </is>
-      </c>
-      <c r="M374" s="40" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/jobs/view/group-hris-specialist-at-lynxeo-4436222526</t>
-        </is>
-      </c>
+          <t>TalentSoft / HR Access, hors SF pur</t>
+        </is>
+      </c>
+      <c r="M374" s="40" t="n"/>
       <c r="N374" s="40" t="n"/>
       <c r="O374" s="40" t="n"/>
-      <c r="P374" s="40" t="n"/>
+      <c r="P374" s="40" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="Q374" s="40" t="n"/>
     </row>
     <row r="375">
@@ -25971,12 +26005,12 @@
       <c r="C375" s="40" t="n"/>
       <c r="D375" s="40" t="inlineStr">
         <is>
-          <t>Business Analyst TalentSoft / HR Access</t>
+          <t>Consultant SAP SuccessFactors (anglais)</t>
         </is>
       </c>
       <c r="E375" s="40" t="inlineStr">
         <is>
-          <t>CELAD</t>
+          <t>Intuition IT Solutions</t>
         </is>
       </c>
       <c r="F375" s="40" t="inlineStr">
@@ -25991,30 +26025,34 @@
       </c>
       <c r="H375" s="40" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="I375" s="40" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride 60/40</t>
         </is>
       </c>
       <c r="J375" s="40" t="inlineStr">
         <is>
-          <t>450-500€/j</t>
+          <t>400-580€/j</t>
         </is>
       </c>
       <c r="K375" s="40" t="inlineStr">
         <is>
-          <t>1 an</t>
+          <t>6 mois</t>
         </is>
       </c>
       <c r="L375" s="40" t="inlineStr">
         <is>
-          <t>TalentSoft / HR Access, hors SF pur</t>
-        </is>
-      </c>
-      <c r="M375" s="40" t="n"/>
+          <t>Luxembourg, hybride, SF ; 15/05/2026</t>
+        </is>
+      </c>
+      <c r="M375" s="40" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/jobs/sap-successfactors</t>
+        </is>
+      </c>
       <c r="N375" s="40" t="n"/>
       <c r="O375" s="40" t="n"/>
       <c r="P375" s="40" t="inlineStr">
@@ -26022,7 +26060,11 @@
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="Q375" s="40" t="n"/>
+      <c r="Q375" s="40" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="88" t="inlineStr">
@@ -26034,52 +26076,52 @@
       <c r="C376" s="40" t="n"/>
       <c r="D376" s="40" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors (anglais)</t>
+          <t>SIRH &amp; Data Manager F/H</t>
         </is>
       </c>
       <c r="E376" s="40" t="inlineStr">
         <is>
-          <t>Intuition IT Solutions</t>
+          <t>GLS France</t>
         </is>
       </c>
       <c r="F376" s="40" t="inlineStr">
         <is>
-          <t>free-work</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G376" s="40" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H376" s="40" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Toulouse (31)</t>
         </is>
       </c>
       <c r="I376" s="40" t="inlineStr">
         <is>
-          <t>Hybride 60/40</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J376" s="40" t="inlineStr">
         <is>
-          <t>400-580€/j</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K376" s="40" t="inlineStr">
         <is>
-          <t>6 mois</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="L376" s="40" t="inlineStr">
         <is>
-          <t>Luxembourg, hybride, SF ; 15/05/2026</t>
+          <t>Data + SIRH Toulouse, hors remote</t>
         </is>
       </c>
       <c r="M376" s="40" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/sap-successfactors</t>
+          <t>https://fr.linkedin.com/jobs/consultant-sirh-emplois</t>
         </is>
       </c>
       <c r="N376" s="40" t="n"/>
@@ -26089,14 +26131,10 @@
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="Q376" s="40" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
+      <c r="Q376" s="40" t="n"/>
     </row>
     <row r="377">
-      <c r="A377" s="88" t="inlineStr">
+      <c r="A377" s="87" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -26105,65 +26143,65 @@
       <c r="C377" s="40" t="n"/>
       <c r="D377" s="40" t="inlineStr">
         <is>
-          <t>SIRH &amp; Data Manager F/H</t>
+          <t>Expert(e) AMOA SIRH – Paie &amp; DSN</t>
         </is>
       </c>
       <c r="E377" s="40" t="inlineStr">
         <is>
-          <t>GLS France</t>
+          <t>BEEZEN</t>
         </is>
       </c>
       <c r="F377" s="40" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Free-Work</t>
         </is>
       </c>
       <c r="G377" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H377" s="40" t="inlineStr">
         <is>
-          <t>Toulouse (31)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I377" s="40" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>À clarifier</t>
         </is>
       </c>
       <c r="J377" s="40" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>À négocier</t>
         </is>
       </c>
       <c r="K377" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>3 mois</t>
         </is>
       </c>
       <c r="L377" s="40" t="inlineStr">
         <is>
-          <t>Data + SIRH Toulouse, hors remote</t>
+          <t>Publié 12/07/2026. Focus paie et DSN française, Pléiades apprécié ; hors coeur de ton expertise SF EC. Ne postuler que si mission tampon requise.</t>
         </is>
       </c>
       <c r="M377" s="40" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/consultant-sirh-emplois</t>
-        </is>
-      </c>
-      <c r="N377" s="40" t="n"/>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/</t>
+        </is>
+      </c>
+      <c r="N377" s="40" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+        </is>
+      </c>
       <c r="O377" s="40" t="n"/>
-      <c r="P377" s="40" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
+      <c r="P377" s="40" t="n"/>
       <c r="Q377" s="40" t="n"/>
     </row>
     <row r="378">
-      <c r="A378" s="87" t="inlineStr">
+      <c r="A378" s="52" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -26172,194 +26210,194 @@
       <c r="C378" s="40" t="n"/>
       <c r="D378" s="40" t="inlineStr">
         <is>
-          <t>Expert(e) AMOA SIRH – Paie &amp; DSN</t>
+          <t>Consultant(e) SIRH Workday (F/H)</t>
         </is>
       </c>
       <c r="E378" s="40" t="inlineStr">
         <is>
-          <t>BEEZEN</t>
+          <t>ACT-ON HRIS</t>
         </is>
       </c>
       <c r="F378" s="40" t="inlineStr">
         <is>
-          <t>Free-Work</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G378" s="40" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H378" s="40" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Neuilly-sur-Seine</t>
         </is>
       </c>
       <c r="I378" s="40" t="inlineStr">
         <is>
-          <t>À clarifier</t>
-        </is>
-      </c>
-      <c r="J378" s="40" t="inlineStr">
-        <is>
-          <t>À négocier</t>
-        </is>
-      </c>
-      <c r="K378" s="40" t="inlineStr">
-        <is>
-          <t>3 mois</t>
-        </is>
-      </c>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J378" s="40" t="n"/>
+      <c r="K378" s="40" t="n"/>
       <c r="L378" s="40" t="inlineStr">
         <is>
-          <t>Publié 12/07/2026. Focus paie et DSN française, Pléiades apprécié ; hors coeur de ton expertise SF EC. Ne postuler que si mission tampon requise.</t>
+          <t>Spécialiste Workday (Core HR, Talent, Comp, Learning) — pas d'expérience Workday affichée ; cabinets conseil SIRH déjà bien représentés dans le tableur</t>
         </is>
       </c>
       <c r="M378" s="40" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/</t>
+          <t>https://www.linkedin.com/jobs/view/4342149906/</t>
         </is>
       </c>
       <c r="N378" s="40" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O378" s="40" t="n"/>
-      <c r="P378" s="40" t="n"/>
-      <c r="Q378" s="40" t="n"/>
+      <c r="P378" s="40" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="Q378" s="42" t="n"/>
     </row>
     <row r="379">
-      <c r="A379" s="52" t="inlineStr">
+      <c r="A379" s="55" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B379" s="40" t="n"/>
-      <c r="C379" s="40" t="n"/>
+      <c r="B379" s="40" t="inlineStr">
+        <is>
+          <t>Senior Manager SIRH - Lyon (CDI)</t>
+        </is>
+      </c>
+      <c r="C379" s="40" t="inlineStr">
+        <is>
+          <t>ALTHEA</t>
+        </is>
+      </c>
       <c r="D379" s="40" t="inlineStr">
         <is>
-          <t>Consultant(e) SIRH Workday (F/H)</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="E379" s="40" t="inlineStr">
         <is>
-          <t>ACT-ON HRIS</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="F379" s="40" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="G379" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="H379" s="40" t="inlineStr">
         <is>
-          <t>Neuilly-sur-Seine</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="I379" s="40" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J379" s="40" t="n"/>
-      <c r="K379" s="40" t="n"/>
+          <t>ALTHEA cabinet conseil SIRH. Senior Manager, Lyon. Frein : Lyon pas remote. Profil senior bien aligné sinon.</t>
+        </is>
+      </c>
+      <c r="J379" s="40" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/althea/jobs/senior-manager-sirh-lyon-cdi_lyon</t>
+        </is>
+      </c>
+      <c r="K379" s="40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
       <c r="L379" s="40" t="inlineStr">
         <is>
-          <t>Spécialiste Workday (Core HR, Talent, Comp, Learning) — pas d'expérience Workday affichée ; cabinets conseil SIRH déjà bien représentés dans le tableur</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M379" s="40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4342149906/</t>
-        </is>
-      </c>
-      <c r="N379" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
+          <t>07/2026</t>
+        </is>
+      </c>
+      <c r="N379" s="40" t="n"/>
       <c r="O379" s="40" t="n"/>
-      <c r="P379" s="40" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
+      <c r="P379" s="40" t="n"/>
       <c r="Q379" s="42" t="n"/>
     </row>
     <row r="380">
-      <c r="A380" s="55" t="inlineStr">
+      <c r="A380" s="87" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B380" s="40" t="inlineStr">
-        <is>
-          <t>Senior Manager SIRH - Lyon (CDI)</t>
-        </is>
-      </c>
-      <c r="C380" s="40" t="inlineStr">
-        <is>
-          <t>ALTHEA</t>
-        </is>
-      </c>
+      <c r="B380" s="40" t="n"/>
+      <c r="C380" s="40" t="n"/>
       <c r="D380" s="40" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Senior SAP HCM Payroll &amp; Time Consultant</t>
         </is>
       </c>
       <c r="E380" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Strada Global</t>
         </is>
       </c>
       <c r="F380" s="40" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>LinkedIn (il y a 12h)</t>
         </is>
       </c>
       <c r="G380" s="40" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>CDI ou Mission</t>
         </is>
       </c>
       <c r="H380" s="40" t="inlineStr">
         <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I380" s="40" t="inlineStr">
+        <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="I380" s="40" t="inlineStr">
-        <is>
-          <t>ALTHEA cabinet conseil SIRH. Senior Manager, Lyon. Frein : Lyon pas remote. Profil senior bien aligné sinon.</t>
-        </is>
-      </c>
       <c r="J380" s="40" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/althea/jobs/senior-manager-sirh-lyon-cdi_lyon</t>
-        </is>
-      </c>
-      <c r="K380" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K380" s="40" t="n"/>
       <c r="L380" s="40" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>Strada Global (ex-Alight) - spécialiste SAP HR France. Très récent (12h). Focus paie/GTA plutôt technique - hors centre de profil mais SAP HR pertinent.</t>
         </is>
       </c>
       <c r="M380" s="40" t="inlineStr">
         <is>
-          <t>07/2026</t>
-        </is>
-      </c>
-      <c r="N380" s="40" t="n"/>
-      <c r="O380" s="40" t="n"/>
+          <t>https://fr.linkedin.com/jobs/sap-hcm-emplois</t>
+        </is>
+      </c>
+      <c r="N380" s="40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+        </is>
+      </c>
+      <c r="O380" s="40" t="inlineStr">
+        <is>
+          <t>700 €/j</t>
+        </is>
+      </c>
       <c r="P380" s="40" t="n"/>
       <c r="Q380" s="42" t="n"/>
     </row>
@@ -26373,65 +26411,69 @@
       <c r="C381" s="40" t="n"/>
       <c r="D381" s="40" t="inlineStr">
         <is>
-          <t>Senior SAP HCM Payroll &amp; Time Consultant</t>
+          <t>Chef de projet IA</t>
         </is>
       </c>
       <c r="E381" s="40" t="inlineStr">
         <is>
-          <t>Strada Global</t>
+          <t>HN SERVICES</t>
         </is>
       </c>
       <c r="F381" s="40" t="inlineStr">
         <is>
-          <t>LinkedIn (il y a 12h)</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G381" s="40" t="inlineStr">
         <is>
-          <t>CDI ou Mission</t>
+          <t>Freelance/CDI</t>
         </is>
       </c>
       <c r="H381" s="40" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I381" s="40" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J381" s="40" t="inlineStr">
         <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K381" s="40" t="n"/>
+          <t>400-710€/j</t>
+        </is>
+      </c>
+      <c r="K381" s="40" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
       <c r="L381" s="40" t="inlineStr">
         <is>
-          <t>Strada Global (ex-Alight) - spécialiste SAP HR France. Très récent (12h). Focus paie/GTA plutôt technique - hors centre de profil mais SAP HR pertinent.</t>
+          <t>Chef de projet IA généraliste. TJM 400-710€/j ou 40-70K€/an. Posté 15/07/2026.</t>
         </is>
       </c>
       <c r="M381" s="40" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/sap-hcm-emplois</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/ingenieur-ia-16</t>
         </is>
       </c>
       <c r="N381" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+          <t>Resume_GaetanFRANCOIS_IA.html</t>
         </is>
       </c>
       <c r="O381" s="40" t="inlineStr">
         <is>
-          <t>700 €/j</t>
+          <t>500-650€/j</t>
         </is>
       </c>
       <c r="P381" s="40" t="n"/>
       <c r="Q381" s="42" t="n"/>
     </row>
     <row r="382">
-      <c r="A382" s="87" t="inlineStr">
+      <c r="A382" s="95" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -26440,62 +26482,54 @@
       <c r="C382" s="40" t="n"/>
       <c r="D382" s="40" t="inlineStr">
         <is>
-          <t>Chef de projet IA</t>
+          <t>Chef de projet SIRH (H/F) / Consultant Paie et SIRH (H/F)</t>
         </is>
       </c>
       <c r="E382" s="40" t="inlineStr">
         <is>
-          <t>HN SERVICES</t>
+          <t>Ayming</t>
         </is>
       </c>
       <c r="F382" s="40" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>ayming.fr / Glassdoor</t>
         </is>
       </c>
       <c r="G382" s="40" t="inlineStr">
         <is>
-          <t>Freelance/CDI</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H382" s="40" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>France / Lyon</t>
         </is>
       </c>
       <c r="I382" s="40" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J382" s="40" t="inlineStr">
-        <is>
-          <t>400-710€/j</t>
-        </is>
-      </c>
-      <c r="K382" s="40" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
+          <t>Non précisé</t>
+        </is>
+      </c>
+      <c r="J382" s="40" t="n"/>
+      <c r="K382" s="40" t="n"/>
       <c r="L382" s="40" t="inlineStr">
         <is>
-          <t>Chef de projet IA généraliste. TJM 400-710€/j ou 40-70K€/an. Posté 15/07/2026.</t>
+          <t>Postes trouvés via recherche mais absents de la liste actuelle des offres ouvertes sur le site ; statut incertain (probablement pourvus). À vérifier manuellement avant de postuler.</t>
         </is>
       </c>
       <c r="M382" s="40" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/ingenieur-ia-16</t>
+          <t>https://www.ayming.fr/jobs/chef-de-projet-sirh-hf/</t>
         </is>
       </c>
       <c r="N382" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_IA.html</t>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
       <c r="O382" s="40" t="inlineStr">
         <is>
-          <t>500-650€/j</t>
+          <t>70-80K€</t>
         </is>
       </c>
       <c r="P382" s="40" t="n"/>
@@ -26511,17 +26545,17 @@
       <c r="C383" s="40" t="n"/>
       <c r="D383" s="40" t="inlineStr">
         <is>
-          <t>Chef de projet SIRH (H/F) / Consultant Paie et SIRH (H/F)</t>
+          <t>Consultant paramétrage SIRH paie (H/F)</t>
         </is>
       </c>
       <c r="E383" s="40" t="inlineStr">
         <is>
-          <t>Ayming</t>
+          <t>Talentia Software</t>
         </is>
       </c>
       <c r="F383" s="40" t="inlineStr">
         <is>
-          <t>ayming.fr / Glassdoor</t>
+          <t>engagement-jeunes.com</t>
         </is>
       </c>
       <c r="G383" s="40" t="inlineStr">
@@ -26531,7 +26565,7 @@
       </c>
       <c r="H383" s="40" t="inlineStr">
         <is>
-          <t>France / Lyon</t>
+          <t>Puteaux (92)</t>
         </is>
       </c>
       <c r="I383" s="40" t="inlineStr">
@@ -26543,12 +26577,12 @@
       <c r="K383" s="40" t="n"/>
       <c r="L383" s="40" t="inlineStr">
         <is>
-          <t>Postes trouvés via recherche mais absents de la liste actuelle des offres ouvertes sur le site ; statut incertain (probablement pourvus). À vérifier manuellement avant de postuler.</t>
+          <t>Éditeur RH/Finance français, poste paramétrage paie SIRH ; source secondaire peu détaillée, à vérifier directement sur le site de l'éditeur.</t>
         </is>
       </c>
       <c r="M383" s="40" t="inlineStr">
         <is>
-          <t>https://www.ayming.fr/jobs/chef-de-projet-sirh-hf/</t>
+          <t>https://www.engagement-jeunes.com/fr/detail-offre/37016104/cdi-talentia-software-consultant-parametrage-sirh-paie-h-f.html</t>
         </is>
       </c>
       <c r="N383" s="40" t="inlineStr">
@@ -26558,77 +26592,85 @@
       </c>
       <c r="O383" s="40" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>65-75K€</t>
         </is>
       </c>
       <c r="P383" s="40" t="n"/>
       <c r="Q383" s="42" t="n"/>
     </row>
     <row r="384">
-      <c r="A384" s="95" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
+      <c r="A384" s="33" t="inlineStr">
+        <is>
+          <t>⭐</t>
         </is>
       </c>
       <c r="B384" s="40" t="n"/>
       <c r="C384" s="40" t="n"/>
       <c r="D384" s="40" t="inlineStr">
         <is>
-          <t>Consultant paramétrage SIRH paie (H/F)</t>
+          <t>Expert HR ACCESS</t>
         </is>
       </c>
       <c r="E384" s="40" t="inlineStr">
         <is>
-          <t>Talentia Software</t>
+          <t>Client anonyme</t>
         </is>
       </c>
       <c r="F384" s="40" t="inlineStr">
         <is>
-          <t>engagement-jeunes.com</t>
+          <t>freelance-informatique.fr</t>
         </is>
       </c>
       <c r="G384" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H384" s="40" t="inlineStr">
         <is>
-          <t>Puteaux (92)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I384" s="40" t="inlineStr">
         <is>
-          <t>Non précisé</t>
-        </is>
-      </c>
-      <c r="J384" s="40" t="n"/>
-      <c r="K384" s="40" t="n"/>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J384" s="40" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K384" s="40" t="inlineStr">
+        <is>
+          <t>3 mois</t>
+        </is>
+      </c>
       <c r="L384" s="40" t="inlineStr">
         <is>
-          <t>Éditeur RH/Finance français, poste paramétrage paie SIRH ; source secondaire peu détaillée, à vérifier directement sur le site de l'éditeur.</t>
+          <t>HR Access — hors du cœur SAP/SF de Gaetan, start 14/07/2026</t>
         </is>
       </c>
       <c r="M384" s="40" t="inlineStr">
         <is>
-          <t>https://www.engagement-jeunes.com/fr/detail-offre/37016104/cdi-talentia-software-consultant-parametrage-sirh-paie-h-f.html</t>
+          <t>https://www.freelance-informatique.fr/mission-expert-hr-access-sur-paris-260702C002</t>
         </is>
       </c>
       <c r="N384" s="40" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O384" s="40" t="inlineStr">
-        <is>
-          <t>65-75K€</t>
-        </is>
-      </c>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O384" s="40" t="n"/>
       <c r="P384" s="40" t="n"/>
-      <c r="Q384" s="42" t="n"/>
+      <c r="Q384" s="42" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="385">
-      <c r="A385" s="33" t="inlineStr">
+      <c r="A385" s="89" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
@@ -26637,17 +26679,17 @@
       <c r="C385" s="40" t="n"/>
       <c r="D385" s="40" t="inlineStr">
         <is>
-          <t>Expert HR ACCESS</t>
+          <t>Intégrateur d'application SIRH</t>
         </is>
       </c>
       <c r="E385" s="40" t="inlineStr">
         <is>
-          <t>Client anonyme</t>
+          <t>n.c. (Freelance-Informatique)</t>
         </is>
       </c>
       <c r="F385" s="40" t="inlineStr">
         <is>
-          <t>freelance-informatique.fr</t>
+          <t>Freelance-Informatique</t>
         </is>
       </c>
       <c r="G385" s="40" t="inlineStr">
@@ -26657,7 +26699,7 @@
       </c>
       <c r="H385" s="40" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="I385" s="40" t="inlineStr">
@@ -26667,30 +26709,34 @@
       </c>
       <c r="J385" s="40" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="K385" s="40" t="inlineStr">
         <is>
-          <t>3 mois</t>
+          <t>6 mois</t>
         </is>
       </c>
       <c r="L385" s="40" t="inlineStr">
         <is>
-          <t>HR Access — hors du cœur SAP/SF de Gaetan, start 14/07/2026</t>
+          <t>Pas remote — Rouen</t>
         </is>
       </c>
       <c r="M385" s="40" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/mission-expert-hr-access-sur-paris-260702C002</t>
+          <t>https://www.freelance-informatique.fr/mission-sirh-2293</t>
         </is>
       </c>
       <c r="N385" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O385" s="40" t="n"/>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+        </is>
+      </c>
+      <c r="O385" s="40" t="inlineStr">
+        <is>
+          <t>650€/j</t>
+        </is>
+      </c>
       <c r="P385" s="40" t="n"/>
       <c r="Q385" s="42" t="inlineStr">
         <is>
@@ -26699,79 +26745,23 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="89" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
+      <c r="A386" s="89" t="n"/>
       <c r="B386" s="40" t="n"/>
       <c r="C386" s="40" t="n"/>
-      <c r="D386" s="40" t="inlineStr">
-        <is>
-          <t>Intégrateur d'application SIRH</t>
-        </is>
-      </c>
-      <c r="E386" s="40" t="inlineStr">
-        <is>
-          <t>n.c. (Freelance-Informatique)</t>
-        </is>
-      </c>
-      <c r="F386" s="40" t="inlineStr">
-        <is>
-          <t>Freelance-Informatique</t>
-        </is>
-      </c>
-      <c r="G386" s="40" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H386" s="40" t="inlineStr">
-        <is>
-          <t>Rouen</t>
-        </is>
-      </c>
-      <c r="I386" s="40" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="J386" s="40" t="inlineStr">
-        <is>
-          <t>nc</t>
-        </is>
-      </c>
-      <c r="K386" s="40" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
-      <c r="L386" s="40" t="inlineStr">
-        <is>
-          <t>Pas remote — Rouen</t>
-        </is>
-      </c>
-      <c r="M386" s="40" t="inlineStr">
-        <is>
-          <t>https://www.freelance-informatique.fr/mission-sirh-2293</t>
-        </is>
-      </c>
-      <c r="N386" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
-        </is>
-      </c>
-      <c r="O386" s="40" t="inlineStr">
-        <is>
-          <t>650€/j</t>
-        </is>
-      </c>
+      <c r="D386" s="40" t="n"/>
+      <c r="E386" s="40" t="n"/>
+      <c r="F386" s="40" t="n"/>
+      <c r="G386" s="40" t="n"/>
+      <c r="H386" s="40" t="n"/>
+      <c r="I386" s="40" t="n"/>
+      <c r="J386" s="40" t="n"/>
+      <c r="K386" s="40" t="n"/>
+      <c r="L386" s="40" t="n"/>
+      <c r="M386" s="40" t="n"/>
+      <c r="N386" s="40" t="n"/>
+      <c r="O386" s="40" t="n"/>
       <c r="P386" s="40" t="n"/>
-      <c r="Q386" s="42" t="inlineStr">
-        <is>
-          <t>02/07/2026</t>
-        </is>
-      </c>
+      <c r="Q386" s="42" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="33" t="n"/>
@@ -26835,7 +26825,7 @@
     </filterColumn>
   </autoFilter>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26847,7 +26837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q241"/>
+  <dimension ref="A1:Q242"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="11.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -41892,56 +41882,62 @@
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="B239" s="40" t="n"/>
+      <c r="C239" s="40" t="n"/>
+      <c r="D239" s="40" t="inlineStr">
         <is>
           <t>Customer Success Manager, EU</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E239" s="40" t="inlineStr">
         <is>
           <t>Pacvue</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
+      <c r="F239" s="40" t="inlineStr">
         <is>
           <t>job-boards.greenhouse.io</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
+      <c r="G239" s="40" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H239" s="40" t="inlineStr">
         <is>
           <t>Remote UK ou Allemagne</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
+      <c r="I239" s="40" t="inlineStr">
         <is>
           <t>Oui (zone EU, France non listée explicitement)</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="J239" s="40" t="n"/>
+      <c r="K239" s="40" t="n"/>
+      <c r="L239" s="40" t="inlineStr">
         <is>
           <t>Zone EU correspond au profil mais la France n'est pas explicitement listée comme éligible ; à vérifier en candidatant.</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr">
+      <c r="M239" s="40" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/pacvue/jobs/4712905004</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr">
+      <c r="N239" s="40" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr">
+      <c r="O239" s="40" t="inlineStr">
         <is>
           <t>75-85K€</t>
         </is>
       </c>
+      <c r="P239" s="40" t="n"/>
+      <c r="Q239" s="40" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="95" t="inlineStr">
@@ -42076,6 +42072,25 @@
           <t>09/07/2026</t>
         </is>
       </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="56" t="n"/>
+      <c r="B242" s="40" t="n"/>
+      <c r="C242" s="40" t="n"/>
+      <c r="D242" s="40" t="n"/>
+      <c r="E242" s="40" t="n"/>
+      <c r="F242" s="40" t="n"/>
+      <c r="G242" s="40" t="n"/>
+      <c r="H242" s="40" t="n"/>
+      <c r="I242" s="40" t="n"/>
+      <c r="J242" s="40" t="n"/>
+      <c r="K242" s="40" t="n"/>
+      <c r="L242" s="40" t="n"/>
+      <c r="M242" s="40" t="n"/>
+      <c r="N242" s="40" t="n"/>
+      <c r="O242" s="40" t="n"/>
+      <c r="P242" s="40" t="n"/>
+      <c r="Q242" s="40" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O115">
@@ -48824,7 +48839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="16" max="17"/>
@@ -53369,7 +53384,307 @@
       </c>
       <c r="Q64" s="42" t="n"/>
     </row>
+    <row r="65">
+      <c r="A65" s="94" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C65" s="40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Operational Onboarding Manager - France</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Biarritz</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>Flexible (présentiel valorisé)</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>n.c. (grille B0-B1)</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="n"/>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>Scale-up assurance santé SaaS, onboarding administratif des plus gros clients, ateliers formation RH/Paie. Localisation Biarritz = très proche Anglet. Rôle plus opérationnel/junior qu'un CSM Senior classique, remote seulement flexible. | Postulé le 04/08/2026. Aussi sur LinkedIn : https://www.linkedin.com/jobs/view/4432803785/</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/alan/149e6bff-b83d-4f7f-bfa8-9eb251bf437c</t>
+        </is>
+      </c>
+      <c r="N65" s="40" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="O65" s="40" t="n"/>
+      <c r="P65" s="40" t="n"/>
+      <c r="Q65" s="42" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="50" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Senior Manager, SAP SuccessFactors Employee Central &amp; Platform</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Foundever</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>UK (remote)</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>£75-90K (~87-105K€)</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="n"/>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>Lead équipe globale SF EC 40+ pays ; gouvernance, stratégie, config EC, RBP, intégrations HR/Payroll/Finance — calque L'Oréal 40+ pays parfait | Postulé le 04/08/2026. Aussi sur LinkedIn : https://www.linkedin.com/jobs/view/4429527206/</t>
+        </is>
+      </c>
+      <c r="M66" s="69" t="inlineStr">
+        <is>
+          <t>https://jobs.foundever.com/job/UK-Wide-Senior-Manager%2C-SAP-SuccessFactors-Employee-Central-&amp;-Platform-Work-Sitel-UK-L/1400161700/</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>95K€</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="Q66" s="42" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="90" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>SuccessFactors Talent Management Consultant</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Empiric</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Suède (remote)</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>100% remote (Suède)</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>12 mois</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>Consultant fonctionnel SAP SuccessFactors : Performance &amp; Goals, Career Development, Succession, Recruiting, Onboarding ; interface entre RH et technique, intégrations SIRH. Anglais courant requis, suédois apprécié. Remote annoncé en Suède, donc à clarifier depuis la France. Postulé le 04/08/2026.</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447004933/</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="Q67" s="42" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="82" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>HRIS Data Consultant - Payroll &amp; HR</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Silver Cloud</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn / Hibob</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>Remote + déplacements clients</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>n.c. (marché : 82-88 K€ / £70-75K)</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="n"/>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>Cabinet conseil HR tech : projets de transformation SIRH/paie, migration de données, mapping, validation, réconciliation, ateliers de découverte. Outils cités : Dayforce, Workday, HiBob. Très bon fit avec les migrations OnePayroll (L'Oréal) et FMC Technologies. Points à clarifier : poste UK depuis la France (devise, contrat, risque de change) et fréquence des déplacements clients depuis Anglet. Comparable marché : Dayforce Data Conversion full remote UK affiché £80K. Postulé le 04/08/2026. Aussi sur Hibob : https://silvercloud.careers.hibob.com/jobs/4c27dd97-5a45-4ed8-9f96-9eefd10c5899</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4443868475/</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>85 K€ (£72K)</t>
+        </is>
+      </c>
+      <c r="Q68" s="42" t="n"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -3931,7 +3931,11 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B46" s="40" t="n"/>
+      <c r="B46" s="40" t="inlineStr">
+        <is>
+          <t>À postuler</t>
+        </is>
+      </c>
       <c r="C46" s="40" t="n"/>
       <c r="D46" s="5" t="inlineStr">
         <is>
@@ -3977,7 +3981,7 @@
       </c>
       <c r="N46" s="40" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+          <t>Resume_GaetanFRANCOIS_Arago.pdf</t>
         </is>
       </c>
       <c r="O46" s="40" t="inlineStr">

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -1388,21 +1388,25 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="n"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Group HRIS Manager</t>
+          <t>HRIS &amp; AI Tech Pre-Sales Specialist</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>CLM Search (groupe industriel mondial)</t>
+          <t>Arago Consulting</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>SmartRecruiters</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1412,41 +1416,42 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris ou Bordeaux</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+          <t>Partiel (déplacements clients)</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Groupe industriel 40+ pays, 170K salariés, 30Mds€ — SF expertise non negotiable (Comp/Recruiting/Reporting) — évolution HRIS Director — FIT PARFAIT (L'Oréal 40+ pays)</t>
+          <t>Arago = 1er partenaire européen SAP SuccessFactors. Croisement parfait pre-sales IA+SIRH : 14 ans SAP, 40 pays L'Oréal, usage quotidien IA générative, profil face-client senior. Bordeaux = 2h d'Anglet. Lien : jobs.smartrecruiters.com/Arago/744000139094386 Postulé le 04/08/2026 (CV Resume_GaetanFRANCOIS_Arago.pdf + message hiring team).</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4415288591</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>95 K€</t>
-        </is>
-      </c>
-      <c r="Q7" s="42" t="n"/>
+          <t>https://jobs.smartrecruiters.com/Arago/744000139094386-hris-ai-tech-pre-sales-specialist</t>
+        </is>
+      </c>
+      <c r="N7" s="40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Arago.pdf</t>
+        </is>
+      </c>
+      <c r="O7" s="40" t="inlineStr">
+        <is>
+          <t>90-110K€</t>
+        </is>
+      </c>
+      <c r="P7" s="40" t="n"/>
+      <c r="Q7" s="42" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="8" hidden="1" ht="40" customHeight="1">
       <c r="A8" s="78" t="inlineStr">
@@ -1458,17 +1463,17 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Senior Manager Conseil Talent Management F/H</t>
+          <t>Group HRIS Manager</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>HRConseil</t>
+          <t>CLM Search (groupe industriel mondial)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>SmartRecruiters</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1483,43 +1488,39 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Hybride (3j/sem)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>75 000 - 85 000 € + 8 000 € bonus</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil SIRH (Workday, SF, Oracle HCM). 15+ ans requis, maîtrise SF, face client, avant-vente, management consultants. Salaire dans la cible haute. Fit parfait avec le profil Gaëtan (15 ans, SAP/SF, L'Oréal, avant-vente).</t>
+          <t>Groupe industriel 40+ pays, 170K salariés, 30Mds€ — SF expertise non negotiable (Comp/Recruiting/Reporting) — évolution HRIS Director — FIT PARFAIT (L'Oréal 40+ pays)</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/HRConseil1/744000100293238-senior-manager-conseil-talent-management-f-h-cdi</t>
+          <t>https://fr.linkedin.com/jobs/view/4415288591</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>82 K€</t>
-        </is>
-      </c>
-      <c r="Q8" s="42" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
+          <t>95 K€</t>
+        </is>
+      </c>
+      <c r="Q8" s="42" t="n"/>
     </row>
     <row r="9" hidden="1" ht="40" customHeight="1">
-      <c r="A9" s="77" t="inlineStr">
+      <c r="A9" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1528,17 +1529,17 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Senior Principal Success Manager</t>
+          <t>Senior Manager Conseil Talent Management F/H</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>HRConseil</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Salesforce Careers</t>
+          <t>SmartRecruiters</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1553,29 +1554,38 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="n"/>
+          <t>Hybride (3j/sem)</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>75 000 - 85 000 € + 8 000 € bonus</t>
+        </is>
+      </c>
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Niveau CSM le plus élevé chez Salesforce France, profil 15 ans exact, posté 23/03/2026</t>
+          <t>Cabinet conseil SIRH (Workday, SF, Oracle HCM). 15+ ans requis, maîtrise SF, face client, avant-vente, management consultants. Salaire dans la cible haute. Fit parfait avec le profil Gaëtan (15 ans, SAP/SF, L'Oréal, avant-vente).</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>https://careers.salesforce.com/en/jobs/jr330883/senior-principal-success-manager/</t>
+          <t>https://jobs.smartrecruiters.com/HRConseil1/744000100293238-senior-manager-conseil-talent-management-f-h-cdi</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>82 K€</t>
         </is>
       </c>
       <c r="Q9" s="42" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
     </row>
@@ -1589,17 +1599,17 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors H/F</t>
+          <t>Senior Principal Success Manager</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>HR Path</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>HR Path Careers</t>
+          <t>Salesforce Careers</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1609,7 +1619,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Paris La Défense</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1621,27 +1631,27 @@
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Cabinet SIRH majeur, projets SF internationaux, 2 ans mini SF — profil L'Oréal 40 pays en cible directe</t>
+          <t>Niveau CSM le plus élevé chez Salesforce France, profil 15 ans exact, posté 23/03/2026</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
+          <t>https://careers.salesforce.com/en/jobs/jr330883/senior-principal-success-manager/</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS.pdf</t>
         </is>
       </c>
       <c r="Q10" s="42" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="11" hidden="1" ht="40" customHeight="1">
-      <c r="A11" s="78" t="inlineStr">
+      <c r="A11" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1650,52 +1660,49 @@
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Directeur de Programme SIRH Senior H/F</t>
+          <t>Consultant SAP SuccessFactors H/F</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>LeHibou (client grand groupe)</t>
+          <t>HR Path</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>HR Path Careers</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris La Défense</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>650-780 €/j</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>18 mois (démarrage août 2026)</t>
-        </is>
-      </c>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Pilotage transformation RH grand groupe international bout en bout. 15 ans requis, SAP SF/TalentSoft/Workday. TJM dans cible haute, durée longue. Profil parfait.</t>
+          <t>Cabinet SIRH majeur, projets SF internationaux, 2 ans mini SF — profil L'Oréal 40 pays en cible directe</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="Q11" s="42" t="inlineStr">
@@ -1705,7 +1712,7 @@
       </c>
     </row>
     <row r="12" hidden="1" ht="40" customHeight="1">
-      <c r="A12" s="77" t="inlineStr">
+      <c r="A12" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1714,124 +1721,121 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>Directeur de Programme SIRH Senior H/F</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>LeHibou (client grand groupe)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>free-work.com</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>650-780 €/j</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>18 mois (démarrage août 2026)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Pilotage transformation RH grand groupe international bout en bout. 15 ans requis, SAP SF/TalentSoft/Workday. TJM dans cible haute, durée longue. Profil parfait.</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
+        </is>
+      </c>
+      <c r="Q12" s="42" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" hidden="1" ht="40" customHeight="1">
+      <c r="A13" s="77" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
           <t>Consultant(e) SIRH – Audit SIRH Grand Groupe</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Client grand groupe (via Le Club des RH)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>leclubdesrh.fr</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>Partiel (2j/sem)</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>900 €/j</t>
         </is>
       </c>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>TJM 900€/j. Audit SIRH grand groupe, 2j/sem Paris. Mission visible uniquement après inscription sur app.leclubdesrh.fr (rejoindre la communauté via airtable.com/appqNConNIfeCCjB8/shrhxbRraMvUqda2C).</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>https://app.leclubdesrh.fr/</t>
-        </is>
-      </c>
-      <c r="N12" s="40" t="n"/>
-      <c r="O12" s="40" t="n"/>
-      <c r="P12" s="40" t="n"/>
-      <c r="Q12" s="42" t="n"/>
-    </row>
-    <row r="13" hidden="1" ht="40" customHeight="1">
-      <c r="A13" s="78" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B13" s="40" t="n"/>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Directeur de Programme SIRH Senior H/F</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>LeHibou (client grand groupe)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>free-work.com</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>650-780 €/j</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>18 mois (démarrage août 2026)</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Pilotage transformation RH grand groupe international bout en bout. 15 ans requis, SAP SF/Workday. TJM dans cible haute, durée longue.</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
         </is>
       </c>
       <c r="N13" s="40" t="n"/>
       <c r="O13" s="40" t="n"/>
       <c r="P13" s="40" t="n"/>
-      <c r="Q13" s="42" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
+      <c r="Q13" s="42" t="n"/>
     </row>
     <row r="14" hidden="1" ht="40" customHeight="1">
-      <c r="A14" s="77" t="inlineStr">
+      <c r="A14" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1840,73 +1844,65 @@
       <c r="C14" s="40" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Data Migration SAP SuccessFactors Consultant (24 mois)</t>
+          <t>Directeur de Programme SIRH Senior H/F</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via Freelance-Informatique)</t>
+          <t>LeHibou (client grand groupe)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Freelance-Informatique</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Clichy (92)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>650-780 €/j</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>24 mois (démarrage ASAP)</t>
+          <t>18 mois (démarrage août 2026)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Spécialité migration données SAP SuccessFactors. Profil Gaëtan : migration SAP HR → SF sur L'Oréal 40+ pays = différenciant majeur. Mission longue et très alignée.</t>
+          <t>Pilotage transformation RH grand groupe international bout en bout. 15 ans requis, SAP SF/Workday. TJM dans cible haute, durée longue.</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/cv-mission-consultant-sap-successfactors-freelance-f11256</t>
-        </is>
-      </c>
-      <c r="N14" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
-        </is>
-      </c>
-      <c r="O14" s="40" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
+        </is>
+      </c>
+      <c r="N14" s="40" t="n"/>
+      <c r="O14" s="40" t="n"/>
       <c r="P14" s="40" t="n"/>
       <c r="Q14" s="42" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
     <row r="15" hidden="1" ht="40" customHeight="1">
-      <c r="A15" s="78" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1915,65 +1911,73 @@
       <c r="C15" s="40" t="n"/>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>HR Tech Run Lead</t>
+          <t>Data Migration SAP SuccessFactors Consultant (24 mois)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>L'Oréal</t>
+          <t>n.c. (via Freelance-Informatique)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Freelance-Informatique</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Clichy (92)</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Hybride (3j bureau / 2j remote)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>nc</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="n"/>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>24 mois (démarrage ASAP)</t>
+        </is>
+      </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>EXCEPTIONNEL : Biarritz + 10 ans L'Oréal SAP HCM/SF dans le profil — 10+ ans HRIS requis — posté il y a 5 jours</t>
+          <t>Spécialité migration données SAP SuccessFactors. Profil Gaëtan : migration SAP HR → SF sur L'Oréal 40+ pays = différenciant majeur. Mission longue et très alignée.</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/hr-tech-run-lead-at-l-or%C3%A9al-4435534808</t>
+          <t>https://www.freelance-informatique.fr/cv-mission-consultant-sap-successfactors-freelance-f11256</t>
         </is>
       </c>
       <c r="N15" s="40" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
         </is>
       </c>
       <c r="O15" s="40" t="inlineStr">
         <is>
-          <t>90-110K€</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P15" s="40" t="n"/>
-      <c r="Q15" s="42" t="n"/>
+      <c r="Q15" s="42" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="16" hidden="1" ht="40" customHeight="1">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -1982,12 +1986,12 @@
       <c r="C16" s="40" t="n"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Senior AMOA Talent Consultant M/F</t>
+          <t>HR Tech Run Lead</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>MP People</t>
+          <t>L'Oréal</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2002,33 +2006,45 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="n"/>
+          <t>Hybride (3j bureau / 2j remote)</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>nc</t>
+        </is>
+      </c>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>AMOA Talent senior = profil exact ; posté hier</t>
+          <t>EXCEPTIONNEL : Biarritz + 10 ans L'Oréal SAP HCM/SF dans le profil — 10+ ans HRIS requis — posté il y a 5 jours</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/senior-amoa-talent-consultant-m-f-at-mp-people-4437133991</t>
-        </is>
-      </c>
-      <c r="N16" s="40" t="n"/>
-      <c r="O16" s="40" t="n"/>
+          <t>https://fr.linkedin.com/jobs/view/hr-tech-run-lead-at-l-or%C3%A9al-4435534808</t>
+        </is>
+      </c>
+      <c r="N16" s="40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+        </is>
+      </c>
+      <c r="O16" s="40" t="inlineStr">
+        <is>
+          <t>90-110K€</t>
+        </is>
+      </c>
       <c r="P16" s="40" t="n"/>
       <c r="Q16" s="42" t="n"/>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="78" t="inlineStr">
+      <c r="A17" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -2037,7 +2053,7 @@
       <c r="C17" s="40" t="n"/>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Consultant Senior AMOA Talent H/F</t>
+          <t>Senior AMOA Talent Consultant M/F</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2069,18 +2085,18 @@
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Variante Senior AMOA Talent ; posté hier</t>
+          <t>AMOA Talent senior = profil exact ; posté hier</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-senior-amoa-talent-h-f-at-mp-people-4437143555</t>
+          <t>https://fr.linkedin.com/jobs/view/senior-amoa-talent-consultant-m-f-at-mp-people-4437133991</t>
         </is>
       </c>
       <c r="N17" s="40" t="n"/>
       <c r="O17" s="40" t="n"/>
       <c r="P17" s="40" t="n"/>
-      <c r="Q17" s="40" t="n"/>
+      <c r="Q17" s="42" t="n"/>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="78" t="inlineStr">
@@ -2092,7 +2108,7 @@
       <c r="C18" s="40" t="n"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Manager AMOA Talent M/F</t>
+          <t>Consultant Senior AMOA Talent H/F</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2124,12 +2140,12 @@
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Manager AMOA Talent ; 3 postes MP People simultanés = cabinet en forte croissance</t>
+          <t>Variante Senior AMOA Talent ; posté hier</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/manager-amoa-talent-m-f-at-mp-people-4437146495</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-senior-amoa-talent-h-f-at-mp-people-4437143555</t>
         </is>
       </c>
       <c r="N18" s="40" t="n"/>
@@ -2138,75 +2154,59 @@
       <c r="Q18" s="40" t="n"/>
     </row>
     <row r="19" hidden="1" ht="40" customHeight="1">
-      <c r="A19" s="83" t="inlineStr">
+      <c r="A19" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B19" s="40" t="n"/>
       <c r="C19" s="40" t="n"/>
-      <c r="D19" s="40" t="inlineStr">
-        <is>
-          <t>Directeur de Programme SIRH Senior H/F</t>
-        </is>
-      </c>
-      <c r="E19" s="40" t="inlineStr">
-        <is>
-          <t>LeHibou</t>
-        </is>
-      </c>
-      <c r="F19" s="40" t="inlineStr">
-        <is>
-          <t>free-work</t>
-        </is>
-      </c>
-      <c r="G19" s="40" t="inlineStr">
-        <is>
-          <t>Mission freelance</t>
-        </is>
-      </c>
-      <c r="H19" s="40" t="inlineStr">
-        <is>
-          <t>Paris (75)</t>
-        </is>
-      </c>
-      <c r="I19" s="40" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="J19" s="40" t="inlineStr">
-        <is>
-          <t>650-780€/j</t>
-        </is>
-      </c>
-      <c r="K19" s="40" t="inlineStr">
-        <is>
-          <t>18 mois</t>
-        </is>
-      </c>
-      <c r="L19" s="40" t="inlineStr">
-        <is>
-          <t>Programme RH grand groupe, SAP SF + PowerBI, fort fit ; 17/06/2026</t>
-        </is>
-      </c>
-      <c r="M19" s="40" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Manager AMOA Talent M/F</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>MP People</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Manager AMOA Talent ; 3 postes MP People simultanés = cabinet en forte croissance</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/manager-amoa-talent-m-f-at-mp-people-4437146495</t>
         </is>
       </c>
       <c r="N19" s="40" t="n"/>
       <c r="O19" s="40" t="n"/>
-      <c r="P19" s="40" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="Q19" s="40" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
+      <c r="P19" s="40" t="n"/>
+      <c r="Q19" s="40" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="83" t="inlineStr">
@@ -2218,52 +2218,52 @@
       <c r="C20" s="40" t="n"/>
       <c r="D20" s="40" t="inlineStr">
         <is>
-          <t>SAP Project Manager / Trainer</t>
+          <t>Directeur de Programme SIRH Senior H/F</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
         <is>
-          <t>N/C (via eursap.eu)</t>
+          <t>LeHibou</t>
         </is>
       </c>
       <c r="F20" s="40" t="inlineStr">
         <is>
-          <t>eursap.eu</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G20" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H20" s="40" t="inlineStr">
         <is>
-          <t>100% Remote</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I20" s="40" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="J20" s="40" t="inlineStr">
         <is>
-          <t>80-156k€/an + equity</t>
+          <t>650-780€/j</t>
         </is>
       </c>
       <c r="K20" s="40" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>18 mois</t>
         </is>
       </c>
       <c r="L20" s="40" t="inlineStr">
         <is>
-          <t>SAP PM + formateur, full remote, fourchette haute, démarrage août 2026 ; ref 34811</t>
+          <t>Programme RH grand groupe, SAP SF + PowerBI, fort fit ; 17/06/2026</t>
         </is>
       </c>
       <c r="M20" s="40" t="inlineStr">
         <is>
-          <t>https://eursap.eu/sap-jobs/france/</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
         </is>
       </c>
       <c r="N20" s="40" t="n"/>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="Q20" s="40" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -2289,27 +2289,27 @@
       <c r="C21" s="40" t="n"/>
       <c r="D21" s="40" t="inlineStr">
         <is>
-          <t>Chef de Projet Fonctionnel SIRH 100% Remote</t>
+          <t>SAP Project Manager / Trainer</t>
         </is>
       </c>
       <c r="E21" s="40" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>N/C (via eursap.eu)</t>
         </is>
       </c>
       <c r="F21" s="40" t="inlineStr">
         <is>
-          <t>freelance-informatique.fr</t>
+          <t>eursap.eu</t>
         </is>
       </c>
       <c r="G21" s="40" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H21" s="40" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>100% Remote</t>
         </is>
       </c>
       <c r="I21" s="40" t="inlineStr">
@@ -2319,34 +2319,34 @@
       </c>
       <c r="J21" s="40" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>80-156k€/an + equity</t>
         </is>
       </c>
       <c r="K21" s="40" t="inlineStr">
         <is>
-          <t>6 mois</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="L21" s="40" t="inlineStr">
         <is>
-          <t>Full remote, ASAP ; freelance-info ; 10/07/2026</t>
+          <t>SAP PM + formateur, full remote, fourchette haute, démarrage août 2026 ; ref 34811</t>
         </is>
       </c>
       <c r="M21" s="40" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/chef-de-projet-sirh-freelance-n112</t>
+          <t>https://eursap.eu/sap-jobs/france/</t>
         </is>
       </c>
       <c r="N21" s="40" t="n"/>
       <c r="O21" s="40" t="n"/>
       <c r="P21" s="40" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="Q21" s="40" t="inlineStr">
         <is>
-          <t>10/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>
@@ -2360,32 +2360,32 @@
       <c r="C22" s="40" t="n"/>
       <c r="D22" s="40" t="inlineStr">
         <is>
-          <t>HRIS Project Manager</t>
+          <t>Chef de Projet Fonctionnel SIRH 100% Remote</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>Next Ventures</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="F22" s="40" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>freelance-informatique.fr</t>
         </is>
       </c>
       <c r="G22" s="40" t="inlineStr">
         <is>
-          <t>Contrat 6 mois</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H22" s="40" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I22" s="40" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J22" s="40" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="L22" s="40" t="inlineStr">
         <is>
-          <t>SAP SF + ServiceNow, secteur financier, fort fit ; 03/07/2026</t>
-        </is>
-      </c>
-      <c r="M22" s="91" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/jobs/view/hris-sirh-project-manager-at-next-ventures-4433811211</t>
+          <t>Full remote, ASAP ; freelance-info ; 10/07/2026</t>
+        </is>
+      </c>
+      <c r="M22" s="40" t="inlineStr">
+        <is>
+          <t>https://www.freelance-informatique.fr/chef-de-projet-sirh-freelance-n112</t>
         </is>
       </c>
       <c r="N22" s="40" t="n"/>
@@ -2417,87 +2417,83 @@
       </c>
       <c r="Q22" s="40" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>10/07/2026</t>
         </is>
       </c>
     </row>
     <row r="23" hidden="1" ht="40" customHeight="1">
-      <c r="A23" s="77" t="inlineStr">
+      <c r="A23" s="83" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B23" s="40" t="n"/>
       <c r="C23" s="40" t="n"/>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Global Tech HR Domain Manager F/M/X</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Sephora</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Indeed</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Neuilly-sur-Seine</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>À clarifier</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>À négocier (viser 90-110K€)</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>Supervision déploiement RH/SAP, coordination équipes internes + partenaires ext = profil DPO exact. LVMH group. Publié 13/07/2026. Proche profil L'Oréal HR Domain.</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>https://fr.indeed.com/q-consultant-sap-successfactors-emplois.html</t>
-        </is>
-      </c>
-      <c r="N23" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O23" s="40" t="inlineStr">
-        <is>
-          <t>90-110K€</t>
-        </is>
-      </c>
-      <c r="P23" s="40" t="n"/>
-      <c r="Q23" s="42" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
+      <c r="D23" s="40" t="inlineStr">
+        <is>
+          <t>HRIS Project Manager</t>
+        </is>
+      </c>
+      <c r="E23" s="40" t="inlineStr">
+        <is>
+          <t>Next Ventures</t>
+        </is>
+      </c>
+      <c r="F23" s="40" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G23" s="40" t="inlineStr">
+        <is>
+          <t>Contrat 6 mois</t>
+        </is>
+      </c>
+      <c r="H23" s="40" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I23" s="40" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J23" s="40" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K23" s="40" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
+      <c r="L23" s="40" t="inlineStr">
+        <is>
+          <t>SAP SF + ServiceNow, secteur financier, fort fit ; 03/07/2026</t>
+        </is>
+      </c>
+      <c r="M23" s="91" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/hris-sirh-project-manager-at-next-ventures-4433811211</t>
+        </is>
+      </c>
+      <c r="N23" s="40" t="n"/>
+      <c r="O23" s="40" t="n"/>
+      <c r="P23" s="40" t="inlineStr">
+        <is>
+          <t>10/07/2026</t>
+        </is>
+      </c>
+      <c r="Q23" s="40" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
         </is>
       </c>
     </row>
     <row r="24" hidden="1" ht="40" customHeight="1">
-      <c r="A24" s="78" t="inlineStr">
+      <c r="A24" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
@@ -2506,12 +2502,12 @@
       <c r="C24" s="40" t="n"/>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>HR Domain Manager</t>
+          <t>Global Tech HR Domain Manager F/M/X</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Parfums Christian Dior</t>
+          <t>Sephora</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2546,7 +2542,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>LVMH. Coordination équipes internes, consultants externes et équipes dev Finance &amp; HR. Fit direct 10 ans L'Oréal = same environment. Publié 13/07/2026.</t>
+          <t>Supervision déploiement RH/SAP, coordination équipes internes + partenaires ext = profil DPO exact. LVMH group. Publié 13/07/2026. Proche profil L'Oréal HR Domain.</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
@@ -2565,33 +2561,33 @@
         </is>
       </c>
       <c r="P24" s="40" t="n"/>
-      <c r="Q24" s="42" t="n"/>
+      <c r="Q24" s="42" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="25" hidden="1" ht="40" customHeight="1">
-      <c r="A25" s="77" t="inlineStr">
+      <c r="A25" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
-        <is>
-          <t>À postuler</t>
-        </is>
-      </c>
+      <c r="B25" s="40" t="n"/>
       <c r="C25" s="40" t="n"/>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Responsable SIRH F/H</t>
+          <t>HR Domain Manager</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>KPMG France</t>
+          <t>Parfums Christian Dior</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle / emplois.kpmg.fr</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -2601,42 +2597,46 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Courbevoie / La Défense</t>
+          <t>Neuilly-sur-Seine</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>À clarifier</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Non affiché</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="n"/>
+          <t>À négocier (viser 90-110K€)</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>KPMG migration PeopleSoft → SAP SuccessFactors. Responsable SIRH = manager équipe + pilote roadmap. Requis 10 ans+ SIRH + team management + Core HR. Parfait fit Gaëtan (14 ans SAP + L'Oréal 40 pays). Démarrage mars 2026.</t>
+          <t>LVMH. Coordination équipes internes, consultants externes et équipes dev Finance &amp; HR. Fit direct 10 ans L'Oréal = same environment. Publié 13/07/2026.</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/kpmg-france/jobs/responsable-sirh-f-h_courbevoie</t>
-        </is>
-      </c>
-      <c r="N25" s="40" t="n"/>
+          <t>https://fr.indeed.com/q-consultant-sap-successfactors-emplois.html</t>
+        </is>
+      </c>
+      <c r="N25" s="40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
       <c r="O25" s="40" t="inlineStr">
         <is>
           <t>90-110K€</t>
         </is>
       </c>
       <c r="P25" s="40" t="n"/>
-      <c r="Q25" s="42" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
+      <c r="Q25" s="42" t="n"/>
     </row>
     <row r="26" hidden="1" ht="40" customHeight="1">
       <c r="A26" s="77" t="inlineStr">
@@ -2652,17 +2652,17 @@
       <c r="C26" s="40" t="n"/>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Consultant Manager SIRH - HR Transformation</t>
+          <t>Responsable SIRH F/H</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Sopra Steria</t>
+          <t>KPMG France</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>careers.soprasteria.com</t>
+          <t>Welcome to the Jungle / emplois.kpmg.fr</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Courbevoie (92)</t>
+          <t>Courbevoie / La Défense</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -2682,24 +2682,24 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Non affiché (2j télétravail/semaine)</t>
+          <t>Non affiché</t>
         </is>
       </c>
       <c r="K26" s="6" t="n"/>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Sopra Steria, Consultant Manager = niveau senior (manage clients + junior consultants). HR Transformation paie + GTA + SIRH. Dossiers complexes, missions variées. 2j/sem télétravail. Big IT services France.</t>
+          <t>KPMG migration PeopleSoft → SAP SuccessFactors. Responsable SIRH = manager équipe + pilote roadmap. Requis 10 ans+ SIRH + team management + Core HR. Parfait fit Gaëtan (14 ans SAP + L'Oréal 40 pays). Démarrage mars 2026.</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>https://careers.soprasteria.com/job/consultant-manager-sirh-hr-transformation-ile-de-france-in-courbevoie-france-jid-792</t>
+          <t>https://www.welcometothejungle.com/fr/companies/kpmg-france/jobs/responsable-sirh-f-h_courbevoie</t>
         </is>
       </c>
       <c r="N26" s="40" t="n"/>
       <c r="O26" s="40" t="inlineStr">
         <is>
-          <t>70-85K€</t>
+          <t>90-110K€</t>
         </is>
       </c>
       <c r="P26" s="40" t="n"/>
@@ -2715,19 +2715,25 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>À postuler</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="n"/>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP HCM (H/F)</t>
+          <t>Consultant Manager SIRH - HR Transformation</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>HR Path</t>
+          <t>Sopra Steria</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>jobs.hr-path.com</t>
+          <t>careers.soprasteria.com</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -2737,7 +2743,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Villeneuve-d'Ascq (59)</t>
+          <t>Courbevoie (92)</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -2745,28 +2751,29 @@
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J27" s="6" t="n"/>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Non affiché (2j télétravail/semaine)</t>
+        </is>
+      </c>
       <c r="K27" s="6" t="n"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>HR Path spécialiste SAP HCM/SF, posté 19/07/2026</t>
+          <t>Sopra Steria, Consultant Manager = niveau senior (manage clients + junior consultants). HR Transformation paie + GTA + SIRH. Dossiers complexes, missions variées. 2j/sem télétravail. Big IT services France.</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Villeneuve-d'Ascq-Consultant-SAP-HCM-(HF)-59-59650/770170201/</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
+          <t>https://careers.soprasteria.com/job/consultant-manager-sirh-hr-transformation-ile-de-france-in-courbevoie-france-jid-792</t>
+        </is>
+      </c>
+      <c r="N27" s="40" t="n"/>
+      <c r="O27" s="40" t="inlineStr">
+        <is>
+          <t>70-85K€</t>
+        </is>
+      </c>
+      <c r="P27" s="40" t="n"/>
       <c r="Q27" s="42" t="inlineStr">
         <is>
           <t>18/06/2026</t>
@@ -2774,14 +2781,14 @@
       </c>
     </row>
     <row r="28" hidden="1" ht="40" customHeight="1">
-      <c r="A28" s="78" t="inlineStr">
+      <c r="A28" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors (H/F)</t>
+          <t>Consultant SAP HCM (H/F)</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2801,7 +2808,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Paris La Défense</t>
+          <t>Villeneuve-d'Ascq (59)</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -2813,12 +2820,12 @@
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>HR Path leader SAP HCM/SF, posté 16/07/2026</t>
+          <t>HR Path spécialiste SAP HCM/SF, posté 19/07/2026</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
+          <t>https://jobs.hr-path.com/job/Villeneuve-d'Ascq-Consultant-SAP-HCM-(HF)-59-59650/770170201/</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2831,7 +2838,11 @@
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="Q28" s="42" t="n"/>
+      <c r="Q28" s="42" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="29" hidden="1" ht="40" customHeight="1">
       <c r="A29" s="78" t="inlineStr">
@@ -2841,7 +2852,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Consultant SIRH (H/F) - Workday / Oracle HCM / SAP SuccessFactors</t>
+          <t>Consultant SAP SuccessFactors (H/F)</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2873,12 +2884,12 @@
       <c r="K29" s="6" t="n"/>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Multi-SIRH, posté 27/07/2026 - très récent</t>
+          <t>HR Path leader SAP HCM/SF, posté 16/07/2026</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SIRH-(HF)-Workday-%E2%80%A2-Oracle-HCM-%E2%80%A2-SAP-SuccessFactors-75-92042/1419350533/</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2888,14 +2899,10 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>650-750€/j ou 70-85K€</t>
-        </is>
-      </c>
-      <c r="Q29" s="42" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+          <t>650-750€/j</t>
+        </is>
+      </c>
+      <c r="Q29" s="42" t="n"/>
     </row>
     <row r="30" hidden="1" ht="40" customHeight="1">
       <c r="A30" s="78" t="inlineStr">
@@ -2905,17 +2912,17 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP HCM Paie Senior</t>
+          <t>Consultant SIRH (H/F) - Workday / Oracle HCM / SAP SuccessFactors</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Strada (ex-Alight)</t>
+          <t>HR Path</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>careers.alight.com</t>
+          <t>jobs.hr-path.com</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -2925,7 +2932,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Colombes, France</t>
+          <t>Paris La Défense</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2937,12 +2944,12 @@
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Strada = 1er partenaire SAP HR monde, 8000+ experts. Posté 2026. Parfait fit expertise L'Oréal/SAP HCM paie</t>
+          <t>Multi-SIRH, posté 27/07/2026 - très récent</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27911STRADAENUS/Consultant-SAP-HCM-Paie-senior</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SIRH-(HF)-Workday-%E2%80%A2-Oracle-HCM-%E2%80%A2-SAP-SuccessFactors-75-92042/1419350533/</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2969,7 +2976,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP HCM Time Senior</t>
+          <t>Consultant SAP HCM Paie Senior</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3001,12 +3008,12 @@
       <c r="K31" s="6" t="n"/>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Strada expert SAP HCM Time, posté 2026</t>
+          <t>Strada = 1er partenaire SAP HR monde, 8000+ experts. Posté 2026. Parfait fit expertise L'Oréal/SAP HCM paie</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27913STRADAENUS/Consultant-SAP-HCM-Time-senior</t>
+          <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27911STRADAENUS/Consultant-SAP-HCM-Paie-senior</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3026,24 +3033,24 @@
       </c>
     </row>
     <row r="32" hidden="1" ht="16" customHeight="1">
-      <c r="A32" s="77" t="inlineStr">
+      <c r="A32" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors expérimenté (H/F)</t>
+          <t>Consultant SAP HCM Time Senior</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>SQORUS</t>
+          <t>Strada (ex-Alight)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn / fr.trabajo.org</t>
+          <t>careers.alight.com</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -3053,7 +3060,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Colombes, France</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
@@ -3061,20 +3068,16 @@
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>60-75K€</t>
-        </is>
-      </c>
+      <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>SQORUS Great Place to Work 8 ans, 1500+ missions CAC40/SBF120. SAP SF expert, posté il y a 1 jour (28/07/2026). Très récent.</t>
+          <t>Strada expert SAP HCM Time, posté 2026</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>https://www.sqorus.com/carrieres/</t>
+          <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27913STRADAENUS/Consultant-SAP-HCM-Time-senior</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3084,34 +3087,34 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>70-85K€</t>
+          <t>650-750€/j ou 70-85K€</t>
         </is>
       </c>
       <c r="Q32" s="42" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
     <row r="33" hidden="1" ht="16" customHeight="1">
-      <c r="A33" s="78" t="inlineStr">
+      <c r="A33" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Principal Solution Advisor, HCM (F/H)</t>
+          <t>Consultant SAP SuccessFactors expérimenté (H/F)</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SQORUS</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn / fr.trabajo.org</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -3121,57 +3124,65 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Levallois-Perret</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="n"/>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>60-75K€</t>
+        </is>
+      </c>
       <c r="K33" s="6" t="n"/>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>SAP pre-sales HCM, posté il y a 4 jours. Profil solution advisor senior, 14 ans SAP = fit parfait. Même famille que le poste SAP SuccessFactors déjà identifié.</t>
+          <t>SQORUS Great Place to Work 8 ans, 1500+ missions CAC40/SBF120. SAP SF expert, posté il y a 1 jour (28/07/2026). Très récent.</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.sap.com/go/SAP-Jobs-in-France/850401/</t>
+          <t>https://www.sqorus.com/carrieres/</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>95-115K€</t>
-        </is>
-      </c>
-      <c r="Q33" s="42" t="n"/>
+          <t>70-85K€</t>
+        </is>
+      </c>
+      <c r="Q33" s="42" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="34" hidden="1" ht="48" customHeight="1">
-      <c r="A34" s="77" t="inlineStr">
+      <c r="A34" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) AMOA SIRH (F/H)</t>
+          <t>Principal Solution Advisor, HCM (F/H)</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>ACT-ON HRIS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>SmartRecruiters / LinkedIn</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -3181,41 +3192,37 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Neuilly-sur-Seine</t>
+          <t>Levallois-Perret</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>ACT-ON HRIS 600+ consultants, 65M€ CA, 1 500+ missions. AMOA SIRH multi-outils (HR Access, Meta4, SAP SF). Posté juillet 2026. Postes actifs en juillet 2026, différent du poste AMOA déjà dans tableur.</t>
+          <t>SAP pre-sales HCM, posté il y a 4 jours. Profil solution advisor senior, 14 ans SAP = fit parfait. Même famille que le poste SAP SuccessFactors déjà identifié.</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/ACT-ON/744000045913473-consultant-e-amoa-sirh-f-h-</t>
+          <t>https://jobs.sap.com/go/SAP-Jobs-in-France/850401/</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
+          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>70-85K€</t>
-        </is>
-      </c>
-      <c r="Q34" s="42" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
+          <t>95-115K€</t>
+        </is>
+      </c>
+      <c r="Q34" s="42" t="n"/>
     </row>
     <row r="35" hidden="1" ht="16" customHeight="1">
       <c r="A35" s="77" t="inlineStr">
@@ -3225,17 +3232,17 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Principal Solution Advisor, SuccessFactors (F/H)</t>
+          <t>Consultant(e) AMOA SIRH (F/H)</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>ACT-ON HRIS</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn / SAP Jobs France</t>
+          <t>SmartRecruiters / LinkedIn</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -3245,7 +3252,7 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Levallois-Perret (92)</t>
+          <t>Neuilly-sur-Seine</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
@@ -3257,22 +3264,22 @@
       <c r="K35" s="6" t="n"/>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Poste pre-sales HCM senior SAP France, publié ~24/07/2026 (il y a 6 jours). 10-15 ans expérience SAP requis dont 3-5 ans HCM, Cloud SaaS B2B, anglais+français. Fit exceptionnel : 14 ans SAP HR, L'Oréal 40 pays, profil face client. Voir jobs.sap.com/go/SAP-Jobs-in-France/850401/ pour le lien actif.</t>
+          <t>ACT-ON HRIS 600+ consultants, 65M€ CA, 1 500+ missions. AMOA SIRH multi-outils (HR Access, Meta4, SAP SF). Posté juillet 2026. Postes actifs en juillet 2026, différent du poste AMOA déjà dans tableur.</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/principal-solution-advisor-successfactors-f-h-at-sap-4415727184</t>
+          <t>https://jobs.smartrecruiters.com/ACT-ON/744000045913473-consultant-e-amoa-sirh-f-h-</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>95-115K€</t>
+          <t>70-85K€</t>
         </is>
       </c>
       <c r="Q35" s="42" t="inlineStr">
@@ -3282,24 +3289,24 @@
       </c>
     </row>
     <row r="36" hidden="1" ht="16" customHeight="1">
-      <c r="A36" s="78" t="inlineStr">
+      <c r="A36" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Consultant Senior HR Transformation - SAP SuccessFactors (F/H)</t>
+          <t>Principal Solution Advisor, SuccessFactors (F/H)</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn / SAP Jobs France</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -3309,37 +3316,41 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Levallois-Perret (92)</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>Deloitte Human Capital. Pilotage projets SAP SuccessFactors, ateliers métier, déploiement opérationnel, certifications SF proposées. 5-10 ans SIRH requis. Fit excellent croisement SAP HR + conseil grands comptes.</t>
+          <t>Poste pre-sales HCM senior SAP France, publié ~24/07/2026 (il y a 6 jours). 10-15 ans expérience SAP requis dont 3-5 ans HCM, Cloud SaaS B2B, anglais+français. Fit exceptionnel : 14 ans SAP HR, L'Oréal 40 pays, profil face client. Voir jobs.sap.com/go/SAP-Jobs-in-France/850401/ pour le lien actif.</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/deloitte/jobs/consultant-senior-hr-transformation-sap-successfactors-f-h_paris</t>
+          <t>https://fr.linkedin.com/jobs/view/principal-solution-advisor-successfactors-f-h-at-sap-4415727184</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
+          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>70-85K€</t>
-        </is>
-      </c>
-      <c r="Q36" s="42" t="n"/>
+          <t>95-115K€</t>
+        </is>
+      </c>
+      <c r="Q36" s="42" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="78" t="inlineStr">
@@ -3349,12 +3360,12 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Responsable SIRH F/H (migration PeopleSoft → SAP SuccessFactors)</t>
+          <t>Consultant Senior HR Transformation - SAP SuccessFactors (F/H)</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>KPMG France</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -3369,24 +3380,24 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>La Défense (92)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Poste interne KPMG : manager la migration PeopleSoft vers SAP SuccessFactors, management d'équipe. Min. 10 ans SIRH. Pas un poste conseil mais fit technique exceptionnel — migration SAP HR = coeur du profil. KPMG groupe international 180+ pays.</t>
+          <t>Deloitte Human Capital. Pilotage projets SAP SuccessFactors, ateliers métier, déploiement opérationnel, certifications SF proposées. 5-10 ans SIRH requis. Fit excellent croisement SAP HR + conseil grands comptes.</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/kpmg-france/jobs/responsable-sirh-f-h_courbevoie</t>
+          <t>https://www.welcometothejungle.com/fr/companies/deloitte/jobs/consultant-senior-hr-transformation-sap-successfactors-f-h_paris</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3396,14 +3407,10 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>90-110K€</t>
-        </is>
-      </c>
-      <c r="Q37" s="42" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+          <t>70-85K€</t>
+        </is>
+      </c>
+      <c r="Q37" s="42" t="n"/>
     </row>
     <row r="38" hidden="1" ht="16" customHeight="1">
       <c r="A38" s="78" t="inlineStr">
@@ -3413,17 +3420,17 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Consultant SIRH Senior/Lead (Workday / Oracle HCM / SAP SuccessFactors) H/F</t>
+          <t>Responsable SIRH F/H (migration PeopleSoft → SAP SuccessFactors)</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>HR Path</t>
+          <t>KPMG France</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>jobs.hr-path.com</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -3433,24 +3440,24 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Paris La Défense</t>
+          <t>La Défense (92)</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>Publié 27/07/2026. Niveau Senior/Lead/Chef de projet SIRH, projets internationaux, min. 4 ans SIRH, Workday ou Oracle HCM ou SAP SF, anglais professionnel. HR Path = spécialiste #1 RH tech Europe. Fit excellent — senior assumé dans l'intitulé.</t>
+          <t>Poste interne KPMG : manager la migration PeopleSoft vers SAP SuccessFactors, management d'équipe. Min. 10 ans SIRH. Pas un poste conseil mais fit technique exceptionnel — migration SAP HR = coeur du profil. KPMG groupe international 180+ pays.</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SIRH-%28HF%29-Workday-%E2%80%A2-Oracle-HCM-%E2%80%A2-SAP-SuccessFactors-75-92042/1419350533/</t>
+          <t>https://www.welcometothejungle.com/fr/companies/kpmg-france/jobs/responsable-sirh-f-h_courbevoie</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3460,7 +3467,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>70-85K€</t>
+          <t>90-110K€</t>
         </is>
       </c>
       <c r="Q38" s="42" t="inlineStr">
@@ -3477,17 +3484,17 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP HCM Paie senior</t>
+          <t>Consultant SIRH Senior/Lead (Workday / Oracle HCM / SAP SuccessFactors) H/F</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Strada (ex-Alight / ex-NGA Human Resources)</t>
+          <t>HR Path</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>careers.alight.com/strada</t>
+          <t>jobs.hr-path.com</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -3497,109 +3504,105 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Colombes (92)</t>
+          <t>Paris La Défense</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Oui (depuis toute la France)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
       <c r="L39" s="5" t="inlineStr">
         <is>
+          <t>Publié 27/07/2026. Niveau Senior/Lead/Chef de projet SIRH, projets internationaux, min. 4 ans SIRH, Workday ou Oracle HCM ou SAP SF, anglais professionnel. HR Path = spécialiste #1 RH tech Europe. Fit excellent — senior assumé dans l'intitulé.</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SIRH-%28HF%29-Workday-%E2%80%A2-Oracle-HCM-%E2%80%A2-SAP-SuccessFactors-75-92042/1419350533/</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>70-85K€</t>
+        </is>
+      </c>
+      <c r="Q39" s="42" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="78" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SAP HCM Paie senior</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Strada (ex-Alight / ex-NGA Human Resources)</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>careers.alight.com/strada</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Colombes (92)</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Oui (depuis toute la France)</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
           <t>Strada = 1er partenaire mondial SAP HR. Configuration payroll SAP HCM France (cycles, schémas, contributions, accounting). 5+ ans SAP HCM Payroll requis. Fit parfait. Remote depuis toute la France confirmé. 2 annonces actives (R-27911 et R-32021).</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>https://careers.alight.com/strada/us/en/job/ALIGUSR32021STRADAENUS/Consultant-SAP-HCM-Paie-senior</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>70-85K€</t>
         </is>
       </c>
-      <c r="Q39" s="42" t="inlineStr">
+      <c r="Q40" s="42" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="77" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SAP Paie HCM Payroll</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Client via Duonext</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>free-work.com</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>Département 92</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>Hybride (2-3j/semaine sur site)</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>6 mois min. renouvelables</t>
-        </is>
-      </c>
-      <c r="L40" s="5" t="inlineStr">
-        <is>
-          <t>Publié 22/06/2026. Démarrage septembre 2026. Transformation RH, expertise paie France obligatoire (DSN, contributions, accounting), 8-10 ans requis. Très bon fit L'Oréal paie France multisite.</t>
-        </is>
-      </c>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/consultant-sap-paie-hcm-payroll</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
-      <c r="Q40" s="42" t="n"/>
     </row>
     <row r="41" hidden="1" ht="16" customHeight="1">
       <c r="A41" s="77" t="inlineStr">
@@ -3609,217 +3612,221 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>Consultant SAP Paie HCM Payroll</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Client via Duonext</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>free-work.com</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Département 92</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Hybride (2-3j/semaine sur site)</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>650-750€/j</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>6 mois min. renouvelables</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Publié 22/06/2026. Démarrage septembre 2026. Transformation RH, expertise paie France obligatoire (DSN, contributions, accounting), 8-10 ans requis. Très bon fit L'Oréal paie France multisite.</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/consultant-sap-paie-hcm-payroll</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>650-750€/j</t>
+        </is>
+      </c>
+      <c r="Q41" s="42" t="n"/>
+    </row>
+    <row r="42" hidden="1" ht="16" customHeight="1">
+      <c r="A42" s="77" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
           <t>SAP HCM Technico-Functional Consultant French Payroll</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Apps IT Limited</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>Oui (100% remote)</t>
         </is>
       </c>
-      <c r="J41" s="6" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="K41" s="6" t="inlineStr">
+      <c r="K42" s="6" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>Publié 17/06/2026. 100% remote — fit parfait pour Anglet. Profil technico-fonctionnel SAP HCM French Payroll. À vérifier disponibilité (publié il y a 6 semaines). Lien : rechercher "Apps IT" sur free-work.com/fr/tech-it/jobs/sap-hcm.</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/jobs/sap-hcm</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="Q41" s="42" t="n"/>
-    </row>
-    <row r="42" hidden="1" ht="16" customHeight="1">
-      <c r="A42" s="78" t="inlineStr">
+      <c r="Q42" s="42" t="n"/>
+    </row>
+    <row r="43" hidden="1" ht="16" customHeight="1">
+      <c r="A43" s="78" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>SAP HCM Consultant French Payroll</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Client via Movement Group</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>movementgroup.uk</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>Oui (100% remote)</t>
         </is>
       </c>
-      <c r="J42" s="6" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="K42" s="6" t="inlineStr">
+      <c r="K43" s="6" t="inlineStr">
         <is>
           <t>12 mois + extension</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>Movement Group = cabinet recrutement SAP UK/Europe. 100% remote, 12 mois extensible. Outside IR35 (client probablement UK/international). 3+ ans SAP Payroll France requis. Durée et remote = fit parfait.</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr">
         <is>
           <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="Q42" s="42" t="n"/>
-    </row>
-    <row r="43" hidden="1" ht="16" customHeight="1">
-      <c r="A43" s="77" t="inlineStr">
+      <c r="Q43" s="42" t="n"/>
+    </row>
+    <row r="44" hidden="1" ht="32" customHeight="1">
+      <c r="A44" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Consultant(e) AMOA SIRH (F/H)</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>ACT-ON HRIS</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>SmartRecruiters / LinkedIn</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>Neuilly-sur-Seine (92)</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="n"/>
-      <c r="K43" s="6" t="n"/>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>ACT-ON HRIS filiale SIRH du groupe ACT-ON (600+ collab., 65M€ CA). Profil exact : SAP SuccessFactors, HR Access, AMOA, specs fonctionnelles, conduite du changement. 15 ans SAP + 40 pays L'Oréal = profil senior idéal. Lien : jobs.smartrecruiters.com/ACT-ON/744000045913473</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>https://jobs.smartrecruiters.com/ACT-ON/744000045913473-consultant-e-amoa-sirh-f-h-</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>75-85K€</t>
-        </is>
-      </c>
-      <c r="Q43" s="42" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" hidden="1" ht="32" customHeight="1">
-      <c r="A44" s="78" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Consultant(e) SuccessFactors (F/H)</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>ACT-ON HRIS</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3841,12 +3848,12 @@
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>Poste SAP SuccessFactors dédié chez ACT-ON HRIS, publié il y a 2 jours — fenêtre idéale pour postuler. Gaëtan cumule 14 ans SAP HR/HCM ; correspond exactement au profil recherché par ce cabinet spécialisé HumanTech.</t>
+          <t>ACT-ON HRIS filiale SIRH du groupe ACT-ON (600+ collab., 65M€ CA). Profil exact : SAP SuccessFactors, HR Access, AMOA, specs fonctionnelles, conduite du changement. 15 ans SAP + 40 pays L'Oréal = profil senior idéal. Lien : jobs.smartrecruiters.com/ACT-ON/744000045913473</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-e-successfactors-f-h-at-act-on-hris</t>
+          <t>https://jobs.smartrecruiters.com/ACT-ON/744000045913473-consultant-e-amoa-sirh-f-h-</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3859,7 +3866,11 @@
           <t>75-85K€</t>
         </is>
       </c>
-      <c r="Q44" s="42" t="n"/>
+      <c r="Q44" s="42" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="45" hidden="1" ht="32" customHeight="1">
       <c r="A45" s="78" t="inlineStr">
@@ -3869,7 +3880,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Consultant Confirmé SIRH - SAP HR (H/F)</t>
+          <t>Consultant(e) SuccessFactors (F/H)</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3901,12 +3912,12 @@
       <c r="K45" s="6" t="n"/>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>Poste SAP HR publié ce matin même (31/07/2026, il y a 17h) — postuler en priorité absolue aujourd'hui. Intitulé "Confirmé" = niveau intermédiaire, Gaëtan au-dessus, peut négocier un niveau senior. ACT-ON HRIS = cabinet SIRH pur spécialisé.</t>
+          <t>Poste SAP SuccessFactors dédié chez ACT-ON HRIS, publié il y a 2 jours — fenêtre idéale pour postuler. Gaëtan cumule 14 ans SAP HR/HCM ; correspond exactement au profil recherché par ce cabinet spécialisé HumanTech.</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-confirme-sirh-sap-hr-h-f-at-act-on-hris</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-e-successfactors-f-h-at-act-on-hris</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3919,11 +3930,7 @@
           <t>75-85K€</t>
         </is>
       </c>
-      <c r="Q45" s="42" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q45" s="42" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="78" t="inlineStr">
@@ -3931,25 +3938,19 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B46" s="40" t="inlineStr">
-        <is>
-          <t>À postuler</t>
-        </is>
-      </c>
-      <c r="C46" s="40" t="n"/>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>HRIS &amp; AI Tech Pre-Sales Specialist</t>
+          <t>Consultant Confirmé SIRH - SAP HR (H/F)</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Arago Consulting</t>
+          <t>ACT-ON HRIS</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>SmartRecruiters</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -3959,37 +3960,36 @@
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Paris ou Bordeaux</t>
+          <t>Neuilly-sur-Seine (92)</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>Partiel (déplacements clients)</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>Arago = 1er partenaire européen SAP SuccessFactors. Croisement parfait pre-sales IA+SIRH : 14 ans SAP, 40 pays L'Oréal, usage quotidien IA générative, profil face-client senior. Bordeaux = 2h d'Anglet. Lien : jobs.smartrecruiters.com/Arago/744000139094386</t>
+          <t>Poste SAP HR publié ce matin même (31/07/2026, il y a 17h) — postuler en priorité absolue aujourd'hui. Intitulé "Confirmé" = niveau intermédiaire, Gaëtan au-dessus, peut négocier un niveau senior. ACT-ON HRIS = cabinet SIRH pur spécialisé.</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.smartrecruiters.com/Arago/744000139094386-hris-ai-tech-pre-sales-specialist</t>
-        </is>
-      </c>
-      <c r="N46" s="40" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_Arago.pdf</t>
-        </is>
-      </c>
-      <c r="O46" s="40" t="inlineStr">
-        <is>
-          <t>90-110K€</t>
-        </is>
-      </c>
-      <c r="P46" s="40" t="n"/>
+          <t>https://fr.linkedin.com/jobs/view/consultant-confirme-sirh-sap-hr-h-f-at-act-on-hris</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>75-85K€</t>
+        </is>
+      </c>
       <c r="Q46" s="42" t="inlineStr">
         <is>
           <t>06/07/2026</t>

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -28425,8 +28425,7 @@
     </filterColumn>
   </autoFilter>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52471,7 +52470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="16" max="17"/>
@@ -57676,6 +57675,84 @@
       <c r="Q73" s="41" t="inlineStr">
         <is>
           <t>06/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="128" customHeight="1">
+      <c r="A74" s="67" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Global Product Owner - SuccessFactors</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Qurated (pour un cabinet d avocats international)</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CDD / FTC 18 mois</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>100% remote</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="n"/>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>18 mois</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>Ownership unique de la plateforme SAP SuccessFactors sur tout le perimetre mondial : vision et roadmap, solution design multi-modules (Employee Central, Performance &amp; Goals, Compensation, Recruiting, Onboarding, Learning), standards globaux, cycles de release, conduite du changement et relation editeur. Fit tres eleve : SuccessFactors multi-modules, contexte global et conduite du changement correspondent au parcours L'Oreal. Full remote. Postule le 07/08/2026.</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4447393087</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
         </is>
       </c>
     </row>

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -7272,75 +7272,83 @@
       <c r="Q95" s="41" t="n"/>
     </row>
     <row r="96" hidden="1" ht="16" customHeight="1">
-      <c r="A96" s="53" t="inlineStr">
+      <c r="A96" s="73" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B96" s="39" t="inlineStr">
+      <c r="B96" s="39" t="n"/>
+      <c r="C96" s="39" t="n"/>
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Consultant Senior SIRH SAP SF Performance &amp; Goals H/F</t>
         </is>
       </c>
-      <c r="C96" s="39" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>Grand groupe international</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
         <is>
           <t>Hellowork</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="H96" s="6" t="inlineStr">
         <is>
           <t>Paris (75)</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="I96" s="6" t="inlineStr">
         <is>
           <t>Hybride</t>
         </is>
       </c>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="J96" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>SF PMGM, 10 ans requis, gouvernance SIRH, pilotage roadmap, publié 11/07/2026. Fit fort sur module Performance &amp; Goals.</t>
-        </is>
-      </c>
-      <c r="J96" s="6" t="inlineStr">
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>SF PMGM, 10 ans requis, gouvernance SIRH, pilotage roadmap. Fit fort sur module Performance &amp; Goals.</t>
+        </is>
+      </c>
+      <c r="M96" s="5" t="inlineStr">
         <is>
           <t>https://www.hellowork.com/fr-fr/emplois/81222357.html</t>
         </is>
       </c>
-      <c r="K96" s="6" t="inlineStr">
+      <c r="N96" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="O96" s="39" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="M96" s="5" t="inlineStr">
+      <c r="P96" s="39" t="inlineStr">
         <is>
           <t>11/07/2026</t>
         </is>
       </c>
-      <c r="N96" s="39" t="n"/>
-      <c r="O96" s="39" t="n"/>
-      <c r="P96" s="39" t="n"/>
-      <c r="Q96" s="41" t="n"/>
+      <c r="Q96" s="41" t="inlineStr">
+        <is>
+          <t>11/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="97" hidden="1" ht="16" customHeight="1">
       <c r="A97" s="73" t="inlineStr">
@@ -20351,70 +20359,78 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B288" s="39" t="inlineStr">
-        <is>
-          <t>Consultant SIRH SuccessFactors (9 mois)</t>
-        </is>
-      </c>
-      <c r="C288" s="39" t="inlineStr">
+      <c r="B288" s="39" t="n"/>
+      <c r="C288" s="39" t="n"/>
+      <c r="D288" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SIRH SuccessFactors</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
         <is>
           <t>Non communiqué</t>
         </is>
       </c>
-      <c r="D288" s="5" t="inlineStr">
+      <c r="F288" s="5" t="inlineStr">
         <is>
           <t>freelance-informatique.fr</t>
         </is>
       </c>
-      <c r="E288" s="5" t="inlineStr">
+      <c r="G288" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="F288" s="5" t="inlineStr">
+      <c r="H288" s="6" t="inlineStr">
         <is>
           <t>Issy-les-Moulineaux (92)</t>
         </is>
       </c>
-      <c r="G288" s="6" t="inlineStr">
+      <c r="I288" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="H288" s="6" t="inlineStr">
+      <c r="J288" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="I288" s="6" t="inlineStr">
+      <c r="K288" s="6" t="inlineStr">
+        <is>
+          <t>9 mois</t>
+        </is>
+      </c>
+      <c r="L288" s="5" t="inlineStr">
         <is>
           <t>Mission 9 mois SAP SuccessFactors, Issy-les-Moulineaux. Profil Gaëtan SF multi-modules = aligné.</t>
         </is>
       </c>
-      <c r="J288" s="6" t="inlineStr">
+      <c r="M288" s="5" t="inlineStr">
         <is>
           <t>https://www.freelance-informatique.fr/mission-consultant-technique-sirh-sap-successfactors-n16466</t>
         </is>
       </c>
-      <c r="K288" s="6" t="inlineStr">
+      <c r="N288" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="L288" s="5" t="inlineStr">
+      <c r="O288" s="39" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="M288" s="5" t="inlineStr">
+      <c r="P288" s="39" t="inlineStr">
         <is>
           <t>07/2026</t>
         </is>
       </c>
-      <c r="N288" s="39" t="n"/>
-      <c r="O288" s="39" t="n"/>
-      <c r="P288" s="39" t="n"/>
-      <c r="Q288" s="41" t="n"/>
+      <c r="Q288" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
     </row>
     <row r="289" hidden="1" ht="32" customHeight="1">
       <c r="A289" s="65" t="inlineStr">
@@ -20422,70 +20438,78 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B289" s="39" t="inlineStr">
-        <is>
-          <t>Manager SIRH - Nantes (CDI)</t>
-        </is>
-      </c>
-      <c r="C289" s="39" t="inlineStr">
+      <c r="B289" s="39" t="n"/>
+      <c r="C289" s="39" t="n"/>
+      <c r="D289" s="5" t="inlineStr">
+        <is>
+          <t>Manager SIRH</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
         <is>
           <t>ALTHEA</t>
         </is>
       </c>
-      <c r="D289" s="5" t="inlineStr">
+      <c r="F289" s="5" t="inlineStr">
         <is>
           <t>Welcome to the Jungle</t>
         </is>
       </c>
-      <c r="E289" s="5" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="F289" s="5" t="inlineStr">
+      <c r="G289" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H289" s="6" t="inlineStr">
         <is>
           <t>Saint-Herblain / Nantes</t>
         </is>
       </c>
-      <c r="G289" s="6" t="inlineStr">
+      <c r="I289" s="6" t="inlineStr">
         <is>
           <t>Hybride</t>
         </is>
       </c>
-      <c r="H289" s="6" t="inlineStr">
+      <c r="J289" s="6" t="inlineStr">
         <is>
           <t>48-62K€</t>
         </is>
       </c>
-      <c r="I289" s="6" t="inlineStr">
+      <c r="K289" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="L289" s="5" t="inlineStr">
         <is>
           <t>Cabinet conseil SIRH, pilotage projets de A à Z, conduite du changement. Nantes = frein pour remote Anglet.</t>
         </is>
       </c>
-      <c r="J289" s="6" t="inlineStr">
+      <c r="M289" s="5" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/fr/companies/althea/jobs/manager-sirh-nantes-cdi-h-f_saint-herblain</t>
         </is>
       </c>
-      <c r="K289" s="6" t="inlineStr">
+      <c r="N289" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="L289" s="5" t="inlineStr">
+      <c r="O289" s="39" t="inlineStr">
         <is>
           <t>48-62K€</t>
         </is>
       </c>
-      <c r="M289" s="5" t="inlineStr">
+      <c r="P289" s="39" t="inlineStr">
         <is>
           <t>07/2026</t>
         </is>
       </c>
-      <c r="N289" s="39" t="n"/>
-      <c r="O289" s="39" t="n"/>
-      <c r="P289" s="39" t="n"/>
-      <c r="Q289" s="41" t="n"/>
+      <c r="Q289" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
     </row>
     <row r="290" hidden="1" ht="32" customHeight="1">
       <c r="A290" s="65" t="inlineStr">
@@ -20493,74 +20517,78 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B290" s="39" t="inlineStr">
+      <c r="B290" s="39" t="n"/>
+      <c r="C290" s="39" t="n"/>
+      <c r="D290" s="5" t="inlineStr">
         <is>
           <t>SAP Payroll Implementation Lead - France</t>
         </is>
       </c>
-      <c r="C290" s="39" t="inlineStr">
+      <c r="E290" s="5" t="inlineStr">
         <is>
           <t>Strada Global</t>
         </is>
       </c>
-      <c r="D290" s="5" t="inlineStr">
+      <c r="F290" s="5" t="inlineStr">
         <is>
           <t>Strada Global Careers / Remote Rocketship</t>
         </is>
       </c>
-      <c r="E290" s="5" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="F290" s="5" t="inlineStr">
+      <c r="G290" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H290" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="G290" s="6" t="inlineStr">
+      <c r="I290" s="6" t="inlineStr">
         <is>
           <t>100% remote</t>
         </is>
       </c>
-      <c r="H290" s="6" t="inlineStr">
+      <c r="J290" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="I290" s="6" t="inlineStr">
+      <c r="K290" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="J290" s="6" t="inlineStr">
+      <c r="L290" s="5" t="inlineStr">
         <is>
           <t>Strada = RH/paie globale (SAP, Oracle, Workday). Lead impl SAP Payroll France, 5+ implémentations SAP HCM requises, connaissance paie FR. Profil Gaëtan SAP HR adjacent mais payroll pur = frein partiel.</t>
         </is>
       </c>
-      <c r="K290" s="6" t="inlineStr">
+      <c r="M290" s="5" t="inlineStr">
         <is>
           <t>https://careers.stradaglobal.com/careers/job/1133913392690-sap-payroll-implementation-lead-france-granada-spain</t>
         </is>
       </c>
-      <c r="L290" s="5" t="inlineStr">
+      <c r="N290" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="M290" s="5" t="inlineStr">
+      <c r="O290" s="39" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="N290" s="39" t="inlineStr">
+      <c r="P290" s="39" t="inlineStr">
         <is>
           <t>07/2026</t>
         </is>
       </c>
-      <c r="O290" s="39" t="n"/>
-      <c r="P290" s="39" t="n"/>
-      <c r="Q290" s="41" t="n"/>
+      <c r="Q290" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
     </row>
     <row r="291" hidden="1" ht="16" customHeight="1">
       <c r="A291" s="65" t="inlineStr">
@@ -29273,75 +29301,83 @@
       <c r="Q420" s="41" t="n"/>
     </row>
     <row r="421">
-      <c r="A421" s="54" t="inlineStr">
+      <c r="A421" s="66" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B421" s="39" t="inlineStr">
-        <is>
-          <t>Senior Manager SIRH - Lyon (CDI)</t>
-        </is>
-      </c>
-      <c r="C421" s="39" t="inlineStr">
+      <c r="B421" s="39" t="n"/>
+      <c r="C421" s="39" t="n"/>
+      <c r="D421" s="39" t="inlineStr">
+        <is>
+          <t>Senior Manager SIRH</t>
+        </is>
+      </c>
+      <c r="E421" s="39" t="inlineStr">
         <is>
           <t>ALTHEA</t>
         </is>
       </c>
-      <c r="D421" s="39" t="inlineStr">
+      <c r="F421" s="39" t="inlineStr">
         <is>
           <t>Welcome to the Jungle</t>
         </is>
       </c>
-      <c r="E421" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="F421" s="39" t="inlineStr">
+      <c r="G421" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H421" s="39" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="G421" s="39" t="inlineStr">
+      <c r="I421" s="39" t="inlineStr">
         <is>
           <t>Hybride</t>
         </is>
       </c>
-      <c r="H421" s="39" t="inlineStr">
+      <c r="J421" s="39" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="I421" s="39" t="inlineStr">
+      <c r="K421" s="39" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="L421" s="39" t="inlineStr">
         <is>
           <t>ALTHEA cabinet conseil SIRH. Senior Manager, Lyon. Frein : Lyon pas remote. Profil senior bien aligné sinon.</t>
         </is>
       </c>
-      <c r="J421" s="39" t="inlineStr">
+      <c r="M421" s="39" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/fr/companies/althea/jobs/senior-manager-sirh-lyon-cdi_lyon</t>
         </is>
       </c>
-      <c r="K421" s="39" t="inlineStr">
+      <c r="N421" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="L421" s="39" t="inlineStr">
+      <c r="O421" s="39" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="M421" s="39" t="inlineStr">
+      <c r="P421" s="39" t="inlineStr">
         <is>
           <t>07/2026</t>
         </is>
       </c>
-      <c r="N421" s="39" t="n"/>
-      <c r="O421" s="39" t="n"/>
-      <c r="P421" s="39" t="n"/>
-      <c r="Q421" s="41" t="n"/>
+      <c r="Q421" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="66" t="inlineStr">
@@ -34190,72 +34226,82 @@
       <c r="Q71" s="41" t="n"/>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="53" t="inlineStr">
+      <c r="A72" s="73" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" s="6" t="n"/>
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Senior Customer Success Manager</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>Sprinklr</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="F72" s="5" t="inlineStr">
         <is>
           <t>Jobgether / Remote Rocketship</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="I72" s="6" t="inlineStr">
         <is>
           <t>100% remote</t>
         </is>
       </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="J72" s="6" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>Plateforme CX unifiée (social, service, marketing). CSM stratégique sur comptes enterprise. Remote France. Publié mai 2026.</t>
-        </is>
-      </c>
-      <c r="J72" s="6" t="inlineStr">
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Plateforme CX unifiée (social, service, marketing). CSM stratégique sur comptes enterprise. Remote France.</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
         <is>
           <t>https://jobgether.com/offer/6a0e8a64cc7b72676990a7dc-senior-customer-success-manager</t>
         </is>
       </c>
-      <c r="K72" s="6" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_CSM_EN.pdf</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>05/2026</t>
         </is>
       </c>
-      <c r="Q72" s="41" t="n"/>
+      <c r="Q72" s="41" t="inlineStr">
+        <is>
+          <t>05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="73" t="inlineStr">
@@ -46333,75 +46379,83 @@
       <c r="Q259" s="39" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="54" t="inlineStr">
+      <c r="A260" s="66" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B260" s="39" t="inlineStr">
+      <c r="B260" s="39" t="n"/>
+      <c r="C260" s="39" t="n"/>
+      <c r="D260" s="39" t="inlineStr">
         <is>
           <t>Customer Success Manager</t>
         </is>
       </c>
-      <c r="C260" s="39" t="inlineStr">
+      <c r="E260" s="39" t="inlineStr">
         <is>
           <t>Okta</t>
         </is>
       </c>
-      <c r="D260" s="39" t="inlineStr">
+      <c r="F260" s="39" t="inlineStr">
         <is>
           <t>Welcome to the Jungle</t>
         </is>
       </c>
-      <c r="E260" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="F260" s="39" t="inlineStr">
+      <c r="G260" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H260" s="39" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="G260" s="39" t="inlineStr">
+      <c r="I260" s="39" t="inlineStr">
         <is>
           <t>Hybride</t>
         </is>
       </c>
-      <c r="H260" s="39" t="inlineStr">
+      <c r="J260" s="39" t="inlineStr">
         <is>
           <t>71-98K€ OTE</t>
         </is>
       </c>
-      <c r="I260" s="39" t="inlineStr">
+      <c r="K260" s="39" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="L260" s="39" t="inlineStr">
         <is>
           <t>IAM/SSO, CSM enterprise, OTE 71-98K€. FREIN MAJEUR : français + italien requis (pas de mention anglais seul).</t>
         </is>
       </c>
-      <c r="J260" s="39" t="inlineStr">
+      <c r="M260" s="39" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/fr/companies/okta/jobs/customer-success-manager_paris_mnpmts4t</t>
         </is>
       </c>
-      <c r="K260" s="39" t="inlineStr">
+      <c r="N260" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_CSM_EN.pdf</t>
         </is>
       </c>
-      <c r="L260" s="39" t="inlineStr">
+      <c r="O260" s="39" t="inlineStr">
         <is>
           <t>71-98K€</t>
         </is>
       </c>
-      <c r="M260" s="39" t="inlineStr">
+      <c r="P260" s="39" t="inlineStr">
         <is>
           <t>07/2026</t>
         </is>
       </c>
-      <c r="N260" s="39" t="n"/>
-      <c r="O260" s="39" t="n"/>
-      <c r="P260" s="39" t="n"/>
-      <c r="Q260" s="39" t="n"/>
+      <c r="Q260" s="39" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="66" t="inlineStr">
@@ -46902,7 +46956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q120"/>
+  <dimension ref="A1:Q119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="13.6640625" customWidth="1" min="1" max="1"/>
@@ -48335,68 +48389,58 @@
       </c>
     </row>
     <row r="23" hidden="1" ht="16" customHeight="1">
-      <c r="A23" s="53" t="inlineStr">
+      <c r="A23" s="73" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Consultant IA Générative &amp; Conduite du changement</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Non communiqué</t>
-        </is>
-      </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Mission Freelances</t>
+          <t>Formateur / Consultant IA générative</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>Mantra Pro (ex-GrowthMakers)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>welcometothejungle.com</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>France - Full Remote</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Conduite du changement IA, ateliers acculturation, identification cas d'usage, pilotage Agile, vulgarisation. Fit excellent profil Gaëtan (sans data science pur).</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>https://www.mission-freelances.fr/r/87a17202</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>Formation dirigeants TPE/PME sur IA générative 1-2 jours ; 100% remote ; missions freelance ponctuelles ; parfait angle formateur IA sans data science</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>07/2026</t>
-        </is>
-      </c>
-      <c r="Q23" s="41" t="n"/>
+          <t>https://www.welcometothejungle.com/en/companies/growthmakers/jobs/formateur-ia-et-ia-generative_paris</t>
+        </is>
+      </c>
+      <c r="Q23" s="41" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="24" hidden="1">
       <c r="A24" s="73" t="inlineStr">
@@ -48406,17 +48450,17 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Formateur / Consultant IA générative</t>
+          <t>Formateur en IA générative et agentique</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Mantra Pro (ex-GrowthMakers)</t>
+          <t>N/C (via mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>welcometothejungle.com</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -48426,7 +48470,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>France - Full Remote</t>
+          <t>Télétravail</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -48438,137 +48482,154 @@
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Formation dirigeants TPE/PME sur IA générative 1-2 jours ; 100% remote ; missions freelance ponctuelles ; parfait angle formateur IA sans data science</t>
+          <t>Animation visioconférence 4-8 personnes ; prompt engineering + no-code + IA agentique ; RGPD/éthique ; statut indépendant requis ; publié 29 juin 2026</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/en/companies/growthmakers/jobs/formateur-ia-et-ia-generative_paris</t>
-        </is>
-      </c>
-      <c r="Q24" s="41" t="inlineStr">
+          <t>https://www.mission-freelances.fr/missions/formateur-en-intelligence-artificielle-generative-et-agentique-teletravail-c892d79e/</t>
+        </is>
+      </c>
+      <c r="Q24" s="41" t="n"/>
+    </row>
+    <row r="25" hidden="1" ht="32" customHeight="1">
+      <c r="A25" s="78" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>À postuler</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Chef de Projet IA</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>HN SERVICES</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>free-work.com</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Paris (75)</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>400-710€/j</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Mission chef de projet IA, Paris hybride. TJM 400-710€/j. 6 mois, démarrage ASAP. Publié 15/07/2026. Bon fit croisement IA × gestion de projet.</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>650-750€/j</t>
+        </is>
+      </c>
+      <c r="Q25" s="41" t="n"/>
+    </row>
+    <row r="26" hidden="1" ht="16" customHeight="1">
+      <c r="A26" s="73" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>À postuler</t>
+        </is>
+      </c>
+      <c r="C26" s="39" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Formateur / Formatrice en Intelligence Artificielle Générative</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Mister IA</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Paris / Île-de-France / Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Non affiché</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Mister IA = leader FR formation IA (30K+ personnes formées, 12M€ CA). CDI formateur IA générative. Présentiel + remote. Interventions auprès de toutes fonctions (exécutifs, métiers, RH). Très bon fit profil pédagogique Gaëtan.</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/mister-ia/jobs/commercial-business-developer-b2b-stage-alternance-h-f_paris</t>
+        </is>
+      </c>
+      <c r="N26" s="39" t="n"/>
+      <c r="O26" s="39" t="inlineStr">
+        <is>
+          <t>70-90K€</t>
+        </is>
+      </c>
+      <c r="P26" s="39" t="n"/>
+      <c r="Q26" s="41" t="inlineStr">
         <is>
           <t>08/07/2026</t>
         </is>
       </c>
-    </row>
-    <row r="25" hidden="1" ht="32" customHeight="1">
-      <c r="A25" s="73" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Formateur en IA générative et agentique</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>N/C (via mission-freelances.fr)</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>mission-freelances.fr</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Télétravail</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>Animation visioconférence 4-8 personnes ; prompt engineering + no-code + IA agentique ; RGPD/éthique ; statut indépendant requis ; publié 29 juin 2026</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>https://www.mission-freelances.fr/missions/formateur-en-intelligence-artificielle-generative-et-agentique-teletravail-c892d79e/</t>
-        </is>
-      </c>
-      <c r="Q25" s="41" t="n"/>
-    </row>
-    <row r="26" hidden="1" ht="16" customHeight="1">
-      <c r="A26" s="78" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>À postuler</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Chef de Projet IA</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>HN SERVICES</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>free-work.com</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Paris (75)</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>400-710€/j</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Mission chef de projet IA, Paris hybride. TJM 400-710€/j. 6 mois, démarrage ASAP. Publié 15/07/2026. Bon fit croisement IA × gestion de projet.</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
-      <c r="Q26" s="41" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="73" t="inlineStr">
@@ -48584,12 +48645,12 @@
       <c r="C27" s="39" t="n"/>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Formateur / Formatrice en Intelligence Artificielle Générative</t>
+          <t>Formateur / Consultant IA générative</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Mister IA</t>
+          <t>Mantra (ex-GrowthMakers)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -48599,47 +48660,43 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Paris / Île-de-France / Hauts-de-France</t>
+          <t>Remote (Paris)</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Non affiché</t>
+          <t>TJM attractif (non affiché)</t>
         </is>
       </c>
       <c r="K27" s="6" t="n"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Mister IA = leader FR formation IA (30K+ personnes formées, 12M€ CA). CDI formateur IA générative. Présentiel + remote. Interventions auprès de toutes fonctions (exécutifs, métiers, RH). Très bon fit profil pédagogique Gaëtan.</t>
+          <t>Mantra = organisme formation IA 100% remote. Freelance formateur IA générative. "TJM Attractif" mentionné. Full remote, flexibilité totale. Parfait pour Anglet.</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/mister-ia/jobs/commercial-business-developer-b2b-stage-alternance-h-f_paris</t>
+          <t>https://www.welcometothejungle.com/en/companies/growthmakers/jobs/formateur-ia-et-ia-generative_paris</t>
         </is>
       </c>
       <c r="N27" s="39" t="n"/>
       <c r="O27" s="39" t="inlineStr">
         <is>
-          <t>70-90K€</t>
+          <t>600-800€/j</t>
         </is>
       </c>
       <c r="P27" s="39" t="n"/>
-      <c r="Q27" s="41" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+      <c r="Q27" s="41" t="n"/>
     </row>
     <row r="28" hidden="1" ht="16" customHeight="1">
       <c r="A28" s="73" t="inlineStr">
@@ -48655,7 +48712,7 @@
       <c r="C28" s="39" t="n"/>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Formateur / Consultant IA générative</t>
+          <t>Formateur IA &amp; Automatisation (N8N, GenAI, Agent)</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -48685,18 +48742,18 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>TJM attractif (non affiché)</t>
+          <t>Non affiché</t>
         </is>
       </c>
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Mantra = organisme formation IA 100% remote. Freelance formateur IA générative. "TJM Attractif" mentionné. Full remote, flexibilité totale. Parfait pour Anglet.</t>
+          <t>Mantra, 2e position : focus automatisation (N8N, agents IA, GenAI). 100% remote. Profil formateur IA avec stack automatisation. Bon fit acculturation IA + outils no-code.</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/en/companies/growthmakers/jobs/formateur-ia-et-ia-generative_paris</t>
+          <t>https://www.welcometothejungle.com/fr/companies/growthmakers/jobs/formateur-ia-automatisation-n8n-genai-agent_paris</t>
         </is>
       </c>
       <c r="N28" s="39" t="n"/>
@@ -48722,12 +48779,12 @@
       <c r="C29" s="39" t="n"/>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA &amp; Automatisation (N8N, GenAI, Agent)</t>
+          <t>Formateur.ice IA génératives</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Mantra (ex-GrowthMakers)</t>
+          <t>Webmyday</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -48742,7 +48799,7 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Remote (Paris)</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -48758,12 +48815,12 @@
       <c r="K29" s="6" t="n"/>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Mantra, 2e position : focus automatisation (N8N, agents IA, GenAI). 100% remote. Profil formateur IA avec stack automatisation. Bon fit acculturation IA + outils no-code.</t>
+          <t>Webmyday = agence digitale, recrutement formateur IA générative. Freelance, 100% télétravail. Interventions formations entreprises.</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/growthmakers/jobs/formateur-ia-automatisation-n8n-genai-agent_paris</t>
+          <t>https://www.welcometothejungle.com/fr/companies/web-my-day/jobs/formateur-ice-referent-e-ia_paris</t>
         </is>
       </c>
       <c r="N29" s="39" t="n"/>
@@ -48781,66 +48838,70 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B30" s="39" t="inlineStr">
-        <is>
-          <t>À postuler</t>
-        </is>
-      </c>
+      <c r="B30" s="39" t="n"/>
       <c r="C30" s="39" t="n"/>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Formateur.ice IA génératives</t>
+          <t>Consultant Formateur IA — H/F</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Webmyday</t>
+          <t>Polaria</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn (il y a 16h)</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Non affiché</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Webmyday = agence digitale, recrutement formateur IA générative. Freelance, 100% télétravail. Interventions formations entreprises.</t>
+          <t>Très récent (16h). Polaria = cabinet formation/conseil IA. Consultant formateur IA CDI Paris. Profil formateur IA générative sans dev pur = fit parfait.</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/web-my-day/jobs/formateur-ice-referent-e-ia_paris</t>
-        </is>
-      </c>
-      <c r="N30" s="39" t="n"/>
+          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
+        </is>
+      </c>
+      <c r="N30" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_IA.html</t>
+        </is>
+      </c>
       <c r="O30" s="39" t="inlineStr">
         <is>
-          <t>600-800€/j</t>
+          <t>75-90K€</t>
         </is>
       </c>
       <c r="P30" s="39" t="n"/>
-      <c r="Q30" s="41" t="n"/>
+      <c r="Q30" s="41" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="31" hidden="1" ht="32" customHeight="1">
       <c r="A31" s="73" t="inlineStr">
@@ -48852,22 +48913,22 @@
       <c r="C31" s="39" t="n"/>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Consultant Formateur IA — H/F</t>
+          <t>Consultant IA Générative &amp; Conduite du changement</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Polaria</t>
+          <t>Client non divulgué</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn (il y a 16h)</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -48877,23 +48938,23 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="n"/>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>Non précisée</t>
+        </is>
+      </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Très récent (16h). Polaria = cabinet formation/conseil IA. Consultant formateur IA CDI Paris. Profil formateur IA générative sans dev pur = fit parfait.</t>
+          <t>Accompagnement déploiement IA générative (ChatGPT/Gemini), ateliers acculturation, lien stratégie-métiers, mode Agile. Posté 17/06/2026. Fit parfait profil non-technique IA.</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
+          <t>https://www.mission-freelances.fr/missions/consultant-ia-generative-conduite-du-changement-paris-87a17202/</t>
         </is>
       </c>
       <c r="N31" s="39" t="inlineStr">
@@ -48903,7 +48964,7 @@
       </c>
       <c r="O31" s="39" t="inlineStr">
         <is>
-          <t>75-90K€</t>
+          <t>500-700€/j</t>
         </is>
       </c>
       <c r="P31" s="39" t="n"/>
@@ -48923,48 +48984,44 @@
       <c r="C32" s="39" t="n"/>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Consultant IA Générative &amp; Conduite du changement</t>
+          <t>Consultant Formateur IA &amp; Management (H/F)</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Client non divulgué</t>
+          <t>Cabinet conseil (via Michael Page)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>michaelpage.fr</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J32" s="6" t="n"/>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>Non précisée</t>
-        </is>
-      </c>
+      <c r="K32" s="6" t="n"/>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>Accompagnement déploiement IA générative (ChatGPT/Gemini), ateliers acculturation, lien stratégie-métiers, mode Agile. Posté 17/06/2026. Fit parfait profil non-technique IA.</t>
+          <t>Concevoir et animer formations IA + management, expert IA interne, création offres RH innovantes. PME formation B2B. Fit excellent profil Gaëtan. Ref JN-032026-6962869.</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/consultant-ia-generative-conduite-du-changement-paris-87a17202/</t>
+          <t>https://www.michaelpage.fr/job-detail/consultant-formateur-ia-management-hf/ref/jn-032026-6962869</t>
         </is>
       </c>
       <c r="N32" s="39" t="inlineStr">
@@ -48974,15 +49031,11 @@
       </c>
       <c r="O32" s="39" t="inlineStr">
         <is>
-          <t>500-700€/j</t>
+          <t>70-85K€</t>
         </is>
       </c>
       <c r="P32" s="39" t="n"/>
-      <c r="Q32" s="41" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+      <c r="Q32" s="41" t="n"/>
     </row>
     <row r="33" hidden="1" ht="16" customHeight="1">
       <c r="A33" s="73" t="inlineStr">
@@ -48994,44 +49047,44 @@
       <c r="C33" s="39" t="n"/>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Consultant Formateur IA &amp; Management (H/F)</t>
+          <t>Consultant IA Générative &amp; Conduite du changement</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil (via Michael Page)</t>
+          <t>Client (via mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>michaelpage.fr</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Sur site Paris</t>
         </is>
       </c>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>Concevoir et animer formations IA + management, expert IA interne, création offres RH innovantes. PME formation B2B. Fit excellent profil Gaëtan. Ref JN-032026-6962869.</t>
+          <t>Mission: déploiement et adoption outils IA générative (ChatGPT, Gemini, Adobe Firefly), lien stratégie globale - équipes métiers (Marketing, CRM, Retail, Studio créatif). Posté 17/06/2026. Profil: consultant freelance ou PO expérimenté transformation digitale. Fit excellent IA + conduite du changement.</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.fr/job-detail/consultant-formateur-ia-management-hf/ref/jn-032026-6962869</t>
+          <t>https://www.mission-freelances.fr/missions/consultant-ia-generative-conduite-du-changement-paris-87a17202/</t>
         </is>
       </c>
       <c r="N33" s="39" t="inlineStr">
@@ -49041,11 +49094,15 @@
       </c>
       <c r="O33" s="39" t="inlineStr">
         <is>
-          <t>70-85K€</t>
+          <t>600-750€/j</t>
         </is>
       </c>
       <c r="P33" s="39" t="n"/>
-      <c r="Q33" s="41" t="n"/>
+      <c r="Q33" s="41" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="34" hidden="1" ht="16" customHeight="1">
       <c r="A34" s="73" t="inlineStr">
@@ -49057,44 +49114,44 @@
       <c r="C34" s="39" t="n"/>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Consultant IA Générative &amp; Conduite du changement</t>
+          <t>Consultant IA générative Innovation (AI Innovation Consultant)</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Client (via mission-freelances.fr)</t>
+          <t>Keyrus France</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>jobs.keyrus.fr</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Bordeaux</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Sur site Paris</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Mission: déploiement et adoption outils IA générative (ChatGPT, Gemini, Adobe Firefly), lien stratégie globale - équipes métiers (Marketing, CRM, Retail, Studio créatif). Posté 17/06/2026. Profil: consultant freelance ou PO expérimenté transformation digitale. Fit excellent IA + conduite du changement.</t>
+          <t>Keyrus cabinet conseil data &amp; IA. Posté 25/06/2026. Accompagnement organisations pour identifier et déployer cas d'usage IA générative, animation ateliers, prototypes no-code/low-code, conduite du changement IA. Bordeaux = accessible depuis Anglet (2h). Fit très bon sans Python/data science pur requis.</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/consultant-ia-generative-conduite-du-changement-paris-87a17202/</t>
+          <t>https://jobs.keyrus.fr/jobs/7969635-ai-innovation-consultant-h-f-nb</t>
         </is>
       </c>
       <c r="N34" s="39" t="inlineStr">
@@ -49104,15 +49161,11 @@
       </c>
       <c r="O34" s="39" t="inlineStr">
         <is>
-          <t>600-750€/j</t>
+          <t>60-75K€</t>
         </is>
       </c>
       <c r="P34" s="39" t="n"/>
-      <c r="Q34" s="41" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+      <c r="Q34" s="41" t="n"/>
     </row>
     <row r="35" hidden="1" ht="16" customHeight="1">
       <c r="A35" s="73" t="inlineStr">
@@ -49124,44 +49177,44 @@
       <c r="C35" s="39" t="n"/>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Consultant IA générative Innovation (AI Innovation Consultant)</t>
+          <t>Formateur.ice IA génératives (freelance)</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Keyrus France</t>
+          <t>Wemodo (ex Webmyday)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>jobs.keyrus.fr</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Bordeaux</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Oui (100% remote)</t>
         </is>
       </c>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>Keyrus cabinet conseil data &amp; IA. Posté 25/06/2026. Accompagnement organisations pour identifier et déployer cas d'usage IA générative, animation ateliers, prototypes no-code/low-code, conduite du changement IA. Bordeaux = accessible depuis Anglet (2h). Fit très bon sans Python/data science pur requis.</t>
+          <t>Wemodo animer formations certifiantes IA générative (ChatGPT, Claude, Gemini, Midjourney, Firefly), rôle jury d'examen. 100% remote = fit parfait Anglet. SIRET requis. Expérience min. 2 ans outils IA générative.</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.keyrus.fr/jobs/7969635-ai-innovation-consultant-h-f-nb</t>
+          <t>https://www.welcometothejungle.com/fr/companies/web-my-day/jobs/formateur-ice-referent-e-ia_paris</t>
         </is>
       </c>
       <c r="N35" s="39" t="inlineStr">
@@ -49171,7 +49224,7 @@
       </c>
       <c r="O35" s="39" t="inlineStr">
         <is>
-          <t>60-75K€</t>
+          <t>400-600€/j</t>
         </is>
       </c>
       <c r="P35" s="39" t="n"/>
@@ -49187,44 +49240,44 @@
       <c r="C36" s="39" t="n"/>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Formateur.ice IA génératives (freelance)</t>
+          <t>Consultant Formateur IA</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Wemodo (ex Webmyday)</t>
+          <t>Nextra-Partners</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>nextra.factorial.fr</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI ou Freelance</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>Oui (100% remote)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>Wemodo animer formations certifiantes IA générative (ChatGPT, Claude, Gemini, Midjourney, Firefly), rôle jury d'examen. 100% remote = fit parfait Anglet. SIRET requis. Expérience min. 2 ans outils IA générative.</t>
+          <t>Cabinet conseil Data &amp; IA Marseille/Toulouse. Conception et animation parcours formation IA/Data + développement commercial de l'Academy. 13e mois + bonus déplafonné. Anglais courant requis. Fit bon : pédagogie + conseil + dev commercial. Marseille = plus accessible qu'IDF depuis Anglet.</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/web-my-day/jobs/formateur-ice-referent-e-ia_paris</t>
+          <t>https://nextra.factorial.fr/job_posting/consultant-e-formateur-rice-ia-cdi-ou-freelance-257298</t>
         </is>
       </c>
       <c r="N36" s="39" t="inlineStr">
@@ -49234,7 +49287,7 @@
       </c>
       <c r="O36" s="39" t="inlineStr">
         <is>
-          <t>400-600€/j</t>
+          <t>60-75K€</t>
         </is>
       </c>
       <c r="P36" s="39" t="n"/>
@@ -49250,44 +49303,48 @@
       <c r="C37" s="39" t="n"/>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Consultant Formateur IA</t>
+          <t>Formateur Intelligence Artificielle générative (CDD 12 mois mi-temps)</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Nextra-Partners</t>
+          <t>Walter Learning</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>nextra.factorial.fr</t>
+          <t>careers.werecruit.io / LinkedIn</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CDI ou Freelance</t>
+          <t>CDD 12 mois mi-temps</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Paris (remote total sauf tournage Marseille)</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Oui (quasi-total)</t>
         </is>
       </c>
       <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>12 mois</t>
+        </is>
+      </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil Data &amp; IA Marseille/Toulouse. Conception et animation parcours formation IA/Data + développement commercial de l'Academy. 13e mois + bonus déplafonné. Anglais courant requis. Fit bon : pédagogie + conseil + dev commercial. Marseille = plus accessible qu'IDF depuis Anglet.</t>
+          <t>Walter Learning formation certifiante. Concevoir et animer ~21h sur IA générative responsable (ChatGPT, Gemini, Copilot, DALL-E, Midjourney, IA Act, RGPD). CDD mi-temps = activité complémentaire possible. SIRET préféré. Tournage vidéo occasionnel Marseille.</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>https://nextra.factorial.fr/job_posting/consultant-e-formateur-rice-ia-cdi-ou-freelance-257298</t>
+          <t>https://careers.werecruit.io/fr/walter-learning/offres/formateur---intelligence-artificielle-generative-3cde70</t>
         </is>
       </c>
       <c r="N37" s="39" t="inlineStr">
@@ -49297,80 +49354,80 @@
       </c>
       <c r="O37" s="39" t="inlineStr">
         <is>
-          <t>60-75K€</t>
+          <t>400-600€/j</t>
         </is>
       </c>
       <c r="P37" s="39" t="n"/>
-      <c r="Q37" s="41" t="n"/>
+      <c r="Q37" s="41" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="73" t="inlineStr">
+      <c r="A38" s="81" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B38" s="39" t="n"/>
       <c r="C38" s="39" t="n"/>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Formateur Intelligence Artificielle générative (CDD 12 mois mi-temps)</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Walter Learning</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>careers.werecruit.io / LinkedIn</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>CDD 12 mois mi-temps</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>Paris (remote total sauf tournage Marseille)</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>Oui (quasi-total)</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="n"/>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>12 mois</t>
-        </is>
-      </c>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>Walter Learning formation certifiante. Concevoir et animer ~21h sur IA générative responsable (ChatGPT, Gemini, Copilot, DALL-E, Midjourney, IA Act, RGPD). CDD mi-temps = activité complémentaire possible. SIRET préféré. Tournage vidéo occasionnel Marseille.</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>https://careers.werecruit.io/fr/walter-learning/offres/formateur---intelligence-artificielle-generative-3cde70</t>
-        </is>
-      </c>
-      <c r="N38" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_IA.html</t>
-        </is>
-      </c>
-      <c r="O38" s="39" t="inlineStr">
-        <is>
-          <t>400-600€/j</t>
-        </is>
-      </c>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
+          <t>Responsable PMO Programme Intelligence Artificielle</t>
+        </is>
+      </c>
+      <c r="E38" s="39" t="inlineStr">
+        <is>
+          <t>CAT-AMANIA</t>
+        </is>
+      </c>
+      <c r="F38" s="39" t="inlineStr">
+        <is>
+          <t>free-work</t>
+        </is>
+      </c>
+      <c r="G38" s="39" t="inlineStr">
+        <is>
+          <t>Mission freelance</t>
+        </is>
+      </c>
+      <c r="H38" s="39" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="I38" s="39" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J38" s="39" t="inlineStr">
+        <is>
+          <t>600-720€/j</t>
+        </is>
+      </c>
+      <c r="K38" s="39" t="inlineStr">
+        <is>
+          <t>6 mois renouv.</t>
+        </is>
+      </c>
+      <c r="L38" s="39" t="inlineStr">
+        <is>
+          <t>PMO programme IA ; 15+ ans ; EU AI Act/RGPD ; 23/06/2026</t>
+        </is>
+      </c>
+      <c r="M38" s="39" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-decisionnel-bi-powerbi-sas-tableau/responsable-pmo-programme-intelligence-artificielle</t>
+        </is>
+      </c>
+      <c r="N38" s="39" t="n"/>
+      <c r="O38" s="39" t="n"/>
       <c r="P38" s="39" t="n"/>
       <c r="Q38" s="41" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
     </row>
@@ -49384,12 +49441,12 @@
       <c r="C39" s="39" t="n"/>
       <c r="D39" s="39" t="inlineStr">
         <is>
-          <t>Responsable PMO Programme Intelligence Artificielle</t>
+          <t>Chef de Projet Technique IA</t>
         </is>
       </c>
       <c r="E39" s="39" t="inlineStr">
         <is>
-          <t>CAT-AMANIA</t>
+          <t>Deodis</t>
         </is>
       </c>
       <c r="F39" s="39" t="inlineStr">
@@ -49409,100 +49466,100 @@
       </c>
       <c r="I39" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J39" s="39" t="inlineStr">
         <is>
-          <t>600-720€/j</t>
+          <t>500€/j</t>
         </is>
       </c>
       <c r="K39" s="39" t="inlineStr">
         <is>
-          <t>6 mois renouv.</t>
+          <t>1 an renouv.</t>
         </is>
       </c>
       <c r="L39" s="39" t="inlineStr">
         <is>
-          <t>PMO programme IA ; 15+ ans ; EU AI Act/RGPD ; 23/06/2026</t>
+          <t>ChatGPT, prompt engineering, support adoption IA ; 01/07/2026</t>
         </is>
       </c>
       <c r="M39" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-decisionnel-bi-powerbi-sas-tableau/responsable-pmo-programme-intelligence-artificielle</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-technique-ia-3</t>
         </is>
       </c>
       <c r="N39" s="39" t="n"/>
       <c r="O39" s="39" t="n"/>
       <c r="P39" s="39" t="n"/>
-      <c r="Q39" s="41" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+      <c r="Q39" s="41" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="81" t="inlineStr">
+      <c r="A40" s="73" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B40" s="39" t="n"/>
       <c r="C40" s="39" t="n"/>
-      <c r="D40" s="39" t="inlineStr">
-        <is>
-          <t>Chef de Projet Technique IA</t>
-        </is>
-      </c>
-      <c r="E40" s="39" t="inlineStr">
-        <is>
-          <t>Deodis</t>
-        </is>
-      </c>
-      <c r="F40" s="39" t="inlineStr">
-        <is>
-          <t>free-work</t>
-        </is>
-      </c>
-      <c r="G40" s="39" t="inlineStr">
-        <is>
-          <t>Mission freelance</t>
-        </is>
-      </c>
-      <c r="H40" s="39" t="inlineStr">
-        <is>
-          <t>Île-de-France</t>
-        </is>
-      </c>
-      <c r="I40" s="39" t="inlineStr">
-        <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J40" s="39" t="inlineStr">
-        <is>
-          <t>500€/j</t>
-        </is>
-      </c>
-      <c r="K40" s="39" t="inlineStr">
-        <is>
-          <t>1 an renouv.</t>
-        </is>
-      </c>
-      <c r="L40" s="39" t="inlineStr">
-        <is>
-          <t>ChatGPT, prompt engineering, support adoption IA ; 01/07/2026</t>
-        </is>
-      </c>
-      <c r="M40" s="39" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-technique-ia-3</t>
-        </is>
-      </c>
-      <c r="N40" s="39" t="n"/>
-      <c r="O40" s="39" t="n"/>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Consultant IA Générative &amp; Conduite du changement</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Client non précisé (via mission-freelances.fr)</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>mission-freelances.fr</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>À préciser</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Mission déploiement et adoption outils IA générative — lien stratégie/équipes métier, ateliers sensibilisation, intégration IA dans workflows. Profil consultant expérimenté avec PO/change management recherché. Gaëtan : expérience PO startup + IA quotidienne + conduite du changement SIRH = fit fort.</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mission-freelances.fr/missions/consultant-ia-generative-conduite-du-changement-paris-87a17202/</t>
+        </is>
+      </c>
+      <c r="N40" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_IA.html</t>
+        </is>
+      </c>
+      <c r="O40" s="39" t="inlineStr">
+        <is>
+          <t>600-750€/j</t>
+        </is>
+      </c>
       <c r="P40" s="39" t="n"/>
-      <c r="Q40" s="41" t="n"/>
+      <c r="Q40" s="41" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="73" t="inlineStr">
@@ -49514,22 +49571,22 @@
       <c r="C41" s="39" t="n"/>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Consultant IA Générative &amp; Conduite du changement</t>
+          <t>Consultant Intelligence Artificielle Sénior</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Client non précisé (via mission-freelances.fr)</t>
+          <t>iQo</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -49539,19 +49596,19 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>À préciser</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>Mission déploiement et adoption outils IA générative — lien stratégie/équipes métier, ateliers sensibilisation, intégration IA dans workflows. Profil consultant expérimenté avec PO/change management recherché. Gaëtan : expérience PO startup + IA quotidienne + conduite du changement SIRH = fit fort.</t>
+          <t>iQo (cabinet conseil impact B Corp, 5 ans) recrute un consultant senior IA — missions de stratégie IA, platformisation IA, programmes de transformation. Gaëtan peut se positionner sur le croisement IA + transformation RH/SIRH. Remote partiel = contrainte pour Anglet.</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/consultant-ia-generative-conduite-du-changement-paris-87a17202/</t>
+          <t>https://www.welcometothejungle.com/fr/companies/iqo/jobs/consultant-senior-ia_paris_IQO_jXWlwra</t>
         </is>
       </c>
       <c r="N41" s="39" t="inlineStr">
@@ -49561,15 +49618,11 @@
       </c>
       <c r="O41" s="39" t="inlineStr">
         <is>
-          <t>600-750€/j</t>
+          <t>80-90K€</t>
         </is>
       </c>
       <c r="P41" s="39" t="n"/>
-      <c r="Q41" s="41" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+      <c r="Q41" s="41" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="73" t="inlineStr">
@@ -49581,22 +49634,22 @@
       <c r="C42" s="39" t="n"/>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Consultant Intelligence Artificielle Sénior</t>
+          <t>Formateur IA et Évangélisation</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>iQo</t>
+          <t>Cherry Pick</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>workdispo.com</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -49606,19 +49659,27 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="6" t="n"/>
+          <t>Partiel (2j minimum remote)</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>550-600€ HT/j</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>Récurrent</t>
+        </is>
+      </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>iQo (cabinet conseil impact B Corp, 5 ans) recrute un consultant senior IA — missions de stratégie IA, platformisation IA, programmes de transformation. Gaëtan peut se positionner sur le croisement IA + transformation RH/SIRH. Remote partiel = contrainte pour Anglet.</t>
+          <t>Cherry Pick recrute régulièrement des formateurs IA / évangélisateurs pour groupes industriels (Microsoft Copilot, chatbot interne, acculturation IA). Mission citée (mars 2026) potentiellement expirée — contacter Cherry Pick directement pour missions similaires. Profil Gaëtan = fit parfait.</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/iqo/jobs/consultant-senior-ia_paris_IQO_jXWlwra</t>
+          <t>https://www.workdispo.com/job/formateur-ia-evangelisation</t>
         </is>
       </c>
       <c r="N42" s="39" t="inlineStr">
@@ -49628,7 +49689,7 @@
       </c>
       <c r="O42" s="39" t="inlineStr">
         <is>
-          <t>80-90K€</t>
+          <t>600-700€/j</t>
         </is>
       </c>
       <c r="P42" s="39" t="n"/>
@@ -49644,17 +49705,17 @@
       <c r="C43" s="39" t="n"/>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA et Évangélisation</t>
+          <t>Formateur·rice·s freelances en IA</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Cherry Pick</t>
+          <t>mission-freelances.fr (client non identifié)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>workdispo.com</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -49664,32 +49725,24 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Télétravail</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Partiel (2j minimum remote)</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>550-600€ HT/j</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>Récurrent</t>
-        </is>
-      </c>
+          <t>100% remote</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Cherry Pick recrute régulièrement des formateurs IA / évangélisateurs pour groupes industriels (Microsoft Copilot, chatbot interne, acculturation IA). Mission citée (mars 2026) potentiellement expirée — contacter Cherry Pick directement pour missions similaires. Profil Gaëtan = fit parfait.</t>
+          <t>Match direct avec le profil formateur IA 100% remote recherché par Gaëtan ; usage quotidien des outils IA générative valorisable directement.</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>https://www.workdispo.com/job/formateur-ia-evangelisation</t>
+          <t>https://mission-freelances.fr/missions/formateur-rice-s-freelances-en-ia-teletravail-9cc97c82/</t>
         </is>
       </c>
       <c r="N43" s="39" t="inlineStr">
@@ -49699,11 +49752,15 @@
       </c>
       <c r="O43" s="39" t="inlineStr">
         <is>
-          <t>600-700€/j</t>
+          <t>500-600€/j</t>
         </is>
       </c>
       <c r="P43" s="39" t="n"/>
-      <c r="Q43" s="41" t="n"/>
+      <c r="Q43" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="73" t="inlineStr">
@@ -49715,27 +49772,27 @@
       <c r="C44" s="39" t="n"/>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Formateur·rice·s freelances en IA</t>
+          <t>AI Enablement Specialist</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr (client non identifié)</t>
+          <t>n.c. (via Jobgether)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>jobs.lever.co</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Freelance / Consulting</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Télétravail</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -49747,12 +49804,12 @@
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>Match direct avec le profil formateur IA 100% remote recherché par Gaëtan ; usage quotidien des outils IA générative valorisable directement.</t>
+          <t>Mission de conseil en enablement IA, 100% remote et à horaires flexibles, publiée il y a une semaine. Le périmètre reste généraliste (acculturation, montée en compétence des équipes) plutôt que technique. À traiter comme un complément de la même famille que l'AI Adoption Manager du même diffuseur ; postuler aux deux.</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>https://mission-freelances.fr/missions/formateur-rice-s-freelances-en-ia-teletravail-9cc97c82/</t>
+          <t>https://jobs.lever.co/jobgether/e436352e-751e-45f9-a2e3-072587338814</t>
         </is>
       </c>
       <c r="N44" s="39" t="inlineStr">
@@ -49762,15 +49819,11 @@
       </c>
       <c r="O44" s="39" t="inlineStr">
         <is>
-          <t>500-600€/j</t>
+          <t>700-850€/j</t>
         </is>
       </c>
       <c r="P44" s="39" t="n"/>
-      <c r="Q44" s="41" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q44" s="41" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="73" t="inlineStr">
@@ -49782,7 +49835,7 @@
       <c r="C45" s="39" t="n"/>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>AI Enablement Specialist</t>
+          <t>AI Strategy &amp; Enablement Lead</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -49797,12 +49850,12 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Freelance / Consulting</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote (monde)</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -49814,12 +49867,12 @@
       <c r="K45" s="6" t="n"/>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>Mission de conseil en enablement IA, 100% remote et à horaires flexibles, publiée il y a une semaine. Le périmètre reste généraliste (acculturation, montée en compétence des équipes) plutôt que technique. À traiter comme un complément de la même famille que l'AI Adoption Manager du même diffuseur ; postuler aux deux.</t>
+          <t>Poste de lead sur la stratégie et l'enablement IA dans une organisation entièrement distribuée. Le niveau attendu est plus stratégique que les deux autres postes Jobgether ; l'expérience de co-fondateur de WallOfTraders.com et le pilotage de programmes mondiaux chez L'Oréal donnent la hauteur demandée. Publié en mai 2026, donc vérifier que l'offre reste ouverte avant de rédiger la LM.</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/jobgether/e436352e-751e-45f9-a2e3-072587338814</t>
+          <t>https://jobs.lever.co/jobgether/4c52dc4b-a501-4cc2-8907-e92704c02367</t>
         </is>
       </c>
       <c r="N45" s="39" t="inlineStr">
@@ -49829,7 +49882,7 @@
       </c>
       <c r="O45" s="39" t="inlineStr">
         <is>
-          <t>700-850€/j</t>
+          <t>95-110K€</t>
         </is>
       </c>
       <c r="P45" s="39" t="n"/>
@@ -49845,12 +49898,12 @@
       <c r="C46" s="39" t="n"/>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>AI Strategy &amp; Enablement Lead</t>
+          <t>AI Adoption &amp; Training Manager</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via Jobgether)</t>
+          <t>Vocal Media</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -49860,29 +49913,33 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>CDD (jusqu'à déc. 2026, extension possible)</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Remote (monde)</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="J46" s="6" t="n"/>
-      <c r="K46" s="6" t="n"/>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Jusqu'à décembre 2026</t>
+        </is>
+      </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>Poste de lead sur la stratégie et l'enablement IA dans une organisation entièrement distribuée. Le niveau attendu est plus stratégique que les deux autres postes Jobgether ; l'expérience de co-fondateur de WallOfTraders.com et le pilotage de programmes mondiaux chez L'Oréal donnent la hauteur demandée. Publié en mai 2026, donc vérifier que l'offre reste ouverte avant de rédiger la LM.</t>
+          <t>Poste dédié à la formation interne et à l'adoption de l'IA, en contrat jusqu'à fin 2026 avec extension possible. Le format temps plein limité dans le temps ressemble à une mission ; il conviendrait bien en attendant un CDI. Vérifier si l'entreprise accepte un contractant basé en France.</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/jobgether/4c52dc4b-a501-4cc2-8907-e92704c02367</t>
+          <t>https://jobs.lever.co/get-vocal-pbc/7e94f2ae-2749-402a-b94a-cbe7cb2ee9d2</t>
         </is>
       </c>
       <c r="N46" s="39" t="inlineStr">
@@ -49892,11 +49949,15 @@
       </c>
       <c r="O46" s="39" t="inlineStr">
         <is>
-          <t>95-110K€</t>
+          <t>80-90K€</t>
         </is>
       </c>
       <c r="P46" s="39" t="n"/>
-      <c r="Q46" s="41" t="n"/>
+      <c r="Q46" s="41" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="73" t="inlineStr">
@@ -49908,48 +49969,44 @@
       <c r="C47" s="39" t="n"/>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>AI Adoption &amp; Training Manager</t>
+          <t>Formateur IA freelance (vivier)</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Vocal Media</t>
+          <t>n.c. (via LinkedIn / mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>jobs.lever.co</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CDD (jusqu'à déc. 2026, extension possible)</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Télétravail</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>100% remote</t>
         </is>
       </c>
       <c r="J47" s="6" t="n"/>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>Jusqu'à décembre 2026</t>
-        </is>
-      </c>
+      <c r="K47" s="6" t="n"/>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Poste dédié à la formation interne et à l'adoption de l'IA, en contrat jusqu'à fin 2026 avec extension possible. Le format temps plein limité dans le temps ressemble à une mission ; il conviendrait bien en attendant un CDI. Vérifier si l'entreprise accepte un contractant basé en France.</t>
+          <t>Appel à candidatures pour constituer un vivier de formateurs IA freelances en télétravail. Le TJM du marché formateur IA se situe entre 700 et 1300€/j selon les données collectées ce jour. Candidature à faible coût qui peut générer un flux de missions récurrentes.</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/get-vocal-pbc/7e94f2ae-2749-402a-b94a-cbe7cb2ee9d2</t>
+          <t>https://www.mission-freelances.fr/missions/</t>
         </is>
       </c>
       <c r="N47" s="39" t="inlineStr">
@@ -49959,13 +50016,13 @@
       </c>
       <c r="O47" s="39" t="inlineStr">
         <is>
-          <t>80-90K€</t>
+          <t>800-1000€/j</t>
         </is>
       </c>
       <c r="P47" s="39" t="n"/>
       <c r="Q47" s="41" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -49979,12 +50036,12 @@
       <c r="C48" s="39" t="n"/>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA freelance (vivier)</t>
+          <t>Responsable Augmentation IA des Métiers</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via LinkedIn / mission-freelances.fr)</t>
+          <t>n.c. (via HelloWork / mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -49994,24 +50051,24 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Télétravail</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>Appel à candidatures pour constituer un vivier de formateurs IA freelances en télétravail. Le TJM du marché formateur IA se situe entre 700 et 1300€/j selon les données collectées ce jour. Candidature à faible coût qui peut générer un flux de missions récurrentes.</t>
+          <t>Le poste porte sur l'augmentation des métiers par l'IA, donc sur l'acculturation et l'outillage des équipes opérationnelles. C'est le type de rôle transverse où l'expérience SIRH mondiale sert de terrain d'application concret. Localisation Paris affichée ; négocier le remote dès le premier échange.</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
@@ -50026,13 +50083,13 @@
       </c>
       <c r="O48" s="39" t="inlineStr">
         <is>
-          <t>800-1000€/j</t>
+          <t>85-100K€</t>
         </is>
       </c>
       <c r="P48" s="39" t="n"/>
       <c r="Q48" s="41" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
     </row>
@@ -50046,12 +50103,12 @@
       <c r="C49" s="39" t="n"/>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Responsable Augmentation IA des Métiers</t>
+          <t>Expert IA / Consultant en transformation</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via HelloWork / mission-freelances.fr)</t>
+          <t>n.c. (via LinkedIn / mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
@@ -50061,24 +50118,24 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Télétravail</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>À vérifier</t>
+          <t>100% remote</t>
         </is>
       </c>
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="n"/>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>Le poste porte sur l'augmentation des métiers par l'IA, donc sur l'acculturation et l'outillage des équipes opérationnelles. C'est le type de rôle transverse où l'expérience SIRH mondiale sert de terrain d'application concret. Localisation Paris affichée ; négocier le remote dès le premier échange.</t>
+          <t>Mission d'expertise IA orientée transformation, en télétravail intégral. Le libellé reste vague ; il faut ouvrir l'annonce LinkedIn pour vérifier qu'il ne s'agit pas d'un poste data science. Si le périmètre est bien conduite du changement, le fit est fort.</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
@@ -50093,18 +50150,18 @@
       </c>
       <c r="O49" s="39" t="inlineStr">
         <is>
-          <t>85-100K€</t>
+          <t>700-900€/j</t>
         </is>
       </c>
       <c r="P49" s="39" t="n"/>
       <c r="Q49" s="41" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>06/12/2026</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="73" t="inlineStr">
+      <c r="A50" s="82" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
@@ -50113,17 +50170,17 @@
       <c r="C50" s="39" t="n"/>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Expert IA / Consultant en transformation</t>
+          <t>AI Governance Consultant / Trainer - Corporate Training &amp; Mentoring</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via LinkedIn / mission-freelances.fr)</t>
+          <t>n.c. (via Upwork)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>upwork.com</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -50133,24 +50190,32 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Télétravail</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="6" t="n"/>
+          <t>100% remote (sessions live)</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>Horaire ou au projet</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>3 à 6 mois, moins de 30h par semaine</t>
+        </is>
+      </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>Mission d'expertise IA orientée transformation, en télétravail intégral. Le libellé reste vague ; il faut ouvrir l'annonce LinkedIn pour vérifier qu'il ne s'agit pas d'un poste data science. Si le périmètre est bien conduite du changement, le fit est fort.</t>
+          <t>Mission de formation et de mentorat en entreprise sur la gouvernance de l'IA : cadres de gouvernance, risques d'implémentation en entreprise, gouvernance des LLM et de l'IA générative, traçabilité des données. Les sessions se tiennent en visio et le rythme de moins de 30h par semaine laisse la place à une autre mission en parallèle. Le volet conformité et gestion des risques dépasse la pratique actuelle et demandera une mise à niveau ; le volet formation et acculturation correspond en revanche pleinement. Renouvellement possible annoncé.</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/</t>
+          <t>https://www.upwork.com/freelance-jobs/apply/Governance-Consultant-Trainer-for-Corporate-Training-Hands-Mentoring_~022054488514687863860/</t>
         </is>
       </c>
       <c r="N50" s="39" t="inlineStr">
@@ -50160,86 +50225,70 @@
       </c>
       <c r="O50" s="39" t="inlineStr">
         <is>
-          <t>700-900€/j</t>
+          <t>À discuter</t>
         </is>
       </c>
       <c r="P50" s="39" t="n"/>
-      <c r="Q50" s="41" t="inlineStr">
-        <is>
-          <t>06/12/2026</t>
-        </is>
-      </c>
+      <c r="Q50" s="41" t="n"/>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="82" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
+      <c r="A51" s="65" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B51" s="39" t="n"/>
       <c r="C51" s="39" t="n"/>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>AI Governance Consultant / Trainer - Corporate Training &amp; Mentoring</t>
+          <t>Formateur/Formatrice en Intelligence Artificielle Générative (CDI)</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via Upwork)</t>
+          <t>MISTER IA</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>upwork.com</t>
+          <t>WelcomeToTheJungle</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>100% remote (sessions live)</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>Horaire ou au projet</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>3 à 6 mois, moins de 30h par semaine</t>
-        </is>
-      </c>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="n"/>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>Mission de formation et de mentorat en entreprise sur la gouvernance de l'IA : cadres de gouvernance, risques d'implémentation en entreprise, gouvernance des LLM et de l'IA générative, traçabilité des données. Les sessions se tiennent en visio et le rythme de moins de 30h par semaine laisse la place à une autre mission en parallèle. Le volet conformité et gestion des risques dépasse la pratique actuelle et demandera une mise à niveau ; le volet formation et acculturation correspond en revanche pleinement. Renouvellement possible annoncé.</t>
+          <t>N°1 formation IA France (30 000 personnes formées, 250+ entreprises). Former sur ChatGPT, Perplexity, Claude, NotebookLM. Profil praticien non-data-scientist = parfait. Recrutent aussi indépendants.</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>https://www.upwork.com/freelance-jobs/apply/Governance-Consultant-Trainer-for-Corporate-Training-Hands-Mentoring_~022054488514687863860/</t>
-        </is>
-      </c>
-      <c r="N51" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_IA.html</t>
-        </is>
-      </c>
-      <c r="O51" s="39" t="inlineStr">
-        <is>
-          <t>À discuter</t>
-        </is>
-      </c>
+          <t>https://www.mister-ia.com/</t>
+        </is>
+      </c>
+      <c r="N51" s="39" t="n"/>
+      <c r="O51" s="39" t="n"/>
       <c r="P51" s="39" t="n"/>
-      <c r="Q51" s="41" t="n"/>
+      <c r="Q51" s="41" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="65" t="inlineStr">
@@ -50251,12 +50300,12 @@
       <c r="C52" s="39" t="n"/>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Formateur/Formatrice en Intelligence Artificielle Générative (CDI)</t>
+          <t>Lead Transformation IA &amp; Automatisation H/F</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>MISTER IA</t>
+          <t>NEXTON Consulting</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
@@ -50276,29 +50325,29 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="n"/>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>~50-70K€</t>
+        </is>
+      </c>
       <c r="K52" s="6" t="n"/>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>N°1 formation IA France (30 000 personnes formées, 250+ entreprises). Former sur ChatGPT, Perplexity, Claude, NotebookLM. Profil praticien non-data-scientist = parfait. Recrutent aussi indépendants.</t>
+          <t>Déploiement IA à l'échelle clients (aéronautique, énergie, luxe), roadmaps automatisation, ROI. Rôle chef d'orchestre transformation IA grands comptes. Paris obligatoire.</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>https://www.mister-ia.com/</t>
+          <t>https://www.welcometothejungle.com/fr/companies/nexton-consulting/jobs/lead-transformation-ia-automatisation-h-f_paris</t>
         </is>
       </c>
       <c r="N52" s="39" t="n"/>
       <c r="O52" s="39" t="n"/>
       <c r="P52" s="39" t="n"/>
-      <c r="Q52" s="41" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
+      <c r="Q52" s="41" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="65" t="inlineStr">
@@ -50306,26 +50355,30 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B53" s="39" t="n"/>
+      <c r="B53" s="39" t="inlineStr">
+        <is>
+          <t>court, plus tard</t>
+        </is>
+      </c>
       <c r="C53" s="39" t="n"/>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Lead Transformation IA &amp; Automatisation H/F</t>
+          <t>Formateur·rice freelance – Intelligence Artificielle Agentique</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>NEXTON Consulting</t>
+          <t>DataBird</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>WelcomeToTheJungle</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -50335,27 +50388,35 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>~50-70K€</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K53" s="6" t="n"/>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>Déploiement IA à l'échelle clients (aéronautique, énergie, luxe), roadmaps automatisation, ROI. Rôle chef d'orchestre transformation IA grands comptes. Paris obligatoire.</t>
+          <t>2h de live/semaine (mardi soir). Outils : Dust, Make, n8n, Zapier. Pas de code pur. Mission partielle. 100% remote. Point d'entrée formateur IA agentique.</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/nexton-consulting/jobs/lead-transformation-ia-automatisation-h-f_paris</t>
-        </is>
-      </c>
-      <c r="N53" s="39" t="n"/>
-      <c r="O53" s="39" t="n"/>
+          <t>https://www.welcometothejungle.com/fr/companies/data-bird/jobs/formateur-rice-freelance-ia-generative_paris</t>
+        </is>
+      </c>
+      <c r="N53" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS</t>
+        </is>
+      </c>
+      <c r="O53" s="39" t="inlineStr">
+        <is>
+          <t>650-750€/j</t>
+        </is>
+      </c>
       <c r="P53" s="39" t="n"/>
       <c r="Q53" s="41" t="n"/>
     </row>
@@ -50365,20 +50426,16 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B54" s="39" t="inlineStr">
-        <is>
-          <t>court, plus tard</t>
-        </is>
-      </c>
+      <c r="B54" s="39" t="n"/>
       <c r="C54" s="39" t="n"/>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Formateur·rice freelance – Intelligence Artificielle Agentique</t>
+          <t>Change Manager Intelligence Artificielle H/F – 3-5 ans</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>DataBird</t>
+          <t>eXalt</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -50388,7 +50445,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
@@ -50398,7 +50455,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
@@ -50409,12 +50466,12 @@
       <c r="K54" s="6" t="n"/>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2h de live/semaine (mardi soir). Outils : Dust, Make, n8n, Zapier. Pas de code pur. Mission partielle. 100% remote. Point d'entrée formateur IA agentique.</t>
+          <t>Variante de l'offre eXalt avec séniorité explicite 3-5 ans. Expérience projet IA appréciée. Double candidature eXalt possible (URL distincte = poste distinct à vérifier).</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/data-bird/jobs/formateur-rice-freelance-ia-generative_paris</t>
+          <t>https://www.welcometothejungle.com/fr/companies/exalt/jobs/change-manager-ia-h-f-3-5-ans_paris</t>
         </is>
       </c>
       <c r="N54" s="39" t="inlineStr">
@@ -50424,7 +50481,7 @@
       </c>
       <c r="O54" s="39" t="inlineStr">
         <is>
-          <t>650-750€/j</t>
+          <t>70-80K€</t>
         </is>
       </c>
       <c r="P54" s="39" t="n"/>
@@ -50440,22 +50497,22 @@
       <c r="C55" s="39" t="n"/>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Change Manager Intelligence Artificielle H/F – 3-5 ans</t>
+          <t>Consultant IA Générative &amp; Conduite du changement</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>eXalt</t>
+          <t>Client anonyme (secteur digital)</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Mission Freelances</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -50476,12 +50533,12 @@
       <c r="K55" s="6" t="n"/>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>Variante de l'offre eXalt avec séniorité explicite 3-5 ans. Expérience projet IA appréciée. Double candidature eXalt possible (URL distincte = poste distinct à vérifier).</t>
+          <t>Publié le 17 juin 2026. Animation workshops, outils ChatGPT/Gemini/Adobe Firefly, cas d'usage, suivi adoption. URL distincte de la mission retail/luxe déjà en tableur.</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/exalt/jobs/change-manager-ia-h-f-3-5-ans_paris</t>
+          <t>https://www.mission-freelances.fr/missions/consultant-ia-generative-conduite-du-changement-paris/</t>
         </is>
       </c>
       <c r="N55" s="39" t="inlineStr">
@@ -50491,7 +50548,7 @@
       </c>
       <c r="O55" s="39" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P55" s="39" t="n"/>
@@ -50507,12 +50564,12 @@
       <c r="C56" s="39" t="n"/>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Consultant IA Générative &amp; Conduite du changement</t>
+          <t>Formateur / Formatrice en Intelligence Artificielle Générative (IDF)</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Client anonyme (secteur digital)</t>
+          <t>Client anonyme (mission-freelances IDF)</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -50527,7 +50584,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
@@ -50543,12 +50600,12 @@
       <c r="K56" s="6" t="n"/>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>Publié le 17 juin 2026. Animation workshops, outils ChatGPT/Gemini/Adobe Firefly, cas d'usage, suivi adoption. URL distincte de la mission retail/luxe déjà en tableur.</t>
+          <t>Formation certifiante IA générative, usage responsable. Présentiel ou distance. Mission distincte des autres annonces IA anonymes déjà en tableur (slug différent).</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/consultant-ia-generative-conduite-du-changement-paris/</t>
+          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
         </is>
       </c>
       <c r="N56" s="39" t="inlineStr">
@@ -50562,7 +50619,11 @@
         </is>
       </c>
       <c r="P56" s="39" t="n"/>
-      <c r="Q56" s="41" t="n"/>
+      <c r="Q56" s="41" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="65" t="inlineStr">
@@ -50574,17 +50635,17 @@
       <c r="C57" s="39" t="n"/>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Formateur / Formatrice en Intelligence Artificielle Générative (IDF)</t>
+          <t>Chef de Projet Intelligence Artificielle / Change Manager IA</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Client anonyme (mission-freelances IDF)</t>
+          <t>Crème de la crème</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Mission Freelances</t>
+          <t>Free-Work</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -50594,7 +50655,7 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Bordeaux, Nouvelle-Aquitaine</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
@@ -50604,18 +50665,22 @@
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="K57" s="6" t="n"/>
+          <t>350-510 €/j</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>7 mois renouvelable</t>
+        </is>
+      </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>Formation certifiante IA générative, usage responsable. Présentiel ou distance. Mission distincte des autres annonces IA anonymes déjà en tableur (slug différent).</t>
+          <t>Publiée 21 mai 2026. Pilotage transformation IA générative, licences, onboarding mensuel, support métier. Outils : Claude, ChatGPT, Copilot, Power Automate. Bordeaux gérable depuis Biarritz. TJM bas mais mission pertinente.</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
+          <t>https://www.free-work.com/fr/tech-it/assistant-chef-de-projet/job-mission/chef-de-projet-ia-changer-manager-ia</t>
         </is>
       </c>
       <c r="N57" s="39" t="inlineStr">
@@ -50625,13 +50690,13 @@
       </c>
       <c r="O57" s="39" t="inlineStr">
         <is>
-          <t>650-750€/j</t>
+          <t>500-650€/j</t>
         </is>
       </c>
       <c r="P57" s="39" t="n"/>
       <c r="Q57" s="41" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
     </row>
@@ -50645,12 +50710,12 @@
       <c r="C58" s="39" t="n"/>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Chef de Projet Intelligence Artificielle / Change Manager IA</t>
+          <t>PMO Senior Portefeuille Projets &amp; Transformation Intelligence Artificielle H/F</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Crème de la crème</t>
+          <t>Argain Consulting Innovation</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
@@ -50660,12 +50725,12 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Bordeaux, Nouvelle-Aquitaine</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
@@ -50675,22 +50740,22 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>350-510 €/j</t>
+          <t>48-58K€/an ou 550-600 €/j</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>7 mois renouvelable</t>
+          <t>6 mois (vérifier si encore active)</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>Publiée 21 mai 2026. Pilotage transformation IA générative, licences, onboarding mensuel, support métier. Outils : Claude, ChatGPT, Copilot, Power Automate. Bordeaux gérable depuis Biarritz. TJM bas mais mission pertinente.</t>
+          <t>Publiée 9 juin 2026, date limite 30/06 potentiellement dépassée — vérifier. Structuration portefeuille projets, roadmap, gouvernance IA. 8+ ans XP requis. IA générative appliquée au pilotage = croisement unique profil Gaëtan.</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/assistant-chef-de-projet/job-mission/chef-de-projet-ia-changer-manager-ia</t>
+          <t>https://www.free-work.com/fr/tech-it/assistant-chef-de-projet/job-mission/pmo-senior-portefeuille-projets-transformation-ia-h-f</t>
         </is>
       </c>
       <c r="N58" s="39" t="inlineStr">
@@ -50700,13 +50765,13 @@
       </c>
       <c r="O58" s="39" t="inlineStr">
         <is>
-          <t>500-650€/j</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P58" s="39" t="n"/>
       <c r="Q58" s="41" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
     </row>
@@ -50720,27 +50785,27 @@
       <c r="C59" s="39" t="n"/>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>PMO Senior Portefeuille Projets &amp; Transformation Intelligence Artificielle H/F</t>
+          <t>Formateur IA / Évangélisation</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Argain Consulting Innovation</t>
+          <t>Cherry Pick</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Free-Work</t>
+          <t>WorkDispo</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris (2j/site min.)</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -50750,38 +50815,38 @@
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>48-58K€/an ou 550-600 €/j</t>
+          <t>550-600€/j</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>6 mois (vérifier si encore active)</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>Publiée 9 juin 2026, date limite 30/06 potentiellement dépassée — vérifier. Structuration portefeuille projets, roadmap, gouvernance IA. 8+ ans XP requis. IA générative appliquée au pilotage = croisement unique profil Gaëtan.</t>
+          <t>Acculturation Microsoft Copilot, ChatGPT, filiales internationales, anglais impératif — à vérifier disponibilité</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/assistant-chef-de-projet/job-mission/pmo-senior-portefeuille-projets-transformation-ia-h-f</t>
+          <t>https://www.workdispo.com/job/formateur-ia-evangelisation</t>
         </is>
       </c>
       <c r="N59" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS</t>
+          <t>Resume_GaetanFRANCOIS.pdf</t>
         </is>
       </c>
       <c r="O59" s="39" t="inlineStr">
         <is>
-          <t>650-750€/j</t>
+          <t>600€/j</t>
         </is>
       </c>
       <c r="P59" s="39" t="n"/>
       <c r="Q59" s="41" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
     </row>
@@ -50795,17 +50860,17 @@
       <c r="C60" s="39" t="n"/>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA / Évangélisation</t>
+          <t>Architecte Data &amp; Intelligence Artificielle International H/F</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Cherry Pick</t>
+          <t>LENA IT</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>WorkDispo</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -50815,48 +50880,36 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>Paris (2j/site min.)</t>
+          <t>Issy-les-Moulineaux, IDF</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>550-600€/j</t>
-        </is>
-      </c>
-      <c r="K60" s="6" t="inlineStr">
-        <is>
-          <t>nc</t>
-        </is>
-      </c>
+          <t>680-710 €/j</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="n"/>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>Acculturation Microsoft Copilot, ChatGPT, filiales internationales, anglais impératif — à vérifier disponibilité</t>
+          <t>TJM excellent mais profil Architecte Data plus technique que Gaëtan</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>https://www.workdispo.com/job/formateur-ia-evangelisation</t>
-        </is>
-      </c>
-      <c r="N60" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS.pdf</t>
-        </is>
-      </c>
-      <c r="O60" s="39" t="inlineStr">
-        <is>
-          <t>600€/j</t>
-        </is>
-      </c>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/architecte-de-base-de-donnees/architecte-data-intelligence-artificielle-international-h-f</t>
+        </is>
+      </c>
+      <c r="N60" s="39" t="n"/>
+      <c r="O60" s="39" t="n"/>
       <c r="P60" s="39" t="n"/>
       <c r="Q60" s="41" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
     </row>
@@ -50870,27 +50923,27 @@
       <c r="C61" s="39" t="n"/>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Architecte Data &amp; Intelligence Artificielle International H/F</t>
+          <t>Consultant IA &amp; Learning Design H/F</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>LENA IT</t>
+          <t>Cegos France</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux, IDF</t>
+          <t>Issy-les-Moulineaux</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -50898,30 +50951,22 @@
           <t>Non précisé</t>
         </is>
       </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>680-710 €/j</t>
-        </is>
-      </c>
+      <c r="J61" s="6" t="n"/>
       <c r="K61" s="6" t="n"/>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>TJM excellent mais profil Architecte Data plus technique que Gaëtan</t>
+          <t>IA appliquée au learning design ; Cegos = leader formation pro ; pas de coding requis</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/architecte-de-base-de-donnees/architecte-data-intelligence-artificielle-international-h-f</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-ia-learning-design-h-f-at-cegos-france-4421252464</t>
         </is>
       </c>
       <c r="N61" s="39" t="n"/>
       <c r="O61" s="39" t="n"/>
       <c r="P61" s="39" t="n"/>
-      <c r="Q61" s="41" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
+      <c r="Q61" s="41" t="n"/>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="65" t="inlineStr">
@@ -50933,17 +50978,17 @@
       <c r="C62" s="39" t="n"/>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Consultant IA &amp; Learning Design H/F</t>
+          <t>Responsable du Développement des Compétences IA H/F</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Cegos France</t>
+          <t>ASTERIA</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -50953,7 +50998,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
@@ -50965,146 +51010,162 @@
       <c r="K62" s="6" t="n"/>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>IA appliquée au learning design ; Cegos = leader formation pro ; pas de coding requis</t>
+          <t>Développement compétences IA en entreprise ; Monaco = déplacement depuis Anglet</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-ia-learning-design-h-f-at-cegos-france-4421252464</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/responsable-infrastructures-production/responsable-du-developpement-des-competences-ia-h-f</t>
         </is>
       </c>
       <c r="N62" s="39" t="n"/>
       <c r="O62" s="39" t="n"/>
       <c r="P62" s="39" t="n"/>
-      <c r="Q62" s="41" t="n"/>
+      <c r="Q62" s="41" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="65" t="inlineStr">
+      <c r="A63" s="74" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B63" s="39" t="n"/>
       <c r="C63" s="39" t="n"/>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Responsable du Développement des Compétences IA H/F</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>ASTERIA</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>free-work.com</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>Non précisé</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="n"/>
-      <c r="K63" s="6" t="n"/>
-      <c r="L63" s="5" t="inlineStr">
-        <is>
-          <t>Développement compétences IA en entreprise ; Monaco = déplacement depuis Anglet</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/responsable-infrastructures-production/responsable-du-developpement-des-competences-ia-h-f</t>
+      <c r="D63" s="39" t="inlineStr">
+        <is>
+          <t>Formateur IA Générative</t>
+        </is>
+      </c>
+      <c r="E63" s="39" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="F63" s="39" t="inlineStr">
+        <is>
+          <t>mission-freelances.fr</t>
+        </is>
+      </c>
+      <c r="G63" s="39" t="inlineStr">
+        <is>
+          <t>Mission freelance</t>
+        </is>
+      </c>
+      <c r="H63" s="39" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="I63" s="39" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J63" s="39" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K63" s="39" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="L63" s="39" t="inlineStr">
+        <is>
+          <t>Formation certifiante IA générative RS6776, ChatGPT/Gemini/Copilot ; 25/06/2026</t>
+        </is>
+      </c>
+      <c r="M63" s="39" t="inlineStr">
+        <is>
+          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
         </is>
       </c>
       <c r="N63" s="39" t="n"/>
       <c r="O63" s="39" t="n"/>
-      <c r="P63" s="39" t="n"/>
-      <c r="Q63" s="41" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
+      <c r="P63" s="39" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="Q63" s="39" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
         </is>
       </c>
     </row>
     <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="74" t="inlineStr">
+      <c r="A64" s="65" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B64" s="39" t="n"/>
       <c r="C64" s="39" t="n"/>
-      <c r="D64" s="39" t="inlineStr">
-        <is>
-          <t>Formateur IA Générative</t>
-        </is>
-      </c>
-      <c r="E64" s="39" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="F64" s="39" t="inlineStr">
-        <is>
-          <t>mission-freelances.fr</t>
-        </is>
-      </c>
-      <c r="G64" s="39" t="inlineStr">
-        <is>
-          <t>Mission freelance</t>
-        </is>
-      </c>
-      <c r="H64" s="39" t="inlineStr">
-        <is>
-          <t>Île-de-France</t>
-        </is>
-      </c>
-      <c r="I64" s="39" t="inlineStr">
-        <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J64" s="39" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="K64" s="39" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="L64" s="39" t="inlineStr">
-        <is>
-          <t>Formation certifiante IA générative RS6776, ChatGPT/Gemini/Copilot ; 25/06/2026</t>
-        </is>
-      </c>
-      <c r="M64" s="39" t="inlineStr">
-        <is>
-          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
-        </is>
-      </c>
-      <c r="N64" s="39" t="n"/>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Formateur(trice) en Intelligence Artificielle / AI Trainer H/F</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>House of Aby</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CDI / Freelance à clarifier</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>Aix-en-Provence</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>À clarifier</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>À négocier</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>Publié il y a 1 jour. Fit formateur IA générique ; localisation Aix loin d'Anglet, vérifier si remote possible avant candidature.</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
+        </is>
+      </c>
+      <c r="N64" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_IA.pdf</t>
+        </is>
+      </c>
       <c r="O64" s="39" t="n"/>
-      <c r="P64" s="39" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="Q64" s="39" t="inlineStr">
-        <is>
-          <t>25/06/2026</t>
+      <c r="P64" s="39" t="n"/>
+      <c r="Q64" s="41" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
         </is>
       </c>
     </row>
@@ -51118,27 +51179,27 @@
       <c r="C65" s="39" t="n"/>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Formateur(trice) en Intelligence Artificielle / AI Trainer H/F</t>
+          <t>Consultant Senior Gouvernance Privacy &amp; IA</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>House of Aby</t>
+          <t>n.c. (via Free-Work)</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Free-Work</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>CDI / Freelance à clarifier</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Aix-en-Provence</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -51148,22 +51209,22 @@
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>À négocier</t>
+          <t>620 €/j</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>4 mois</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>Publié il y a 1 jour. Fit formateur IA générique ; localisation Aix loin d'Anglet, vérifier si remote possible avant candidature.</t>
+          <t>Publié 26/06/2026. Niche gouvernance/privacy IA = compliance ; croisement RGPD (que tu connais côté SIRH) + IA. Vérifier si le rôle a une composante conduite du changement ou pure compliance juridique.</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
+          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
         </is>
       </c>
       <c r="N65" s="39" t="inlineStr">
@@ -51175,12 +51236,12 @@
       <c r="P65" s="39" t="n"/>
       <c r="Q65" s="41" t="inlineStr">
         <is>
-          <t>28/06/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="65" t="inlineStr">
+      <c r="A66" s="50" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
@@ -51189,64 +51250,64 @@
       <c r="C66" s="39" t="n"/>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Consultant Senior Gouvernance Privacy &amp; IA</t>
+          <t>Chef de projet IA</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via Free-Work)</t>
+          <t>HN SERVICES</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Free-Work</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>À clarifier</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>620 €/j</t>
+          <t>400-710€/j</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>4 mois</t>
+          <t>6 mois renouv.</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>Publié 26/06/2026. Niche gouvernance/privacy IA = compliance ; croisement RGPD (que tu connais côté SIRH) + IA. Vérifier si le rôle a une composante conduite du changement ou pure compliance juridique.</t>
+          <t>Pilotage infra IA hybride (GCP + souverain), gouvernance COPIL/COPROJ, dossiers architecture HLD/LLD — non technique mais nécessite 3 ans projets IA/ML ; fit partiel (pilotage oui, bagage IA à valoriser)</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
-        </is>
-      </c>
-      <c r="N66" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_IA.pdf</t>
-        </is>
-      </c>
+          <t>https://free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/ingenieur-ia-16</t>
+        </is>
+      </c>
+      <c r="N66" s="39" t="n"/>
       <c r="O66" s="39" t="n"/>
-      <c r="P66" s="39" t="n"/>
+      <c r="P66" s="39" t="inlineStr">
+        <is>
+          <t>13/07/2026</t>
+        </is>
+      </c>
       <c r="Q66" s="41" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
     </row>
@@ -51260,17 +51321,17 @@
       <c r="C67" s="39" t="n"/>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Chef de projet IA</t>
+          <t>Formateur en IA et no-code</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>HN SERVICES</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>free-work</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr">
@@ -51285,27 +51346,23 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
+          <t>En ligne</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>400-710€/j</t>
-        </is>
-      </c>
-      <c r="K67" s="6" t="inlineStr">
-        <is>
-          <t>6 mois renouv.</t>
-        </is>
-      </c>
+      <c r="K67" s="6" t="n"/>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Pilotage infra IA hybride (GCP + souverain), gouvernance COPIL/COPROJ, dossiers architecture HLD/LLD — non technique mais nécessite 3 ans projets IA/ML ; fit partiel (pilotage oui, bagage IA à valoriser)</t>
+          <t>Concevoir et animer formations en ligne IA + no-code, vulgarisation pédagogique, aisance face caméra — fit bon pour angle formateur IA ; no-code secondaire mais non bloquant</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>https://free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/ingenieur-ia-16</t>
+          <t>https://www.mission-freelances.fr/missions/formateur-en-ia-et-no-code-paris/</t>
         </is>
       </c>
       <c r="N67" s="39" t="n"/>
@@ -51322,7 +51379,7 @@
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="50" t="inlineStr">
+      <c r="A68" s="65" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
@@ -51331,12 +51388,12 @@
       <c r="C68" s="39" t="n"/>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Formateur en IA et no-code</t>
+          <t>Formateur IA appliquée à l'acquisition client</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>N/C (via mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
@@ -51346,47 +51403,35 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Télétravail</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>En ligne</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="n"/>
       <c r="K68" s="6" t="n"/>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>Concevoir et animer formations en ligne IA + no-code, vulgarisation pédagogique, aisance face caméra — fit bon pour angle formateur IA ; no-code secondaire mais non bloquant</t>
+          <t>Formation à distance IA pour prospection/acquisition client ; marketing + IA ; statut SIREN requis ; publié 15 juillet 2026</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/formateur-en-ia-et-no-code-paris/</t>
+          <t>https://www.mission-freelances.fr/missions/formateur-ia-appliquee-a-l-acquisition-client-teletravail-68ec066a/</t>
         </is>
       </c>
       <c r="N68" s="39" t="n"/>
       <c r="O68" s="39" t="n"/>
-      <c r="P68" s="39" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="Q68" s="41" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
+      <c r="P68" s="39" t="n"/>
+      <c r="Q68" s="41" t="n"/>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="65" t="inlineStr">
@@ -51394,21 +51439,25 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B69" s="39" t="n"/>
+      <c r="B69" s="39" t="inlineStr">
+        <is>
+          <t>À postuler</t>
+        </is>
+      </c>
       <c r="C69" s="39" t="n"/>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA appliquée à l'acquisition client</t>
+          <t>Consultant Senior Stratégie &amp; Transformation IA</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>N/C (via mission-freelances.fr)</t>
+          <t>Bifora</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -51418,30 +51467,46 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Télétravail</t>
+          <t>Levallois-Perret (92)</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="n"/>
-      <c r="K69" s="6" t="n"/>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>310-600€/j</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>Formation à distance IA pour prospection/acquisition client ; marketing + IA ; statut SIREN requis ; publié 15 juillet 2026</t>
+          <t>Bifora, mission consultant transformation IA senior. TJM 310-600€/j (fourchette large). 6 mois, hybride Levallois. Publié 20/07/2026. Conduite du changement IA.</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/formateur-ia-appliquee-a-l-acquisition-client-teletravail-68ec066a/</t>
+          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
         </is>
       </c>
       <c r="N69" s="39" t="n"/>
-      <c r="O69" s="39" t="n"/>
+      <c r="O69" s="39" t="inlineStr">
+        <is>
+          <t>600-800€/j</t>
+        </is>
+      </c>
       <c r="P69" s="39" t="n"/>
-      <c r="Q69" s="41" t="n"/>
+      <c r="Q69" s="41" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="65" t="inlineStr">
@@ -51457,12 +51522,12 @@
       <c r="C70" s="39" t="n"/>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Consultant Senior Stratégie &amp; Transformation IA</t>
+          <t>PMO IA</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Bifora</t>
+          <t>DAVRICOURT</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
@@ -51472,12 +51537,12 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Levallois-Perret (92)</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
@@ -51487,17 +51552,13 @@
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>310-600€/j</t>
-        </is>
-      </c>
-      <c r="K70" s="6" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
+          <t>45-50K€/an</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="n"/>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>Bifora, mission consultant transformation IA senior. TJM 310-600€/j (fourchette large). 6 mois, hybride Levallois. Publié 20/07/2026. Conduite du changement IA.</t>
+          <t>PMO programme IA, CDI, Lille. Publié 17/07/2026. Moins fit (présentiel Lille), mais CDI PMO IA profil intéressant. Salaire en dessous cible senior.</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
@@ -51508,13 +51569,13 @@
       <c r="N70" s="39" t="n"/>
       <c r="O70" s="39" t="inlineStr">
         <is>
-          <t>600-800€/j</t>
+          <t>70-90K€</t>
         </is>
       </c>
       <c r="P70" s="39" t="n"/>
       <c r="Q70" s="41" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -51532,27 +51593,27 @@
       <c r="C71" s="39" t="n"/>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>PMO IA</t>
+          <t>Formateur.rice freelance - IA Agentique</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>DAVRICOURT</t>
+          <t>DataBird</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -51562,32 +51623,28 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>45-50K€/an</t>
+          <t>Non affiché</t>
         </is>
       </c>
       <c r="K71" s="6" t="n"/>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>PMO programme IA, CDI, Lille. Publié 17/07/2026. Moins fit (présentiel Lille), mais CDI PMO IA profil intéressant. Salaire en dessous cible senior.</t>
+          <t>DataBird = école data/IA. Formateur IA agentique, focus agents et LLM. Profil plus technique que formateur IA métier. Moins fit si pas de dev.</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
+          <t>https://www.welcometothejungle.com/fr/companies/data-bird/jobs/formateur-rice-freelance-ia-generative_paris</t>
         </is>
       </c>
       <c r="N71" s="39" t="n"/>
       <c r="O71" s="39" t="inlineStr">
         <is>
-          <t>70-90K€</t>
+          <t>600-800€/j</t>
         </is>
       </c>
       <c r="P71" s="39" t="n"/>
-      <c r="Q71" s="41" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q71" s="41" t="n"/>
     </row>
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="65" t="inlineStr">
@@ -51603,12 +51660,12 @@
       <c r="C72" s="39" t="n"/>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Formateur.rice freelance - IA Agentique</t>
+          <t>Formateur F/H</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>DataBird</t>
+          <t>SociaNova</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
@@ -51618,17 +51675,17 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
@@ -51639,22 +51696,26 @@
       <c r="K72" s="6" t="n"/>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>DataBird = école data/IA. Formateur IA agentique, focus agents et LLM. Profil plus technique que formateur IA métier. Moins fit si pas de dev.</t>
+          <t>SociaNova, formateur CDI 100% télétravail. Périmètre IA/digital (à confirmer). Full remote = bon fit Anglet.</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/data-bird/jobs/formateur-rice-freelance-ia-generative_paris</t>
+          <t>https://www.welcometothejungle.com/fr/companies/socianova/jobs/formateur-f-h</t>
         </is>
       </c>
       <c r="N72" s="39" t="n"/>
       <c r="O72" s="39" t="inlineStr">
         <is>
-          <t>600-800€/j</t>
+          <t>70-90K€</t>
         </is>
       </c>
       <c r="P72" s="39" t="n"/>
-      <c r="Q72" s="41" t="n"/>
+      <c r="Q72" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="65" t="inlineStr">
@@ -51670,12 +51731,12 @@
       <c r="C73" s="39" t="n"/>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Formateur F/H</t>
+          <t>Chef de projet BU Conseil H/F</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>SociaNova</t>
+          <t>Mister IA</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -51690,12 +51751,12 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris 8e</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
@@ -51706,12 +51767,12 @@
       <c r="K73" s="6" t="n"/>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>SociaNova, formateur CDI 100% télétravail. Périmètre IA/digital (à confirmer). Full remote = bon fit Anglet.</t>
+          <t>Mister IA (leader formation IA générative), poste chef de projet côté Business Unit Conseil. Paris 8e, CDI ASAP. Pilotage missions conseil IA. Intersection gestion de projet + IA.</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/socianova/jobs/formateur-f-h</t>
+          <t>https://www.welcometothejungle.com/fr/companies/mister-ia/jobs/chef-de-projet-bu-conseil-h-f-cdi-paris-8e-asap_paris</t>
         </is>
       </c>
       <c r="N73" s="39" t="n"/>
@@ -51721,11 +51782,7 @@
         </is>
       </c>
       <c r="P73" s="39" t="n"/>
-      <c r="Q73" s="41" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q73" s="41" t="n"/>
     </row>
     <row r="74" ht="32" customHeight="1">
       <c r="A74" s="65" t="inlineStr">
@@ -51733,66 +51790,70 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B74" s="39" t="inlineStr">
-        <is>
-          <t>À postuler</t>
-        </is>
-      </c>
+      <c r="B74" s="39" t="n"/>
       <c r="C74" s="39" t="n"/>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Chef de projet BU Conseil H/F</t>
+          <t>Formateur en Intelligence Artificielle F/H</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Mister IA</t>
+          <t>Groupe MDA</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn (il y a 3 semaines)</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>CDI ou Freelance</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>Paris 8e</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>Non affiché</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="K74" s="6" t="n"/>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>Mister IA (leader formation IA générative), poste chef de projet côté Business Unit Conseil. Paris 8e, CDI ASAP. Pilotage missions conseil IA. Intersection gestion de projet + IA.</t>
+          <t>Groupe MDA recherche formateur IA indépendant pour formations interentreprises. Profil non-développeur = bon fit.</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/mister-ia/jobs/chef-de-projet-bu-conseil-h-f-cdi-paris-8e-asap_paris</t>
-        </is>
-      </c>
-      <c r="N74" s="39" t="n"/>
+          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
+        </is>
+      </c>
+      <c r="N74" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_IA.html</t>
+        </is>
+      </c>
       <c r="O74" s="39" t="inlineStr">
         <is>
-          <t>70-90K€</t>
+          <t>700-800 €/j</t>
         </is>
       </c>
       <c r="P74" s="39" t="n"/>
-      <c r="Q74" s="41" t="n"/>
+      <c r="Q74" s="41" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="65" t="inlineStr">
@@ -51804,48 +51865,48 @@
       <c r="C75" s="39" t="n"/>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Formateur en Intelligence Artificielle F/H</t>
+          <t>Formateur / Formatrice en Intelligence Artificielle Générative</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Groupe MDA</t>
+          <t>Client non divulgué</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn (il y a 3 semaines)</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>CDI ou Freelance</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K75" s="6" t="n"/>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="n"/>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>Non précisée</t>
+        </is>
+      </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>Groupe MDA recherche formateur IA indépendant pour formations interentreprises. Profil non-développeur = bon fit.</t>
+          <t>Formation certifiante IA générative, usage responsable IA. Outils ChatGPT/Gemini/Copilot. Certification RS6776 souhaitée. Posté 25/06/2026.</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
+          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
         </is>
       </c>
       <c r="N75" s="39" t="inlineStr">
@@ -51855,15 +51916,11 @@
       </c>
       <c r="O75" s="39" t="inlineStr">
         <is>
-          <t>700-800 €/j</t>
+          <t>400-600€/j</t>
         </is>
       </c>
       <c r="P75" s="39" t="n"/>
-      <c r="Q75" s="41" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="Q75" s="41" t="n"/>
     </row>
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="65" t="inlineStr">
@@ -51875,17 +51932,17 @@
       <c r="C76" s="39" t="n"/>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Formateur / Formatrice en Intelligence Artificielle Générative</t>
+          <t>Formateur IA H/F</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Client non divulgué</t>
+          <t>OUICODING</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -51895,7 +51952,7 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
@@ -51904,19 +51961,15 @@
         </is>
       </c>
       <c r="J76" s="6" t="n"/>
-      <c r="K76" s="6" t="inlineStr">
-        <is>
-          <t>Non précisée</t>
-        </is>
-      </c>
+      <c r="K76" s="6" t="n"/>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>Formation certifiante IA générative, usage responsable IA. Outils ChatGPT/Gemini/Copilot. Certification RS6776 souhaitée. Posté 25/06/2026.</t>
+          <t>Formation IA freelance via OUICODING. Posté 2026.</t>
         </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
+          <t>https://www.free-work.com/fr/tech-it/formateur/job-mission/formateur-ia-h-f</t>
         </is>
       </c>
       <c r="N76" s="39" t="inlineStr">
@@ -51942,22 +51995,22 @@
       <c r="C77" s="39" t="n"/>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA H/F</t>
+          <t>Formateur - Intelligence Artificielle Générative (F/H)</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>OUICODING</t>
+          <t>Walter Learning</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -51967,19 +52020,19 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="6" t="n"/>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>Formation IA freelance via OUICODING. Posté 2026.</t>
+          <t>Walter Learning organisme formation leader, formateur IA générative. Posté il y a 2 mois. A vérifier disponibilité.</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/formateur/job-mission/formateur-ia-h-f</t>
+          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
         </is>
       </c>
       <c r="N77" s="39" t="inlineStr">
@@ -51989,11 +52042,15 @@
       </c>
       <c r="O77" s="39" t="inlineStr">
         <is>
-          <t>400-600€/j</t>
+          <t>60-75K€</t>
         </is>
       </c>
       <c r="P77" s="39" t="n"/>
-      <c r="Q77" s="41" t="n"/>
+      <c r="Q77" s="41" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="32" customHeight="1">
       <c r="A78" s="65" t="inlineStr">
@@ -52005,12 +52062,12 @@
       <c r="C78" s="39" t="n"/>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Formateur - Intelligence Artificielle Générative (F/H)</t>
+          <t>Formateur en Intelligence Artificielle (F/H)</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Walter Learning</t>
+          <t>Groupe MDA</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -52025,7 +52082,7 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
@@ -52037,7 +52094,7 @@
       <c r="K78" s="6" t="n"/>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>Walter Learning organisme formation leader, formateur IA générative. Posté il y a 2 mois. A vérifier disponibilité.</t>
+          <t>Groupe MDA formation IT/IA, CDI formateur IA France. Posté il y a 3 semaines. MDA = cabinet conseil ET formation.</t>
         </is>
       </c>
       <c r="M78" s="5" t="inlineStr">
@@ -52052,13 +52109,13 @@
       </c>
       <c r="O78" s="39" t="inlineStr">
         <is>
-          <t>60-75K€</t>
+          <t>65-80K€</t>
         </is>
       </c>
       <c r="P78" s="39" t="n"/>
       <c r="Q78" s="41" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
     </row>
@@ -52072,27 +52129,27 @@
       <c r="C79" s="39" t="n"/>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Formateur en Intelligence Artificielle (F/H)</t>
+          <t>Formateur IA - Usages outils numériques en collectivité (F/H)</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Groupe MDA</t>
+          <t>Editions ENI</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Auvergne-Rhône-Alpes</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -52104,12 +52161,12 @@
       <c r="K79" s="6" t="n"/>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>Groupe MDA formation IT/IA, CDI formateur IA France. Posté il y a 3 semaines. MDA = cabinet conseil ET formation.</t>
+          <t>Editions ENI n°1 éditeur livres informatique. Formateur IA pour collectivités territoriales, sessions 1-3 jours. Posté mars 2026. Freelance. Secteur public. Profil formateur terrain IA générative = fit. Zone géographique éloignée d'Anglet mais remote partiel.</t>
         </is>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
+          <t>https://www.free-work.com/fr/tech-it/directeur-des-systemes-dinformation-dsi/job-mission/nous-recrutons-formateur-rice-usages-des-outils-numeriques-et-de-lia-encollectivite</t>
         </is>
       </c>
       <c r="N79" s="39" t="inlineStr">
@@ -52119,7 +52176,7 @@
       </c>
       <c r="O79" s="39" t="inlineStr">
         <is>
-          <t>65-80K€</t>
+          <t>400-600€/j</t>
         </is>
       </c>
       <c r="P79" s="39" t="n"/>
@@ -52139,17 +52196,17 @@
       <c r="C80" s="39" t="n"/>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA - Usages outils numériques en collectivité (F/H)</t>
+          <t>Consultant Formateur IA au service des marchés publics (H/F)</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Editions ENI</t>
+          <t>Cegos</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>recrutement.cegos.com</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -52159,7 +52216,7 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>Auvergne-Rhône-Alpes</t>
+          <t>Issy-les-Moulineaux / France</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
@@ -52171,12 +52228,12 @@
       <c r="K80" s="6" t="n"/>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>Editions ENI n°1 éditeur livres informatique. Formateur IA pour collectivités territoriales, sessions 1-3 jours. Posté mars 2026. Freelance. Secteur public. Profil formateur terrain IA générative = fit. Zone géographique éloignée d'Anglet mais remote partiel.</t>
+          <t>Cegos organisme formation #1 FR, 1 000 formateurs réseau. Formation IA pour marchés publics (appels d'offres, sourcing automatisé, rédaction specs). Formateur indépendant réseau externe Cegos. Posté il y a 2 mois. Profil IA générative + secteur public.</t>
         </is>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/directeur-des-systemes-dinformation-dsi/job-mission/nous-recrutons-formateur-rice-usages-des-outils-numeriques-et-de-lia-encollectivite</t>
+          <t>https://recrutement.cegos.com/jobs/7672957-consultant-formateur-h-f-en-ia-au-service-des-marches-publics</t>
         </is>
       </c>
       <c r="N80" s="39" t="inlineStr">
@@ -52190,11 +52247,7 @@
         </is>
       </c>
       <c r="P80" s="39" t="n"/>
-      <c r="Q80" s="41" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="Q80" s="41" t="n"/>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="65" t="inlineStr">
@@ -52206,17 +52259,17 @@
       <c r="C81" s="39" t="n"/>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Consultant Formateur IA au service des marchés publics (H/F)</t>
+          <t>Formateur IA générative agentique (freelance)</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Cegos</t>
+          <t>DataBird</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>recrutement.cegos.com</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -52226,24 +52279,28 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux / France</t>
+          <t>Paris (à distance)</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Oui (2h de live mardi soir)</t>
         </is>
       </c>
       <c r="J81" s="6" t="n"/>
-      <c r="K81" s="6" t="n"/>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>Récurrent</t>
+        </is>
+      </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>Cegos organisme formation #1 FR, 1 000 formateurs réseau. Formation IA pour marchés publics (appels d'offres, sourcing automatisé, rédaction specs). Formateur indépendant réseau externe Cegos. Posté il y a 2 mois. Profil IA générative + secteur public.</t>
+          <t>DataBird forme profils métier à l'IA agentique (agents IA, Make, Dust). Animation 2h/semaine le mardi soir. Mission complémentaire idéale — charge légère. DataBird forme des non-développeurs.</t>
         </is>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>https://recrutement.cegos.com/jobs/7672957-consultant-formateur-h-f-en-ia-au-service-des-marches-publics</t>
+          <t>https://www.welcometothejungle.com/fr/companies/data-bird/jobs/formateur-rice-freelance-ia-generative_paris</t>
         </is>
       </c>
       <c r="N81" s="39" t="inlineStr">
@@ -52257,7 +52314,11 @@
         </is>
       </c>
       <c r="P81" s="39" t="n"/>
-      <c r="Q81" s="41" t="n"/>
+      <c r="Q81" s="41" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="65" t="inlineStr">
@@ -52269,12 +52330,12 @@
       <c r="C82" s="39" t="n"/>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA générative agentique (freelance)</t>
+          <t>Formateur Automations No-Code IA générative (freelance)</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>DataBird</t>
+          <t>Wemodo (ex Webmyday)</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
@@ -52289,28 +52350,24 @@
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Paris (à distance)</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>Oui (2h de live mardi soir)</t>
+          <t>Oui (100% remote)</t>
         </is>
       </c>
       <c r="J82" s="6" t="n"/>
-      <c r="K82" s="6" t="inlineStr">
-        <is>
-          <t>Récurrent</t>
-        </is>
-      </c>
+      <c r="K82" s="6" t="n"/>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>DataBird forme profils métier à l'IA agentique (agents IA, Make, Dust). Animation 2h/semaine le mardi soir. Mission complémentaire idéale — charge légère. DataBird forme des non-développeurs.</t>
+          <t>Wemodo formation automation no-code (Make, Zapier, n8n). Intégration agents IA via API. 100% remote. Un peu plus technique que le poste IA générative Wemodo, mais sans Python/data science. À considérer si Gaëtan à l'aise avec no-code automation.</t>
         </is>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/data-bird/jobs/formateur-rice-freelance-ia-generative_paris</t>
+          <t>https://www.welcometothejungle.com/fr/companies/web-my-day/jobs/formateur-ice-referent-automations-no-code_paris</t>
         </is>
       </c>
       <c r="N82" s="39" t="inlineStr">
@@ -52324,11 +52381,7 @@
         </is>
       </c>
       <c r="P82" s="39" t="n"/>
-      <c r="Q82" s="41" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="Q82" s="41" t="n"/>
     </row>
     <row r="83" ht="32" customHeight="1">
       <c r="A83" s="65" t="inlineStr">
@@ -52340,17 +52393,17 @@
       <c r="C83" s="39" t="n"/>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Formateur Automations No-Code IA générative (freelance)</t>
+          <t>Formateur Intelligence Artificielle générative (freelance)</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Wemodo (ex Webmyday)</t>
+          <t>Client non précisé (via mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
@@ -52360,24 +52413,24 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>Oui (100% remote)</t>
+          <t>Partiel (présentiel et/ou distanciel)</t>
         </is>
       </c>
       <c r="J83" s="6" t="n"/>
       <c r="K83" s="6" t="n"/>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>Wemodo formation automation no-code (Make, Zapier, n8n). Intégration agents IA via API. 100% remote. Un peu plus technique que le poste IA générative Wemodo, mais sans Python/data science. À considérer si Gaëtan à l'aise avec no-code automation.</t>
+          <t>Publiée 25/06/2026. Formation certifiante IA générative responsable. ChatGPT, Gemini, Copilot, DALL-E, Midjourney, Adobe Firefly ; prompt engineering ; IA Act + RGPD. NDA + SIRET requis. Certification RS6776 souhaitée. Fit bon.</t>
         </is>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/web-my-day/jobs/formateur-ice-referent-automations-no-code_paris</t>
+          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
         </is>
       </c>
       <c r="N83" s="39" t="inlineStr">
@@ -52391,74 +52444,74 @@
         </is>
       </c>
       <c r="P83" s="39" t="n"/>
-      <c r="Q83" s="41" t="n"/>
+      <c r="Q83" s="41" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="65" t="inlineStr">
+      <c r="A84" s="75" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B84" s="39" t="n"/>
       <c r="C84" s="39" t="n"/>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>Formateur Intelligence Artificielle générative (freelance)</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>Client non précisé (via mission-freelances.fr)</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>mission-freelances.fr</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>Île-de-France</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>Partiel (présentiel et/ou distanciel)</t>
-        </is>
-      </c>
-      <c r="J84" s="6" t="n"/>
-      <c r="K84" s="6" t="n"/>
-      <c r="L84" s="5" t="inlineStr">
-        <is>
-          <t>Publiée 25/06/2026. Formation certifiante IA générative responsable. ChatGPT, Gemini, Copilot, DALL-E, Midjourney, Adobe Firefly ; prompt engineering ; IA Act + RGPD. NDA + SIRET requis. Certification RS6776 souhaitée. Fit bon.</t>
-        </is>
-      </c>
-      <c r="M84" s="5" t="inlineStr">
-        <is>
-          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
-        </is>
-      </c>
-      <c r="N84" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_IA.html</t>
-        </is>
-      </c>
-      <c r="O84" s="39" t="inlineStr">
-        <is>
-          <t>400-600€/j</t>
-        </is>
-      </c>
+      <c r="D84" s="39" t="inlineStr">
+        <is>
+          <t>Chef de projet Opérationnel IA &amp; Organisationnel</t>
+        </is>
+      </c>
+      <c r="E84" s="39" t="inlineStr">
+        <is>
+          <t>Espritek</t>
+        </is>
+      </c>
+      <c r="F84" s="39" t="inlineStr">
+        <is>
+          <t>free-work</t>
+        </is>
+      </c>
+      <c r="G84" s="39" t="inlineStr">
+        <is>
+          <t>Mission freelance</t>
+        </is>
+      </c>
+      <c r="H84" s="39" t="inlineStr">
+        <is>
+          <t>Vélizy-Villacoublay (78)</t>
+        </is>
+      </c>
+      <c r="I84" s="39" t="inlineStr">
+        <is>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J84" s="39" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K84" s="39" t="inlineStr">
+        <is>
+          <t>2 ans</t>
+        </is>
+      </c>
+      <c r="L84" s="39" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA + IA générative ; &gt;10 ans ; 12/06/2026</t>
+        </is>
+      </c>
+      <c r="M84" s="39" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-operationnel-ia-organisationnel</t>
+        </is>
+      </c>
+      <c r="N84" s="39" t="n"/>
+      <c r="O84" s="39" t="n"/>
       <c r="P84" s="39" t="n"/>
-      <c r="Q84" s="41" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
+      <c r="Q84" s="41" t="n"/>
     </row>
     <row r="85" ht="32" customHeight="1">
       <c r="A85" s="75" t="inlineStr">
@@ -52470,12 +52523,12 @@
       <c r="C85" s="39" t="n"/>
       <c r="D85" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet Opérationnel IA &amp; Organisationnel</t>
+          <t>Consultant AMOA IA / Data H/F</t>
         </is>
       </c>
       <c r="E85" s="39" t="inlineStr">
         <is>
-          <t>Espritek</t>
+          <t>Webnet</t>
         </is>
       </c>
       <c r="F85" s="39" t="inlineStr">
@@ -52490,32 +52543,32 @@
       </c>
       <c r="H85" s="39" t="inlineStr">
         <is>
-          <t>Vélizy-Villacoublay (78)</t>
+          <t>Tours (37)</t>
         </is>
       </c>
       <c r="I85" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J85" s="39" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>430-450€/j</t>
         </is>
       </c>
       <c r="K85" s="39" t="inlineStr">
         <is>
-          <t>2 ans</t>
+          <t>12 mois</t>
         </is>
       </c>
       <c r="L85" s="39" t="inlineStr">
         <is>
-          <t>SAP S/4HANA + IA générative ; &gt;10 ans ; 12/06/2026</t>
+          <t>AMOA IA/Data ; Python/SQL requis ; 7+ ans ; 28/06/2026</t>
         </is>
       </c>
       <c r="M85" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-operationnel-ia-organisationnel</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/consultant-amoa-ia-data-h-f-tours</t>
         </is>
       </c>
       <c r="N85" s="39" t="n"/>
@@ -52533,12 +52586,12 @@
       <c r="C86" s="39" t="n"/>
       <c r="D86" s="39" t="inlineStr">
         <is>
-          <t>Consultant AMOA IA / Data H/F</t>
+          <t>Chef de projet Intelligence Artificielle ChatGPT</t>
         </is>
       </c>
       <c r="E86" s="39" t="inlineStr">
         <is>
-          <t>Webnet</t>
+          <t>BI Solutions</t>
         </is>
       </c>
       <c r="F86" s="39" t="inlineStr">
@@ -52553,38 +52606,42 @@
       </c>
       <c r="H86" s="39" t="inlineStr">
         <is>
-          <t>Tours (37)</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I86" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J86" s="39" t="inlineStr">
         <is>
-          <t>430-450€/j</t>
+          <t>400-500€/j</t>
         </is>
       </c>
       <c r="K86" s="39" t="inlineStr">
         <is>
-          <t>12 mois</t>
+          <t>2 ans renouv.</t>
         </is>
       </c>
       <c r="L86" s="39" t="inlineStr">
         <is>
-          <t>AMOA IA/Data ; Python/SQL requis ; 7+ ans ; 28/06/2026</t>
+          <t>ChatGPT, prompt engineering, bilingue FR/EN ; 03/07/2026</t>
         </is>
       </c>
       <c r="M86" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/consultant-amoa-ia-data-h-f-tours</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-intelligence-artificielle-chat-gpt-anglais-500-e-par-j</t>
         </is>
       </c>
       <c r="N86" s="39" t="n"/>
       <c r="O86" s="39" t="n"/>
       <c r="P86" s="39" t="n"/>
-      <c r="Q86" s="41" t="n"/>
+      <c r="Q86" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="75" t="inlineStr">
@@ -52596,12 +52653,12 @@
       <c r="C87" s="39" t="n"/>
       <c r="D87" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet Intelligence Artificielle ChatGPT</t>
+          <t>Consultant Formateur IA, Secteur Bancaire H/F</t>
         </is>
       </c>
       <c r="E87" s="39" t="inlineStr">
         <is>
-          <t>BI Solutions</t>
+          <t>OUICODING</t>
         </is>
       </c>
       <c r="F87" s="39" t="inlineStr">
@@ -52616,32 +52673,32 @@
       </c>
       <c r="H87" s="39" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I87" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Hybride + Afrique</t>
         </is>
       </c>
       <c r="J87" s="39" t="inlineStr">
         <is>
-          <t>400-500€/j</t>
+          <t>400-600€/j</t>
         </is>
       </c>
       <c r="K87" s="39" t="inlineStr">
         <is>
-          <t>2 ans renouv.</t>
+          <t>1 mois</t>
         </is>
       </c>
       <c r="L87" s="39" t="inlineStr">
         <is>
-          <t>ChatGPT, prompt engineering, bilingue FR/EN ; 03/07/2026</t>
+          <t>Formation IA banque ; LLM+MLOps requis ; déplacement Afrique de l'Ouest ; 07/07/2026</t>
         </is>
       </c>
       <c r="M87" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-intelligence-artificielle-chat-gpt-anglais-500-e-par-j</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant/consultant-formateur-ia-secteur-bancaire-h-f</t>
         </is>
       </c>
       <c r="N87" s="39" t="n"/>
@@ -52654,71 +52711,67 @@
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="75" t="inlineStr">
+      <c r="A88" s="65" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B88" s="39" t="n"/>
       <c r="C88" s="39" t="n"/>
-      <c r="D88" s="39" t="inlineStr">
-        <is>
-          <t>Consultant Formateur IA, Secteur Bancaire H/F</t>
-        </is>
-      </c>
-      <c r="E88" s="39" t="inlineStr">
-        <is>
-          <t>OUICODING</t>
-        </is>
-      </c>
-      <c r="F88" s="39" t="inlineStr">
-        <is>
-          <t>free-work</t>
-        </is>
-      </c>
-      <c r="G88" s="39" t="inlineStr">
-        <is>
-          <t>Mission freelance</t>
-        </is>
-      </c>
-      <c r="H88" s="39" t="inlineStr">
-        <is>
-          <t>Paris (75)</t>
-        </is>
-      </c>
-      <c r="I88" s="39" t="inlineStr">
-        <is>
-          <t>Hybride + Afrique</t>
-        </is>
-      </c>
-      <c r="J88" s="39" t="inlineStr">
-        <is>
-          <t>400-600€/j</t>
-        </is>
-      </c>
-      <c r="K88" s="39" t="inlineStr">
-        <is>
-          <t>1 mois</t>
-        </is>
-      </c>
-      <c r="L88" s="39" t="inlineStr">
-        <is>
-          <t>Formation IA banque ; LLM+MLOps requis ; déplacement Afrique de l'Ouest ; 07/07/2026</t>
-        </is>
-      </c>
-      <c r="M88" s="39" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant/consultant-formateur-ia-secteur-bancaire-h-f</t>
-        </is>
-      </c>
-      <c r="N88" s="39" t="n"/>
-      <c r="O88" s="39" t="n"/>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>AI Adoption Leader - Intelligence Artificielle</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Valeo</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="n"/>
+      <c r="K88" s="6" t="n"/>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>Valeo (équipementier automobile mondial) recrute un AI Adoption Leader — acculturation, déploiement IA, conduite du changement. Publié ce matin (31/07/2026). Poste interne grand groupe = moins freelance-friendly mais valorise l'expérience transformation digitale de Gaëtan.</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/ai-adoption-leader-at-valeo</t>
+        </is>
+      </c>
+      <c r="N88" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_IA.html</t>
+        </is>
+      </c>
+      <c r="O88" s="39" t="inlineStr">
+        <is>
+          <t>80-95K€</t>
+        </is>
+      </c>
       <c r="P88" s="39" t="n"/>
-      <c r="Q88" s="41" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q88" s="41" t="n"/>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="65" t="inlineStr">
@@ -52730,12 +52783,12 @@
       <c r="C89" s="39" t="n"/>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>AI Adoption Leader - Intelligence Artificielle</t>
+          <t>Formateur en Intelligence Artificielle (F/H)</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Valeo</t>
+          <t>Groupe MDA</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -52750,24 +52803,24 @@
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="J89" s="6" t="n"/>
       <c r="K89" s="6" t="n"/>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>Valeo (équipementier automobile mondial) recrute un AI Adoption Leader — acculturation, déploiement IA, conduite du changement. Publié ce matin (31/07/2026). Poste interne grand groupe = moins freelance-friendly mais valorise l'expérience transformation digitale de Gaëtan.</t>
+          <t>Groupe MDA recrute un formateur IA en CDI — profil formateur terrain. Gaëtan peut valoriser ses compétences pédagogiques et son usage quotidien IA. Publié il y a 1 mois = probablement encore actif. Consulter site MDA directement pour détails.</t>
         </is>
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/ai-adoption-leader-at-valeo</t>
+          <t>https://fr.linkedin.com/jobs/view/formateur-en-intelligence-artificielle-f-h-at-groupe-mda</t>
         </is>
       </c>
       <c r="N89" s="39" t="inlineStr">
@@ -52777,11 +52830,15 @@
       </c>
       <c r="O89" s="39" t="inlineStr">
         <is>
-          <t>80-95K€</t>
+          <t>55-70K€</t>
         </is>
       </c>
       <c r="P89" s="39" t="n"/>
-      <c r="Q89" s="41" t="n"/>
+      <c r="Q89" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="32" customHeight="1">
       <c r="A90" s="65" t="inlineStr">
@@ -52793,27 +52850,27 @@
       <c r="C90" s="39" t="n"/>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Formateur en Intelligence Artificielle (F/H)</t>
+          <t>Consultant Change Management &amp; IA générative - Assurance IARD</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Groupe MDA</t>
+          <t>YGL Consulting</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Non précisée</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
@@ -52821,16 +52878,20 @@
           <t>Non précisé</t>
         </is>
       </c>
-      <c r="J90" s="6" t="n"/>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>600-700€/j</t>
+        </is>
+      </c>
       <c r="K90" s="6" t="n"/>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>Groupe MDA recrute un formateur IA en CDI — profil formateur terrain. Gaëtan peut valoriser ses compétences pédagogiques et son usage quotidien IA. Publié il y a 1 mois = probablement encore actif. Consulter site MDA directement pour détails.</t>
+          <t>YGL Consulting recrute un consultant conduite du changement IA dans le secteur assurance IARD — profil assurance requis. Gaëtan n'a pas d'expérience assurance mais profil change management + IA générative peut être transférable. Posté le 30/07/2026.</t>
         </is>
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/formateur-en-intelligence-artificielle-f-h-at-groupe-mda</t>
+          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
         </is>
       </c>
       <c r="N90" s="39" t="inlineStr">
@@ -52840,7 +52901,7 @@
       </c>
       <c r="O90" s="39" t="inlineStr">
         <is>
-          <t>55-70K€</t>
+          <t>650-700€/j</t>
         </is>
       </c>
       <c r="P90" s="39" t="n"/>
@@ -52860,17 +52921,17 @@
       <c r="C91" s="39" t="n"/>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Consultant Change Management &amp; IA générative - Assurance IARD</t>
+          <t>Formateur IA appliquée à l'acquisition client</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>YGL Consulting</t>
+          <t>mission-freelances.fr (client non identifié)</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
@@ -52880,28 +52941,24 @@
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>Non précisée</t>
+          <t>Télétravail</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>Non précisé</t>
-        </is>
-      </c>
-      <c r="J91" s="6" t="inlineStr">
-        <is>
-          <t>600-700€/j</t>
-        </is>
-      </c>
+          <t>100% remote</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="n"/>
       <c r="K91" s="6" t="n"/>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>YGL Consulting recrute un consultant conduite du changement IA dans le secteur assurance IARD — profil assurance requis. Gaëtan n'a pas d'expérience assurance mais profil change management + IA générative peut être transférable. Posté le 30/07/2026.</t>
+          <t>Formation IA orientée usage commercial ; nécessite SIRET/inscription directe sur la plateforme, pas de data science pure.</t>
         </is>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
+          <t>https://mission-freelances.fr/missions/formateur-ia-appliquee-a-l-acquisition-client-teletravail-68ec066a/</t>
         </is>
       </c>
       <c r="N91" s="39" t="inlineStr">
@@ -52911,13 +52968,13 @@
       </c>
       <c r="O91" s="39" t="inlineStr">
         <is>
-          <t>650-700€/j</t>
+          <t>500€/j</t>
         </is>
       </c>
       <c r="P91" s="39" t="n"/>
       <c r="Q91" s="41" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -52931,27 +52988,27 @@
       <c r="C92" s="39" t="n"/>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA appliquée à l'acquisition client</t>
+          <t>AI Transformation Engineer</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr (client non identifié)</t>
+          <t>Insider One</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>jobs.lever.co</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>Télétravail</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
@@ -52963,12 +53020,12 @@
       <c r="K92" s="6" t="n"/>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>Formation IA orientée usage commercial ; nécessite SIRET/inscription directe sur la plateforme, pas de data science pure.</t>
+          <t>Le poste consiste à coacher les équipes sur l'adoption de l'IA et à ancrer les changements de comportement, ce qui relève de la conduite du changement plus que de l'ingénierie. L'intitulé « Engineer » risque toutefois de cacher des attendus techniques ; lire la fiche complète avant de postuler.</t>
         </is>
       </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
-          <t>https://mission-freelances.fr/missions/formateur-ia-appliquee-a-l-acquisition-client-teletravail-68ec066a/</t>
+          <t>https://jobs.lever.co/insiderone/49f7e3c9-2a0e-4f45-99bd-1af880b7615b</t>
         </is>
       </c>
       <c r="N92" s="39" t="inlineStr">
@@ -52978,13 +53035,13 @@
       </c>
       <c r="O92" s="39" t="inlineStr">
         <is>
-          <t>500€/j</t>
+          <t>80-95K€</t>
         </is>
       </c>
       <c r="P92" s="39" t="n"/>
       <c r="Q92" s="41" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
     </row>
@@ -52998,17 +53055,17 @@
       <c r="C93" s="39" t="n"/>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>AI Transformation Engineer</t>
+          <t>Responsable Pilotage IA de la Performance Commerciale H/F</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Insider One</t>
+          <t>n.c. (via HelloWork / mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>jobs.lever.co</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G93" s="6" t="inlineStr">
@@ -53018,24 +53075,24 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
+          <t>À vérifier</t>
         </is>
       </c>
       <c r="J93" s="6" t="n"/>
       <c r="K93" s="6" t="n"/>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>Le poste consiste à coacher les équipes sur l'adoption de l'IA et à ancrer les changements de comportement, ce qui relève de la conduite du changement plus que de l'ingénierie. L'intitulé « Engineer » risque toutefois de cacher des attendus techniques ; lire la fiche complète avant de postuler.</t>
+          <t>Poste à l'intersection IA et performance commerciale, donc proche du suivi de portefeuille et des indicateurs de rétention pratiqués en Customer Success. La dimension analytique risque d'être plus forte que sur les postes formateur IA ; à confirmer.</t>
         </is>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/insiderone/49f7e3c9-2a0e-4f45-99bd-1af880b7615b</t>
+          <t>https://www.mission-freelances.fr/missions/</t>
         </is>
       </c>
       <c r="N93" s="39" t="inlineStr">
@@ -53051,7 +53108,7 @@
       <c r="P93" s="39" t="n"/>
       <c r="Q93" s="41" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -53065,12 +53122,12 @@
       <c r="C94" s="39" t="n"/>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Responsable Pilotage IA de la Performance Commerciale H/F</t>
+          <t>Formateur IA appliquée à l'acquisition client</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via HelloWork / mission-freelances.fr)</t>
+          <t>n.c. (via Indeed / mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
@@ -53080,24 +53137,24 @@
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Télétravail</t>
         </is>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>À vérifier</t>
+          <t>100% remote</t>
         </is>
       </c>
       <c r="J94" s="6" t="n"/>
       <c r="K94" s="6" t="n"/>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>Poste à l'intersection IA et performance commerciale, donc proche du suivi de portefeuille et des indicateurs de rétention pratiqués en Customer Success. La dimension analytique risque d'être plus forte que sur les postes formateur IA ; à confirmer.</t>
+          <t>Formation à l'usage de l'IA sur les sujets d'acquisition client, en télétravail. Le sujet commercial reste dans la zone de confort après quinze ans de relation client ; le format formation correspond au transfert de connaissances déjà pratiqué sur les projets SIRH. Annonce publiée il y a trois semaines, vérifier qu'elle est toujours active.</t>
         </is>
       </c>
       <c r="M94" s="5" t="inlineStr">
@@ -53112,18 +53169,18 @@
       </c>
       <c r="O94" s="39" t="inlineStr">
         <is>
-          <t>80-95K€</t>
+          <t>700-850€/j</t>
         </is>
       </c>
       <c r="P94" s="39" t="n"/>
       <c r="Q94" s="41" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
     </row>
     <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="65" t="inlineStr">
+      <c r="A95" s="84" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
@@ -53132,12 +53189,12 @@
       <c r="C95" s="39" t="n"/>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA appliquée à l'acquisition client</t>
+          <t>Formateur / Formatrice en Intelligence Artificielle Générative</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via Indeed / mission-freelances.fr)</t>
+          <t>n.c. (via mission-freelances.fr)</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
@@ -53152,24 +53209,24 @@
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>Télétravail</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
+          <t>Présentiel ou distanciel</t>
         </is>
       </c>
       <c r="J95" s="6" t="n"/>
       <c r="K95" s="6" t="n"/>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>Formation à l'usage de l'IA sur les sujets d'acquisition client, en télétravail. Le sujet commercial reste dans la zone de confort après quinze ans de relation client ; le format formation correspond au transfert de connaissances déjà pratiqué sur les projets SIRH. Annonce publiée il y a trois semaines, vérifier qu'elle est toujours active.</t>
+          <t>Animation de formations certifiantes sur l'usage responsable de l'IA générative, avec sessions possibles à distance. Deux prérequis administratifs bloquent aujourd'hui : un numéro de déclaration d'activité de formateur et idéalement la certification RS6776. Obtenir un NDA est faisable et ouvrirait tout le segment formation certifiante ; c'est le vrai enseignement de cette annonce, au delà de la mission elle-même. Publiée le 25/06/2026.</t>
         </is>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/</t>
+          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
         </is>
       </c>
       <c r="N95" s="39" t="inlineStr">
@@ -53179,13 +53236,13 @@
       </c>
       <c r="O95" s="39" t="inlineStr">
         <is>
-          <t>700-850€/j</t>
+          <t>700-900€/j</t>
         </is>
       </c>
       <c r="P95" s="39" t="n"/>
       <c r="Q95" s="41" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -53199,17 +53256,17 @@
       <c r="C96" s="39" t="n"/>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Formateur / Formatrice en Intelligence Artificielle Générative</t>
+          <t>Chef de Produit Plateforme IA</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via mission-freelances.fr)</t>
+          <t>JCW Search Ltd</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
@@ -53219,24 +53276,28 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>Présentiel ou distanciel</t>
-        </is>
-      </c>
-      <c r="J96" s="6" t="n"/>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>610-1110€/j</t>
+        </is>
+      </c>
       <c r="K96" s="6" t="n"/>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>Animation de formations certifiantes sur l'usage responsable de l'IA générative, avec sessions possibles à distance. Deux prérequis administratifs bloquent aujourd'hui : un numéro de déclaration d'activité de formateur et idéalement la certification RS6776. Obtenir un NDA est faisable et ouvrirait tout le segment formation certifiante ; c'est le vrai enseignement de cette annonce, au delà de la mission elle-même. Publiée le 25/06/2026.</t>
+          <t>Mission publiée le 05/08/2026, avec un TJM très au-dessus de la fourchette cible. Le rôle consiste à définir la vision et la feuille de route d'une plateforme IA, ce qui rejoint l'expérience produit ; la partie industrialisation LLMOps demande en revanche un socle technique que le profil n'a pas. À tenter uniquement si l'annonce complète confirme un poste de pilotage et non d'ingénierie.</t>
         </is>
       </c>
       <c r="M96" s="5" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/formateur-formatrice-en-intelligence-artificielle-generative-ile-de-france-a5471a52/</t>
+          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
         </is>
       </c>
       <c r="N96" s="39" t="inlineStr">
@@ -53246,13 +53307,13 @@
       </c>
       <c r="O96" s="39" t="inlineStr">
         <is>
-          <t>700-900€/j</t>
+          <t>800-900€/j</t>
         </is>
       </c>
       <c r="P96" s="39" t="n"/>
       <c r="Q96" s="41" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
     </row>
@@ -53266,7 +53327,7 @@
       <c r="C97" s="39" t="n"/>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Chef de Produit Plateforme IA</t>
+          <t>Chef de Produit Plateforme IA (AI Platform Product Manager)</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -53281,7 +53342,7 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
@@ -53296,53 +53357,61 @@
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>610-1110€/j</t>
-        </is>
-      </c>
-      <c r="K97" s="6" t="n"/>
+          <t>610-1110 £/j</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>12 mois</t>
+        </is>
+      </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>Mission publiée le 05/08/2026, avec un TJM très au-dessus de la fourchette cible. Le rôle consiste à définir la vision et la feuille de route d'une plateforme IA, ce qui rejoint l'expérience produit ; la partie industrialisation LLMOps demande en revanche un socle technique que le profil n'a pas. À tenter uniquement si l'annonce complète confirme un poste de pilotage et non d'ingénierie.</t>
+          <t>Vision et strategie d'une plateforme IA d'entreprise, avec industrialisation LLMOps. Le TJM est le plus eleve rencontre sur cette relance. La composante LLMOps est technique et sort du perimetre non-data-science vise ; a tenter si l'angle produit domine.</t>
         </is>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/ia</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/responsable-produit/chef-de-produit-plateforme-ia-ai-platform-product-manager</t>
         </is>
       </c>
       <c r="N97" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_IA.html</t>
+          <t>Resume_GaetanFRANCOIS_IA.pdf</t>
         </is>
       </c>
       <c r="O97" s="39" t="inlineStr">
         <is>
-          <t>800-900€/j</t>
-        </is>
-      </c>
-      <c r="P97" s="39" t="n"/>
-      <c r="Q97" s="41" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
+          <t>750-900 €/j</t>
+        </is>
+      </c>
+      <c r="P97" s="39" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="Q97" s="39" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="84" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
+      <c r="A98" s="66" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="B98" s="39" t="n"/>
       <c r="C98" s="39" t="n"/>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Chef de Produit Plateforme IA (AI Platform Product Manager)</t>
+          <t>MOA Technico-Fonctionnel ChatGPT / IA</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>JCW Search Ltd</t>
+          <t>Deodis (client IDF)</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -53352,12 +53421,12 @@
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
@@ -53367,42 +53436,30 @@
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>610-1110 £/j</t>
+          <t>480 €/j</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>12 mois</t>
+          <t>1 an</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>Vision et strategie d'une plateforme IA d'entreprise, avec industrialisation LLMOps. Le TJM est le plus eleve rencontre sur cette relance. La composante LLMOps est technique et sort du perimetre non-data-science vise ; a tenter si l'angle produit domine.</t>
+          <t>Accompagner utilisateurs métier dans identification et qualification cas d'usage IA (ChatGPT). Profil MOA + transformation digitale + GenAI. Fit très fort : MOA + IA + accompagnement métier = profil Gaëtan.</t>
         </is>
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/responsable-produit/chef-de-produit-plateforme-ia-ai-platform-product-manager</t>
-        </is>
-      </c>
-      <c r="N98" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_IA.pdf</t>
-        </is>
-      </c>
-      <c r="O98" s="39" t="inlineStr">
-        <is>
-          <t>750-900 €/j</t>
-        </is>
-      </c>
-      <c r="P98" s="39" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="Q98" s="39" t="inlineStr">
-        <is>
-          <t>05/08/2026</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/moa-technico-fonctionnelle-chatgpt-experimente</t>
+        </is>
+      </c>
+      <c r="N98" s="39" t="n"/>
+      <c r="O98" s="39" t="n"/>
+      <c r="P98" s="39" t="n"/>
+      <c r="Q98" s="41" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
         </is>
       </c>
     </row>
@@ -53416,12 +53473,12 @@
       <c r="C99" s="39" t="n"/>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>MOA Technico-Fonctionnel ChatGPT / IA</t>
+          <t>AMOA Consultant IA / Data</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Deodis (client IDF)</t>
+          <t>Webnet (client région Centre)</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -53436,7 +53493,7 @@
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Tours</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
@@ -53446,22 +53503,22 @@
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>480 €/j</t>
+          <t>430-450 €/j</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>1 an</t>
+          <t>12 mois</t>
         </is>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>Accompagner utilisateurs métier dans identification et qualification cas d'usage IA (ChatGPT). Profil MOA + transformation digitale + GenAI. Fit très fort : MOA + IA + accompagnement métier = profil Gaëtan.</t>
+          <t>Déploiement solutions IA (document management, automatisation processus, GenAI). Profil AMOA avec sensibilité IA/Data. 14 ans AMOA SAP grands comptes = très crédible.</t>
         </is>
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/moa-technico-fonctionnelle-chatgpt-experimente</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/consultant-amoa-ia-data-h-f-tours</t>
         </is>
       </c>
       <c r="N99" s="39" t="n"/>
@@ -53469,7 +53526,7 @@
       <c r="P99" s="39" t="n"/>
       <c r="Q99" s="41" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
     </row>
@@ -53483,62 +53540,54 @@
       <c r="C100" s="39" t="n"/>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>AMOA Consultant IA / Data</t>
+          <t>Consultant Acculturation &amp; Change AI</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Webnet (client région Centre)</t>
+          <t>VO2 GROUP</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>WelcomeToTheJungle</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>Tours</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Partiel (2j/sem)</t>
         </is>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>430-450 €/j</t>
-        </is>
-      </c>
-      <c r="K100" s="6" t="inlineStr">
-        <is>
-          <t>12 mois</t>
-        </is>
-      </c>
+          <t>~40-70K€</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="n"/>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>Déploiement solutions IA (document management, automatisation processus, GenAI). Profil AMOA avec sensibilité IA/Data. 14 ans AMOA SAP grands comptes = très crédible.</t>
+          <t>Accompagner client bancaire dans stratégie IA. Benchmark, programme acculturation, bibliothèque prompts par métier. Conduite du changement IA. Contrainte : hybride Paris.</t>
         </is>
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/consultant-amoa-ia-data-h-f-tours</t>
+          <t>https://www.welcometothejungle.com/fr/companies/vo2-group/jobs/vo2-finance-consultant-acculturation-change-ai_paris</t>
         </is>
       </c>
       <c r="N100" s="39" t="n"/>
       <c r="O100" s="39" t="n"/>
       <c r="P100" s="39" t="n"/>
-      <c r="Q100" s="41" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="Q100" s="41" t="n"/>
     </row>
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="66" t="inlineStr">
@@ -53550,17 +53599,17 @@
       <c r="C101" s="39" t="n"/>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Consultant Acculturation &amp; Change AI</t>
+          <t>Consultant(e) Formateur(rice) IA</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>VO2 GROUP</t>
+          <t>Nextra-Partners</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>WelcomeToTheJungle</t>
+          <t>nextra.factorial.fr</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
@@ -53570,28 +53619,32 @@
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>Partiel (2j/sem)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>~40-70K€</t>
-        </is>
-      </c>
-      <c r="K101" s="6" t="n"/>
+          <t>Attractif + 13e mois + bonus</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>Accompagner client bancaire dans stratégie IA. Benchmark, programme acculturation, bibliothèque prompts par métier. Conduite du changement IA. Contrainte : hybride Paris.</t>
+          <t>Hub innovation Data/IA. Concevoir parcours formation, animer formations, conduite du changement. Marseille plus accessible que Paris depuis Biarritz. Fit solide si télétravail 4/5 négociable.</t>
         </is>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/vo2-group/jobs/vo2-finance-consultant-acculturation-change-ai_paris</t>
+          <t>https://nextra.factorial.fr/job_posting/consultant-e-formateur-rice-ia-cdi-ou-freelance-257298</t>
         </is>
       </c>
       <c r="N101" s="39" t="n"/>
@@ -53609,58 +53662,58 @@
       <c r="C102" s="39" t="n"/>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) Formateur(rice) IA</t>
+          <t>Formateur IA H/F</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Nextra-Partners</t>
+          <t>OUIcoding</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>nextra.factorial.fr</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>Attractif + 13e mois + bonus</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>300-500 €/j</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="n"/>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>Hub innovation Data/IA. Concevoir parcours formation, animer formations, conduite du changement. Marseille plus accessible que Paris depuis Biarritz. Fit solide si télétravail 4/5 négociable.</t>
+          <t>Conception parcours pédagogiques sur IA générative, LLMs, acculturation IA. Profil ingénieur-formateur. TJM en dessous du marché. Fit modéré.</t>
         </is>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>https://nextra.factorial.fr/job_posting/consultant-e-formateur-rice-ia-cdi-ou-freelance-257298</t>
+          <t>https://www.free-work.com/fr/tech-it/formateur/job-mission/formateur-ia-h-f</t>
         </is>
       </c>
       <c r="N102" s="39" t="n"/>
       <c r="O102" s="39" t="n"/>
       <c r="P102" s="39" t="n"/>
-      <c r="Q102" s="41" t="n"/>
+      <c r="Q102" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="66" t="inlineStr">
@@ -53672,12 +53725,12 @@
       <c r="C103" s="39" t="n"/>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Formateur IA H/F</t>
+          <t>Ingénieur / Consultant Senior en IA Générative</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>OUIcoding</t>
+          <t>Comet (grand groupe audiovisuel)</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
@@ -53692,28 +53745,32 @@
       </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>Non précisé</t>
+          <t>Partiel (50%)</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>300-500 €/j</t>
-        </is>
-      </c>
-      <c r="K103" s="6" t="n"/>
+          <t>400-560 €/j</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>18 mois</t>
+        </is>
+      </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>Conception parcours pédagogiques sur IA générative, LLMs, acculturation IA. Profil ingénieur-formateur. TJM en dessous du marché. Fit modéré.</t>
+          <t>Piloter expérimentations IA générative. Pédagogie et vulgarisation critères explicites. 50% présentiel contraignant. Fit modéré : angle technique génération images hors profil mais qualités requises = bon fit.</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/formateur/job-mission/formateur-ia-h-f</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant/ingenieur-consultant-senior-en-ia-generative</t>
         </is>
       </c>
       <c r="N103" s="39" t="n"/>
@@ -53735,12 +53792,12 @@
       <c r="C104" s="39" t="n"/>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Ingénieur / Consultant Senior en IA Générative</t>
+          <t>Expert Data SAP &amp; IA Générative</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Comet (grand groupe audiovisuel)</t>
+          <t>Pickmeup (client industrie)</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
@@ -53755,32 +53812,32 @@
       </c>
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Châtillon (92)</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>Partiel (50%)</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>400-560 €/j</t>
+          <t>400-570 €/j</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>18 mois</t>
+          <t>6 mois renouvelable</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>Piloter expérimentations IA générative. Pédagogie et vulgarisation critères explicites. 50% présentiel contraignant. Fit modéré : angle technique génération images hors profil mais qualités requises = bon fit.</t>
+          <t>Valorisation data SAP + développement cas d'usage IA. Volet formation équipes métier intéressant. Mais data engineering Python requis = hors profil principal. Publié 28/06/2026.</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant/ingenieur-consultant-senior-en-ia-generative</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/expert-data-sap-ia-generative-h-f</t>
         </is>
       </c>
       <c r="N104" s="39" t="n"/>
@@ -53788,7 +53845,7 @@
       <c r="P104" s="39" t="n"/>
       <c r="Q104" s="41" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
     </row>
@@ -53802,62 +53859,50 @@
       <c r="C105" s="39" t="n"/>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Expert Data SAP &amp; IA Générative</t>
+          <t>Senior Technical AI Trainer</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Pickmeup (client industrie)</t>
+          <t>Iron Skills</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>LinkedIn France</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
         <is>
-          <t>Châtillon (92)</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J105" s="6" t="inlineStr">
-        <is>
-          <t>400-570 €/j</t>
-        </is>
-      </c>
-      <c r="K105" s="6" t="inlineStr">
-        <is>
-          <t>6 mois renouvelable</t>
-        </is>
-      </c>
+          <t>Non précisé</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="n"/>
+      <c r="K105" s="6" t="n"/>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>Valorisation data SAP + développement cas d'usage IA. Volet formation équipes métier intéressant. Mais data engineering Python requis = hors profil principal. Publié 28/06/2026.</t>
+          <t>Société de formation tech. Profil senior valorisé. "Technical" peut impliquer dev ou simplement expert tech. Contrainte géographique Annecy à négocier. Publié 30/06/2026.</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/expert-data-sap-ia-generative-h-f</t>
+          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
         </is>
       </c>
       <c r="N105" s="39" t="n"/>
       <c r="O105" s="39" t="n"/>
       <c r="P105" s="39" t="n"/>
-      <c r="Q105" s="41" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="Q105" s="41" t="n"/>
     </row>
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="66" t="inlineStr">
@@ -53869,50 +53914,62 @@
       <c r="C106" s="39" t="n"/>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Senior Technical AI Trainer</t>
+          <t>PMO Data &amp; IA</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Iron Skills</t>
+          <t>Unitech Solutions</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn France</t>
+          <t>collective.work</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>Non précisé</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>Non précisé</t>
-        </is>
-      </c>
-      <c r="J106" s="6" t="n"/>
-      <c r="K106" s="6" t="n"/>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>~550 €/j</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>2-4 semaines</t>
+        </is>
+      </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>Société de formation tech. Profil senior valorisé. "Technical" peut impliquer dev ou simplement expert tech. Contrainte géographique Annecy à négocier. Publié 30/06/2026.</t>
+          <t>Mission PMO portefeuille Data/IA, gouvernance, reporting. Urgente démarrage juillet. Mission très courte (2-4 semaines).</t>
         </is>
       </c>
       <c r="M106" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
+          <t>https://www.collective.work/jobs/fr/pmo-data-and-ia-7sy5</t>
         </is>
       </c>
       <c r="N106" s="39" t="n"/>
       <c r="O106" s="39" t="n"/>
       <c r="P106" s="39" t="n"/>
-      <c r="Q106" s="41" t="n"/>
+      <c r="Q106" s="41" t="inlineStr">
+        <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="32" customHeight="1">
       <c r="A107" s="66" t="inlineStr">
@@ -53924,17 +53981,17 @@
       <c r="C107" s="39" t="n"/>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>PMO Data &amp; IA</t>
+          <t>Chef de Projet IA / Transformation Digitale F/H</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Unitech Solutions</t>
+          <t>Celad</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>collective.work</t>
+          <t>workdispo.com</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
@@ -53944,32 +54001,28 @@
       </c>
       <c r="H107" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Noisy-le-Grand</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Partiel (1j/sem)</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>~550 €/j</t>
-        </is>
-      </c>
-      <c r="K107" s="6" t="inlineStr">
-        <is>
-          <t>2-4 semaines</t>
-        </is>
-      </c>
+          <t>550-650 €/j</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="n"/>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>Mission PMO portefeuille Data/IA, gouvernance, reporting. Urgente démarrage juillet. Mission très courte (2-4 semaines).</t>
+          <t>Pilotage projets IA (chatbot, speech-to-text, assistants), gouvernance stakeholders. Compétences alignées mais présentiel 4j/sem depuis Biarritz = rédhibitoire.</t>
         </is>
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
-          <t>https://www.collective.work/jobs/fr/pmo-data-and-ia-7sy5</t>
+          <t>https://www.workdispo.com/job/chef-de-projet-ia-transformation-digitale-f-h</t>
         </is>
       </c>
       <c r="N107" s="39" t="n"/>
@@ -53977,7 +54030,7 @@
       <c r="P107" s="39" t="n"/>
       <c r="Q107" s="41" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
     </row>
@@ -53991,56 +54044,64 @@
       <c r="C108" s="39" t="n"/>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Chef de Projet IA / Transformation Digitale F/H</t>
+          <t>Consultant Formateur Intelligence Artificielle &amp; Management H/F</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Celad</t>
+          <t>PME cabinet de formation BtoB (via Michael Page)</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>workdispo.com</t>
+          <t>Michael Page</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>Noisy-le-Grand</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>Partiel (1j/sem)</t>
+          <t>Présentiel</t>
         </is>
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>550-650 €/j</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K108" s="6" t="n"/>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>Pilotage projets IA (chatbot, speech-to-text, assistants), gouvernance stakeholders. Compétences alignées mais présentiel 4j/sem depuis Biarritz = rédhibitoire.</t>
+          <t>Création de poste. Offre IA + management en contexte formation BtoB. Pas remote = contrainte forte (Biarritz). Profil pertinent mais géo bloquante.</t>
         </is>
       </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
-          <t>https://www.workdispo.com/job/chef-de-projet-ia-transformation-digitale-f-h</t>
-        </is>
-      </c>
-      <c r="N108" s="39" t="n"/>
-      <c r="O108" s="39" t="n"/>
+          <t>https://www.michaelpage.fr/job-detail/consultant-formateur-ia-management-hf/ref/jn-032026-6962869</t>
+        </is>
+      </c>
+      <c r="N108" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS</t>
+        </is>
+      </c>
+      <c r="O108" s="39" t="inlineStr">
+        <is>
+          <t>65-75K€</t>
+        </is>
+      </c>
       <c r="P108" s="39" t="n"/>
       <c r="Q108" s="41" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/03/2026</t>
         </is>
       </c>
     </row>
@@ -54054,17 +54115,17 @@
       <c r="C109" s="39" t="n"/>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Consultant Formateur Intelligence Artificielle &amp; Management H/F</t>
+          <t>Consultant IA Agentique &amp; Transformation des Processus Industriels</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>PME cabinet de formation BtoB (via Michael Page)</t>
+          <t>Signe + (client pharmaceutique)</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Michael Page</t>
+          <t>Free-Work</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
@@ -54074,28 +54135,28 @@
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Suresnes (92)</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>Présentiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>60-65K€/an ou 429-650 €/j</t>
         </is>
       </c>
       <c r="K109" s="6" t="n"/>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>Création de poste. Offre IA + management en contexte formation BtoB. Pas remote = contrainte forte (Biarritz). Profil pertinent mais géo bloquante.</t>
+          <t>Animation ateliers, identification cas usage IA, conduite du changement. RAG/LLM mentionnés = profil plus technique que Gaëtan. Manufacturing/pharma. À évaluer avec discernement.</t>
         </is>
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>https://www.michaelpage.fr/job-detail/consultant-formateur-ia-management-hf/ref/jn-032026-6962869</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant/consultant-ia-agentique-transformation-des-processus-industriels</t>
         </is>
       </c>
       <c r="N109" s="39" t="inlineStr">
@@ -54105,13 +54166,13 @@
       </c>
       <c r="O109" s="39" t="inlineStr">
         <is>
-          <t>65-75K€</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P109" s="39" t="n"/>
       <c r="Q109" s="41" t="inlineStr">
         <is>
-          <t>09/03/2026</t>
+          <t>07/02/2026</t>
         </is>
       </c>
     </row>
@@ -54125,17 +54186,17 @@
       <c r="C110" s="39" t="n"/>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Consultant IA Agentique &amp; Transformation des Processus Industriels</t>
+          <t>Technical Field Trainer AI H/F</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Signe + (client pharmaceutique)</t>
+          <t>nonplusultra</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Free-Work</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
@@ -54145,46 +54206,42 @@
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>Suresnes (92)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Peu probable (field)</t>
         </is>
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>60-65K€/an ou 429-650 €/j</t>
-        </is>
-      </c>
-      <c r="K110" s="6" t="n"/>
+          <t>À négocier</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>Animation ateliers, identification cas usage IA, conduite du changement. RAG/LLM mentionnés = profil plus technique que Gaëtan. Manufacturing/pharma. À évaluer avec discernement.</t>
+          <t>Publié il y a 6 jours. "Field" = terrain client donc probable déplacements ; à évaluer si compatible remote 100%.</t>
         </is>
       </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant/consultant-ia-agentique-transformation-des-processus-industriels</t>
+          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
         </is>
       </c>
       <c r="N110" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS</t>
-        </is>
-      </c>
-      <c r="O110" s="39" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
+          <t>Resume_GaetanFRANCOIS_IA.pdf</t>
+        </is>
+      </c>
+      <c r="O110" s="39" t="n"/>
       <c r="P110" s="39" t="n"/>
-      <c r="Q110" s="41" t="inlineStr">
-        <is>
-          <t>07/02/2026</t>
-        </is>
-      </c>
+      <c r="Q110" s="41" t="n"/>
     </row>
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="66" t="inlineStr">
@@ -54194,67 +54251,63 @@
       </c>
       <c r="B111" s="39" t="n"/>
       <c r="C111" s="39" t="n"/>
-      <c r="D111" s="5" t="inlineStr">
-        <is>
-          <t>Technical Field Trainer AI H/F</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>nonplusultra</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H111" s="6" t="inlineStr">
+      <c r="D111" s="39" t="inlineStr">
+        <is>
+          <t>Scrum Master Senior - IA Générative / SAFe</t>
+        </is>
+      </c>
+      <c r="E111" s="39" t="inlineStr">
+        <is>
+          <t>CELAD</t>
+        </is>
+      </c>
+      <c r="F111" s="39" t="inlineStr">
+        <is>
+          <t>free-work.com</t>
+        </is>
+      </c>
+      <c r="G111" s="39" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H111" s="39" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>Peu probable (field)</t>
-        </is>
-      </c>
-      <c r="J111" s="6" t="inlineStr">
-        <is>
-          <t>À négocier</t>
-        </is>
-      </c>
-      <c r="K111" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="L111" s="5" t="inlineStr">
-        <is>
-          <t>Publié il y a 6 jours. "Field" = terrain client donc probable déplacements ; à évaluer si compatible remote 100%.</t>
-        </is>
-      </c>
-      <c r="M111" s="5" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/jobs/formateur-intelligence-artificielle-emplois-france</t>
+      <c r="I111" s="39" t="inlineStr">
+        <is>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J111" s="39" t="n"/>
+      <c r="K111" s="39" t="n"/>
+      <c r="L111" s="39" t="inlineStr">
+        <is>
+          <t>Scrum Master equipes IA générative, SAFe. Posté 21/07/2026. Profil plus technique que cible.</t>
+        </is>
+      </c>
+      <c r="M111" s="39" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/scrum-master-agile-coach/scrum-master-senior-ia-generative-safe</t>
         </is>
       </c>
       <c r="N111" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_IA.pdf</t>
-        </is>
-      </c>
-      <c r="O111" s="39" t="n"/>
+          <t>Resume_GaetanFRANCOIS_IA.html</t>
+        </is>
+      </c>
+      <c r="O111" s="39" t="inlineStr">
+        <is>
+          <t>500-600€/j</t>
+        </is>
+      </c>
       <c r="P111" s="39" t="n"/>
-      <c r="Q111" s="41" t="n"/>
+      <c r="Q111" s="39" t="n"/>
     </row>
     <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="66" t="inlineStr">
+      <c r="A112" s="77" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -54263,56 +54316,56 @@
       <c r="C112" s="39" t="n"/>
       <c r="D112" s="39" t="inlineStr">
         <is>
-          <t>Scrum Master Senior - IA Générative / SAFe</t>
+          <t>Chef de projet Formation IA (Monaco)</t>
         </is>
       </c>
       <c r="E112" s="39" t="inlineStr">
         <is>
-          <t>CELAD</t>
+          <t>Synergie Technologies</t>
         </is>
       </c>
       <c r="F112" s="39" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G112" s="39" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H112" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Nice/Monaco</t>
         </is>
       </c>
       <c r="I112" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J112" s="39" t="n"/>
-      <c r="K112" s="39" t="n"/>
+          <t>Hybride 2j</t>
+        </is>
+      </c>
+      <c r="J112" s="39" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K112" s="39" t="inlineStr">
+        <is>
+          <t>3 ans renouv.</t>
+        </is>
+      </c>
       <c r="L112" s="39" t="inlineStr">
         <is>
-          <t>Scrum Master equipes IA générative, SAFe. Posté 21/07/2026. Profil plus technique que cible.</t>
+          <t>Ingénierie pédagogique IA ; CDI Nice/Monaco ; nationalité EU requis ; 02/07/2026</t>
         </is>
       </c>
       <c r="M112" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/scrum-master-agile-coach/scrum-master-senior-ia-generative-safe</t>
-        </is>
-      </c>
-      <c r="N112" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_IA.html</t>
-        </is>
-      </c>
-      <c r="O112" s="39" t="inlineStr">
-        <is>
-          <t>500-600€/j</t>
-        </is>
-      </c>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-formation-ia-monaco</t>
+        </is>
+      </c>
+      <c r="N112" s="39" t="n"/>
+      <c r="O112" s="39" t="n"/>
       <c r="P112" s="39" t="n"/>
       <c r="Q112" s="39" t="n"/>
     </row>
@@ -54326,12 +54379,12 @@
       <c r="C113" s="39" t="n"/>
       <c r="D113" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet Formation IA (Monaco)</t>
+          <t>Product Owner Socle IA &amp; Agentique</t>
         </is>
       </c>
       <c r="E113" s="39" t="inlineStr">
         <is>
-          <t>Synergie Technologies</t>
+          <t>WorldWide People</t>
         </is>
       </c>
       <c r="F113" s="39" t="inlineStr">
@@ -54341,37 +54394,37 @@
       </c>
       <c r="G113" s="39" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H113" s="39" t="inlineStr">
         <is>
-          <t>Nice/Monaco</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I113" s="39" t="inlineStr">
         <is>
-          <t>Hybride 2j</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J113" s="39" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>400€/j</t>
         </is>
       </c>
       <c r="K113" s="39" t="inlineStr">
         <is>
-          <t>3 ans renouv.</t>
+          <t>12 mois renouv.</t>
         </is>
       </c>
       <c r="L113" s="39" t="inlineStr">
         <is>
-          <t>Ingénierie pédagogique IA ; CDI Nice/Monaco ; nationalité EU requis ; 02/07/2026</t>
+          <t>ML platform + agentic IA ; trop technique (MLOps) ; 07/07/2026</t>
         </is>
       </c>
       <c r="M113" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-formation-ia-monaco</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/product-owner/100960-product-owner-technique-socle-ia-et-agentique-ia-gen-de-la-plateforme-data-ia-nantes-1</t>
         </is>
       </c>
       <c r="N113" s="39" t="n"/>
@@ -54380,7 +54433,7 @@
       <c r="Q113" s="39" t="n"/>
     </row>
     <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="77" t="inlineStr">
+      <c r="A114" s="66" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -54389,75 +54442,79 @@
       <c r="C114" s="39" t="n"/>
       <c r="D114" s="39" t="inlineStr">
         <is>
-          <t>Product Owner Socle IA &amp; Agentique</t>
+          <t>Consultant indépendant en intelligence artificielle pour PME</t>
         </is>
       </c>
       <c r="E114" s="39" t="inlineStr">
         <is>
-          <t>WorldWide People</t>
+          <t>mission-freelances.fr (client non identifié)</t>
         </is>
       </c>
       <c r="F114" s="39" t="inlineStr">
         <is>
-          <t>free-work</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G114" s="39" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H114" s="39" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Gironde</t>
         </is>
       </c>
       <c r="I114" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J114" s="39" t="inlineStr">
-        <is>
-          <t>400€/j</t>
-        </is>
-      </c>
-      <c r="K114" s="39" t="inlineStr">
-        <is>
-          <t>12 mois renouv.</t>
-        </is>
-      </c>
+          <t>Non précisé</t>
+        </is>
+      </c>
+      <c r="J114" s="39" t="n"/>
+      <c r="K114" s="39" t="n"/>
       <c r="L114" s="39" t="inlineStr">
         <is>
-          <t>ML platform + agentic IA ; trop technique (MLOps) ; 07/07/2026</t>
+          <t>Proximité géographique Sud-Ouest intéressante (Gironde proche d'Anglet) ; offre peu détaillée, à creuser manuellement.</t>
         </is>
       </c>
       <c r="M114" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/product-owner/100960-product-owner-technique-socle-ia-et-agentique-ia-gen-de-la-plateforme-data-ia-nantes-1</t>
-        </is>
-      </c>
-      <c r="N114" s="39" t="n"/>
-      <c r="O114" s="39" t="n"/>
+          <t>https://mission-freelances.fr/missions/</t>
+        </is>
+      </c>
+      <c r="N114" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_IA.html</t>
+        </is>
+      </c>
+      <c r="O114" s="39" t="inlineStr">
+        <is>
+          <t>500-600€/j</t>
+        </is>
+      </c>
       <c r="P114" s="39" t="n"/>
-      <c r="Q114" s="39" t="n"/>
+      <c r="Q114" s="41" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="66" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
+      <c r="A115" s="61" t="inlineStr">
+        <is>
+          <t>⭐</t>
         </is>
       </c>
       <c r="B115" s="39" t="n"/>
       <c r="C115" s="39" t="n"/>
       <c r="D115" s="39" t="inlineStr">
         <is>
-          <t>Consultant indépendant en intelligence artificielle pour PME</t>
+          <t>Formateur / Formatrice en Intelligence Artificielle Générative</t>
         </is>
       </c>
       <c r="E115" s="39" t="inlineStr">
         <is>
-          <t>mission-freelances.fr (client non identifié)</t>
+          <t>Client anonyme</t>
         </is>
       </c>
       <c r="F115" s="39" t="inlineStr">
@@ -54472,42 +54529,30 @@
       </c>
       <c r="H115" s="39" t="inlineStr">
         <is>
-          <t>Gironde</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I115" s="39" t="inlineStr">
         <is>
-          <t>Non précisé</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J115" s="39" t="n"/>
       <c r="K115" s="39" t="n"/>
       <c r="L115" s="39" t="inlineStr">
         <is>
-          <t>Proximité géographique Sud-Ouest intéressante (Gironde proche d'Anglet) ; offre peu détaillée, à creuser manuellement.</t>
+          <t>Formation certifiante IA générative (IA Act, RGPD). Certification RS6776 souhaitée. NDA requis. Présentiel IDF potentiellement requis. Bon point d'entrée pour se référencer comme formateur IA.</t>
         </is>
       </c>
       <c r="M115" s="39" t="inlineStr">
         <is>
-          <t>https://mission-freelances.fr/missions/</t>
-        </is>
-      </c>
-      <c r="N115" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_IA.html</t>
-        </is>
-      </c>
-      <c r="O115" s="39" t="inlineStr">
-        <is>
-          <t>500-600€/j</t>
-        </is>
-      </c>
+          <t>https://www.mission-freelances.fr/r/a5471a52</t>
+        </is>
+      </c>
+      <c r="N115" s="39" t="n"/>
+      <c r="O115" s="39" t="n"/>
       <c r="P115" s="39" t="n"/>
-      <c r="Q115" s="41" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
+      <c r="Q115" s="39" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="61" t="inlineStr">
@@ -54519,27 +54564,27 @@
       <c r="C116" s="39" t="n"/>
       <c r="D116" s="39" t="inlineStr">
         <is>
-          <t>Formateur / Formatrice en Intelligence Artificielle Générative</t>
+          <t>Formateur / Formatrice en Intelligence Artificielle Générative (21h)</t>
         </is>
       </c>
       <c r="E116" s="39" t="inlineStr">
         <is>
-          <t>Client anonyme</t>
+          <t>Walter Learning</t>
         </is>
       </c>
       <c r="F116" s="39" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>werecruit.io</t>
         </is>
       </c>
       <c r="G116" s="39" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDD</t>
         </is>
       </c>
       <c r="H116" s="39" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>Paris (tournages Marseille)</t>
         </is>
       </c>
       <c r="I116" s="39" t="inlineStr">
@@ -54548,24 +54593,32 @@
         </is>
       </c>
       <c r="J116" s="39" t="n"/>
-      <c r="K116" s="39" t="n"/>
+      <c r="K116" s="39" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
       <c r="L116" s="39" t="inlineStr">
         <is>
-          <t>Formation certifiante IA générative (IA Act, RGPD). Certification RS6776 souhaitée. NDA requis. Présentiel IDF potentiellement requis. Bon point d'entrée pour se référencer comme formateur IA.</t>
+          <t>Mission ponctuelle 21h. Concevoir et animer formation certifiante IA générative. NDA + SIRET requis. Bon point d'entrée pour se faire référencer formateur IA, peu lucratif.</t>
         </is>
       </c>
       <c r="M116" s="39" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/r/a5471a52</t>
+          <t>https://careers.werecruit.io/fr/walter-learning/offres/formateur---intelligence-artificielle-generative-3cde70</t>
         </is>
       </c>
       <c r="N116" s="39" t="n"/>
       <c r="O116" s="39" t="n"/>
       <c r="P116" s="39" t="n"/>
-      <c r="Q116" s="39" t="n"/>
+      <c r="Q116" s="41" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="61" t="inlineStr">
+      <c r="A117" s="59" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
@@ -54574,27 +54627,27 @@
       <c r="C117" s="39" t="n"/>
       <c r="D117" s="39" t="inlineStr">
         <is>
-          <t>Formateur / Formatrice en Intelligence Artificielle Générative (21h)</t>
+          <t>Tech Lead IA Agentique H/F</t>
         </is>
       </c>
       <c r="E117" s="39" t="inlineStr">
         <is>
-          <t>Walter Learning</t>
+          <t>Signe +</t>
         </is>
       </c>
       <c r="F117" s="39" t="inlineStr">
         <is>
-          <t>werecruit.io</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G117" s="39" t="inlineStr">
         <is>
-          <t>CDD</t>
+          <t>CDI/Freelance</t>
         </is>
       </c>
       <c r="H117" s="39" t="inlineStr">
         <is>
-          <t>Paris (tournages Marseille)</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I117" s="39" t="inlineStr">
@@ -54602,30 +54655,28 @@
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J117" s="39" t="n"/>
+      <c r="J117" s="39" t="inlineStr">
+        <is>
+          <t>286-450€/j</t>
+        </is>
+      </c>
       <c r="K117" s="39" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>24 mois</t>
         </is>
       </c>
       <c r="L117" s="39" t="inlineStr">
         <is>
-          <t>Mission ponctuelle 21h. Concevoir et animer formation certifiante IA générative. NDA + SIRET requis. Bon point d'entrée pour se faire référencer formateur IA, peu lucratif.</t>
+          <t>Dev (LangChain, GitLab CI) — hors profil ; 05/07/2026</t>
         </is>
       </c>
       <c r="M117" s="39" t="inlineStr">
         <is>
-          <t>https://careers.werecruit.io/fr/walter-learning/offres/formateur---intelligence-artificielle-generative-3cde70</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/lead-developer/tech-lead-ia-agentique-h-f</t>
         </is>
       </c>
       <c r="N117" s="39" t="n"/>
       <c r="O117" s="39" t="n"/>
-      <c r="P117" s="39" t="n"/>
-      <c r="Q117" s="41" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="59" t="inlineStr">
@@ -54637,7 +54688,7 @@
       <c r="C118" s="39" t="n"/>
       <c r="D118" s="39" t="inlineStr">
         <is>
-          <t>Tech Lead IA Agentique H/F</t>
+          <t>Consultant IA Agentique Processus Industriels</t>
         </is>
       </c>
       <c r="E118" s="39" t="inlineStr">
@@ -54657,17 +54708,17 @@
       </c>
       <c r="H118" s="39" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Suresnes (92)</t>
         </is>
       </c>
       <c r="I118" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J118" s="39" t="inlineStr">
         <is>
-          <t>286-450€/j</t>
+          <t>429-650€/j</t>
         </is>
       </c>
       <c r="K118" s="39" t="inlineStr">
@@ -54677,12 +54728,12 @@
       </c>
       <c r="L118" s="39" t="inlineStr">
         <is>
-          <t>Dev (LangChain, GitLab CI) — hors profil ; 05/07/2026</t>
+          <t>Manufacturing/Supply Chain + RAG — hors profil ; 02/07/2026</t>
         </is>
       </c>
       <c r="M118" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/lead-developer/tech-lead-ia-agentique-h-f</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant/consultant-ia-agentique-transformation-des-processus-industriels</t>
         </is>
       </c>
       <c r="N118" s="39" t="n"/>
@@ -54698,7 +54749,7 @@
       <c r="C119" s="39" t="n"/>
       <c r="D119" s="39" t="inlineStr">
         <is>
-          <t>Consultant IA Agentique Processus Industriels</t>
+          <t>Développeur IA Agentique Senior H/F</t>
         </is>
       </c>
       <c r="E119" s="39" t="inlineStr">
@@ -54718,17 +54769,17 @@
       </c>
       <c r="H119" s="39" t="inlineStr">
         <is>
-          <t>Suresnes (92)</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I119" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J119" s="39" t="inlineStr">
         <is>
-          <t>429-650€/j</t>
+          <t>286-450€/j</t>
         </is>
       </c>
       <c r="K119" s="39" t="inlineStr">
@@ -54738,79 +54789,18 @@
       </c>
       <c r="L119" s="39" t="inlineStr">
         <is>
-          <t>Manufacturing/Supply Chain + RAG — hors profil ; 02/07/2026</t>
+          <t>Dev RAG/LLM/CI-CD — hors profil ; 29/06/2026</t>
         </is>
       </c>
       <c r="M119" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant/consultant-ia-agentique-transformation-des-processus-industriels</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/developpeur-autre-langage-cobol-perl-vba-ruby-shell/developpeur-ia-agentique-senior-h-f</t>
         </is>
       </c>
       <c r="N119" s="39" t="n"/>
       <c r="O119" s="39" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="59" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="B120" s="39" t="n"/>
-      <c r="C120" s="39" t="n"/>
-      <c r="D120" s="39" t="inlineStr">
-        <is>
-          <t>Développeur IA Agentique Senior H/F</t>
-        </is>
-      </c>
-      <c r="E120" s="39" t="inlineStr">
-        <is>
-          <t>Signe +</t>
-        </is>
-      </c>
-      <c r="F120" s="39" t="inlineStr">
-        <is>
-          <t>free-work</t>
-        </is>
-      </c>
-      <c r="G120" s="39" t="inlineStr">
-        <is>
-          <t>CDI/Freelance</t>
-        </is>
-      </c>
-      <c r="H120" s="39" t="inlineStr">
-        <is>
-          <t>Nantes</t>
-        </is>
-      </c>
-      <c r="I120" s="39" t="inlineStr">
-        <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J120" s="39" t="inlineStr">
-        <is>
-          <t>286-450€/j</t>
-        </is>
-      </c>
-      <c r="K120" s="39" t="inlineStr">
-        <is>
-          <t>24 mois</t>
-        </is>
-      </c>
-      <c r="L120" s="39" t="inlineStr">
-        <is>
-          <t>Dev RAG/LLM/CI-CD — hors profil ; 29/06/2026</t>
-        </is>
-      </c>
-      <c r="M120" s="39" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/developpeur-autre-langage-cobol-perl-vba-ruby-shell/developpeur-ia-agentique-senior-h-f</t>
-        </is>
-      </c>
-      <c r="N120" s="39" t="n"/>
-      <c r="O120" s="39" t="n"/>
-      <c r="P120" s="39" t="n"/>
-      <c r="Q120" s="39" t="n"/>
+      <c r="P119" s="39" t="n"/>
+      <c r="Q119" s="39" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O41">

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -31316,8 +31316,7 @@
     </filterColumn>
   </autoFilter>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -58063,7 +58062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q91"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="16" max="17"/>
@@ -58597,29 +58596,29 @@
       </c>
     </row>
     <row r="8" ht="380" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Refusé</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="A8" s="88" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Customer Success Manager</t>
+          <t>SIRH Solution Expert</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>SAP Taulia</t>
+          <t>Biogroup</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -58629,45 +58628,51 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Londres (UK)</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>85-110 K€</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Fit fort — 5+ ans requis, projets mondiaux (L'Oréal 40 pays), QBR, escalades. Working capital/supply chain finance angle (lien OnePayroll L'Oréal). CV + LM Taulia déjà prêts. Question visa UK à clarifier. Fourchette salaire 85-110k€ exactement visée.</t>
+          <t>Biogroup (réseau de laboratoires de biologie médicale) recrute un SIRH Solution Expert. Candidature déposée via le portail carrière Cornerstone OnDemand du groupe, poste également relayé sur LinkedIn.</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4421991103/</t>
+          <t>https://biogroup.csod.com/ux/ats/careersite/1/home?c=biogroup&amp;lang=fr-FR#/requisition/272&amp;source=linkedin</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_Taulia_EN.pdf</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>100 K€</t>
-        </is>
-      </c>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="Q8" s="41" t="n"/>
     </row>
     <row r="9" ht="320" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -58677,7 +58682,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Expiré</t>
+          <t>Refusé</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -58687,17 +58692,17 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Solutions Consultant, HRIS | France</t>
+          <t>Customer Success Manager</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>SAP Taulia</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>deel.com/careers / builtin.com</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -58707,50 +58712,50 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Londres (UK)</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Full remote</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>85-110 K€</t>
         </is>
       </c>
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Pré-sales HRIS pour plateforme RH globale Deel (150+ pays), démonstrations SF-like, 2+ ans selling HR tech, FR+EN — FIT PARFAIT. Vérifier statut actif sur deel.com/careers ou jobs.ashbyhq.com/deel</t>
+          <t>Fit fort — 5+ ans requis, projets mondiaux (L'Oréal 40 pays), QBR, escalades. Working capital/supply chain finance angle (lien OnePayroll L'Oréal). CV + LM Taulia déjà prêts. Question visa UK à clarifier. Fourchette salaire 85-110k€ exactement visée.</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>https://www.deel.com/careers/</t>
+          <t>https://www.linkedin.com/jobs/view/4421991103/</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>CV_GaetanFRANCOIS_Taulia_EN.pdf</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>85 K€</t>
+          <t>100 K€</t>
         </is>
       </c>
     </row>
     <row r="10" ht="128" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Hors profil</t>
+          <t>Expiré</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -58760,27 +58765,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>People Operations Specialist</t>
+          <t>Solutions Consultant, HRIS | France</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Mercor</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>deel.com/careers / builtin.com</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>100% Remote</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -58790,18 +58795,18 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>60-80 $/h</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Bon match — HRIS (SAP SF ✓, Workday, Oracle), Fortune 500 ✓, multi-pays ✓</t>
+          <t>Pré-sales HRIS pour plateforme RH globale Deel (150+ pays), démonstrations SF-like, 2+ ans selling HR tech, FR+EN — FIT PARFAIT. Vérifier statut actif sur deel.com/careers ou jobs.ashbyhq.com/deel</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4428131075/</t>
+          <t>https://www.deel.com/careers/</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -58811,7 +58816,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>75 $/h</t>
+          <t>85 K€</t>
         </is>
       </c>
     </row>
@@ -58833,144 +58838,140 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>People Operations Specialist</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Mercor</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>100% Remote</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>60-80 $/h</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Bon match — HRIS (SAP SF ✓, Workday, Oracle), Fortune 500 ✓, multi-pays ✓</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4428131075/</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>75 $/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="176" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Hors profil</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
           <t>Expert Intégration SAP SuccessFactors BTP</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>LINKWAY</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>12 mois</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Projet bancaire, intégration SF + SAP BTP — full remote, anglais courant requis</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/expert-integration-sap-successfactors-btp</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>750 €/j</t>
         </is>
       </c>
-      <c r="Q11" s="41" t="inlineStr">
+      <c r="Q12" s="41" t="inlineStr">
         <is>
           <t>06/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="176" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>salaire fixe 40k</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Customer Success Manager</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>AssessFirst</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>welcometothejungle.com</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Full remote</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>12 mois</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>HR Tech, full remote, renouvellement / adoption produit — profil CSM Senior</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/fr/companies/assessfirst/jobs/customer-success-manager_paris_ASSES_M4x97o8</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>70 K€</t>
         </is>
       </c>
     </row>
@@ -58982,7 +58983,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>30% voyage</t>
+          <t>salaire fixe 40k</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -58992,17 +58993,17 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>SAP Consultant OR Trainer (Any module)</t>
+          <t>Customer Success Manager</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Eursap</t>
+          <t>AssessFirst</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>eursap.eu</t>
+          <t>welcometothejungle.com</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -59012,7 +59013,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -59022,32 +59023,32 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>80-100 K€ + equity</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>3 mois renouvelable</t>
+          <t>12 mois</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>French language, remote, consultant ou formateur SAP — bon fit profil formateur/consultant</t>
+          <t>HR Tech, full remote, renouvellement / adoption produit — profil CSM Senior</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>https://eursap.eu/jobs/sap-consultant-or-trainer-any-module-34811-remote</t>
+          <t>https://www.welcometothejungle.com/fr/companies/assessfirst/jobs/customer-success-manager_paris_ASSES_M4x97o8</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>90 K€</t>
+          <t>70 K€</t>
         </is>
       </c>
     </row>
@@ -59059,7 +59060,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>allemand</t>
+          <t>30% voyage</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -59069,17 +59070,17 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Senior SAP SF Inhouse Consultant – Integration EC</t>
+          <t>SAP Consultant OR Trainer (Any module)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Hornbach Baumarkt AG</t>
+          <t>Eursap</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>indeed.fr</t>
+          <t>eursap.eu</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -59089,7 +59090,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -59099,18 +59100,22 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="n"/>
+          <t>80-100 K€ + equity</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>3 mois renouvelable</t>
+        </is>
+      </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Remote, avancement technique des systèmes RH via SuccessFactors EC</t>
+          <t>French language, remote, consultant ou formateur SAP — bon fit profil formateur/consultant</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>https://karriere.hornbach.de/technologie/stellenangebot/remote-senior-sap-sf-inhouse-consul/bbdff4bc-96bb-4498-b529-c61a335ca3db</t>
+          <t>https://eursap.eu/jobs/sap-consultant-or-trainer-any-module-34811-remote</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -59120,7 +59125,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>80 K€</t>
+          <t>90 K€</t>
         </is>
       </c>
     </row>
@@ -59132,204 +59137,204 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
+          <t>allemand</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Senior SAP SF Inhouse Consultant – Integration EC</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Hornbach Baumarkt AG</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>indeed.fr</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>Remote, avancement technique des systèmes RH via SuccessFactors EC</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>https://karriere.hornbach.de/technologie/stellenangebot/remote-senior-sap-sf-inhouse-consul/bbdff4bc-96bb-4498-b529-c61a335ca3db</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>80 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="160" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
           <t>fermé</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Customer Success Manager SaaS</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Mobility Work (GMAO)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>3 mois</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>CSM industriel SaaS, full remote, FR+EN+ES requis - Biarritz compatible</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/customer-success-manager-saas-full-remote-at-mobility-work-gmao-4344455726</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.pdf</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>65 K€</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="160" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="17" ht="128" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Éliminé</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Software Implementation Consultant</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Avature</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>Non (80% déplacements)</t>
         </is>
       </c>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>HR software implémentation, bon profil fonctionnel, mais 80% sur site client = incompatible remote</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4400989929/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="128" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Hors profil</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>SAP HCM Consultant – French Payroll</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Movement Group</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>movementgroup.uk</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>Full remote</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+      <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Fit parfait — SAP HCM paie française, remote</t>
+          <t>HR software implémentation, bon profil fonctionnel, mais 80% sur site client = incompatible remote</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>90 K€</t>
+          <t>https://www.linkedin.com/jobs/view/4400989929/</t>
         </is>
       </c>
     </row>
@@ -59351,67 +59356,58 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Directeur de Programme SIRH Senior</t>
+          <t>SAP HCM Consultant – French Payroll</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>LeHibou</t>
+          <t>Movement Group</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>movementgroup.uk</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>n.p.</t>
+          <t>Full remote</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>650-780 €/j</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>18 mois</t>
-        </is>
-      </c>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="n"/>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Transformation RH globale, gouvernance, budget — profil senior idéal</t>
+          <t>Fit parfait — SAP HCM paie française, remote</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
+          <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>750 €/j</t>
-        </is>
-      </c>
-      <c r="Q18" s="41" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
+          <t>90 K€</t>
         </is>
       </c>
     </row>
@@ -59431,59 +59427,69 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Data Consultant HCM / Workday</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Jobgether</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Directeur de Programme SIRH Senior</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>LeHibou</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>free-work.com</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>100% Remote</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Full remote</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>SQL avancé, ETL, migration Workday — trop technique, mauvais stack</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4425836016/</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>n.p.</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>650-780 €/j</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>18 mois</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Transformation RH globale, gouvernance, budget — profil senior idéal</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>650 €/j</t>
+          <t>750 €/j</t>
+        </is>
+      </c>
+      <c r="Q19" s="41" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -59495,7 +59501,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Non pertinent</t>
+          <t>Hors profil</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -59505,12 +59511,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Management Consultant (évaluation tâches IA)</t>
+          <t>Data Consultant HCM / Workday</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Call For Referral</t>
+          <t>Jobgether</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -59525,27 +59531,37 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Londres, UK</t>
+          <t>100% Remote</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Full remote</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>$90-200/h</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Évaluation de tâches IA pour entraînement modèles - pas pertinent pour le profil</t>
+          <t>SQL avancé, ETL, migration Workday — trop technique, mauvais stack</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4414336302/</t>
+          <t>https://www.linkedin.com/jobs/view/4425836016/</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>650 €/j</t>
         </is>
       </c>
     </row>
@@ -59567,119 +59583,104 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Management Consultant (évaluation tâches IA)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Call For Referral</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Londres, UK</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>$90-200/h</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Évaluation de tâches IA pour entraînement modèles - pas pertinent pour le profil</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4414336302/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="176" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Non pertinent</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>Consultant Expérimenté HR Transformation - SAP SuccessFactors</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>La Défense</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Entry level (1-3 ans) - trop junior pour le profil 15 ans XP</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426166097/</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="176" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>no remote</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SIRH SuccessFactors</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>freelance-informatique.fr</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>Issy-les-Moulineaux (92)</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>n.p.</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>9 mois</t>
-        </is>
-      </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SIRH SF, durée intéressante, proche Paris</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>https://www.freelance-informatique.fr/mission-chef-de-projet-technico-fonctionnel-h-f-260603C004</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>700 €/j</t>
         </is>
       </c>
     </row>
@@ -59691,228 +59692,223 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
+          <t>no remote</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SIRH SuccessFactors</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>freelance-informatique.fr</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Issy-les-Moulineaux (92)</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>n.p.</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>9 mois</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SIRH SF, durée intéressante, proche Paris</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.freelance-informatique.fr/mission-chef-de-projet-technico-fonctionnel-h-f-260603C004</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>700 €/j</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="409.5" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
           <t>pourvu</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Implementation Consultant</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Deel</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>builtin.com/company/deel/jobs</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>Remote (EMEA probable)</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>Implémentation plateforme HRIS/paie globale Deel, onboarding clients, configuration, formation — 3+ ans exp SaaS/HRIS/paie. Posté il y a 12 jours (19/06/2026)</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>https://builtin.com/job/implementation-consultant/8081628</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>80 K€</t>
-        </is>
-      </c>
-      <c r="Q23" s="41" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="409.5" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>postulé</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>SAP Consultant / Trainer (Any Module) – IA + S/4HANA</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Startup IA/SAP (via Eursap)</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Eursap.eu</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>Full remote UE (30% déplacements Europe/mois)</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>80 000 - 100 000 € + stock-options jusqu'à 120K€</t>
         </is>
       </c>
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="5" t="inlineStr">
         <is>
+          <t>Implémentation plateforme HRIS/paie globale Deel, onboarding clients, configuration, formation — 3+ ans exp SaaS/HRIS/paie. Posté il y a 12 jours (19/06/2026)</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/implementation-consultant/8081628</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>80 K€</t>
+        </is>
+      </c>
+      <c r="Q24" s="41" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="192" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>postulé</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>SAP Consultant / Trainer (Any Module) – IA + S/4HANA</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Startup IA/SAP (via Eursap)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Eursap.eu</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Full remote UE (30% déplacements Europe/mois)</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>80 000 - 100 000 € + stock-options jusqu'à 120K€</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
           <t>Startup US pionnière IA + SAP S/4HANA, 1er collaborateur européen. Rôle hybride consultant/formateur : intégrer IA dans projets SAP S/4HANA, former partenaires intégrateurs, retours engineering US. Tous modules acceptés (HCM inclus). 5+ ans SAP requis. Salaire excellent + equity. Profil formateur SAP de Gaëtan = fit très fort. Démarrage août 2026.</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>https://eursap.eu/jobs/sap-consultant-or-trainer-any-module-34811-remote</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>95 K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="192" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>postulé</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SAP SuccessFactors (H/F)</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>HR Path</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn / HR Path careers</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Paris La Défense (92)</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Télétravail + déplacements intl</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>SF multi-modules, 2+ ans, anglais requis, projets intl, cabinet conseil RH mondial 22 pays</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>60 K€</t>
-        </is>
-      </c>
-      <c r="Q25" s="41" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -59934,17 +59930,17 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Consultant Confirmé SIRH - SAP HR H/F</t>
+          <t>Consultant SAP SuccessFactors (H/F)</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>ACT-ON HRIS</t>
+          <t>HR Path</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn / HR Path careers</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -59954,12 +59950,12 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Neuilly-sur-Seine (92)</t>
+          <t>Paris La Défense (92)</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>Télétravail flexible</t>
+          <t>Télétravail + déplacements intl</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
@@ -59967,15 +59963,19 @@
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K26" s="6" t="n"/>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>SAP HR multi-modules (paramétrage, déploiement, recette), grands groupes, 3+ ans exp — différent du poste SF déjà en base</t>
+          <t>SF multi-modules, 2+ ans, anglais requis, projets intl, cabinet conseil RH mondial 22 pays</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4342380005</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -59985,7 +59985,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>55 K€</t>
+          <t>60 K€</t>
+        </is>
+      </c>
+      <c r="Q26" s="41" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -60007,17 +60012,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Solutions Engineer, Deel HR | DACH</t>
+          <t>Consultant Confirmé SIRH - SAP HR H/F</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>ACT-ON HRIS</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>deel.com/careers</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -60027,183 +60032,183 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>DACH (AT/DE/CH)</t>
+          <t>Neuilly-sur-Seine (92)</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Remote (à confirmer depuis FR)</t>
+          <t>Télétravail flexible</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>$95,000-$170,000 USD</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K27" s="6" t="n"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
+          <t>SAP HR multi-modules (paramétrage, déploiement, recette), grands groupes, 3+ ans exp — différent du poste SF déjà en base</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/4342380005</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>55 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="112" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>postulé</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Solutions Engineer, Deel HR | DACH</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Deel</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>deel.com/careers</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>DACH (AT/DE/CH)</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Remote (à confirmer depuis FR)</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>$95,000-$170,000 USD</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
           <t>Pre-sales HRIS Deel HR, angle L'Oréal client grand compte = différenciant, multilingual bonus, allemand limité peut freiner, remote depuis FR à confirmer</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>https://www.deel.com/careers/job/?ats_id=0e920f65-a385-47d8-9129-58386b2722f9</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM_EN</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>95-110K€</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="112" customHeight="1">
-      <c r="A28" s="21" t="inlineStr">
+    <row r="29" ht="208" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>pourvu</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Enablement Trainer</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Hostaway</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>100% Remote Europe</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="J28" s="6" t="inlineStr">
+      <c r="J29" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K28" s="6" t="inlineStr">
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>Formation &amp; coaching EMEA ✓ — loin du SAP/HR (hospitality SaaS)</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426695837/</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>à créer</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>60 K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="208" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>no remote</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Consultant(e) Stratégie et Transformation RH F/H</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>ACT-ON STRATEGY</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>Neuilly-sur-Seine</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>sur site</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Accompagnement transformation RH, conduite du changement, SF/Workday/Talentsoft, 2-5 ans — profil junior/mid sur le fond</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/jobs/view/4342420186</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -60220,7 +60225,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>postulé</t>
+          <t>no remote</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -60230,12 +60235,12 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Senior HRIS Analyst – SAP SuccessFactors Recruiting &amp; Onboarding</t>
+          <t>Consultant(e) Stratégie et Transformation RH F/H</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Foundever</t>
+          <t>ACT-ON STRATEGY</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -60250,50 +60255,50 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Neuilly-sur-Seine</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
+          <t>sur site</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>£75 000</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>170k employés, 40+ pays — scale L'Oréal comparable. SF Recruiting &amp; Onboarding global, remote. Lacune : 3+ ans admin SF requis (pas SAP HCM). UK basé mais full remote.</t>
+          <t>Accompagnement transformation RH, conduite du changement, SF/Workday/Talentsoft, 2-5 ans — profil junior/mid sur le fond</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4426322458</t>
+          <t>https://fr.linkedin.com/jobs/view/4342420186</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>80 K€</t>
+          <t>60 K€</t>
         </is>
       </c>
     </row>
     <row r="31" ht="176" customHeight="1">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>out of scope</t>
+          <t>postulé</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -60303,12 +60308,12 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Solutions Consultant (French Speaking)</t>
+          <t>Senior HRIS Analyst – SAP SuccessFactors Recruiting &amp; Onboarding</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Synthesia</t>
+          <t>Foundever</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -60323,50 +60328,50 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>Paris / Europe</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Full remote</t>
+          <t>100% remote</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>£75 000</t>
         </is>
       </c>
       <c r="K31" s="6" t="n"/>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Pre/post-sales hybride, plateforme vidéo IA. French speaker, ML background asset. Hors périmètre SAP/SIRH.</t>
+          <t>170k employés, 40+ pays — scale L'Oréal comparable. SF Recruiting &amp; Onboarding global, remote. Lacune : 3+ ans admin SF requis (pas SAP HCM). UK basé mais full remote.</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4404547243/</t>
+          <t>https://www.linkedin.com/jobs/view/4426322458</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>80-95 K€</t>
+          <t>80 K€</t>
         </is>
       </c>
     </row>
     <row r="32" ht="160" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>postulé</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -60376,12 +60381,12 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Consultant SIRH Senior</t>
+          <t>Solutions Consultant (French Speaking)</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>SIGMA-HR</t>
+          <t>Synthesia</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -60396,34 +60401,38 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris / Europe</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="n"/>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>SIRH Senior CDI, implémentation logiciel proprio (pas SAP) - moins valorisant mais fit fonctionnel correct</t>
+          <t>Pre/post-sales hybride, plateforme vidéo IA. French speaker, ML background asset. Hors périmètre SAP/SIRH.</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4408767527/</t>
+          <t>https://www.linkedin.com/jobs/view/4404547243/</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
+          <t>Resume_GaetanFRANCOIS.pdf</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>80-95 K€</t>
         </is>
       </c>
     </row>
@@ -60435,7 +60444,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>pourvu</t>
+          <t>postulé</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -60445,17 +60454,17 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Pre-Sales Consultant</t>
+          <t>Consultant SIRH Senior</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Agatha Inc.</t>
+          <t>SIGMA-HR</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -60465,38 +60474,34 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Lyon / Full Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>Agatha = éditeur logiciel Life Sciences (essais cliniques, 400+ entreprises, 60k users, Boston/Tokyo/Lyon). Pre-Sales : démos produit, accompagnement avant-vente. Full remote possible. Secteur Life Sciences ≠ HR Tech mais le rôle pre-sales est exactement dans la cible compétences. Anglais fort requis.</t>
+          <t>SIRH Senior CDI, implémentation logiciel proprio (pas SAP) - moins valorisant mais fit fonctionnel correct</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/agatha-inc/jobs/pre-sales-consultant_lyon</t>
+          <t>https://www.linkedin.com/jobs/view/4408767527/</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>85 K€</t>
+          <t>70-80K€</t>
         </is>
       </c>
     </row>
@@ -60516,49 +60521,50 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Remote HRIS IT Project Manager Europe</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>JELD-WEN</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>LinkedIn / Jobrapido</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>CDD / Freelance</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Remote France ou UK</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Pre-Sales Consultant</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Agatha Inc.</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Lyon / Full Remote</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>JELD-WEN = fabricant mondial portes/fenêtres (NYSE). HRIS IT PM Europe, déploiement UKG Pro WFM/Kronos, projets IT multi-sites Europe, bilingue FR/EN. Remote depuis France. Publié février 2026 — à vérifier si toujours ouvert.</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>https://talents.studysmarter.co.uk/companies/jeld-wen-uk/remote-hris-it-project-manager-europe-en-fr-27061545/</t>
+      <c r="K34" s="6" t="n"/>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Agatha = éditeur logiciel Life Sciences (essais cliniques, 400+ entreprises, 60k users, Boston/Tokyo/Lyon). Pre-Sales : démos produit, accompagnement avant-vente. Full remote possible. Secteur Life Sciences ≠ HR Tech mais le rôle pre-sales est exactement dans la cible compétences. Anglais fort requis.</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/agatha-inc/jobs/pre-sales-consultant_lyon</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -60568,7 +60574,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>75 K€</t>
+          <t>85 K€</t>
         </is>
       </c>
     </row>
@@ -60588,107 +60594,106 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Remote HRIS IT Project Manager Europe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>JELD-WEN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>LinkedIn / Jobrapido</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>CDD / Freelance</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Remote France ou UK</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>JELD-WEN = fabricant mondial portes/fenêtres (NYSE). HRIS IT PM Europe, déploiement UKG Pro WFM/Kronos, projets IT multi-sites Europe, bilingue FR/EN. Remote depuis France. Publié février 2026 — à vérifier si toujours ouvert.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://talents.studysmarter.co.uk/companies/jeld-wen-uk/remote-hris-it-project-manager-europe-en-fr-27061545/</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>75 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="176" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>pourvu</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Chef de Projet SIRH N2F (100% remote)</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>N2JSOFT</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Welcome to the Jungle</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>Montagnat (01) – télétravail total</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="n"/>
-      <c r="L35" s="5" t="inlineStr">
-        <is>
-          <t>N2F = SaaS gestion notes de frais. Chef de projet pour intégration N2F avec SIRH clients. 100% full remote = parfait Biarritz. Gap : N2F n'est pas un HRIS/SAP traditionnel mais outil adjacent. Compétences intégration SIRH, formation, déploiement de Gaëtan applicables.</t>
-        </is>
-      </c>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/fr/companies/n2jsoft-fr/jobs/chef-de-projet-sirh-h-f-n2f_montagnat_N2JSO_YbKVlVW</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>72 K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="176" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>hors profil</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Senior People Systems Analyst – Automations</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Deel</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>Full remote</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
@@ -60699,143 +60704,147 @@
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="5" t="inlineStr">
         <is>
+          <t>N2F = SaaS gestion notes de frais. Chef de projet pour intégration N2F avec SIRH clients. 100% full remote = parfait Biarritz. Gap : N2F n'est pas un HRIS/SAP traditionnel mais outil adjacent. Compétences intégration SIRH, formation, déploiement de Gaëtan applicables.</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/n2jsoft-fr/jobs/chef-de-projet-sirh-h-f-n2f_montagnat_N2JSO_YbKVlVW</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>72 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>hors profil</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Senior People Systems Analyst – Automations</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Deel</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
           <t>Automatisation HRIS interne Deel (Zapier, Jira, API, Deel HRIS), 5+ ans systems ops — trop technique, peu de face-client</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/4428710760</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>85 K€</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
+    <row r="38" ht="160" customHeight="1">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Consultant(e) GTA F/H</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>ACT-ON HRIS</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Hybride</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>GTA pure (Chronotime, Octime, Kelio) — pas SAP SF. Déjà postulé.</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4358595664/</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="160" customHeight="1">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Refusé</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Customer Success Manager</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Conga</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="n"/>
-      <c r="K38" s="6" t="n"/>
-      <c r="L38" s="5" t="inlineStr">
-        <is>
-          <t>10-15 comptes enterprise €7M+ ARR, French/English C2, 100% remote France — cœur de cible</t>
-        </is>
-      </c>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/conga/jobs/5105438007</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS.pdf</t>
-        </is>
-      </c>
-      <c r="Q38" s="41" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -60847,196 +60856,201 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
+          <t>Refusé</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Conga</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>10-15 comptes enterprise €7M+ ARR, French/English C2, 100% remote France — cœur de cible</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/conga/jobs/5105438007</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS.pdf</t>
+        </is>
+      </c>
+      <c r="Q39" s="41" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="128" customHeight="1">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
           <t>postulé</t>
         </is>
       </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>Consultant SIRH</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>https://careers.clap-partners.com/job/MONTROUGE-Consultant-SIRH-92120/827018802</t>
         </is>
       </c>
-      <c r="Q39" s="41" t="inlineStr">
+      <c r="Q40" s="41" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="128" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
+    <row r="41" ht="176" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>payroll</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>SAP HCM Consultant – French Payroll</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Movement Group</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>movementgroup.uk</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J40" s="6" t="n"/>
-      <c r="K40" s="6" t="inlineStr">
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="inlineStr">
         <is>
           <t>12 mois</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>SAP Payroll France 100% remote, 12 mois + extension, outside IR35 — start ASAP</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="176" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
+    <row r="42" ht="160" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>postulé</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Customer Success Manager EMEA</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Camunda</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>Greenhouse</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>Europe</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="n"/>
-      <c r="K41" s="6" t="n"/>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>BPM/automatisation enterprise, remote 75+ pays, profil CSM senior SaaS B2B parfait</t>
-        </is>
-      </c>
-      <c r="M41" s="5" t="inlineStr">
-        <is>
-          <t>https://camunda.com/careers/all-jobs/?gh_jid=6502803003&amp;ashby_jid=79980213-ee2c-41a0-bbab-4fcf6e312745</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_Camunda_EN.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="160" customHeight="1">
-      <c r="A42" s="27" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>pourvu</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Directeur de Projet SIRH H/F</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Actual Talent</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Welcome to the Jungle</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>France</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -61048,49 +61062,49 @@
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>100% télétravail, CDI, intégrateur SIRH/GTA, 5+ ans requis — remote parfait depuis Biarritz</t>
+          <t>BPM/automatisation enterprise, remote 75+ pays, profil CSM senior SaaS B2B parfait</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/ergalis/jobs/directeur-de-projet-sirh-h-f_lyon_AT_2AgaeJo</t>
+          <t>https://camunda.com/careers/all-jobs/?gh_jid=6502803003&amp;ashby_jid=79980213-ee2c-41a0-bbab-4fcf6e312745</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>CV_GaetanFRANCOIS_Camunda_EN.pdf</t>
         </is>
       </c>
     </row>
     <row r="43" ht="176" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>pourvu</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Consultant SIRH</t>
+          <t>Directeur de Projet SIRH H/F</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Onepoint</t>
+          <t>Actual Talent</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -61100,46 +61114,41 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil SIRH, ERP SAP/Oracle/Workday, 2-8 ans requis - sous-positionnement mais cabinet sérieux</t>
+          <t>100% télétravail, CDI, intégrateur SIRH/GTA, 5+ ans requis — remote parfait depuis Biarritz</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4329056727/</t>
+          <t>https://www.welcometothejungle.com/fr/companies/ergalis/jobs/directeur-de-projet-sirh-h-f_lyon_AT_2AgaeJo</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>70-80K€</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
     </row>
     <row r="44" ht="176" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Expiré</t>
+          <t>Postulé</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -61149,17 +61158,17 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) fonctionnel SIRH F/H</t>
+          <t>Consultant SIRH</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>CGI</t>
+          <t>Onepoint</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>CGI Careers (njoyn)</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -61174,29 +61183,29 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>?</t>
         </is>
       </c>
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>5 ans requis, SAP HR/SF/Workday/ADP, jusqu'à 3j remote — différent du Chef de Projet SIRH CGI déjà dans tableur</t>
+          <t>Cabinet conseil SIRH, ERP SAP/Oracle/Workday, 2-8 ans requis - sous-positionnement mais cabinet sérieux</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>https://cgi.njoyn.com/corp/xweb/xweb.asp?CLID=21001&amp;page=jobdetails&amp;JobID=J1225-1824&amp;lang=1</t>
+          <t>https://www.linkedin.com/jobs/view/4329056727/</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="Q44" s="41" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>70-80K€</t>
         </is>
       </c>
     </row>
@@ -61208,27 +61217,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
+          <t>Expiré</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) transformations et solutions RH</t>
+          <t>Consultant(e) fonctionnel SIRH F/H</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Artimon</t>
+          <t>CGI</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>CGI Careers (njoyn)</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -61250,12 +61259,12 @@
       <c r="K45" s="6" t="n"/>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil RH indépendant, diagnostic, sélection SIRH, transformation RH — profil L'Oréal 40 pays très aligné</t>
+          <t>5 ans requis, SAP HR/SF/Workday/ADP, jusqu'à 3j remote — différent du Chef de Projet SIRH CGI déjà dans tableur</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4400205394/</t>
+          <t>https://cgi.njoyn.com/corp/xweb/xweb.asp?CLID=21001&amp;page=jobdetails&amp;JobID=J1225-1824&amp;lang=1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -61263,11 +61272,16 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
+      <c r="Q45" s="41" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="272" customHeight="1">
-      <c r="A46" s="31" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -61282,12 +61296,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Chargé de projet SIRH H/F</t>
+          <t>Consultant(e) transformations et solutions RH</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Crédit Agricole Assurances</t>
+          <t>Artimon</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
@@ -61297,7 +61311,7 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>CDD</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
@@ -61307,31 +61321,36 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>Partiel (40%)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>Déploiement PeopleDoc (UKG), gestion MyDev (carrières), campagnes RH. Pas SAP mais SIRH projet direct. CDD + Paris hybride = contraintes. 82j télétravail/an.</t>
+          <t>Cabinet conseil RH indépendant, diagnostic, sélection SIRH, transformation RH — profil L'Oréal 40 pays très aligné</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4426879208/</t>
+          <t>https://www.linkedin.com/jobs/view/4400205394/</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
     </row>
     <row r="47" ht="256" customHeight="1">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="31" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Refusé</t>
+          <t>Postulé</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -61341,58 +61360,44 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Consultant SIRH AMOA</t>
+          <t>Chargé de projet SIRH H/F</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Clap Partners</t>
+          <t>Crédit Agricole Assurances</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>CDD</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Montrouge (92)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+          <t>Partiel (40%)</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Clap Partners = cabinet spécialisé SAP SuccessFactors. AMOA SIRH = cœur du profil Gaëtan. Fit excellent techniquement. Frein : Montrouge, pas full remote.</t>
+          <t>Déploiement PeopleDoc (UKG), gestion MyDev (carrières), campagnes RH. Pas SAP mais SIRH projet direct. CDD + Paris hybride = contraintes. 82j télétravail/an.</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/clap-partners-fr/jobs/consultant-sirh-amoa_montrouge_CP_GypWOaJ</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>75 K€</t>
+          <t>https://www.linkedin.com/jobs/view/4426879208/</t>
         </is>
       </c>
     </row>
@@ -61402,7 +61407,7 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Refusé</t>
         </is>
@@ -61414,7 +61419,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Consultant AMOA SIRH Learning H/F</t>
+          <t>Consultant SIRH AMOA</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -61450,12 +61455,12 @@
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>Clap Partners, spécialisé SAP SF. Module Learning (formation) = fit fort pour Gaëtan (formateur SF, transfert de connaissances L'Oréal). Frein : Montrouge, pas full remote.</t>
+          <t>Clap Partners = cabinet spécialisé SAP SuccessFactors. AMOA SIRH = cœur du profil Gaëtan. Fit excellent techniquement. Frein : Montrouge, pas full remote.</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/clap-partners-fr/jobs/consultant-amoa-sirh-learning-h-f_montrouge</t>
+          <t>https://www.welcometothejungle.com/fr/companies/clap-partners-fr/jobs/consultant-sirh-amoa_montrouge_CP_GypWOaJ</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -61470,14 +61475,14 @@
       </c>
     </row>
     <row r="49" ht="176" customHeight="1">
-      <c r="A49" s="32" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>out of scope, paie</t>
+          <t>Refusé</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -61487,17 +61492,17 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>SAP HCM-Payroll Consultant</t>
+          <t>Consultant AMOA SIRH Learning H/F</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil global (via Eursap)</t>
+          <t>Clap Partners</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Eursap (réf. 29132)</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -61507,41 +61512,50 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Montrouge (92)</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="n"/>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
       <c r="K49" s="6" t="n"/>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>14 ans SAP HR/HCM payroll multi-pays, jusqu'à 100% remote EU, 15 pays éligibles — profil L'Oréal parfait</t>
+          <t>Clap Partners, spécialisé SAP SF. Module Learning (formation) = fit fort pour Gaëtan (formateur SF, transfert de connaissances L'Oréal). Frein : Montrouge, pas full remote.</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>https://eursap.eu/jobs/sap-hcm-payroll-consultant-remote-work-29132</t>
+          <t>https://www.welcometothejungle.com/fr/companies/clap-partners-fr/jobs/consultant-amoa-sirh-learning-h-f_montrouge</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>75 K€</t>
         </is>
       </c>
     </row>
     <row r="50" ht="176" customHeight="1">
-      <c r="A50" s="34" t="inlineStr">
+      <c r="A50" s="32" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Postulé</t>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>out of scope, paie</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -61551,17 +61565,17 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>SAP Pre-sales Lead – HCM, Payroll, SuccessFactors</t>
+          <t>SAP HCM-Payroll Consultant</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Whitehall Resources</t>
+          <t>Cabinet conseil global (via Eursap)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Whitehall Resources</t>
+          <t>Eursap (réf. 29132)</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -61571,55 +61585,41 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Royaume-Uni (remote depuis France)</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="n"/>
       <c r="K50" s="6" t="n"/>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>14 ans SAP, L'Oréal 40+ pays, face client grands comptes = match parfait. Vérifier éligibilité UK depuis France.</t>
+          <t>14 ans SAP HR/HCM payroll multi-pays, jusqu'à 100% remote EU, 15 pays éligibles — profil L'Oréal parfait</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>https://www.whitehallresources.com/job/sap-pre-sales-lead-hcm-payroll-successfactors/</t>
+          <t>https://eursap.eu/jobs/sap-hcm-payroll-consultant-remote-work-29132</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>95-115K€</t>
-        </is>
-      </c>
-      <c r="Q50" s="41" t="inlineStr">
-        <is>
-          <t>25/09/2025</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
     </row>
     <row r="51" ht="128" customHeight="1">
-      <c r="A51" s="32" t="inlineStr">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>postulé</t>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Postulé</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -61629,17 +61629,17 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>SAP Project Manager</t>
+          <t>SAP Pre-sales Lead – HCM, Payroll, SuccessFactors</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Via EurSAP (remote)</t>
+          <t>Whitehall Resources</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>EurSAP</t>
+          <t>Whitehall Resources</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -61649,528 +61649,524 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Royaume-Uni (remote depuis France)</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Oui (100%)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>80-150K€ + equity</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K51" s="6" t="n"/>
       <c r="L51" s="5" t="inlineStr">
         <is>
+          <t>14 ans SAP, L'Oréal 40+ pays, face client grands comptes = match parfait. Vérifier éligibilité UK depuis France.</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.whitehallresources.com/job/sap-pre-sales-lead-hcm-payroll-successfactors/</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>95-115K€</t>
+        </is>
+      </c>
+      <c r="Q51" s="41" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>postulé</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>SAP Project Manager</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Via EurSAP (remote)</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>EurSAP</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>Oui (100%)</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>80-150K€ + equity</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="n"/>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
           <t>SAP PM remote CDI — 80-150k€ + equity/stock options — démarrage 03/08/2026</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="M52" s="5" t="inlineStr">
         <is>
           <t>https://eursap.eu/jobs/sap-project-manager-34811-remote</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>100-115K€</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="36" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="36" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Formateur / Consultant IA Freelance</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Mantra (ex-GrowthMakers)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>WelcomeToTheJungle</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>TJM attractif (marché 500-900 €/j)</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Récurrent</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>100% remote. Animer formations IA générative distanciel, créer contenus pédagogiques, personnaliser cas d'usage par secteur. Profil praticien IA valorisé. Idéal depuis Biarritz.</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/growthmakers/jobs/formateur-ia-et-ia-generative_paris</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_IA.html</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="35" t="inlineStr">
+    <row r="54" ht="160" customHeight="1">
+      <c r="A54" s="35" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Refusé</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Formateur en Intelligence Artificielle F/H</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Groupe MDA (MDA Performance)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Biarritz</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Basé à Biarritz, 100% distanciel — fit géographique parfait. Former entreprises adultes sur ChatGPT, Copilot, Gemini, Claude. Publié 01/07/2026.</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/formateur-en-intelligence-artificielle-f-h-at-groupe-mda-4435134586</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="160" customHeight="1">
-      <c r="A54" s="42" t="inlineStr">
+    <row r="55" ht="240" customHeight="1">
+      <c r="A55" s="42" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B54" s="43" t="inlineStr">
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>expiré</t>
         </is>
       </c>
-      <c r="C54" s="43" t="inlineStr">
+      <c r="C55" s="43" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D54" s="26" t="inlineStr">
+      <c r="D55" s="26" t="inlineStr">
         <is>
           <t>Chef de Projet Fonctionnel SIRH</t>
         </is>
       </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="E55" s="26" t="inlineStr">
         <is>
           <t>Client anonyme</t>
         </is>
       </c>
-      <c r="F54" s="26" t="inlineStr">
+      <c r="F55" s="26" t="inlineStr">
         <is>
           <t>freelance-informatique.fr</t>
         </is>
       </c>
-      <c r="G54" s="44" t="inlineStr">
+      <c r="G55" s="44" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H54" s="44" t="inlineStr">
+      <c r="H55" s="44" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I54" s="44" t="inlineStr">
+      <c r="I55" s="44" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J54" s="44" t="n"/>
-      <c r="K54" s="44" t="inlineStr">
+      <c r="J55" s="44" t="n"/>
+      <c r="K55" s="44" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="L54" s="26" t="inlineStr">
+      <c r="L55" s="26" t="inlineStr">
         <is>
           <t>100% remote — seule mission Chef de Projet SIRH full remote trouvée aujourd'hui, start ASAP</t>
         </is>
       </c>
-      <c r="M54" s="45" t="inlineStr">
+      <c r="M55" s="45" t="inlineStr">
         <is>
           <t>https://www.freelance-informatique.fr/mission-chef-de-projet-sirh-n112</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="240" customHeight="1">
-      <c r="A55" s="37" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="37" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="D55" s="26" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>Consultant SAP SuccessFactors (24 mois)</t>
         </is>
       </c>
-      <c r="E55" s="26" t="inlineStr">
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>n.c. (via Free-Work)</t>
         </is>
       </c>
-      <c r="F55" s="26" t="inlineStr">
+      <c r="F56" s="26" t="inlineStr">
         <is>
           <t>Free-Work</t>
         </is>
       </c>
-      <c r="G55" s="44" t="inlineStr">
+      <c r="G56" s="44" t="inlineStr">
         <is>
           <t>Mission</t>
         </is>
       </c>
-      <c r="H55" s="44" t="inlineStr">
+      <c r="H56" s="44" t="inlineStr">
         <is>
           <t>Versailles (78)</t>
         </is>
       </c>
-      <c r="I55" s="44" t="inlineStr">
+      <c r="I56" s="44" t="inlineStr">
         <is>
           <t>Hybride</t>
         </is>
       </c>
-      <c r="J55" s="44" t="inlineStr">
+      <c r="J56" s="44" t="inlineStr">
         <is>
           <t>450-690 €/j</t>
         </is>
       </c>
-      <c r="K55" s="44" t="inlineStr">
+      <c r="K56" s="44" t="inlineStr">
         <is>
           <t>24 mois (démarrage ASAP)</t>
         </is>
       </c>
-      <c r="L55" s="26" t="inlineStr">
+      <c r="L56" s="26" t="inlineStr">
         <is>
           <t>Mission longue 24 mois, expertise implementation SF. TJM 450-690€/j. Versailles = déplacements possibles depuis Biarritz. Profil Gaëtan bien adapté.</t>
         </is>
       </c>
-      <c r="M55" s="26" t="inlineStr">
+      <c r="M56" s="26" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/jobs/sap-successfactors</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="Q55" s="41" t="inlineStr">
+      <c r="Q56" s="41" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="38" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="38" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>postulé</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Chef de projet Intelligence Artificielle ChatGPT</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>BI SOLUTIONS</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>IDF</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Non précisé</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>400-500 €/j</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Chef de projet IA GenAI ; anglais requis</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-intelligence-artificielle-chat-gpt-anglais-500-e-par-j</t>
         </is>
       </c>
-      <c r="Q56" s="41" t="inlineStr">
+      <c r="Q57" s="41" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="46" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="46" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B57" s="47" t="inlineStr">
+      <c r="B58" s="47" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C57" s="47" t="inlineStr">
+      <c r="C58" s="47" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Principal Solution Advisor SuccessFactors F/H</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t>Levallois-Perret</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>Hybride (0-10% déplacements)</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>100-130K€ (estimé)</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Pre-sales SF — différent du HCM déjà postulé — 10-15 ans grandes orgas, 3-5 ans HCM requis — posté il y a 4 jours</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/principal-solution-advisor-successfactors-f-h-at-sap-4415727184</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>100-115K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="48" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B58" s="47" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C58" s="47" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Manager SIRH</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>TalHenT</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Paris (75)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>n.p.</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Cabinet conseil SIRH ~100p, 10+ ans exp, dev commercial et structuration offres SIRH - profil senior idéal</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>https://www.emplois-informatique.fr/cdi/manager-sirh-6893801</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>70 K€</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -62182,7 +62178,7 @@
       </c>
       <c r="B59" s="47" t="inlineStr">
         <is>
-          <t>pourvu</t>
+          <t>Postulé</t>
         </is>
       </c>
       <c r="C59" s="47" t="inlineStr">
@@ -62192,12 +62188,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Senior Manager SIRH H/F</t>
+          <t>Manager SIRH</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ALTHEA</t>
+          <t>TalHenT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -62212,7 +62208,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -62222,17 +62218,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>60-80 K€ + 8 K€ variable</t>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>6 mois</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Cabinet conseil 150+ consultants RH, pilotage transformation SIRH (SAP SF/Workday/Oracle HCM), management équipe, 5-15 ans exp, FR+EN obligatoire</t>
+          <t>Cabinet conseil SIRH ~100p, 10+ ans exp, dev commercial et structuration offres SIRH - profil senior idéal</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4417058716</t>
+          <t>https://www.emplois-informatique.fr/cdi/manager-sirh-6893801</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -62242,7 +62243,12 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>72 K€</t>
+          <t>70 K€</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -62254,7 +62260,7 @@
       </c>
       <c r="B60" s="47" t="inlineStr">
         <is>
-          <t>Postulé</t>
+          <t>pourvu</t>
         </is>
       </c>
       <c r="C60" s="47" t="inlineStr">
@@ -62264,12 +62270,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors expérimenté H/F</t>
+          <t>Senior Manager SIRH H/F</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SQORUS</t>
+          <t>ALTHEA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -62284,7 +62290,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paris et périphérie</t>
+          <t>Issy-les-Moulineaux</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -62294,17 +62300,17 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>60-80 K€ + 8 K€ variable</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Cabinet RH digital, 5+ ans SIRH, SF multi-modules (TA/Perf/Career/LMS/Comp), projets clients FR+EN B2 min, ateliers, specs fonctionnelles</t>
+          <t>Cabinet conseil 150+ consultants RH, pilotage transformation SIRH (SAP SF/Workday/Oracle HCM), management équipe, 5-15 ans exp, FR+EN obligatoire</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4396619283</t>
+          <t>https://fr.linkedin.com/jobs/view/4417058716</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -62314,7 +62320,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>60 K€</t>
+          <t>72 K€</t>
         </is>
       </c>
     </row>
@@ -62336,194 +62342,193 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>Consultant SAP SuccessFactors expérimenté H/F</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SQORUS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Paris et périphérie</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>n.p.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Cabinet RH digital, 5+ ans SIRH, SF multi-modules (TA/Perf/Career/LMS/Comp), projets clients FR+EN B2 min, ateliers, specs fonctionnelles</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/4396619283</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>60 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="288" customHeight="1">
+      <c r="A62" s="48" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B62" s="47" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C62" s="47" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>SAP SuccessFactors Consultant – Succession Calibration Performance (12 mois)</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Movement Group</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>LinkedIn / Movement Group</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Mission</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>N/C (négociable)</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>12 mois + extension</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Mission distincte de la mission Movement Group SF déjà en tableur. Modules Succession / Calibration / Performance. Contact : Shane Breen (shane.breen@movementgroup.uk). CV Word demandé.</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/sap-successfactors-consultant-france-remote-hybrid-freelance-12-months-%2B-at-movement-group-4433063782</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="288" customHeight="1">
-      <c r="A62" s="54" t="inlineStr">
+    <row r="63" ht="335" customHeight="1">
+      <c r="A63" s="54" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>HCM Senior Associate Consultant</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>Huron Consulting Group</t>
         </is>
       </c>
-      <c r="F62" s="5" t="inlineStr">
+      <c r="F63" s="5" t="inlineStr">
         <is>
           <t>LinkedIn / Workday</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J62" s="6" t="n"/>
-      <c r="K62" s="6" t="n"/>
-      <c r="L62" s="5" t="inlineStr">
-        <is>
-          <t>Cabinet conseil US coté Nasdaq, 6800+ experts. Poste HCM consultant Paris — Oracle Cloud HCM ou SAP HCM. Réf JR-0016012.</t>
-        </is>
-      </c>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>https://huron.wd1.myworkdayjobs.com/fr-FR/huroncareers/job/Paris-France/HCM-Senior-Associate-Consultant_JR-0016012 | https://www.linkedin.com/jobs/view/4441064885/</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>70-85K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="335" customHeight="1">
-      <c r="A63" s="55" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>HR Business Solutions Architect</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>Sinch</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn / Sinch Careers (Oracle ATS)</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>Paris, France</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>80-100K€</t>
-        </is>
-      </c>
+      <c r="J63" s="6" t="n"/>
       <c r="K63" s="6" t="n"/>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>Boîte SaaS messaging suédoise (Nasdaq). 80% exécution / 20% stratégie. Requis : 3 ans Oracle HCM (lacune SAP→Oracle à argumenter), 5 ans solutions RH globales, 7 ans HRIT. Remote confirmé. EU requis OK.</t>
+          <t>Cabinet conseil US coté Nasdaq, 6800+ experts. Poste HCM consultant Paris — Oracle Cloud HCM ou SAP HCM. Réf JR-0016012.</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4444461445/ | https://iaings.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/SinchCareer/job/1256/</t>
+          <t>https://huron.wd1.myworkdayjobs.com/fr-FR/huroncareers/job/Paris-France/HCM-Senior-Associate-Consultant_JR-0016012 | https://www.linkedin.com/jobs/view/4441064885/</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -62533,40 +62538,39 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>90-100K€</t>
-        </is>
-      </c>
-      <c r="Q63" s="41" t="n"/>
+          <t>70-85K€</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="240" customHeight="1">
-      <c r="A64" s="54" t="inlineStr">
+      <c r="A64" s="55" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Refusé</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Responsable SIRH et DATA RH (F/H)</t>
+          <t>HR Business Solutions Architect</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>TDF (Groupe TDF)</t>
+          <t>Sinch</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn / Aplitrak</t>
+          <t>LinkedIn / Sinch Careers (Oracle ATS)</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -62576,67 +62580,71 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Montrouge (92)</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="n"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>80-100K€</t>
+        </is>
+      </c>
       <c r="K64" s="6" t="n"/>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>Pilotage SIRH + gouvernance data RH. Outils : Workday, ADP, SIMBEL. 7-10 ans SIRH requis. Bac+5 RH/info/data. Anglais courant.</t>
+          <t>Boîte SaaS messaging suédoise (Nasdaq). 80% exécution / 20% stratégie. Requis : 3 ans Oracle HCM (lacune SAP→Oracle à argumenter), 5 ans solutions RH globales, 7 ans HRIT. Remote confirmé. EU requis OK.</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4440037261/ | https://www.aplitrak.com/?adid=Q2F0aGVyaW5lLmxpdi44NTY4MS4xNTUwQGdyb3VwZXRkZi5hcGxpdHJhay5jb20</t>
+          <t>https://www.linkedin.com/jobs/view/4444461445/ | https://iaings.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/SinchCareer/job/1256/</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>80-95K€</t>
+          <t>90-100K€</t>
         </is>
       </c>
       <c r="Q64" s="41" t="n"/>
     </row>
     <row r="65" ht="409.5" customHeight="1">
-      <c r="A65" s="62" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C65" s="39" t="inlineStr">
+      <c r="A65" s="54" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Refusé</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Operational Onboarding Manager - France</t>
+          <t>Responsable SIRH et DATA RH (F/H)</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>TDF (Groupe TDF)</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn / Aplitrak</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -62646,63 +62654,62 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Montrouge (92)</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Flexible (présentiel valorisé)</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>n.c. (grille B0-B1)</t>
-        </is>
-      </c>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="n"/>
       <c r="K65" s="6" t="n"/>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>Scale-up assurance santé SaaS, onboarding administratif des plus gros clients, ateliers formation RH/Paie. Localisation Biarritz = très proche Anglet. Rôle plus opérationnel/junior qu'un CSM Senior classique, remote seulement flexible. | Postulé le 04/08/2026. Aussi sur LinkedIn : https://www.linkedin.com/jobs/view/4432803785/</t>
+          <t>Pilotage SIRH + gouvernance data RH. Outils : Workday, ADP, SIMBEL. 7-10 ans SIRH requis. Bac+5 RH/info/data. Anglais courant.</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/alan/149e6bff-b83d-4f7f-bfa8-9eb251bf437c</t>
-        </is>
-      </c>
-      <c r="N65" s="39" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
-        </is>
-      </c>
-      <c r="O65" s="39" t="n"/>
-      <c r="P65" s="39" t="n"/>
+          <t>https://www.linkedin.com/jobs/view/4440037261/ | https://www.aplitrak.com/?adid=Q2F0aGVyaW5lLmxpdi44NTY4MS4xNTUwQGdyb3VwZXRkZi5hcGxpdHJhay5jb20</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>80-95K€</t>
+        </is>
+      </c>
       <c r="Q65" s="41" t="n"/>
     </row>
     <row r="66" ht="350" customHeight="1">
-      <c r="A66" s="49" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
+      <c r="A66" s="62" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Senior Manager, SAP SuccessFactors Employee Central &amp; Platform</t>
+          <t>Operational Onboarding Manager - France</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Foundever</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
@@ -62717,190 +62724,187 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>UK (remote)</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Flexible (présentiel valorisé)</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>£75-90K (~87-105K€)</t>
+          <t>n.c. (grille B0-B1)</t>
         </is>
       </c>
       <c r="K66" s="6" t="n"/>
       <c r="L66" s="5" t="inlineStr">
         <is>
+          <t>Scale-up assurance santé SaaS, onboarding administratif des plus gros clients, ateliers formation RH/Paie. Localisation Biarritz = très proche Anglet. Rôle plus opérationnel/junior qu'un CSM Senior classique, remote seulement flexible. | Postulé le 04/08/2026. Aussi sur LinkedIn : https://www.linkedin.com/jobs/view/4432803785/</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/alan/149e6bff-b83d-4f7f-bfa8-9eb251bf437c</t>
+        </is>
+      </c>
+      <c r="N66" s="39" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="O66" s="39" t="n"/>
+      <c r="P66" s="39" t="n"/>
+      <c r="Q66" s="41" t="n"/>
+    </row>
+    <row r="67" ht="409.5" customHeight="1">
+      <c r="A67" s="49" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Senior Manager, SAP SuccessFactors Employee Central &amp; Platform</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Foundever</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>UK (remote)</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>£75-90K (~87-105K€)</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="n"/>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
           <t>Lead équipe globale SF EC 40+ pays ; gouvernance, stratégie, config EC, RBP, intégrations HR/Payroll/Finance — calque L'Oréal 40+ pays parfait | Postulé le 04/08/2026. Aussi sur LinkedIn : https://www.linkedin.com/jobs/view/4429527206/</t>
         </is>
       </c>
-      <c r="M66" s="56" t="inlineStr">
+      <c r="M67" s="56" t="inlineStr">
         <is>
           <t>https://jobs.foundever.com/job/UK-Wide-Senior-Manager%2C-SAP-SuccessFactors-Employee-Central-&amp;-Platform-Work-Sitel-UK-L/1400161700/</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>95K€</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="Q66" s="41" t="n"/>
-    </row>
-    <row r="67" ht="409.5" customHeight="1">
-      <c r="A67" s="60" t="inlineStr">
+      <c r="Q67" s="41" t="n"/>
+    </row>
+    <row r="68" ht="409.5" customHeight="1">
+      <c r="A68" s="60" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>SuccessFactors Talent Management Consultant</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>Empiric</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G67" s="6" t="inlineStr">
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>Suède (remote)</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>100% remote (Suède)</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
+      <c r="J68" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K67" s="6" t="inlineStr">
+      <c r="K68" s="6" t="inlineStr">
         <is>
           <t>12 mois</t>
         </is>
       </c>
-      <c r="L67" s="5" t="inlineStr">
+      <c r="L68" s="5" t="inlineStr">
         <is>
           <t>Consultant fonctionnel SAP SuccessFactors : Performance &amp; Goals, Career Development, Succession, Recruiting, Onboarding ; interface entre RH et technique, intégrations SIRH. Anglais courant requis, suédois apprécié. Remote annoncé en Suède, donc à clarifier depuis la France. Postulé le 04/08/2026.</t>
         </is>
       </c>
-      <c r="M67" s="5" t="inlineStr">
+      <c r="M68" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447004933/</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="Q67" s="41" t="n"/>
-    </row>
-    <row r="68" ht="409.5" customHeight="1">
-      <c r="A68" s="58" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>HRIS Data Consultant - Payroll &amp; HR</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>Silver Cloud</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn / Hibob</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>Royaume-Uni</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>Remote + déplacements clients</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>n.c. (marché : 82-88 K€ / £70-75K)</t>
-        </is>
-      </c>
-      <c r="K68" s="6" t="n"/>
-      <c r="L68" s="5" t="inlineStr">
-        <is>
-          <t>Cabinet conseil HR tech : projets de transformation SIRH/paie, migration de données, mapping, validation, réconciliation, ateliers de découverte. Outils cités : Dayforce, Workday, HiBob. Très bon fit avec les migrations OnePayroll (L'Oréal) et FMC Technologies. Points à clarifier : poste UK depuis la France (devise, contrat, risque de change) et fréquence des déplacements clients depuis Anglet. Comparable marché : Dayforce Data Conversion full remote UK affiché £80K. Postulé le 04/08/2026. Aussi sur Hibob : https://silvercloud.careers.hibob.com/jobs/4c27dd97-5a45-4ed8-9f96-9eefd10c5899</t>
-        </is>
-      </c>
-      <c r="M68" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4443868475/</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>85 K€ (£72K)</t>
         </is>
       </c>
       <c r="Q68" s="41" t="n"/>
@@ -62923,17 +62927,17 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>HRIS Implementation Project Manager</t>
+          <t>HRIS Data Consultant - Payroll &amp; HR</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Yassir</t>
+          <t>Silver Cloud</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn / Lever</t>
+          <t>LinkedIn / Hibob</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
@@ -62943,42 +62947,46 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>Non précisée (super-app Afrique/MENA)</t>
+          <t>Royaume-Uni</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>À confirmer</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="n"/>
+          <t>Remote + déplacements clients</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>n.c. (marché : 82-88 K€ / £70-75K)</t>
+        </is>
+      </c>
       <c r="K69" s="6" t="n"/>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>Yassir = super-app Algérie/MENA (transport, livraison, fintech). Chef de projet implémentation SIRH. Profil déploiement SIRH grands comptes de Gaëtan directement applicable. Postulé le 31/07/2026 via LinkedIn.</t>
+          <t>Cabinet conseil HR tech : projets de transformation SIRH/paie, migration de données, mapping, validation, réconciliation, ateliers de découverte. Outils cités : Dayforce, Workday, HiBob. Très bon fit avec les migrations OnePayroll (L'Oréal) et FMC Technologies. Points à clarifier : poste UK depuis la France (devise, contrat, risque de change) et fréquence des déplacements clients depuis Anglet. Comparable marché : Dayforce Data Conversion full remote UK affiché £80K. Postulé le 04/08/2026. Aussi sur Hibob : https://silvercloud.careers.hibob.com/jobs/4c27dd97-5a45-4ed8-9f96-9eefd10c5899</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/Yassir/0c61130f-8b15-4366-b253-5662b6ba4c0c</t>
+          <t>https://www.linkedin.com/jobs/view/4443868475/</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>70-85K€</t>
+          <t>85 K€ (£72K)</t>
         </is>
       </c>
       <c r="Q69" s="41" t="n"/>
     </row>
     <row r="70" ht="409.5" customHeight="1">
-      <c r="A70" s="60" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
+      <c r="A70" s="58" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
@@ -62993,17 +63001,17 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Principal HR Specialist</t>
+          <t>HRIS Implementation Project Manager</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Skillsoft</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>skillsoft.com / Greenhouse</t>
+          <t>LinkedIn / Lever</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -63013,68 +63021,67 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Non précisée (super-app Afrique/MENA)</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Oui (100% remote)</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="J70" s="6" t="n"/>
       <c r="K70" s="6" t="n"/>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>Skillsoft (e-learning/L&amp;D SaaS enterprise). Rôle interne RH : cycle de vie employés, onboarding/offboarding, gestion CSE, paie et avantages France + Allemagne. Poste RH opérationnel plutôt que SIRH consulting — fit partiel. 100% remote France. Postulé le 31/07/2026.</t>
+          <t>Yassir = super-app Algérie/MENA (transport, livraison, fintech). Chef de projet implémentation SIRH. Profil déploiement SIRH grands comptes de Gaëtan directement applicable. Postulé le 31/07/2026 via LinkedIn.</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>https://www.skillsoft.com/about/job/apply?id=4707524005&amp;gh_jid=4707524005</t>
-        </is>
-      </c>
-      <c r="N70" s="39" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O70" s="39" t="inlineStr">
-        <is>
-          <t>70-80K€</t>
-        </is>
-      </c>
-      <c r="P70" s="39" t="n"/>
+          <t>https://jobs.lever.co/Yassir/0c61130f-8b15-4366-b253-5662b6ba4c0c</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>70-85K€</t>
+        </is>
+      </c>
       <c r="Q70" s="41" t="n"/>
     </row>
     <row r="71" ht="409.5" customHeight="1">
-      <c r="A71" s="62" t="inlineStr">
+      <c r="A71" s="60" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B71" s="39" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C71" s="39" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>People Operations and HRIS Lead</t>
+          <t>Principal HR Specialist</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>Skillsoft</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>euremotejobs.com</t>
+          <t>skillsoft.com / Greenhouse</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -63084,342 +63091,339 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Oui (100% remote)</t>
         </is>
       </c>
       <c r="J71" s="6" t="n"/>
       <c r="K71" s="6" t="n"/>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>Builder role HRIS + People Ops : talent management, performance, L&amp;D, succession, org design, compensation. AI company 11B USD, scale rapide. Pas de plateforme SAP mentionnee. Worldwide remote. Postulé le 04/08/2026 (formulaire : question mission ElevenLabs + hard problem).</t>
+          <t>Skillsoft (e-learning/L&amp;D SaaS enterprise). Rôle interne RH : cycle de vie employés, onboarding/offboarding, gestion CSE, paie et avantages France + Allemagne. Poste RH opérationnel plutôt que SIRH consulting — fit partiel. 100% remote France. Postulé le 31/07/2026.</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>https://euremotejobs.com/job/people-operations-and-hris-lead/</t>
+          <t>https://www.skillsoft.com/about/job/apply?id=4707524005&amp;gh_jid=4707524005</t>
         </is>
       </c>
       <c r="N71" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
-        </is>
-      </c>
-      <c r="O71" s="39" t="n"/>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O71" s="39" t="inlineStr">
+        <is>
+          <t>70-80K€</t>
+        </is>
+      </c>
       <c r="P71" s="39" t="n"/>
       <c r="Q71" s="41" t="n"/>
     </row>
     <row r="72" ht="128" customHeight="1">
-      <c r="A72" s="65" t="inlineStr">
+      <c r="A72" s="62" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B72" s="39" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C72" s="39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>People Operations and HRIS Lead</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>euremotejobs.com</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="n"/>
+      <c r="K72" s="6" t="n"/>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>Builder role HRIS + People Ops : talent management, performance, L&amp;D, succession, org design, compensation. AI company 11B USD, scale rapide. Pas de plateforme SAP mentionnee. Worldwide remote. Postulé le 04/08/2026 (formulaire : question mission ElevenLabs + hard problem).</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
+          <t>https://euremotejobs.com/job/people-operations-and-hris-lead/</t>
+        </is>
+      </c>
+      <c r="N72" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
+        </is>
+      </c>
+      <c r="O72" s="39" t="n"/>
+      <c r="P72" s="39" t="n"/>
+      <c r="Q72" s="41" t="n"/>
+    </row>
+    <row r="73" ht="409.5" customHeight="1">
+      <c r="A73" s="65" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B72" s="39" t="inlineStr">
+      <c r="B73" s="39" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C72" s="39" t="inlineStr">
+      <c r="C73" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D72" s="39" t="inlineStr">
+      <c r="D73" s="39" t="inlineStr">
         <is>
           <t>SAP Project Manager / Trainer</t>
         </is>
       </c>
-      <c r="E72" s="39" t="inlineStr">
+      <c r="E73" s="39" t="inlineStr">
         <is>
           <t>N/C (via eursap.eu)</t>
         </is>
       </c>
-      <c r="F72" s="39" t="inlineStr">
+      <c r="F73" s="39" t="inlineStr">
         <is>
           <t>eursap.eu</t>
         </is>
       </c>
-      <c r="G72" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H72" s="39" t="inlineStr">
+      <c r="G73" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H73" s="39" t="inlineStr">
         <is>
           <t>100% Remote</t>
         </is>
       </c>
-      <c r="I72" s="39" t="inlineStr">
+      <c r="I73" s="39" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J72" s="39" t="inlineStr">
+      <c r="J73" s="39" t="inlineStr">
         <is>
           <t>80-156k€/an + equity</t>
         </is>
       </c>
-      <c r="K72" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="L72" s="39" t="inlineStr">
+      <c r="K73" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="L73" s="39" t="inlineStr">
         <is>
           <t>SAP PM + formateur, full remote, fourchette haute, démarrage août 2026 ; ref 34811</t>
         </is>
       </c>
-      <c r="M72" s="39" t="inlineStr">
+      <c r="M73" s="39" t="inlineStr">
         <is>
           <t>https://eursap.eu/jobs/sap-project-manager-or-trainer-34811-remote</t>
         </is>
       </c>
-      <c r="N72" s="39" t="n"/>
-      <c r="O72" s="39" t="n"/>
-      <c r="P72" s="39" t="inlineStr">
+      <c r="N73" s="39" t="n"/>
+      <c r="O73" s="39" t="n"/>
+      <c r="P73" s="39" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="Q72" s="39" t="inlineStr">
+      <c r="Q73" s="39" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="409.5" customHeight="1">
-      <c r="A73" s="67" t="inlineStr">
+    <row r="74" ht="128" customHeight="1">
+      <c r="A74" s="67" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B73" s="39" t="n"/>
-      <c r="C73" s="39" t="inlineStr">
+      <c r="B74" s="39" t="n"/>
+      <c r="C74" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Chef de Projet SIRH / AMOA SIRH</t>
         </is>
       </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>N/C (via freelance-informatique.fr)</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>freelance-informatique.fr</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>Mission freelance</t>
         </is>
       </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>Courbevoie (92026)</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>Non indiqué (sur site)</t>
         </is>
       </c>
-      <c r="J73" s="6" t="inlineStr">
+      <c r="J74" s="6" t="inlineStr">
         <is>
           <t>N/C</t>
         </is>
       </c>
-      <c r="K73" s="6" t="inlineStr">
+      <c r="K74" s="6" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="L74" s="5" t="inlineStr">
         <is>
           <t>Réf. 260716H003, publiée le 16/07/2026, démarrage 01/09/2026. Le périmètre couvre le recueil des besoins des directions RH et la coordination entre RH, DSI et éditeurs jusqu'à la mise en production, avec SAP SuccessFactors et SmartRecruiters cités ainsi que la recette et la conduite du changement ; le fit fonctionnel est donc élevé. L'annonce n'indique aucun télétravail et le site est à Courbevoie, ce qui pose un problème depuis Anglet. Contact : Anais NAESSENS, 01 80 87 54 30.</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr">
         <is>
           <t>https://www.freelance-informatique.fr/mission-chef-de-projet-sirh-amoa-sirh-sur-courbevoie-260716H003</t>
         </is>
       </c>
-      <c r="N73" s="39" t="inlineStr">
+      <c r="N74" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.html</t>
         </is>
       </c>
-      <c r="O73" s="39" t="inlineStr">
+      <c r="O74" s="39" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="P73" s="39" t="n"/>
-      <c r="Q73" s="41" t="inlineStr">
+      <c r="P74" s="39" t="n"/>
+      <c r="Q74" s="41" t="inlineStr">
         <is>
           <t>06/10/2026</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="128" customHeight="1">
-      <c r="A74" s="64" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="64" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B74" s="7" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Global Product Owner - SuccessFactors</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>Qurated (pour un cabinet d avocats international)</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>CDD / FTC 18 mois</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>Royaume-Uni</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>100% remote</t>
         </is>
       </c>
-      <c r="J74" s="6" t="n"/>
-      <c r="K74" s="6" t="inlineStr">
+      <c r="J75" s="6" t="n"/>
+      <c r="K75" s="6" t="inlineStr">
         <is>
           <t>18 mois</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>Ownership unique de la plateforme SAP SuccessFactors sur tout le perimetre mondial : vision et roadmap, solution design multi-modules (Employee Central, Performance &amp; Goals, Compensation, Recruiting, Onboarding, Learning), standards globaux, cycles de release, conduite du changement et relation editeur. Fit tres eleve : SuccessFactors multi-modules, contexte global et conduite du changement correspondent au parcours L'Oreal. Full remote. Postule le 07/08/2026.</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
+      <c r="M75" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447393087</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>06/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="79" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Expiré</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SAP HCM Time Senior</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>Strada (ex-Alight)</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>careers.alight.com</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>Colombes, France</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="n"/>
-      <c r="K75" s="6" t="n"/>
-      <c r="L75" s="5" t="inlineStr">
-        <is>
-          <t>Strada expert SAP HCM Time, posté 2026</t>
-        </is>
-      </c>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27913STRADAENUS/Consultant-SAP-HCM-Time-senior</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>650-750€/j ou 70-85K€</t>
-        </is>
-      </c>
-      <c r="Q75" s="41" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -63429,29 +63433,29 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Expiré</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP HCM Paie senior</t>
+          <t>Consultant SAP HCM Time Senior</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Strada (ex-Alight / ex-NGA Human Resources)</t>
+          <t>Strada (ex-Alight)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>careers.alight.com/strada</t>
+          <t>careers.alight.com</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -63461,267 +63465,270 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>Colombes (92)</t>
+          <t>Colombes, France</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>Oui (depuis toute la France)</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J76" s="6" t="n"/>
       <c r="K76" s="6" t="n"/>
       <c r="L76" s="5" t="inlineStr">
         <is>
+          <t>Strada expert SAP HCM Time, posté 2026</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
+          <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27913STRADAENUS/Consultant-SAP-HCM-Time-senior</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>650-750€/j ou 70-85K€</t>
+        </is>
+      </c>
+      <c r="Q76" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="79" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>paie</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SAP HCM Paie senior</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Strada (ex-Alight / ex-NGA Human Resources)</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>careers.alight.com/strada</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Colombes (92)</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>Oui (depuis toute la France)</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="n"/>
+      <c r="K77" s="6" t="n"/>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
           <t>Strada = 1er partenaire mondial SAP HR. Configuration payroll SAP HCM France (cycles, schémas, contributions, accounting). 5+ ans SAP HCM Payroll requis. Fit parfait. Remote depuis toute la France confirmé. 2 annonces actives (R-27911 et R-32021).</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
+      <c r="M77" s="5" t="inlineStr">
         <is>
           <t>https://careers.alight.com/strada/us/en/job/ALIGUSR32021STRADAENUS/Consultant-SAP-HCM-Paie-senior</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>70-85K€</t>
         </is>
       </c>
-      <c r="Q76" s="41" t="inlineStr">
+      <c r="Q77" s="41" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="80" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="80" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>paie</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>SAP HCM Technico-Functional Consultant French Payroll</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>Apps IT Limited</t>
         </is>
       </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F78" s="5" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G78" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="H78" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>Oui (100% remote)</t>
         </is>
       </c>
-      <c r="J77" s="6" t="inlineStr">
+      <c r="J78" s="6" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="K77" s="6" t="inlineStr">
+      <c r="K78" s="6" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="L77" s="5" t="inlineStr">
+      <c r="L78" s="5" t="inlineStr">
         <is>
           <t>Publié 17/06/2026. 100% remote — fit parfait pour Anglet. Profil technico-fonctionnel SAP HCM French Payroll. À vérifier disponibilité (publié il y a 6 semaines). Lien : rechercher "Apps IT" sur free-work.com/fr/tech-it/jobs/sap-hcm.</t>
         </is>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="M78" s="5" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/jobs/sap-hcm</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="Q77" s="41" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="79" t="inlineStr">
+      <c r="Q78" s="41" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="79" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>paie</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>SAP HCM Consultant French Payroll</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>Client via Movement Group</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>movementgroup.uk</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Oui (100% remote)</t>
         </is>
       </c>
-      <c r="J78" s="6" t="inlineStr">
+      <c r="J79" s="6" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="K78" s="6" t="inlineStr">
+      <c r="K79" s="6" t="inlineStr">
         <is>
           <t>12 mois + extension</t>
         </is>
       </c>
-      <c r="L78" s="5" t="inlineStr">
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>Movement Group = cabinet recrutement SAP UK/Europe. 100% remote, 12 mois extensible. Outside IR35 (client probablement UK/international). 3+ ans SAP Payroll France requis. Durée et remote = fit parfait.</t>
         </is>
       </c>
-      <c r="M78" s="5" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr">
         <is>
           <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="Q78" s="41" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="80" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B79" s="39" t="inlineStr">
-        <is>
-          <t>postulé</t>
-        </is>
-      </c>
-      <c r="C79" s="39" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Expert(e) AMOA et/ou Intégration SIRH (Freelance)</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>Mercer | ConvictionsRH</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>convictionsrh.com</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H79" s="6" t="inlineStr">
-        <is>
-          <t>Selon missions clients</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>Flexible selon clients</t>
-        </is>
-      </c>
-      <c r="J79" s="6" t="n"/>
-      <c r="K79" s="6" t="n"/>
-      <c r="L79" s="5" t="inlineStr">
-        <is>
-          <t>Mission freelance sous-traitance chez Mercer | ConvictionsRH sur SAP SF, Workday, Oracle HCM — cadrage, specs, recette, montées de version. Contact direct : soustraitance@convictionsrh.com. Gaëtan = profil expert indépendant idéal.</t>
-        </is>
-      </c>
-      <c r="M79" s="5" t="inlineStr">
-        <is>
-          <t>https://www.convictionsrh.com/job/expert-amoa-et-ou-integration-sirh-freelance/</t>
-        </is>
-      </c>
-      <c r="N79" s="39" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O79" s="39" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
-      <c r="P79" s="39" t="n"/>
       <c r="Q79" s="41" t="n"/>
     </row>
     <row r="80">
@@ -63730,29 +63737,29 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="B80" s="39" t="inlineStr">
+        <is>
+          <t>postulé</t>
+        </is>
+      </c>
+      <c r="C80" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Technico-Fonctionnel SAP HCM French Payroll</t>
+          <t>Expert(e) AMOA et/ou Intégration SIRH (Freelance)</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Apps IT Limited</t>
+          <t>Mercer | ConvictionsRH</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>convictionsrh.com</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr">
@@ -63762,24 +63769,24 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Selon missions clients</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
+          <t>Flexible selon clients</t>
         </is>
       </c>
       <c r="J80" s="6" t="n"/>
       <c r="K80" s="6" t="n"/>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>Mission 100% remote sur SAP HCM paie française, correspond exactement aux 14 ans d'expertise SAP HR de Gaëtan. Peu de missions SAP HCM affichent un remote total ; à prioriser.</t>
+          <t>Mission freelance sous-traitance chez Mercer | ConvictionsRH sur SAP SF, Workday, Oracle HCM — cadrage, specs, recette, montées de version. Contact direct : soustraitance@convictionsrh.com. Gaëtan = profil expert indépendant idéal.</t>
         </is>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/sap-hcm</t>
+          <t>https://www.convictionsrh.com/job/expert-amoa-et-ou-integration-sirh-freelance/</t>
         </is>
       </c>
       <c r="N80" s="39" t="inlineStr">
@@ -63789,15 +63796,11 @@
       </c>
       <c r="O80" s="39" t="inlineStr">
         <is>
-          <t>600-700€/j</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P80" s="39" t="n"/>
-      <c r="Q80" s="41" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
+      <c r="Q80" s="41" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="80" t="inlineStr">
@@ -63805,29 +63808,29 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B81" s="39" t="inlineStr">
-        <is>
-          <t>out of scope</t>
-        </is>
-      </c>
-      <c r="C81" s="39" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>paie</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>SAP SuccessFactors ESM Consultant</t>
+          <t>Technico-Fonctionnel SAP HCM French Payroll</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via Whitehall Resources)</t>
+          <t>Apps IT Limited</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>whitehallresources.com</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -63837,7 +63840,7 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>Anywhere (remote)</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
@@ -63849,22 +63852,22 @@
       <c r="K81" s="6" t="n"/>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>Mission SuccessFactors annoncée en remote total sans contrainte de pays, ce qui est rare sur ce marché. Whitehall place régulièrement des consultants SAP HR en Europe et le contact se fait directement avec un recruteur spécialisé. Référence BBBH67445 à citer lors de la prise de contact.</t>
+          <t>Mission 100% remote sur SAP HCM paie française, correspond exactement aux 14 ans d'expertise SAP HR de Gaëtan. Peu de missions SAP HCM affichent un remote total ; à prioriser.</t>
         </is>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>https://www.whitehallresources.com/jobs/?search=SuccessFactors</t>
+          <t>https://www.free-work.com/fr/tech-it/jobs/sap-hcm</t>
         </is>
       </c>
       <c r="N81" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
       <c r="O81" s="39" t="inlineStr">
         <is>
-          <t>650-750€/j</t>
+          <t>600-700€/j</t>
         </is>
       </c>
       <c r="P81" s="39" t="n"/>
@@ -63882,7 +63885,7 @@
       </c>
       <c r="B82" s="39" t="inlineStr">
         <is>
-          <t>Postulé</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="C82" s="39" t="inlineStr">
@@ -63892,27 +63895,27 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Senior HR Transformation Consultant</t>
+          <t>SAP SuccessFactors ESM Consultant</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Resultance</t>
+          <t>n.c. (via Whitehall Resources)</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>whitehallresources.com</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>Freelance / indépendant (CDD de mission)</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Union européenne</t>
+          <t>Anywhere (remote)</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -63920,34 +63923,26 @@
           <t>100% remote</t>
         </is>
       </c>
-      <c r="J82" s="6" t="inlineStr">
-        <is>
-          <t>Non affiché</t>
-        </is>
-      </c>
-      <c r="K82" s="6" t="inlineStr">
-        <is>
-          <t>Sept. à déc. 2026, extension possible ; 2 à 3 jours par semaine</t>
-        </is>
-      </c>
+      <c r="J82" s="6" t="n"/>
+      <c r="K82" s="6" t="n"/>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>Cabinet de conseil né au Luxembourg, présent en France, Belgique et Royaume-Uni, 51 à 200 salariés, qui adosse une part de ses honoraires aux résultats obtenus. La mission porte sur la refonte du modèle opérationnel RH et des processus de bout en bout : animation d'ateliers de conception, consolidation des processus sur tous les piliers RH, définition des rôles et de la gouvernance, feuille de route de transformation et conduite du changement, plus la supervision d'un consultant junior. Les 7 à 10 ans demandés couvrent explicitement l'implémentation SIRH, donc les quinze ans sur SAP HR répondent au critère ; l'expérience de supervision de l'équipe Inde chez ALTI répond au volet encadrement, et le passage en cabinet est présenté comme un atout fort. Le format à temps partiel et en remote intégral permet de cumuler avec une autre mission. Offre publiée le 05/08/2026, déjà 67 candidats, réponse annoncée sous une semaine ; candidature simplifiée LinkedIn. Recruteuse : Olga Adam, Talent Acquisition Manager. Point d'entrée réseau : Ludovic Van Sinay, relation de 3e degré et ancien de L'Oréal, à contacter avant de postuler.</t>
+          <t>Mission SuccessFactors annoncée en remote total sans contrainte de pays, ce qui est rare sur ce marché. Whitehall place régulièrement des consultants SAP HR en Europe et le contact se fait directement avec un recruteur spécialisé. Référence BBBH67445 à citer lors de la prise de contact.</t>
         </is>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4448991282/</t>
+          <t>https://www.whitehallresources.com/jobs/?search=SuccessFactors</t>
         </is>
       </c>
       <c r="N82" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_Resultance.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
       <c r="O82" s="39" t="inlineStr">
         <is>
-          <t>À discuter</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P82" s="39" t="n"/>
@@ -63958,84 +63953,85 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="77" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="A83" s="80" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C83" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>SAP HCM Consultant (French Payroll)</t>
+          <t>Senior HR Transformation Consultant</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Movement Group</t>
+          <t>Resultance</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>movementgroup.uk</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Freelance (12 mois + extension)</t>
+          <t>Freelance / indépendant (CDD de mission)</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Remote (100%)</t>
+          <t>Union européenne</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>100% remote</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>TJM Outside IR35</t>
+          <t>Non affiché</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>12 mois</t>
+          <t>Sept. à déc. 2026, extension possible ; 2 à 3 jours par semaine</t>
         </is>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>Mission freelance remote, paie française SAP HCM. 3 ans expérience requis. Fit parfait.</t>
+          <t>Cabinet de conseil né au Luxembourg, présent en France, Belgique et Royaume-Uni, 51 à 200 salariés, qui adosse une part de ses honoraires aux résultats obtenus. La mission porte sur la refonte du modèle opérationnel RH et des processus de bout en bout : animation d'ateliers de conception, consolidation des processus sur tous les piliers RH, définition des rôles et de la gouvernance, feuille de route de transformation et conduite du changement, plus la supervision d'un consultant junior. Les 7 à 10 ans demandés couvrent explicitement l'implémentation SIRH, donc les quinze ans sur SAP HR répondent au critère ; l'expérience de supervision de l'équipe Inde chez ALTI répond au volet encadrement, et le passage en cabinet est présenté comme un atout fort. Le format à temps partiel et en remote intégral permet de cumuler avec une autre mission. Offre publiée le 05/08/2026, déjà 67 candidats, réponse annoncée sous une semaine ; candidature simplifiée LinkedIn. Recruteuse : Olga Adam, Talent Acquisition Manager. Point d'entrée réseau : Ludovic Van Sinay, relation de 3e degré et ancien de L'Oréal, à contacter avant de postuler.</t>
         </is>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4448991282/</t>
+        </is>
+      </c>
+      <c r="N83" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Resultance.pdf</t>
+        </is>
+      </c>
+      <c r="O83" s="39" t="inlineStr">
+        <is>
+          <t>À discuter</t>
+        </is>
+      </c>
+      <c r="P83" s="39" t="n"/>
       <c r="Q83" s="41" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -64047,7 +64043,7 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>pourvu</t>
+          <t>paie</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
@@ -64057,27 +64053,27 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Consultant AMOA SIRH (Performance &amp; International) - Full remote possible</t>
+          <t>SAP HCM Consultant (French Payroll)</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Cherry Pick (pour client)</t>
+          <t>Movement Group</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>movementgroup.uk</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Freelance (12 mois + extension)</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote (100%)</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
@@ -64085,16 +64081,24 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="J84" s="6" t="n"/>
-      <c r="K84" s="6" t="n"/>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>TJM Outside IR35</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>12 mois</t>
+        </is>
+      </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>AMOA SIRH international, lien Group HR et entités locales, évaluation de la performance. Full remote possible. Très bon fit profil L'Oréal mondial.</t>
+          <t>Mission freelance remote, paie française SAP HCM. 3 ans expérience requis. Fit parfait.</t>
         </is>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/consultant-moa-amoa/job-mission/consultant-amoa-sirh-performance-international-full-remote-possible</t>
+          <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -64119,155 +64123,146 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B85" s="39" t="inlineStr">
-        <is>
-          <t>Expiré</t>
-        </is>
-      </c>
-      <c r="C85" s="39" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>pourvu</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP HCM Time senior</t>
+          <t>Consultant AMOA SIRH (Performance &amp; International) - Full remote possible</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Strada (ex-Alight)</t>
+          <t>Cherry Pick (pour client)</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>careers.alight.com/strada</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>Colombes (92)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>Oui (depuis toute la France)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J85" s="6" t="n"/>
       <c r="K85" s="6" t="n"/>
       <c r="L85" s="5" t="inlineStr">
         <is>
+          <t>AMOA SIRH international, lien Group HR et entités locales, évaluation de la performance. Full remote possible. Très bon fit profil L'Oréal mondial.</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/consultant-moa-amoa/job-mission/consultant-amoa-sirh-performance-international-full-remote-possible</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>650-750€/j</t>
+        </is>
+      </c>
+      <c r="Q85" s="41" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="77" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B86" s="39" t="inlineStr">
+        <is>
+          <t>Expiré</t>
+        </is>
+      </c>
+      <c r="C86" s="39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SAP HCM Time senior</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>Strada (ex-Alight)</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>careers.alight.com/strada</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>Colombes (92)</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>Oui (depuis toute la France)</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="n"/>
+      <c r="K86" s="6" t="n"/>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
           <t>Strada 1er partenaire SAP HR. Module Time Management SAP HCM. Remote France confirmé. En complément du poste Paie senior (voir autre entrée).</t>
         </is>
       </c>
-      <c r="M85" s="5" t="inlineStr">
+      <c r="M86" s="5" t="inlineStr">
         <is>
           <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27913STRADAENUS/Consultant-SAP-HCM-Time-senior</t>
         </is>
       </c>
-      <c r="N85" s="39" t="inlineStr">
+      <c r="N86" s="39" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O85" s="39" t="inlineStr">
+      <c r="O86" s="39" t="inlineStr">
         <is>
           <t>70-85K€</t>
-        </is>
-      </c>
-      <c r="P85" s="39" t="n"/>
-      <c r="Q85" s="41" t="inlineStr">
-        <is>
-          <t>07/05/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="78" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="inlineStr">
-        <is>
-          <t>Technico-Fonctionnel SAP HCM French Payroll</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>Apps IT Limited</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>Free-Work</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J86" s="6" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="K86" s="6" t="inlineStr">
-        <is>
-          <t>6 mois renouvelable</t>
-        </is>
-      </c>
-      <c r="L86" s="5" t="inlineStr">
-        <is>
-          <t>100% télétravail, démarrage ASAP. SAP HCM Payroll FR. Profil orienté technique (ABAP) – Gaëtan est fonctionnel mais maîtrise le domaine. À évaluer.</t>
-        </is>
-      </c>
-      <c r="M86" s="5" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/technico-fonctionnel-sap-hcm-french-payroll</t>
-        </is>
-      </c>
-      <c r="N86" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
-        </is>
-      </c>
-      <c r="O86" s="39" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P86" s="39" t="n"/>
       <c r="Q86" s="41" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>07/05/2025</t>
         </is>
       </c>
     </row>
@@ -64289,224 +64284,220 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
+          <t>Technico-Fonctionnel SAP HCM French Payroll</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Apps IT Limited</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Free-Work</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>6 mois renouvelable</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>100% télétravail, démarrage ASAP. SAP HCM Payroll FR. Profil orienté technique (ABAP) – Gaëtan est fonctionnel mais maîtrise le domaine. À évaluer.</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/technico-fonctionnel-sap-hcm-french-payroll</t>
+        </is>
+      </c>
+      <c r="N87" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
+        </is>
+      </c>
+      <c r="O87" s="39" t="inlineStr">
+        <is>
+          <t>650-750€/j</t>
+        </is>
+      </c>
+      <c r="P87" s="39" t="n"/>
+      <c r="Q87" s="41" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="78" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>paie</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
           <t>SAP HCM Consultant (French Payroll)</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>Client anonyme (via Movement Group)</t>
         </is>
       </c>
-      <c r="F87" s="5" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>movementgroup.uk</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H87" s="6" t="inlineStr">
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
+      <c r="I88" s="6" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J87" s="6" t="inlineStr">
+      <c r="J88" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K87" s="6" t="inlineStr">
+      <c r="K88" s="6" t="inlineStr">
         <is>
           <t>12 mois</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="L88" s="5" t="inlineStr">
         <is>
           <t>SAP HCM payroll FR config, 100% remote, Outside IR35 — bon fit SAP HR mais spécialisé paie France uniquement (profil Gaetan = SAP HR international L'Oréal 40+ pays)</t>
         </is>
       </c>
-      <c r="M87" s="5" t="inlineStr">
+      <c r="M88" s="5" t="inlineStr">
         <is>
           <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
-      <c r="N87" s="39" t="inlineStr">
+      <c r="N88" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O87" s="39" t="n"/>
-      <c r="P87" s="39" t="n"/>
-      <c r="Q87" s="41" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="82" t="inlineStr">
+      <c r="O88" s="39" t="n"/>
+      <c r="P88" s="39" t="n"/>
+      <c r="Q88" s="41" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="82" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>paie</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D88" s="39" t="inlineStr">
+      <c r="D89" s="39" t="inlineStr">
         <is>
           <t>SAP HCM-Payroll Consultant</t>
         </is>
       </c>
-      <c r="E88" s="39" t="inlineStr">
+      <c r="E89" s="39" t="inlineStr">
         <is>
           <t>N/C (via eursap.eu)</t>
         </is>
       </c>
-      <c r="F88" s="39" t="inlineStr">
+      <c r="F89" s="39" t="inlineStr">
         <is>
           <t>eursap.eu</t>
         </is>
       </c>
-      <c r="G88" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H88" s="39" t="inlineStr">
+      <c r="G89" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H89" s="39" t="inlineStr">
         <is>
           <t>Multiple EU + Remote</t>
         </is>
       </c>
-      <c r="I88" s="39" t="inlineStr">
+      <c r="I89" s="39" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J88" s="39" t="inlineStr">
+      <c r="J89" s="39" t="inlineStr">
         <is>
           <t>N/C</t>
         </is>
       </c>
-      <c r="K88" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="L88" s="39" t="inlineStr">
+      <c r="K89" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="L89" s="39" t="inlineStr">
         <is>
           <t>SAP HCM Payroll international, remote-friendly ; ref 29132</t>
         </is>
       </c>
-      <c r="M88" s="39" t="inlineStr">
+      <c r="M89" s="39" t="inlineStr">
         <is>
           <t>https://eursap.eu/sap-jobs/france/</t>
         </is>
       </c>
-      <c r="N88" s="39" t="n"/>
-      <c r="O88" s="39" t="n"/>
-      <c r="P88" s="39" t="inlineStr">
+      <c r="N89" s="39" t="n"/>
+      <c r="O89" s="39" t="n"/>
+      <c r="P89" s="39" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="Q88" s="39" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="78" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>SAP Payroll Implementation Lead - France</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>Strada Global</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Strada Global Careers / Remote Rocketship</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>100% remote</t>
-        </is>
-      </c>
-      <c r="J89" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K89" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="L89" s="5" t="inlineStr">
-        <is>
-          <t>Strada = RH/paie globale (SAP, Oracle, Workday). Lead impl SAP Payroll France, 5+ implémentations SAP HCM requises, connaissance paie FR. Profil Gaëtan SAP HR adjacent mais payroll pur = frein partiel.</t>
-        </is>
-      </c>
-      <c r="M89" s="5" t="inlineStr">
-        <is>
-          <t>https://careers.stradaglobal.com/careers/job/1133913392690-sap-payroll-implementation-lead-france-granada-spain</t>
-        </is>
-      </c>
-      <c r="N89" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O89" s="39" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="P89" s="39" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
-      <c r="Q89" s="41" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
+      <c r="Q89" s="39" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="78" t="inlineStr">
@@ -64526,137 +64517,224 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
+          <t>SAP Payroll Implementation Lead - France</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Strada Global</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Strada Global Careers / Remote Rocketship</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>100% remote</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>Strada = RH/paie globale (SAP, Oracle, Workday). Lead impl SAP Payroll France, 5+ implémentations SAP HCM requises, connaissance paie FR. Profil Gaëtan SAP HR adjacent mais payroll pur = frein partiel.</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
+          <t>https://careers.stradaglobal.com/careers/job/1133913392690-sap-payroll-implementation-lead-france-granada-spain</t>
+        </is>
+      </c>
+      <c r="N90" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O90" s="39" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="P90" s="39" t="inlineStr">
+        <is>
+          <t>07/2026</t>
+        </is>
+      </c>
+      <c r="Q90" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="78" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>paie</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
           <t>Formateur SAP Employee Central &amp; Payroll Integration</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="E91" s="5" t="inlineStr">
         <is>
           <t>n.c. (via Freelancer.com)</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F91" s="5" t="inlineStr">
         <is>
           <t>freelancer.com</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H90" s="6" t="inlineStr">
+      <c r="H91" s="6" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I90" s="6" t="inlineStr">
+      <c r="I91" s="6" t="inlineStr">
         <is>
           <t>100% remote</t>
         </is>
       </c>
-      <c r="J90" s="6" t="inlineStr">
+      <c r="J91" s="6" t="inlineStr">
         <is>
           <t>~488 $ (enchère moyenne)</t>
         </is>
       </c>
-      <c r="K90" s="6" t="inlineStr">
+      <c r="K91" s="6" t="inlineStr">
         <is>
           <t>Court, 4 jours restants pour candidater</t>
         </is>
       </c>
-      <c r="L90" s="5" t="inlineStr">
+      <c r="L91" s="5" t="inlineStr">
         <is>
           <t>Le client cherche un praticien SuccessFactors expérimenté pour dispenser une formation sur Employee Central et son intégration paie de bout en bout. C'est exactement le périmètre des go-live OneProfile et OnePayroll ; peu de profils peuvent enseigner cette intégration pour l'avoir livrée en production sur 40 pays. Le budget est faible et la mission courte, mais le format se prête à une première référence de formateur SAP, utile pour ouvrir le segment formation. Date limite proche, à traiter vite.</t>
         </is>
       </c>
-      <c r="M90" s="5" t="inlineStr">
+      <c r="M91" s="5" t="inlineStr">
         <is>
           <t>https://www.freelancer.com/jobs/sap/</t>
         </is>
       </c>
-      <c r="N90" s="39" t="inlineStr">
+      <c r="N91" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
-      <c r="O90" s="39" t="inlineStr">
+      <c r="O91" s="39" t="inlineStr">
         <is>
           <t>À discuter</t>
         </is>
       </c>
-      <c r="P90" s="39" t="n"/>
-      <c r="Q90" s="41" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="77" t="inlineStr">
+      <c r="P91" s="39" t="n"/>
+      <c r="Q91" s="41" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B91" s="39" t="inlineStr">
+      <c r="B92" s="39" t="inlineStr">
         <is>
           <t>pourvu</t>
         </is>
       </c>
-      <c r="C91" s="39" t="inlineStr">
+      <c r="C92" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Consultant SIRH (H/F) - N2F</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>N2jsoft</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>welcometothejungle.com</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
         <is>
           <t>Montagnat (remote)</t>
         </is>
       </c>
-      <c r="I91" s="6" t="inlineStr">
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>100% remote</t>
         </is>
       </c>
-      <c r="J91" s="6" t="n"/>
-      <c r="K91" s="6" t="n"/>
-      <c r="L91" s="5" t="inlineStr">
+      <c r="J92" s="6" t="n"/>
+      <c r="K92" s="6" t="n"/>
+      <c r="L92" s="5" t="inlineStr">
         <is>
           <t>Poste en CDI intégralement remote chez l'éditeur de N2F, avec formation interne sur le produit. Le remote total lève la contrainte principale ; le chef de projet SIRH du même éditeur est déjà suivi dans le tableur. Éditeur de taille moyenne, donc rémunération probablement sous la fourchette cible.</t>
         </is>
       </c>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="M92" s="5" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/n2jsoft-fr/jobs/consultant-logiciel-rh-h-f-n2f_montagnat_N2JSO_M2lVjoW</t>
         </is>
       </c>
-      <c r="N91" s="39" t="inlineStr">
+      <c r="N92" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.html</t>
         </is>
       </c>
-      <c r="O91" s="39" t="inlineStr">
+      <c r="O92" s="39" t="inlineStr">
         <is>
           <t>65-75K€</t>
         </is>
       </c>
-      <c r="P91" s="39" t="n"/>
-      <c r="Q91" s="41" t="inlineStr">
+      <c r="P92" s="39" t="n"/>
+      <c r="Q92" s="41" t="inlineStr">
         <is>
           <t>06/10/2026</t>
         </is>

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -384,7 +384,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -587,6 +587,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="50" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -58062,7 +58065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="16" max="17"/>
@@ -58675,77 +58678,83 @@
       <c r="Q8" s="41" t="n"/>
     </row>
     <row r="9" ht="320" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Refusé</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="A9" s="98" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Customer Success Manager</t>
+          <t>Chef de Produit Confirmé(e)</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>SAP Taulia</t>
+          <t>Octime</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>octime.com</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Londres (UK)</t>
+          <t>Biron (64)</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>85-110 K€</t>
+          <t>NC (estimation marché 55-65K€)</t>
         </is>
       </c>
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Fit fort — 5+ ans requis, projets mondiaux (L'Oréal 40 pays), QBR, escalades. Working capital/supply chain finance angle (lien OnePayroll L'Oréal). CV + LM Taulia déjà prêts. Question visa UK à clarifier. Fourchette salaire 85-110k€ exactement visée.</t>
+          <t>Éditeur de logiciels RH (gestion des temps et planification, workforce management). Poste chef de produit sur la roadmap fonctionnelle. Virage produit plutot que consultant SIRH ; candidature appuyée sur la refonte d'un outil de gestion des temps chez L'Oréal et l'expérience de gestion produit à WallOfTraders.com. CV dédié envoyé (Resume_GaetanFRANCOIS_Octime).</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4421991103/</t>
+          <t>https://www.octime.com/le-groupe-octime-recrute-chef-de-produit-confirme-f-h/</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_Taulia_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_Octime.pdf</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>100 K€</t>
-        </is>
-      </c>
+          <t>60-65K€</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="Q9" s="41" t="n"/>
     </row>
     <row r="10" ht="128" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
@@ -58755,7 +58764,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Expiré</t>
+          <t>Refusé</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -58765,17 +58774,17 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Solutions Consultant, HRIS | France</t>
+          <t>Customer Success Manager</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>SAP Taulia</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>deel.com/careers / builtin.com</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -58785,50 +58794,50 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Londres (UK)</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Full remote</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>85-110 K€</t>
         </is>
       </c>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Pré-sales HRIS pour plateforme RH globale Deel (150+ pays), démonstrations SF-like, 2+ ans selling HR tech, FR+EN — FIT PARFAIT. Vérifier statut actif sur deel.com/careers ou jobs.ashbyhq.com/deel</t>
+          <t>Fit fort — 5+ ans requis, projets mondiaux (L'Oréal 40 pays), QBR, escalades. Working capital/supply chain finance angle (lien OnePayroll L'Oréal). CV + LM Taulia déjà prêts. Question visa UK à clarifier. Fourchette salaire 85-110k€ exactement visée.</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>https://www.deel.com/careers/</t>
+          <t>https://www.linkedin.com/jobs/view/4421991103/</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>CV_GaetanFRANCOIS_Taulia_EN.pdf</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>85 K€</t>
+          <t>100 K€</t>
         </is>
       </c>
     </row>
     <row r="11" ht="224" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Hors profil</t>
+          <t>Expiré</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -58838,27 +58847,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>People Operations Specialist</t>
+          <t>Solutions Consultant, HRIS | France</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Mercor</t>
+          <t>Deel</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>deel.com/careers / builtin.com</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>100% Remote</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -58868,18 +58877,18 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>60-80 $/h</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K11" s="6" t="n"/>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Bon match — HRIS (SAP SF ✓, Workday, Oracle), Fortune 500 ✓, multi-pays ✓</t>
+          <t>Pré-sales HRIS pour plateforme RH globale Deel (150+ pays), démonstrations SF-like, 2+ ans selling HR tech, FR+EN — FIT PARFAIT. Vérifier statut actif sur deel.com/careers ou jobs.ashbyhq.com/deel</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4428131075/</t>
+          <t>https://www.deel.com/careers/</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -58889,7 +58898,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>75 $/h</t>
+          <t>85 K€</t>
         </is>
       </c>
     </row>
@@ -58911,144 +58920,140 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
+          <t>People Operations Specialist</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Mercor</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>100% Remote</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>60-80 $/h</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>Bon match — HRIS (SAP SF ✓, Workday, Oracle), Fortune 500 ✓, multi-pays ✓</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4428131075/</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>75 $/h</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="160" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Hors profil</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
           <t>Expert Intégration SAP SuccessFactors BTP</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>LINKWAY</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>12 mois</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Projet bancaire, intégration SF + SAP BTP — full remote, anglais courant requis</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/expert-integration-sap-successfactors-btp</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>750 €/j</t>
         </is>
       </c>
-      <c r="Q12" s="41" t="inlineStr">
+      <c r="Q13" s="41" t="inlineStr">
         <is>
           <t>06/03/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="160" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>salaire fixe 40k</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Customer Success Manager</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>AssessFirst</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>welcometothejungle.com</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>Full remote</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>12 mois</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>HR Tech, full remote, renouvellement / adoption produit — profil CSM Senior</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/fr/companies/assessfirst/jobs/customer-success-manager_paris_ASSES_M4x97o8</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>70 K€</t>
         </is>
       </c>
     </row>
@@ -59060,7 +59065,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>30% voyage</t>
+          <t>salaire fixe 40k</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -59070,17 +59075,17 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>SAP Consultant OR Trainer (Any module)</t>
+          <t>Customer Success Manager</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Eursap</t>
+          <t>AssessFirst</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>eursap.eu</t>
+          <t>welcometothejungle.com</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -59090,7 +59095,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -59100,32 +59105,32 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>80-100 K€ + equity</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>3 mois renouvelable</t>
+          <t>12 mois</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>French language, remote, consultant ou formateur SAP — bon fit profil formateur/consultant</t>
+          <t>HR Tech, full remote, renouvellement / adoption produit — profil CSM Senior</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>https://eursap.eu/jobs/sap-consultant-or-trainer-any-module-34811-remote</t>
+          <t>https://www.welcometothejungle.com/fr/companies/assessfirst/jobs/customer-success-manager_paris_ASSES_M4x97o8</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>90 K€</t>
+          <t>70 K€</t>
         </is>
       </c>
     </row>
@@ -59137,7 +59142,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>allemand</t>
+          <t>30% voyage</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -59147,17 +59152,17 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Senior SAP SF Inhouse Consultant – Integration EC</t>
+          <t>SAP Consultant OR Trainer (Any module)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Hornbach Baumarkt AG</t>
+          <t>Eursap</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>indeed.fr</t>
+          <t>eursap.eu</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -59167,7 +59172,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -59177,18 +59182,22 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="n"/>
+          <t>80-100 K€ + equity</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>3 mois renouvelable</t>
+        </is>
+      </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>Remote, avancement technique des systèmes RH via SuccessFactors EC</t>
+          <t>French language, remote, consultant ou formateur SAP — bon fit profil formateur/consultant</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>https://karriere.hornbach.de/technologie/stellenangebot/remote-senior-sap-sf-inhouse-consul/bbdff4bc-96bb-4498-b529-c61a335ca3db</t>
+          <t>https://eursap.eu/jobs/sap-consultant-or-trainer-any-module-34811-remote</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -59198,7 +59207,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>80 K€</t>
+          <t>90 K€</t>
         </is>
       </c>
     </row>
@@ -59210,204 +59219,204 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
+          <t>allemand</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Senior SAP SF Inhouse Consultant – Integration EC</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Hornbach Baumarkt AG</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>indeed.fr</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Remote, avancement technique des systèmes RH via SuccessFactors EC</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>https://karriere.hornbach.de/technologie/stellenangebot/remote-senior-sap-sf-inhouse-consul/bbdff4bc-96bb-4498-b529-c61a335ca3db</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>80 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="128" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
           <t>fermé</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Customer Success Manager SaaS</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Mobility Work (GMAO)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="K17" s="6" t="inlineStr">
         <is>
           <t>3 mois</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>CSM industriel SaaS, full remote, FR+EN+ES requis - Biarritz compatible</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/customer-success-manager-saas-full-remote-at-mobility-work-gmao-4344455726</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.pdf</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>65 K€</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="128" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="18" ht="224" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Éliminé</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Software Implementation Consultant</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Avature</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>Non (80% déplacements)</t>
         </is>
       </c>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>HR software implémentation, bon profil fonctionnel, mais 80% sur site client = incompatible remote</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4400989929/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="224" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Hors profil</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>SAP HCM Consultant – French Payroll</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Movement Group</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>movementgroup.uk</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Full remote</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+      <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Fit parfait — SAP HCM paie française, remote</t>
+          <t>HR software implémentation, bon profil fonctionnel, mais 80% sur site client = incompatible remote</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>90 K€</t>
+          <t>https://www.linkedin.com/jobs/view/4400989929/</t>
         </is>
       </c>
     </row>
@@ -59429,67 +59438,58 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Directeur de Programme SIRH Senior</t>
+          <t>SAP HCM Consultant – French Payroll</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>LeHibou</t>
+          <t>Movement Group</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>movementgroup.uk</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>n.p.</t>
+          <t>Full remote</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>650-780 €/j</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>18 mois</t>
-        </is>
-      </c>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="n"/>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Transformation RH globale, gouvernance, budget — profil senior idéal</t>
+          <t>Fit parfait — SAP HCM paie française, remote</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
+          <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>750 €/j</t>
-        </is>
-      </c>
-      <c r="Q19" s="41" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
+          <t>90 K€</t>
         </is>
       </c>
     </row>
@@ -59509,59 +59509,69 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Data Consultant HCM / Workday</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Jobgether</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Directeur de Programme SIRH Senior</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>LeHibou</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>free-work.com</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>100% Remote</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Full remote</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>SQL avancé, ETL, migration Workday — trop technique, mauvais stack</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4425836016/</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>n.p.</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>650-780 €/j</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>18 mois</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Transformation RH globale, gouvernance, budget — profil senior idéal</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/mission-freelance-directeur-de-programme-sirh-senior-h-f</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>650 €/j</t>
+          <t>750 €/j</t>
+        </is>
+      </c>
+      <c r="Q20" s="41" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -59573,7 +59583,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Non pertinent</t>
+          <t>Hors profil</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -59583,12 +59593,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Management Consultant (évaluation tâches IA)</t>
+          <t>Data Consultant HCM / Workday</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Call For Referral</t>
+          <t>Jobgether</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -59603,27 +59613,37 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Londres, UK</t>
+          <t>100% Remote</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Full remote</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>$90-200/h</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Évaluation de tâches IA pour entraînement modèles - pas pertinent pour le profil</t>
+          <t>SQL avancé, ETL, migration Workday — trop technique, mauvais stack</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4414336302/</t>
+          <t>https://www.linkedin.com/jobs/view/4425836016/</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>650 €/j</t>
         </is>
       </c>
     </row>
@@ -59645,119 +59665,104 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Management Consultant (évaluation tâches IA)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Call For Referral</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Londres, UK</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>$90-200/h</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Évaluation de tâches IA pour entraînement modèles - pas pertinent pour le profil</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4414336302/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="240" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Non pertinent</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Consultant Expérimenté HR Transformation - SAP SuccessFactors</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>La Défense</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Entry level (1-3 ans) - trop junior pour le profil 15 ans XP</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426166097/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="240" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>no remote</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SIRH SuccessFactors</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>freelance-informatique.fr</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>Issy-les-Moulineaux (92)</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>n.p.</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>9 mois</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SIRH SF, durée intéressante, proche Paris</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>https://www.freelance-informatique.fr/mission-chef-de-projet-technico-fonctionnel-h-f-260603C004</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>700 €/j</t>
         </is>
       </c>
     </row>
@@ -59769,228 +59774,223 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
+          <t>no remote</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SIRH SuccessFactors</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>freelance-informatique.fr</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Issy-les-Moulineaux (92)</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>n.p.</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>9 mois</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SIRH SF, durée intéressante, proche Paris</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.freelance-informatique.fr/mission-chef-de-projet-technico-fonctionnel-h-f-260603C004</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>700 €/j</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="192" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
           <t>pourvu</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Implementation Consultant</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Deel</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>builtin.com/company/deel/jobs</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>Remote (EMEA probable)</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="J24" s="6" t="inlineStr">
+      <c r="J25" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Implémentation plateforme HRIS/paie globale Deel, onboarding clients, configuration, formation — 3+ ans exp SaaS/HRIS/paie. Posté il y a 12 jours (19/06/2026)</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>https://builtin.com/job/implementation-consultant/8081628</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>80 K€</t>
-        </is>
-      </c>
-      <c r="Q24" s="41" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="192" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>postulé</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>SAP Consultant / Trainer (Any Module) – IA + S/4HANA</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Startup IA/SAP (via Eursap)</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Eursap.eu</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>Full remote UE (30% déplacements Europe/mois)</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>80 000 - 100 000 € + stock-options jusqu'à 120K€</t>
         </is>
       </c>
       <c r="K25" s="6" t="n"/>
       <c r="L25" s="5" t="inlineStr">
         <is>
+          <t>Implémentation plateforme HRIS/paie globale Deel, onboarding clients, configuration, formation — 3+ ans exp SaaS/HRIS/paie. Posté il y a 12 jours (19/06/2026)</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>https://builtin.com/job/implementation-consultant/8081628</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>80 K€</t>
+        </is>
+      </c>
+      <c r="Q25" s="41" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="208" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>postulé</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>SAP Consultant / Trainer (Any Module) – IA + S/4HANA</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Startup IA/SAP (via Eursap)</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Eursap.eu</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Full remote UE (30% déplacements Europe/mois)</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>80 000 - 100 000 € + stock-options jusqu'à 120K€</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
           <t>Startup US pionnière IA + SAP S/4HANA, 1er collaborateur européen. Rôle hybride consultant/formateur : intégrer IA dans projets SAP S/4HANA, former partenaires intégrateurs, retours engineering US. Tous modules acceptés (HCM inclus). 5+ ans SAP requis. Salaire excellent + equity. Profil formateur SAP de Gaëtan = fit très fort. Démarrage août 2026.</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>https://eursap.eu/jobs/sap-consultant-or-trainer-any-module-34811-remote</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>95 K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="208" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>postulé</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SAP SuccessFactors (H/F)</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>HR Path</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn / HR Path careers</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>Paris La Défense (92)</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Télétravail + déplacements intl</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>SF multi-modules, 2+ ans, anglais requis, projets intl, cabinet conseil RH mondial 22 pays</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>60 K€</t>
-        </is>
-      </c>
-      <c r="Q26" s="41" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -60012,17 +60012,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Consultant Confirmé SIRH - SAP HR H/F</t>
+          <t>Consultant SAP SuccessFactors (H/F)</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>ACT-ON HRIS</t>
+          <t>HR Path</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn / HR Path careers</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -60032,12 +60032,12 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Neuilly-sur-Seine (92)</t>
+          <t>Paris La Défense (92)</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Télétravail flexible</t>
+          <t>Télétravail + déplacements intl</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -60045,15 +60045,19 @@
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K27" s="6" t="n"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>SAP HR multi-modules (paramétrage, déploiement, recette), grands groupes, 3+ ans exp — différent du poste SF déjà en base</t>
+          <t>SF multi-modules, 2+ ans, anglais requis, projets intl, cabinet conseil RH mondial 22 pays</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4342380005</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-SAP-SuccessFactors-(HF)-75-92042/818651901/</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -60063,7 +60067,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>55 K€</t>
+          <t>60 K€</t>
+        </is>
+      </c>
+      <c r="Q27" s="41" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
         </is>
       </c>
     </row>
@@ -60085,17 +60094,17 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Solutions Engineer, Deel HR | DACH</t>
+          <t>Consultant Confirmé SIRH - SAP HR H/F</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Deel</t>
+          <t>ACT-ON HRIS</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>deel.com/careers</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -60105,183 +60114,183 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>DACH (AT/DE/CH)</t>
+          <t>Neuilly-sur-Seine (92)</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>Remote (à confirmer depuis FR)</t>
+          <t>Télétravail flexible</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>$95,000-$170,000 USD</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
+          <t>SAP HR multi-modules (paramétrage, déploiement, recette), grands groupes, 3+ ans exp — différent du poste SF déjà en base</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/4342380005</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>55 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="208" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>postulé</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Solutions Engineer, Deel HR | DACH</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Deel</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>deel.com/careers</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>DACH (AT/DE/CH)</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Remote (à confirmer depuis FR)</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>$95,000-$170,000 USD</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
           <t>Pre-sales HRIS Deel HR, angle L'Oréal client grand compte = différenciant, multilingual bonus, allemand limité peut freiner, remote depuis FR à confirmer</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>https://www.deel.com/careers/job/?ats_id=0e920f65-a385-47d8-9129-58386b2722f9</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM_EN</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>95-110K€</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="208" customHeight="1">
-      <c r="A29" s="21" t="inlineStr">
+    <row r="30" ht="256" customHeight="1">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>pourvu</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Enablement Trainer</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Hostaway</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>100% Remote Europe</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="J29" s="6" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K29" s="6" t="inlineStr">
+      <c r="K30" s="6" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>Formation &amp; coaching EMEA ✓ — loin du SAP/HR (hospitality SaaS)</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4426695837/</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>à créer</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>60 K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="256" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>no remote</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Consultant(e) Stratégie et Transformation RH F/H</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>ACT-ON STRATEGY</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>Neuilly-sur-Seine</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>sur site</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>Accompagnement transformation RH, conduite du changement, SF/Workday/Talentsoft, 2-5 ans — profil junior/mid sur le fond</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/jobs/view/4342420186</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -60298,7 +60307,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>postulé</t>
+          <t>no remote</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -60308,12 +60317,12 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Senior HRIS Analyst – SAP SuccessFactors Recruiting &amp; Onboarding</t>
+          <t>Consultant(e) Stratégie et Transformation RH F/H</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Foundever</t>
+          <t>ACT-ON STRATEGY</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -60328,50 +60337,50 @@
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Neuilly-sur-Seine</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
+          <t>sur site</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>£75 000</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K31" s="6" t="n"/>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>170k employés, 40+ pays — scale L'Oréal comparable. SF Recruiting &amp; Onboarding global, remote. Lacune : 3+ ans admin SF requis (pas SAP HCM). UK basé mais full remote.</t>
+          <t>Accompagnement transformation RH, conduite du changement, SF/Workday/Talentsoft, 2-5 ans — profil junior/mid sur le fond</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4426322458</t>
+          <t>https://fr.linkedin.com/jobs/view/4342420186</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>80 K€</t>
+          <t>60 K€</t>
         </is>
       </c>
     </row>
     <row r="32" ht="160" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>out of scope</t>
+          <t>postulé</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -60381,12 +60390,12 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Solutions Consultant (French Speaking)</t>
+          <t>Senior HRIS Analyst – SAP SuccessFactors Recruiting &amp; Onboarding</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Synthesia</t>
+          <t>Foundever</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -60401,50 +60410,50 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Paris / Europe</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Full remote</t>
+          <t>100% remote</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>£75 000</t>
         </is>
       </c>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>Pre/post-sales hybride, plateforme vidéo IA. French speaker, ML background asset. Hors périmètre SAP/SIRH.</t>
+          <t>170k employés, 40+ pays — scale L'Oréal comparable. SF Recruiting &amp; Onboarding global, remote. Lacune : 3+ ans admin SF requis (pas SAP HCM). UK basé mais full remote.</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4404547243/</t>
+          <t>https://www.linkedin.com/jobs/view/4426322458</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>80-95 K€</t>
+          <t>80 K€</t>
         </is>
       </c>
     </row>
     <row r="33" ht="409.5" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>postulé</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -60454,12 +60463,12 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Consultant SIRH Senior</t>
+          <t>Solutions Consultant (French Speaking)</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>SIGMA-HR</t>
+          <t>Synthesia</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -60474,34 +60483,38 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris / Europe</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="n"/>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
       <c r="K33" s="6" t="n"/>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>SIRH Senior CDI, implémentation logiciel proprio (pas SAP) - moins valorisant mais fit fonctionnel correct</t>
+          <t>Pre/post-sales hybride, plateforme vidéo IA. French speaker, ML background asset. Hors périmètre SAP/SIRH.</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4408767527/</t>
+          <t>https://www.linkedin.com/jobs/view/4404547243/</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
+          <t>Resume_GaetanFRANCOIS.pdf</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>80-95 K€</t>
         </is>
       </c>
     </row>
@@ -60513,7 +60526,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>pourvu</t>
+          <t>postulé</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -60523,17 +60536,17 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Pre-Sales Consultant</t>
+          <t>Consultant SIRH Senior</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Agatha Inc.</t>
+          <t>SIGMA-HR</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -60543,38 +60556,34 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Lyon / Full Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Agatha = éditeur logiciel Life Sciences (essais cliniques, 400+ entreprises, 60k users, Boston/Tokyo/Lyon). Pre-Sales : démos produit, accompagnement avant-vente. Full remote possible. Secteur Life Sciences ≠ HR Tech mais le rôle pre-sales est exactement dans la cible compétences. Anglais fort requis.</t>
+          <t>SIRH Senior CDI, implémentation logiciel proprio (pas SAP) - moins valorisant mais fit fonctionnel correct</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/agatha-inc/jobs/pre-sales-consultant_lyon</t>
+          <t>https://www.linkedin.com/jobs/view/4408767527/</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>85 K€</t>
+          <t>70-80K€</t>
         </is>
       </c>
     </row>
@@ -60594,49 +60603,50 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Remote HRIS IT Project Manager Europe</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>JELD-WEN</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>LinkedIn / Jobrapido</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>CDD / Freelance</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Remote France ou UK</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Pre-Sales Consultant</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Agatha Inc.</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Lyon / Full Remote</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>JELD-WEN = fabricant mondial portes/fenêtres (NYSE). HRIS IT PM Europe, déploiement UKG Pro WFM/Kronos, projets IT multi-sites Europe, bilingue FR/EN. Remote depuis France. Publié février 2026 — à vérifier si toujours ouvert.</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>https://talents.studysmarter.co.uk/companies/jeld-wen-uk/remote-hris-it-project-manager-europe-en-fr-27061545/</t>
+      <c r="K35" s="6" t="n"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Agatha = éditeur logiciel Life Sciences (essais cliniques, 400+ entreprises, 60k users, Boston/Tokyo/Lyon). Pre-Sales : démos produit, accompagnement avant-vente. Full remote possible. Secteur Life Sciences ≠ HR Tech mais le rôle pre-sales est exactement dans la cible compétences. Anglais fort requis.</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/agatha-inc/jobs/pre-sales-consultant_lyon</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -60646,7 +60656,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>75 K€</t>
+          <t>85 K€</t>
         </is>
       </c>
     </row>
@@ -60666,107 +60676,106 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Remote HRIS IT Project Manager Europe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>JELD-WEN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>LinkedIn / Jobrapido</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CDD / Freelance</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Remote France ou UK</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>JELD-WEN = fabricant mondial portes/fenêtres (NYSE). HRIS IT PM Europe, déploiement UKG Pro WFM/Kronos, projets IT multi-sites Europe, bilingue FR/EN. Remote depuis France. Publié février 2026 — à vérifier si toujours ouvert.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://talents.studysmarter.co.uk/companies/jeld-wen-uk/remote-hris-it-project-manager-europe-en-fr-27061545/</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>75 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>pourvu</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Chef de Projet SIRH N2F (100% remote)</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>N2JSOFT</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Welcome to the Jungle</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>Montagnat (01) – télétravail total</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="n"/>
-      <c r="L36" s="5" t="inlineStr">
-        <is>
-          <t>N2F = SaaS gestion notes de frais. Chef de projet pour intégration N2F avec SIRH clients. 100% full remote = parfait Biarritz. Gap : N2F n'est pas un HRIS/SAP traditionnel mais outil adjacent. Compétences intégration SIRH, formation, déploiement de Gaëtan applicables.</t>
-        </is>
-      </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/fr/companies/n2jsoft-fr/jobs/chef-de-projet-sirh-h-f-n2f_montagnat_N2JSO_YbKVlVW</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>72 K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>hors profil</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Senior People Systems Analyst – Automations</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Deel</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>EMEA</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>Full remote</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
@@ -60777,143 +60786,147 @@
       <c r="K37" s="6" t="n"/>
       <c r="L37" s="5" t="inlineStr">
         <is>
+          <t>N2F = SaaS gestion notes de frais. Chef de projet pour intégration N2F avec SIRH clients. 100% full remote = parfait Biarritz. Gap : N2F n'est pas un HRIS/SAP traditionnel mais outil adjacent. Compétences intégration SIRH, formation, déploiement de Gaëtan applicables.</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/n2jsoft-fr/jobs/chef-de-projet-sirh-h-f-n2f_montagnat_N2JSO_YbKVlVW</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>72 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="160" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>hors profil</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Senior People Systems Analyst – Automations</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Deel</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="n"/>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
           <t>Automatisation HRIS interne Deel (Zapier, Jira, API, Deel HRIS), 5+ ans systems ops — trop technique, peu de face-client</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/4428710760</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>85 K€</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="160" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Consultant(e) GTA F/H</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>ACT-ON HRIS</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>Neuilly-sur-Seine</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Hybride</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>GTA pure (Chronotime, Octime, Kelio) — pas SAP SF. Déjà postulé.</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4358595664/</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="22" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Refusé</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Customer Success Manager</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Conga</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Greenhouse</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="n"/>
-      <c r="K39" s="6" t="n"/>
-      <c r="L39" s="5" t="inlineStr">
-        <is>
-          <t>10-15 comptes enterprise €7M+ ARR, French/English C2, 100% remote France — cœur de cible</t>
-        </is>
-      </c>
-      <c r="M39" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/conga/jobs/5105438007</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS.pdf</t>
-        </is>
-      </c>
-      <c r="Q39" s="41" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
     </row>
@@ -60925,196 +60938,201 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
+          <t>Refusé</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Conga</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n"/>
+      <c r="K40" s="6" t="n"/>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>10-15 comptes enterprise €7M+ ARR, French/English C2, 100% remote France — cœur de cible</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/conga/jobs/5105438007</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS.pdf</t>
+        </is>
+      </c>
+      <c r="Q40" s="41" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="176" customHeight="1">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
           <t>postulé</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>Consultant SIRH</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>https://careers.clap-partners.com/job/MONTROUGE-Consultant-SIRH-92120/827018802</t>
         </is>
       </c>
-      <c r="Q40" s="41" t="inlineStr">
+      <c r="Q41" s="41" t="inlineStr">
         <is>
           <t>23/06/2026</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="176" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
+    <row r="42" ht="160" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>payroll</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>SAP HCM Consultant – French Payroll</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Movement Group</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>movementgroup.uk</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J41" s="6" t="n"/>
-      <c r="K41" s="6" t="inlineStr">
+      <c r="J42" s="6" t="n"/>
+      <c r="K42" s="6" t="inlineStr">
         <is>
           <t>12 mois</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>SAP Payroll France 100% remote, 12 mois + extension, outside IR35 — start ASAP</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr">
         <is>
           <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="160" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
+    <row r="43" ht="176" customHeight="1">
+      <c r="A43" s="25" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>postulé</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Customer Success Manager EMEA</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Camunda</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Greenhouse</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>Europe</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="n"/>
-      <c r="K42" s="6" t="n"/>
-      <c r="L42" s="5" t="inlineStr">
-        <is>
-          <t>BPM/automatisation enterprise, remote 75+ pays, profil CSM senior SaaS B2B parfait</t>
-        </is>
-      </c>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>https://camunda.com/careers/all-jobs/?gh_jid=6502803003&amp;ashby_jid=79980213-ee2c-41a0-bbab-4fcf6e312745</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_Camunda_EN.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="176" customHeight="1">
-      <c r="A43" s="27" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>pourvu</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Directeur de Projet SIRH H/F</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Actual Talent</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Welcome to the Jungle</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>France</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -61126,49 +61144,49 @@
       <c r="K43" s="6" t="n"/>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>100% télétravail, CDI, intégrateur SIRH/GTA, 5+ ans requis — remote parfait depuis Biarritz</t>
+          <t>BPM/automatisation enterprise, remote 75+ pays, profil CSM senior SaaS B2B parfait</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/ergalis/jobs/directeur-de-projet-sirh-h-f_lyon_AT_2AgaeJo</t>
+          <t>https://camunda.com/careers/all-jobs/?gh_jid=6502803003&amp;ashby_jid=79980213-ee2c-41a0-bbab-4fcf6e312745</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>CV_GaetanFRANCOIS_Camunda_EN.pdf</t>
         </is>
       </c>
     </row>
     <row r="44" ht="176" customHeight="1">
-      <c r="A44" s="28" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>pourvu</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Consultant SIRH</t>
+          <t>Directeur de Projet SIRH H/F</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>Onepoint</t>
+          <t>Actual Talent</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -61178,46 +61196,41 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil SIRH, ERP SAP/Oracle/Workday, 2-8 ans requis - sous-positionnement mais cabinet sérieux</t>
+          <t>100% télétravail, CDI, intégrateur SIRH/GTA, 5+ ans requis — remote parfait depuis Biarritz</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4329056727/</t>
+          <t>https://www.welcometothejungle.com/fr/companies/ergalis/jobs/directeur-de-projet-sirh-h-f_lyon_AT_2AgaeJo</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>70-80K€</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
     </row>
     <row r="45" ht="176" customHeight="1">
-      <c r="A45" s="30" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Expiré</t>
+          <t>Postulé</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -61227,17 +61240,17 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) fonctionnel SIRH F/H</t>
+          <t>Consultant SIRH</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>CGI</t>
+          <t>Onepoint</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>CGI Careers (njoyn)</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -61252,29 +61265,29 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>?</t>
         </is>
       </c>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>5 ans requis, SAP HR/SF/Workday/ADP, jusqu'à 3j remote — différent du Chef de Projet SIRH CGI déjà dans tableur</t>
+          <t>Cabinet conseil SIRH, ERP SAP/Oracle/Workday, 2-8 ans requis - sous-positionnement mais cabinet sérieux</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>https://cgi.njoyn.com/corp/xweb/xweb.asp?CLID=21001&amp;page=jobdetails&amp;JobID=J1225-1824&amp;lang=1</t>
+          <t>https://www.linkedin.com/jobs/view/4329056727/</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="Q45" s="41" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>70-80K€</t>
         </is>
       </c>
     </row>
@@ -61286,27 +61299,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
+          <t>Expiré</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) transformations et solutions RH</t>
+          <t>Consultant(e) fonctionnel SIRH F/H</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Artimon</t>
+          <t>CGI</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>CGI Careers (njoyn)</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -61328,12 +61341,12 @@
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil RH indépendant, diagnostic, sélection SIRH, transformation RH — profil L'Oréal 40 pays très aligné</t>
+          <t>5 ans requis, SAP HR/SF/Workday/ADP, jusqu'à 3j remote — différent du Chef de Projet SIRH CGI déjà dans tableur</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4400205394/</t>
+          <t>https://cgi.njoyn.com/corp/xweb/xweb.asp?CLID=21001&amp;page=jobdetails&amp;JobID=J1225-1824&amp;lang=1</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -61341,11 +61354,16 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
+      <c r="Q46" s="41" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="256" customHeight="1">
-      <c r="A47" s="31" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -61360,12 +61378,12 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Chargé de projet SIRH H/F</t>
+          <t>Consultant(e) transformations et solutions RH</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Crédit Agricole Assurances</t>
+          <t>Artimon</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -61375,7 +61393,7 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CDD</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -61385,31 +61403,36 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Partiel (40%)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Déploiement PeopleDoc (UKG), gestion MyDev (carrières), campagnes RH. Pas SAP mais SIRH projet direct. CDD + Paris hybride = contraintes. 82j télétravail/an.</t>
+          <t>Cabinet conseil RH indépendant, diagnostic, sélection SIRH, transformation RH — profil L'Oréal 40 pays très aligné</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4426879208/</t>
+          <t>https://www.linkedin.com/jobs/view/4400205394/</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
     </row>
     <row r="48" ht="288" customHeight="1">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" s="31" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Refusé</t>
+          <t>Postulé</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -61419,58 +61442,44 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Consultant SIRH AMOA</t>
+          <t>Chargé de projet SIRH H/F</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Clap Partners</t>
+          <t>Crédit Agricole Assurances</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>CDD</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Montrouge (92)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+          <t>Partiel (40%)</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>Clap Partners = cabinet spécialisé SAP SuccessFactors. AMOA SIRH = cœur du profil Gaëtan. Fit excellent techniquement. Frein : Montrouge, pas full remote.</t>
+          <t>Déploiement PeopleDoc (UKG), gestion MyDev (carrières), campagnes RH. Pas SAP mais SIRH projet direct. CDD + Paris hybride = contraintes. 82j télétravail/an.</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/clap-partners-fr/jobs/consultant-sirh-amoa_montrouge_CP_GypWOaJ</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>75 K€</t>
+          <t>https://www.linkedin.com/jobs/view/4426879208/</t>
         </is>
       </c>
     </row>
@@ -61480,7 +61489,7 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Refusé</t>
         </is>
@@ -61492,7 +61501,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Consultant AMOA SIRH Learning H/F</t>
+          <t>Consultant SIRH AMOA</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -61528,12 +61537,12 @@
       <c r="K49" s="6" t="n"/>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>Clap Partners, spécialisé SAP SF. Module Learning (formation) = fit fort pour Gaëtan (formateur SF, transfert de connaissances L'Oréal). Frein : Montrouge, pas full remote.</t>
+          <t>Clap Partners = cabinet spécialisé SAP SuccessFactors. AMOA SIRH = cœur du profil Gaëtan. Fit excellent techniquement. Frein : Montrouge, pas full remote.</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/clap-partners-fr/jobs/consultant-amoa-sirh-learning-h-f_montrouge</t>
+          <t>https://www.welcometothejungle.com/fr/companies/clap-partners-fr/jobs/consultant-sirh-amoa_montrouge_CP_GypWOaJ</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -61548,14 +61557,14 @@
       </c>
     </row>
     <row r="50" ht="176" customHeight="1">
-      <c r="A50" s="32" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
+      <c r="A50" s="29" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>out of scope, paie</t>
+          <t>Refusé</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -61565,17 +61574,17 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>SAP HCM-Payroll Consultant</t>
+          <t>Consultant AMOA SIRH Learning H/F</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>Cabinet conseil global (via Eursap)</t>
+          <t>Clap Partners</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Eursap (réf. 29132)</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -61585,41 +61594,50 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Montrouge (92)</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="n"/>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
       <c r="K50" s="6" t="n"/>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>14 ans SAP HR/HCM payroll multi-pays, jusqu'à 100% remote EU, 15 pays éligibles — profil L'Oréal parfait</t>
+          <t>Clap Partners, spécialisé SAP SF. Module Learning (formation) = fit fort pour Gaëtan (formateur SF, transfert de connaissances L'Oréal). Frein : Montrouge, pas full remote.</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
-          <t>https://eursap.eu/jobs/sap-hcm-payroll-consultant-remote-work-29132</t>
+          <t>https://www.welcometothejungle.com/fr/companies/clap-partners-fr/jobs/consultant-amoa-sirh-learning-h-f_montrouge</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>75 K€</t>
         </is>
       </c>
     </row>
     <row r="51" ht="128" customHeight="1">
-      <c r="A51" s="34" t="inlineStr">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Postulé</t>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>out of scope, paie</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -61629,17 +61647,17 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>SAP Pre-sales Lead – HCM, Payroll, SuccessFactors</t>
+          <t>SAP HCM-Payroll Consultant</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Whitehall Resources</t>
+          <t>Cabinet conseil global (via Eursap)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Whitehall Resources</t>
+          <t>Eursap (réf. 29132)</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -61649,55 +61667,41 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Royaume-Uni (remote depuis France)</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="n"/>
       <c r="K51" s="6" t="n"/>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>14 ans SAP, L'Oréal 40+ pays, face client grands comptes = match parfait. Vérifier éligibilité UK depuis France.</t>
+          <t>14 ans SAP HR/HCM payroll multi-pays, jusqu'à 100% remote EU, 15 pays éligibles — profil L'Oréal parfait</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t>https://www.whitehallresources.com/job/sap-pre-sales-lead-hcm-payroll-successfactors/</t>
+          <t>https://eursap.eu/jobs/sap-hcm-payroll-consultant-remote-work-29132</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>95-115K€</t>
-        </is>
-      </c>
-      <c r="Q51" s="41" t="inlineStr">
-        <is>
-          <t>25/09/2025</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="32" t="inlineStr">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>postulé</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Postulé</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -61707,17 +61711,17 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>SAP Project Manager</t>
+          <t>SAP Pre-sales Lead – HCM, Payroll, SuccessFactors</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>Via EurSAP (remote)</t>
+          <t>Whitehall Resources</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>EurSAP</t>
+          <t>Whitehall Resources</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -61727,528 +61731,524 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Royaume-Uni (remote depuis France)</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>Oui (100%)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>80-150K€ + equity</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K52" s="6" t="n"/>
       <c r="L52" s="5" t="inlineStr">
         <is>
+          <t>14 ans SAP, L'Oréal 40+ pays, face client grands comptes = match parfait. Vérifier éligibilité UK depuis France.</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
+          <t>https://www.whitehallresources.com/job/sap-pre-sales-lead-hcm-payroll-successfactors/</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>95-115K€</t>
+        </is>
+      </c>
+      <c r="Q52" s="41" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>postulé</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>SAP Project Manager</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Via EurSAP (remote)</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>EurSAP</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>Oui (100%)</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>80-150K€ + equity</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="n"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
           <t>SAP PM remote CDI — 80-150k€ + equity/stock options — démarrage 03/08/2026</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
+      <c r="M53" s="5" t="inlineStr">
         <is>
           <t>https://eursap.eu/jobs/sap-project-manager-34811-remote</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>100-115K€</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="36" t="inlineStr">
+    <row r="54" ht="160" customHeight="1">
+      <c r="A54" s="36" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Formateur / Consultant IA Freelance</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Mantra (ex-GrowthMakers)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>WelcomeToTheJungle</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>TJM attractif (marché 500-900 €/j)</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Récurrent</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>100% remote. Animer formations IA générative distanciel, créer contenus pédagogiques, personnaliser cas d'usage par secteur. Profil praticien IA valorisé. Idéal depuis Biarritz.</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/growthmakers/jobs/formateur-ia-et-ia-generative_paris</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_IA.html</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="160" customHeight="1">
-      <c r="A54" s="35" t="inlineStr">
+    <row r="55" ht="240" customHeight="1">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Refusé</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Formateur en Intelligence Artificielle F/H</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Groupe MDA (MDA Performance)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Biarritz</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Basé à Biarritz, 100% distanciel — fit géographique parfait. Former entreprises adultes sur ChatGPT, Copilot, Gemini, Claude. Publié 01/07/2026.</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/formateur-en-intelligence-artificielle-f-h-at-groupe-mda-4435134586</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="240" customHeight="1">
-      <c r="A55" s="42" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="42" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B55" s="43" t="inlineStr">
+      <c r="B56" s="43" t="inlineStr">
         <is>
           <t>expiré</t>
         </is>
       </c>
-      <c r="C55" s="43" t="inlineStr">
+      <c r="C56" s="43" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D55" s="26" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>Chef de Projet Fonctionnel SIRH</t>
         </is>
       </c>
-      <c r="E55" s="26" t="inlineStr">
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>Client anonyme</t>
         </is>
       </c>
-      <c r="F55" s="26" t="inlineStr">
+      <c r="F56" s="26" t="inlineStr">
         <is>
           <t>freelance-informatique.fr</t>
         </is>
       </c>
-      <c r="G55" s="44" t="inlineStr">
+      <c r="G56" s="44" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H55" s="44" t="inlineStr">
+      <c r="H56" s="44" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I55" s="44" t="inlineStr">
+      <c r="I56" s="44" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J55" s="44" t="n"/>
-      <c r="K55" s="44" t="inlineStr">
+      <c r="J56" s="44" t="n"/>
+      <c r="K56" s="44" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="L55" s="26" t="inlineStr">
+      <c r="L56" s="26" t="inlineStr">
         <is>
           <t>100% remote — seule mission Chef de Projet SIRH full remote trouvée aujourd'hui, start ASAP</t>
         </is>
       </c>
-      <c r="M55" s="45" t="inlineStr">
+      <c r="M56" s="45" t="inlineStr">
         <is>
           <t>https://www.freelance-informatique.fr/mission-chef-de-projet-sirh-n112</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="37" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="37" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="D56" s="26" t="inlineStr">
+      <c r="D57" s="26" t="inlineStr">
         <is>
           <t>Consultant SAP SuccessFactors (24 mois)</t>
         </is>
       </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="E57" s="26" t="inlineStr">
         <is>
           <t>n.c. (via Free-Work)</t>
         </is>
       </c>
-      <c r="F56" s="26" t="inlineStr">
+      <c r="F57" s="26" t="inlineStr">
         <is>
           <t>Free-Work</t>
         </is>
       </c>
-      <c r="G56" s="44" t="inlineStr">
+      <c r="G57" s="44" t="inlineStr">
         <is>
           <t>Mission</t>
         </is>
       </c>
-      <c r="H56" s="44" t="inlineStr">
+      <c r="H57" s="44" t="inlineStr">
         <is>
           <t>Versailles (78)</t>
         </is>
       </c>
-      <c r="I56" s="44" t="inlineStr">
+      <c r="I57" s="44" t="inlineStr">
         <is>
           <t>Hybride</t>
         </is>
       </c>
-      <c r="J56" s="44" t="inlineStr">
+      <c r="J57" s="44" t="inlineStr">
         <is>
           <t>450-690 €/j</t>
         </is>
       </c>
-      <c r="K56" s="44" t="inlineStr">
+      <c r="K57" s="44" t="inlineStr">
         <is>
           <t>24 mois (démarrage ASAP)</t>
         </is>
       </c>
-      <c r="L56" s="26" t="inlineStr">
+      <c r="L57" s="26" t="inlineStr">
         <is>
           <t>Mission longue 24 mois, expertise implementation SF. TJM 450-690€/j. Versailles = déplacements possibles depuis Biarritz. Profil Gaëtan bien adapté.</t>
         </is>
       </c>
-      <c r="M56" s="26" t="inlineStr">
+      <c r="M57" s="26" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/jobs/sap-successfactors</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="Q56" s="41" t="inlineStr">
+      <c r="Q57" s="41" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="38" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="38" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>postulé</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Chef de projet Intelligence Artificielle ChatGPT</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>BI SOLUTIONS</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>IDF</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>Non précisé</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>400-500 €/j</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Chef de projet IA GenAI ; anglais requis</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/chef-de-projet-intelligence-artificielle-chat-gpt-anglais-500-e-par-j</t>
         </is>
       </c>
-      <c r="Q57" s="41" t="inlineStr">
+      <c r="Q58" s="41" t="inlineStr">
         <is>
           <t>07/03/2026</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="46" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B58" s="47" t="inlineStr">
+      <c r="B59" s="47" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C58" s="47" t="inlineStr">
+      <c r="C59" s="47" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Principal Solution Advisor SuccessFactors F/H</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t>Levallois-Perret</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>Hybride (0-10% déplacements)</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>100-130K€ (estimé)</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>Pre-sales SF — différent du HCM déjà postulé — 10-15 ans grandes orgas, 3-5 ans HCM requis — posté il y a 4 jours</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/principal-solution-advisor-successfactors-f-h-at-sap-4415727184</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>100-115K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="48" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B59" s="47" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C59" s="47" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Manager SIRH</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>TalHenT</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Paris (75)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>n.p.</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Cabinet conseil SIRH ~100p, 10+ ans exp, dev commercial et structuration offres SIRH - profil senior idéal</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>https://www.emplois-informatique.fr/cdi/manager-sirh-6893801</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>70 K€</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -62260,7 +62260,7 @@
       </c>
       <c r="B60" s="47" t="inlineStr">
         <is>
-          <t>pourvu</t>
+          <t>Postulé</t>
         </is>
       </c>
       <c r="C60" s="47" t="inlineStr">
@@ -62270,12 +62270,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Senior Manager SIRH H/F</t>
+          <t>Manager SIRH</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ALTHEA</t>
+          <t>TalHenT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -62290,7 +62290,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Issy-les-Moulineaux</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -62300,17 +62300,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>60-80 K€ + 8 K€ variable</t>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>6 mois</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Cabinet conseil 150+ consultants RH, pilotage transformation SIRH (SAP SF/Workday/Oracle HCM), management équipe, 5-15 ans exp, FR+EN obligatoire</t>
+          <t>Cabinet conseil SIRH ~100p, 10+ ans exp, dev commercial et structuration offres SIRH - profil senior idéal</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4417058716</t>
+          <t>https://www.emplois-informatique.fr/cdi/manager-sirh-6893801</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -62320,7 +62325,12 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>72 K€</t>
+          <t>70 K€</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -62332,7 +62342,7 @@
       </c>
       <c r="B61" s="47" t="inlineStr">
         <is>
-          <t>Postulé</t>
+          <t>pourvu</t>
         </is>
       </c>
       <c r="C61" s="47" t="inlineStr">
@@ -62342,12 +62352,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors expérimenté H/F</t>
+          <t>Senior Manager SIRH H/F</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SQORUS</t>
+          <t>ALTHEA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -62362,7 +62372,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paris et périphérie</t>
+          <t>Issy-les-Moulineaux</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -62372,17 +62382,17 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>60-80 K€ + 8 K€ variable</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Cabinet RH digital, 5+ ans SIRH, SF multi-modules (TA/Perf/Career/LMS/Comp), projets clients FR+EN B2 min, ateliers, specs fonctionnelles</t>
+          <t>Cabinet conseil 150+ consultants RH, pilotage transformation SIRH (SAP SF/Workday/Oracle HCM), management équipe, 5-15 ans exp, FR+EN obligatoire</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4396619283</t>
+          <t>https://fr.linkedin.com/jobs/view/4417058716</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -62392,7 +62402,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>60 K€</t>
+          <t>72 K€</t>
         </is>
       </c>
     </row>
@@ -62414,194 +62424,193 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>Consultant SAP SuccessFactors expérimenté H/F</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SQORUS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Paris et périphérie</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>n.p.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Cabinet RH digital, 5+ ans SIRH, SF multi-modules (TA/Perf/Career/LMS/Comp), projets clients FR+EN B2 min, ateliers, specs fonctionnelles</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/4396619283</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>60 K€</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="335" customHeight="1">
+      <c r="A63" s="48" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B63" s="47" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C63" s="47" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>SAP SuccessFactors Consultant – Succession Calibration Performance (12 mois)</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Movement Group</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>LinkedIn / Movement Group</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Mission</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>N/C (négociable)</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>12 mois + extension</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Mission distincte de la mission Movement Group SF déjà en tableur. Modules Succession / Calibration / Performance. Contact : Shane Breen (shane.breen@movementgroup.uk). CV Word demandé.</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>https://fr.linkedin.com/jobs/view/sap-successfactors-consultant-france-remote-hybrid-freelance-12-months-%2B-at-movement-group-4433063782</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="335" customHeight="1">
-      <c r="A63" s="54" t="inlineStr">
+    <row r="64" ht="240" customHeight="1">
+      <c r="A64" s="54" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>HCM Senior Associate Consultant</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>Huron Consulting Group</t>
         </is>
       </c>
-      <c r="F63" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>LinkedIn / Workday</t>
         </is>
       </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J63" s="6" t="n"/>
-      <c r="K63" s="6" t="n"/>
-      <c r="L63" s="5" t="inlineStr">
-        <is>
-          <t>Cabinet conseil US coté Nasdaq, 6800+ experts. Poste HCM consultant Paris — Oracle Cloud HCM ou SAP HCM. Réf JR-0016012.</t>
-        </is>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>https://huron.wd1.myworkdayjobs.com/fr-FR/huroncareers/job/Paris-France/HCM-Senior-Associate-Consultant_JR-0016012 | https://www.linkedin.com/jobs/view/4441064885/</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>70-85K€</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="240" customHeight="1">
-      <c r="A64" s="55" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>HR Business Solutions Architect</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>Sinch</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn / Sinch Careers (Oracle ATS)</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>Paris, France</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>80-100K€</t>
-        </is>
-      </c>
+      <c r="J64" s="6" t="n"/>
       <c r="K64" s="6" t="n"/>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>Boîte SaaS messaging suédoise (Nasdaq). 80% exécution / 20% stratégie. Requis : 3 ans Oracle HCM (lacune SAP→Oracle à argumenter), 5 ans solutions RH globales, 7 ans HRIT. Remote confirmé. EU requis OK.</t>
+          <t>Cabinet conseil US coté Nasdaq, 6800+ experts. Poste HCM consultant Paris — Oracle Cloud HCM ou SAP HCM. Réf JR-0016012.</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4444461445/ | https://iaings.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/SinchCareer/job/1256/</t>
+          <t>https://huron.wd1.myworkdayjobs.com/fr-FR/huroncareers/job/Paris-France/HCM-Senior-Associate-Consultant_JR-0016012 | https://www.linkedin.com/jobs/view/4441064885/</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -62611,40 +62620,39 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>90-100K€</t>
-        </is>
-      </c>
-      <c r="Q64" s="41" t="n"/>
+          <t>70-85K€</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="409.5" customHeight="1">
-      <c r="A65" s="54" t="inlineStr">
+      <c r="A65" s="55" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Refusé</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Responsable SIRH et DATA RH (F/H)</t>
+          <t>HR Business Solutions Architect</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>TDF (Groupe TDF)</t>
+          <t>Sinch</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn / Aplitrak</t>
+          <t>LinkedIn / Sinch Careers (Oracle ATS)</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -62654,67 +62662,71 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Montrouge (92)</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="n"/>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>80-100K€</t>
+        </is>
+      </c>
       <c r="K65" s="6" t="n"/>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>Pilotage SIRH + gouvernance data RH. Outils : Workday, ADP, SIMBEL. 7-10 ans SIRH requis. Bac+5 RH/info/data. Anglais courant.</t>
+          <t>Boîte SaaS messaging suédoise (Nasdaq). 80% exécution / 20% stratégie. Requis : 3 ans Oracle HCM (lacune SAP→Oracle à argumenter), 5 ans solutions RH globales, 7 ans HRIT. Remote confirmé. EU requis OK.</t>
         </is>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4440037261/ | https://www.aplitrak.com/?adid=Q2F0aGVyaW5lLmxpdi44NTY4MS4xNTUwQGdyb3VwZXRkZi5hcGxpdHJhay5jb20</t>
+          <t>https://www.linkedin.com/jobs/view/4444461445/ | https://iaings.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/SinchCareer/job/1256/</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>80-95K€</t>
+          <t>90-100K€</t>
         </is>
       </c>
       <c r="Q65" s="41" t="n"/>
     </row>
     <row r="66" ht="350" customHeight="1">
-      <c r="A66" s="62" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C66" s="39" t="inlineStr">
+      <c r="A66" s="54" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Refusé</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Operational Onboarding Manager - France</t>
+          <t>Responsable SIRH et DATA RH (F/H)</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>TDF (Groupe TDF)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn / Aplitrak</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
@@ -62724,63 +62736,62 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Montrouge (92)</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Flexible (présentiel valorisé)</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>n.c. (grille B0-B1)</t>
-        </is>
-      </c>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="n"/>
       <c r="K66" s="6" t="n"/>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>Scale-up assurance santé SaaS, onboarding administratif des plus gros clients, ateliers formation RH/Paie. Localisation Biarritz = très proche Anglet. Rôle plus opérationnel/junior qu'un CSM Senior classique, remote seulement flexible. | Postulé le 04/08/2026. Aussi sur LinkedIn : https://www.linkedin.com/jobs/view/4432803785/</t>
+          <t>Pilotage SIRH + gouvernance data RH. Outils : Workday, ADP, SIMBEL. 7-10 ans SIRH requis. Bac+5 RH/info/data. Anglais courant.</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/alan/149e6bff-b83d-4f7f-bfa8-9eb251bf437c</t>
-        </is>
-      </c>
-      <c r="N66" s="39" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
-        </is>
-      </c>
-      <c r="O66" s="39" t="n"/>
-      <c r="P66" s="39" t="n"/>
+          <t>https://www.linkedin.com/jobs/view/4440037261/ | https://www.aplitrak.com/?adid=Q2F0aGVyaW5lLmxpdi44NTY4MS4xNTUwQGdyb3VwZXRkZi5hcGxpdHJhay5jb20</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>80-95K€</t>
+        </is>
+      </c>
       <c r="Q66" s="41" t="n"/>
     </row>
     <row r="67" ht="409.5" customHeight="1">
-      <c r="A67" s="49" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
+      <c r="A67" s="62" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Senior Manager, SAP SuccessFactors Employee Central &amp; Platform</t>
+          <t>Operational Onboarding Manager - France</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Foundever</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -62795,190 +62806,187 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>UK (remote)</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Flexible (présentiel valorisé)</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>£75-90K (~87-105K€)</t>
+          <t>n.c. (grille B0-B1)</t>
         </is>
       </c>
       <c r="K67" s="6" t="n"/>
       <c r="L67" s="5" t="inlineStr">
         <is>
+          <t>Scale-up assurance santé SaaS, onboarding administratif des plus gros clients, ateliers formation RH/Paie. Localisation Biarritz = très proche Anglet. Rôle plus opérationnel/junior qu'un CSM Senior classique, remote seulement flexible. | Postulé le 04/08/2026. Aussi sur LinkedIn : https://www.linkedin.com/jobs/view/4432803785/</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/alan/149e6bff-b83d-4f7f-bfa8-9eb251bf437c</t>
+        </is>
+      </c>
+      <c r="N67" s="39" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="O67" s="39" t="n"/>
+      <c r="P67" s="39" t="n"/>
+      <c r="Q67" s="41" t="n"/>
+    </row>
+    <row r="68" ht="409.5" customHeight="1">
+      <c r="A68" s="49" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Senior Manager, SAP SuccessFactors Employee Central &amp; Platform</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Foundever</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>UK (remote)</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>£75-90K (~87-105K€)</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="n"/>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
           <t>Lead équipe globale SF EC 40+ pays ; gouvernance, stratégie, config EC, RBP, intégrations HR/Payroll/Finance — calque L'Oréal 40+ pays parfait | Postulé le 04/08/2026. Aussi sur LinkedIn : https://www.linkedin.com/jobs/view/4429527206/</t>
         </is>
       </c>
-      <c r="M67" s="56" t="inlineStr">
+      <c r="M68" s="56" t="inlineStr">
         <is>
           <t>https://jobs.foundever.com/job/UK-Wide-Senior-Manager%2C-SAP-SuccessFactors-Employee-Central-&amp;-Platform-Work-Sitel-UK-L/1400161700/</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>95K€</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>13/07/2026</t>
         </is>
       </c>
-      <c r="Q67" s="41" t="n"/>
-    </row>
-    <row r="68" ht="409.5" customHeight="1">
-      <c r="A68" s="60" t="inlineStr">
+      <c r="Q68" s="41" t="n"/>
+    </row>
+    <row r="69" ht="320" customHeight="1">
+      <c r="A69" s="60" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>SuccessFactors Talent Management Consultant</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>Empiric</t>
         </is>
       </c>
-      <c r="F68" s="5" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>Suède (remote)</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>100% remote (Suède)</t>
         </is>
       </c>
-      <c r="J68" s="6" t="inlineStr">
+      <c r="J69" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K68" s="6" t="inlineStr">
+      <c r="K69" s="6" t="inlineStr">
         <is>
           <t>12 mois</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr">
+      <c r="L69" s="5" t="inlineStr">
         <is>
           <t>Consultant fonctionnel SAP SuccessFactors : Performance &amp; Goals, Career Development, Succession, Recruiting, Onboarding ; interface entre RH et technique, intégrations SIRH. Anglais courant requis, suédois apprécié. Remote annoncé en Suède, donc à clarifier depuis la France. Postulé le 04/08/2026.</t>
         </is>
       </c>
-      <c r="M68" s="5" t="inlineStr">
+      <c r="M69" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447004933/</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="Q68" s="41" t="n"/>
-    </row>
-    <row r="69" ht="320" customHeight="1">
-      <c r="A69" s="58" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Postulé</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>HRIS Data Consultant - Payroll &amp; HR</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>Silver Cloud</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn / Hibob</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>Royaume-Uni</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>Remote + déplacements clients</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>n.c. (marché : 82-88 K€ / £70-75K)</t>
-        </is>
-      </c>
-      <c r="K69" s="6" t="n"/>
-      <c r="L69" s="5" t="inlineStr">
-        <is>
-          <t>Cabinet conseil HR tech : projets de transformation SIRH/paie, migration de données, mapping, validation, réconciliation, ateliers de découverte. Outils cités : Dayforce, Workday, HiBob. Très bon fit avec les migrations OnePayroll (L'Oréal) et FMC Technologies. Points à clarifier : poste UK depuis la France (devise, contrat, risque de change) et fréquence des déplacements clients depuis Anglet. Comparable marché : Dayforce Data Conversion full remote UK affiché £80K. Postulé le 04/08/2026. Aussi sur Hibob : https://silvercloud.careers.hibob.com/jobs/4c27dd97-5a45-4ed8-9f96-9eefd10c5899</t>
-        </is>
-      </c>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4443868475/</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>85 K€ (£72K)</t>
         </is>
       </c>
       <c r="Q69" s="41" t="n"/>
@@ -63001,17 +63009,17 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>HRIS Implementation Project Manager</t>
+          <t>HRIS Data Consultant - Payroll &amp; HR</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Yassir</t>
+          <t>Silver Cloud</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn / Lever</t>
+          <t>LinkedIn / Hibob</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
@@ -63021,42 +63029,46 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Non précisée (super-app Afrique/MENA)</t>
+          <t>Royaume-Uni</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>À confirmer</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="n"/>
+          <t>Remote + déplacements clients</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>n.c. (marché : 82-88 K€ / £70-75K)</t>
+        </is>
+      </c>
       <c r="K70" s="6" t="n"/>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>Yassir = super-app Algérie/MENA (transport, livraison, fintech). Chef de projet implémentation SIRH. Profil déploiement SIRH grands comptes de Gaëtan directement applicable. Postulé le 31/07/2026 via LinkedIn.</t>
+          <t>Cabinet conseil HR tech : projets de transformation SIRH/paie, migration de données, mapping, validation, réconciliation, ateliers de découverte. Outils cités : Dayforce, Workday, HiBob. Très bon fit avec les migrations OnePayroll (L'Oréal) et FMC Technologies. Points à clarifier : poste UK depuis la France (devise, contrat, risque de change) et fréquence des déplacements clients depuis Anglet. Comparable marché : Dayforce Data Conversion full remote UK affiché £80K. Postulé le 04/08/2026. Aussi sur Hibob : https://silvercloud.careers.hibob.com/jobs/4c27dd97-5a45-4ed8-9f96-9eefd10c5899</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/Yassir/0c61130f-8b15-4366-b253-5662b6ba4c0c</t>
+          <t>https://www.linkedin.com/jobs/view/4443868475/</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>70-85K€</t>
+          <t>85 K€ (£72K)</t>
         </is>
       </c>
       <c r="Q70" s="41" t="n"/>
     </row>
     <row r="71" ht="409.5" customHeight="1">
-      <c r="A71" s="60" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
+      <c r="A71" s="58" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
@@ -63071,17 +63083,17 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Principal HR Specialist</t>
+          <t>HRIS Implementation Project Manager</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Skillsoft</t>
+          <t>Yassir</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>skillsoft.com / Greenhouse</t>
+          <t>LinkedIn / Lever</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -63091,68 +63103,67 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Non précisée (super-app Afrique/MENA)</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Oui (100% remote)</t>
+          <t>À confirmer</t>
         </is>
       </c>
       <c r="J71" s="6" t="n"/>
       <c r="K71" s="6" t="n"/>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>Skillsoft (e-learning/L&amp;D SaaS enterprise). Rôle interne RH : cycle de vie employés, onboarding/offboarding, gestion CSE, paie et avantages France + Allemagne. Poste RH opérationnel plutôt que SIRH consulting — fit partiel. 100% remote France. Postulé le 31/07/2026.</t>
+          <t>Yassir = super-app Algérie/MENA (transport, livraison, fintech). Chef de projet implémentation SIRH. Profil déploiement SIRH grands comptes de Gaëtan directement applicable. Postulé le 31/07/2026 via LinkedIn.</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>https://www.skillsoft.com/about/job/apply?id=4707524005&amp;gh_jid=4707524005</t>
-        </is>
-      </c>
-      <c r="N71" s="39" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O71" s="39" t="inlineStr">
-        <is>
-          <t>70-80K€</t>
-        </is>
-      </c>
-      <c r="P71" s="39" t="n"/>
+          <t>https://jobs.lever.co/Yassir/0c61130f-8b15-4366-b253-5662b6ba4c0c</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>70-85K€</t>
+        </is>
+      </c>
       <c r="Q71" s="41" t="n"/>
     </row>
     <row r="72" ht="128" customHeight="1">
-      <c r="A72" s="62" t="inlineStr">
+      <c r="A72" s="60" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B72" s="39" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C72" s="39" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>People Operations and HRIS Lead</t>
+          <t>Principal HR Specialist</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>Skillsoft</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>euremotejobs.com</t>
+          <t>skillsoft.com / Greenhouse</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -63162,342 +63173,339 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Worldwide</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Oui (100% remote)</t>
         </is>
       </c>
       <c r="J72" s="6" t="n"/>
       <c r="K72" s="6" t="n"/>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>Builder role HRIS + People Ops : talent management, performance, L&amp;D, succession, org design, compensation. AI company 11B USD, scale rapide. Pas de plateforme SAP mentionnee. Worldwide remote. Postulé le 04/08/2026 (formulaire : question mission ElevenLabs + hard problem).</t>
+          <t>Skillsoft (e-learning/L&amp;D SaaS enterprise). Rôle interne RH : cycle de vie employés, onboarding/offboarding, gestion CSE, paie et avantages France + Allemagne. Poste RH opérationnel plutôt que SIRH consulting — fit partiel. 100% remote France. Postulé le 31/07/2026.</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>https://euremotejobs.com/job/people-operations-and-hris-lead/</t>
+          <t>https://www.skillsoft.com/about/job/apply?id=4707524005&amp;gh_jid=4707524005</t>
         </is>
       </c>
       <c r="N72" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
-        </is>
-      </c>
-      <c r="O72" s="39" t="n"/>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O72" s="39" t="inlineStr">
+        <is>
+          <t>70-80K€</t>
+        </is>
+      </c>
       <c r="P72" s="39" t="n"/>
       <c r="Q72" s="41" t="n"/>
     </row>
     <row r="73" ht="409.5" customHeight="1">
-      <c r="A73" s="65" t="inlineStr">
+      <c r="A73" s="62" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B73" s="39" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C73" s="39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>People Operations and HRIS Lead</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>euremotejobs.com</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="n"/>
+      <c r="K73" s="6" t="n"/>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>Builder role HRIS + People Ops : talent management, performance, L&amp;D, succession, org design, compensation. AI company 11B USD, scale rapide. Pas de plateforme SAP mentionnee. Worldwide remote. Postulé le 04/08/2026 (formulaire : question mission ElevenLabs + hard problem).</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
+          <t>https://euremotejobs.com/job/people-operations-and-hris-lead/</t>
+        </is>
+      </c>
+      <c r="N73" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN</t>
+        </is>
+      </c>
+      <c r="O73" s="39" t="n"/>
+      <c r="P73" s="39" t="n"/>
+      <c r="Q73" s="41" t="n"/>
+    </row>
+    <row r="74" ht="128" customHeight="1">
+      <c r="A74" s="65" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B73" s="39" t="inlineStr">
+      <c r="B74" s="39" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C73" s="39" t="inlineStr">
+      <c r="C74" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D73" s="39" t="inlineStr">
+      <c r="D74" s="39" t="inlineStr">
         <is>
           <t>SAP Project Manager / Trainer</t>
         </is>
       </c>
-      <c r="E73" s="39" t="inlineStr">
+      <c r="E74" s="39" t="inlineStr">
         <is>
           <t>N/C (via eursap.eu)</t>
         </is>
       </c>
-      <c r="F73" s="39" t="inlineStr">
+      <c r="F74" s="39" t="inlineStr">
         <is>
           <t>eursap.eu</t>
         </is>
       </c>
-      <c r="G73" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H73" s="39" t="inlineStr">
+      <c r="G74" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H74" s="39" t="inlineStr">
         <is>
           <t>100% Remote</t>
         </is>
       </c>
-      <c r="I73" s="39" t="inlineStr">
+      <c r="I74" s="39" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J73" s="39" t="inlineStr">
+      <c r="J74" s="39" t="inlineStr">
         <is>
           <t>80-156k€/an + equity</t>
         </is>
       </c>
-      <c r="K73" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="L73" s="39" t="inlineStr">
+      <c r="K74" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="L74" s="39" t="inlineStr">
         <is>
           <t>SAP PM + formateur, full remote, fourchette haute, démarrage août 2026 ; ref 34811</t>
         </is>
       </c>
-      <c r="M73" s="39" t="inlineStr">
+      <c r="M74" s="39" t="inlineStr">
         <is>
           <t>https://eursap.eu/jobs/sap-project-manager-or-trainer-34811-remote</t>
         </is>
       </c>
-      <c r="N73" s="39" t="n"/>
-      <c r="O73" s="39" t="n"/>
-      <c r="P73" s="39" t="inlineStr">
+      <c r="N74" s="39" t="n"/>
+      <c r="O74" s="39" t="n"/>
+      <c r="P74" s="39" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="Q73" s="39" t="inlineStr">
+      <c r="Q74" s="39" t="inlineStr">
         <is>
           <t>03/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="128" customHeight="1">
-      <c r="A74" s="67" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="67" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B74" s="39" t="n"/>
-      <c r="C74" s="39" t="inlineStr">
+      <c r="B75" s="39" t="n"/>
+      <c r="C75" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Chef de Projet SIRH / AMOA SIRH</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>N/C (via freelance-informatique.fr)</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>freelance-informatique.fr</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>Mission freelance</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>Courbevoie (92026)</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>Non indiqué (sur site)</t>
         </is>
       </c>
-      <c r="J74" s="6" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
         <is>
           <t>N/C</t>
         </is>
       </c>
-      <c r="K74" s="6" t="inlineStr">
+      <c r="K75" s="6" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="L75" s="5" t="inlineStr">
         <is>
           <t>Réf. 260716H003, publiée le 16/07/2026, démarrage 01/09/2026. Le périmètre couvre le recueil des besoins des directions RH et la coordination entre RH, DSI et éditeurs jusqu'à la mise en production, avec SAP SuccessFactors et SmartRecruiters cités ainsi que la recette et la conduite du changement ; le fit fonctionnel est donc élevé. L'annonce n'indique aucun télétravail et le site est à Courbevoie, ce qui pose un problème depuis Anglet. Contact : Anais NAESSENS, 01 80 87 54 30.</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
+      <c r="M75" s="5" t="inlineStr">
         <is>
           <t>https://www.freelance-informatique.fr/mission-chef-de-projet-sirh-amoa-sirh-sur-courbevoie-260716H003</t>
         </is>
       </c>
-      <c r="N74" s="39" t="inlineStr">
+      <c r="N75" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.html</t>
         </is>
       </c>
-      <c r="O74" s="39" t="inlineStr">
+      <c r="O75" s="39" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="P74" s="39" t="n"/>
-      <c r="Q74" s="41" t="inlineStr">
+      <c r="P75" s="39" t="n"/>
+      <c r="Q75" s="41" t="inlineStr">
         <is>
           <t>06/10/2026</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="64" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="64" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Postulé</t>
         </is>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Global Product Owner - SuccessFactors</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>Qurated (pour un cabinet d avocats international)</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G76" s="6" t="inlineStr">
         <is>
           <t>CDD / FTC 18 mois</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>Royaume-Uni</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>100% remote</t>
         </is>
       </c>
-      <c r="J75" s="6" t="n"/>
-      <c r="K75" s="6" t="inlineStr">
+      <c r="J76" s="6" t="n"/>
+      <c r="K76" s="6" t="inlineStr">
         <is>
           <t>18 mois</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="L76" s="5" t="inlineStr">
         <is>
           <t>Ownership unique de la plateforme SAP SuccessFactors sur tout le perimetre mondial : vision et roadmap, solution design multi-modules (Employee Central, Performance &amp; Goals, Compensation, Recruiting, Onboarding, Learning), standards globaux, cycles de release, conduite du changement et relation editeur. Fit tres eleve : SuccessFactors multi-modules, contexte global et conduite du changement correspondent au parcours L'Oreal. Full remote. Postule le 07/08/2026.</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="M76" s="5" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/jobs/view/4447393087</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>06/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="79" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Expiré</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Consultant SAP HCM Time Senior</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>Strada (ex-Alight)</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>careers.alight.com</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>Colombes, France</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J76" s="6" t="n"/>
-      <c r="K76" s="6" t="n"/>
-      <c r="L76" s="5" t="inlineStr">
-        <is>
-          <t>Strada expert SAP HCM Time, posté 2026</t>
-        </is>
-      </c>
-      <c r="M76" s="5" t="inlineStr">
-        <is>
-          <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27913STRADAENUS/Consultant-SAP-HCM-Time-senior</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>650-750€/j ou 70-85K€</t>
-        </is>
-      </c>
-      <c r="Q76" s="41" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
         </is>
       </c>
     </row>
@@ -63507,29 +63515,29 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Expiré</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP HCM Paie senior</t>
+          <t>Consultant SAP HCM Time Senior</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Strada (ex-Alight / ex-NGA Human Resources)</t>
+          <t>Strada (ex-Alight)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>careers.alight.com/strada</t>
+          <t>careers.alight.com</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr">
@@ -63539,267 +63547,270 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>Colombes (92)</t>
+          <t>Colombes, France</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Oui (depuis toute la France)</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="6" t="n"/>
       <c r="L77" s="5" t="inlineStr">
         <is>
+          <t>Strada expert SAP HCM Time, posté 2026</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27913STRADAENUS/Consultant-SAP-HCM-Time-senior</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>650-750€/j ou 70-85K€</t>
+        </is>
+      </c>
+      <c r="Q77" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="79" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>paie</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SAP HCM Paie senior</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>Strada (ex-Alight / ex-NGA Human Resources)</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>careers.alight.com/strada</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>Colombes (92)</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Oui (depuis toute la France)</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="n"/>
+      <c r="K78" s="6" t="n"/>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
           <t>Strada = 1er partenaire mondial SAP HR. Configuration payroll SAP HCM France (cycles, schémas, contributions, accounting). 5+ ans SAP HCM Payroll requis. Fit parfait. Remote depuis toute la France confirmé. 2 annonces actives (R-27911 et R-32021).</t>
         </is>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="M78" s="5" t="inlineStr">
         <is>
           <t>https://careers.alight.com/strada/us/en/job/ALIGUSR32021STRADAENUS/Consultant-SAP-HCM-Paie-senior</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>70-85K€</t>
         </is>
       </c>
-      <c r="Q77" s="41" t="inlineStr">
+      <c r="Q78" s="41" t="inlineStr">
         <is>
           <t>06/07/2026</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="80" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="80" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>paie</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>SAP HCM Technico-Functional Consultant French Payroll</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>Apps IT Limited</t>
         </is>
       </c>
-      <c r="F78" s="5" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H79" s="6" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Oui (100% remote)</t>
         </is>
       </c>
-      <c r="J78" s="6" t="inlineStr">
+      <c r="J79" s="6" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="K78" s="6" t="inlineStr">
+      <c r="K79" s="6" t="inlineStr">
         <is>
           <t>6 mois</t>
         </is>
       </c>
-      <c r="L78" s="5" t="inlineStr">
+      <c r="L79" s="5" t="inlineStr">
         <is>
           <t>Publié 17/06/2026. 100% remote — fit parfait pour Anglet. Profil technico-fonctionnel SAP HCM French Payroll. À vérifier disponibilité (publié il y a 6 semaines). Lien : rechercher "Apps IT" sur free-work.com/fr/tech-it/jobs/sap-hcm.</t>
         </is>
       </c>
-      <c r="M78" s="5" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/jobs/sap-hcm</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="Q78" s="41" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="79" t="inlineStr">
+      <c r="Q79" s="41" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="79" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>paie</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>SAP HCM Consultant French Payroll</t>
         </is>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E80" s="5" t="inlineStr">
         <is>
           <t>Client via Movement Group</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F80" s="5" t="inlineStr">
         <is>
           <t>movementgroup.uk</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>Oui (100% remote)</t>
         </is>
       </c>
-      <c r="J79" s="6" t="inlineStr">
+      <c r="J80" s="6" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="K79" s="6" t="inlineStr">
+      <c r="K80" s="6" t="inlineStr">
         <is>
           <t>12 mois + extension</t>
         </is>
       </c>
-      <c r="L79" s="5" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>Movement Group = cabinet recrutement SAP UK/Europe. 100% remote, 12 mois extensible. Outside IR35 (client probablement UK/international). 3+ ans SAP Payroll France requis. Durée et remote = fit parfait.</t>
         </is>
       </c>
-      <c r="M79" s="5" t="inlineStr">
+      <c r="M80" s="5" t="inlineStr">
         <is>
           <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>650-750€/j</t>
         </is>
       </c>
-      <c r="Q79" s="41" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="80" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B80" s="39" t="inlineStr">
-        <is>
-          <t>postulé</t>
-        </is>
-      </c>
-      <c r="C80" s="39" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Expert(e) AMOA et/ou Intégration SIRH (Freelance)</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>Mercer | ConvictionsRH</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>convictionsrh.com</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H80" s="6" t="inlineStr">
-        <is>
-          <t>Selon missions clients</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>Flexible selon clients</t>
-        </is>
-      </c>
-      <c r="J80" s="6" t="n"/>
-      <c r="K80" s="6" t="n"/>
-      <c r="L80" s="5" t="inlineStr">
-        <is>
-          <t>Mission freelance sous-traitance chez Mercer | ConvictionsRH sur SAP SF, Workday, Oracle HCM — cadrage, specs, recette, montées de version. Contact direct : soustraitance@convictionsrh.com. Gaëtan = profil expert indépendant idéal.</t>
-        </is>
-      </c>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>https://www.convictionsrh.com/job/expert-amoa-et-ou-integration-sirh-freelance/</t>
-        </is>
-      </c>
-      <c r="N80" s="39" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O80" s="39" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
-      <c r="P80" s="39" t="n"/>
       <c r="Q80" s="41" t="n"/>
     </row>
     <row r="81">
@@ -63808,29 +63819,29 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="B81" s="39" t="inlineStr">
+        <is>
+          <t>postulé</t>
+        </is>
+      </c>
+      <c r="C81" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Technico-Fonctionnel SAP HCM French Payroll</t>
+          <t>Expert(e) AMOA et/ou Intégration SIRH (Freelance)</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Apps IT Limited</t>
+          <t>Mercer | ConvictionsRH</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>convictionsrh.com</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -63840,24 +63851,24 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Selon missions clients</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>100% remote</t>
+          <t>Flexible selon clients</t>
         </is>
       </c>
       <c r="J81" s="6" t="n"/>
       <c r="K81" s="6" t="n"/>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>Mission 100% remote sur SAP HCM paie française, correspond exactement aux 14 ans d'expertise SAP HR de Gaëtan. Peu de missions SAP HCM affichent un remote total ; à prioriser.</t>
+          <t>Mission freelance sous-traitance chez Mercer | ConvictionsRH sur SAP SF, Workday, Oracle HCM — cadrage, specs, recette, montées de version. Contact direct : soustraitance@convictionsrh.com. Gaëtan = profil expert indépendant idéal.</t>
         </is>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/sap-hcm</t>
+          <t>https://www.convictionsrh.com/job/expert-amoa-et-ou-integration-sirh-freelance/</t>
         </is>
       </c>
       <c r="N81" s="39" t="inlineStr">
@@ -63867,15 +63878,11 @@
       </c>
       <c r="O81" s="39" t="inlineStr">
         <is>
-          <t>600-700€/j</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P81" s="39" t="n"/>
-      <c r="Q81" s="41" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
+      <c r="Q81" s="41" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="80" t="inlineStr">
@@ -63883,29 +63890,29 @@
           <t>⭐⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B82" s="39" t="inlineStr">
-        <is>
-          <t>out of scope</t>
-        </is>
-      </c>
-      <c r="C82" s="39" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>paie</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>SAP SuccessFactors ESM Consultant</t>
+          <t>Technico-Fonctionnel SAP HCM French Payroll</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>n.c. (via Whitehall Resources)</t>
+          <t>Apps IT Limited</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>whitehallresources.com</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
@@ -63915,7 +63922,7 @@
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>Anywhere (remote)</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -63927,22 +63934,22 @@
       <c r="K82" s="6" t="n"/>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>Mission SuccessFactors annoncée en remote total sans contrainte de pays, ce qui est rare sur ce marché. Whitehall place régulièrement des consultants SAP HR en Europe et le contact se fait directement avec un recruteur spécialisé. Référence BBBH67445 à citer lors de la prise de contact.</t>
+          <t>Mission 100% remote sur SAP HCM paie française, correspond exactement aux 14 ans d'expertise SAP HR de Gaëtan. Peu de missions SAP HCM affichent un remote total ; à prioriser.</t>
         </is>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>https://www.whitehallresources.com/jobs/?search=SuccessFactors</t>
+          <t>https://www.free-work.com/fr/tech-it/jobs/sap-hcm</t>
         </is>
       </c>
       <c r="N82" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
       <c r="O82" s="39" t="inlineStr">
         <is>
-          <t>650-750€/j</t>
+          <t>600-700€/j</t>
         </is>
       </c>
       <c r="P82" s="39" t="n"/>
@@ -63960,7 +63967,7 @@
       </c>
       <c r="B83" s="39" t="inlineStr">
         <is>
-          <t>Postulé</t>
+          <t>out of scope</t>
         </is>
       </c>
       <c r="C83" s="39" t="inlineStr">
@@ -63970,27 +63977,27 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Senior HR Transformation Consultant</t>
+          <t>SAP SuccessFactors ESM Consultant</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Resultance</t>
+          <t>n.c. (via Whitehall Resources)</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>whitehallresources.com</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Freelance / indépendant (CDD de mission)</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Union européenne</t>
+          <t>Anywhere (remote)</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -63998,34 +64005,26 @@
           <t>100% remote</t>
         </is>
       </c>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>Non affiché</t>
-        </is>
-      </c>
-      <c r="K83" s="6" t="inlineStr">
-        <is>
-          <t>Sept. à déc. 2026, extension possible ; 2 à 3 jours par semaine</t>
-        </is>
-      </c>
+      <c r="J83" s="6" t="n"/>
+      <c r="K83" s="6" t="n"/>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>Cabinet de conseil né au Luxembourg, présent en France, Belgique et Royaume-Uni, 51 à 200 salariés, qui adosse une part de ses honoraires aux résultats obtenus. La mission porte sur la refonte du modèle opérationnel RH et des processus de bout en bout : animation d'ateliers de conception, consolidation des processus sur tous les piliers RH, définition des rôles et de la gouvernance, feuille de route de transformation et conduite du changement, plus la supervision d'un consultant junior. Les 7 à 10 ans demandés couvrent explicitement l'implémentation SIRH, donc les quinze ans sur SAP HR répondent au critère ; l'expérience de supervision de l'équipe Inde chez ALTI répond au volet encadrement, et le passage en cabinet est présenté comme un atout fort. Le format à temps partiel et en remote intégral permet de cumuler avec une autre mission. Offre publiée le 05/08/2026, déjà 67 candidats, réponse annoncée sous une semaine ; candidature simplifiée LinkedIn. Recruteuse : Olga Adam, Talent Acquisition Manager. Point d'entrée réseau : Ludovic Van Sinay, relation de 3e degré et ancien de L'Oréal, à contacter avant de postuler.</t>
+          <t>Mission SuccessFactors annoncée en remote total sans contrainte de pays, ce qui est rare sur ce marché. Whitehall place régulièrement des consultants SAP HR en Europe et le contact se fait directement avec un recruteur spécialisé. Référence BBBH67445 à citer lors de la prise de contact.</t>
         </is>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4448991282/</t>
+          <t>https://www.whitehallresources.com/jobs/?search=SuccessFactors</t>
         </is>
       </c>
       <c r="N83" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_Resultance.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
       <c r="O83" s="39" t="inlineStr">
         <is>
-          <t>À discuter</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P83" s="39" t="n"/>
@@ -64036,84 +64035,85 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="77" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="A84" s="80" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B84" s="39" t="inlineStr">
+        <is>
+          <t>Postulé</t>
+        </is>
+      </c>
+      <c r="C84" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>SAP HCM Consultant (French Payroll)</t>
+          <t>Senior HR Transformation Consultant</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Movement Group</t>
+          <t>Resultance</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>movementgroup.uk</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>Freelance (12 mois + extension)</t>
+          <t>Freelance / indépendant (CDD de mission)</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>Remote (100%)</t>
+          <t>Union européenne</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>100% remote</t>
         </is>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>TJM Outside IR35</t>
+          <t>Non affiché</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>12 mois</t>
+          <t>Sept. à déc. 2026, extension possible ; 2 à 3 jours par semaine</t>
         </is>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>Mission freelance remote, paie française SAP HCM. 3 ans expérience requis. Fit parfait.</t>
+          <t>Cabinet de conseil né au Luxembourg, présent en France, Belgique et Royaume-Uni, 51 à 200 salariés, qui adosse une part de ses honoraires aux résultats obtenus. La mission porte sur la refonte du modèle opérationnel RH et des processus de bout en bout : animation d'ateliers de conception, consolidation des processus sur tous les piliers RH, définition des rôles et de la gouvernance, feuille de route de transformation et conduite du changement, plus la supervision d'un consultant junior. Les 7 à 10 ans demandés couvrent explicitement l'implémentation SIRH, donc les quinze ans sur SAP HR répondent au critère ; l'expérience de supervision de l'équipe Inde chez ALTI répond au volet encadrement, et le passage en cabinet est présenté comme un atout fort. Le format à temps partiel et en remote intégral permet de cumuler avec une autre mission. Offre publiée le 05/08/2026, déjà 67 candidats, réponse annoncée sous une semaine ; candidature simplifiée LinkedIn. Recruteuse : Olga Adam, Talent Acquisition Manager. Point d'entrée réseau : Ludovic Van Sinay, relation de 3e degré et ancien de L'Oréal, à contacter avant de postuler.</t>
         </is>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4448991282/</t>
+        </is>
+      </c>
+      <c r="N84" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Resultance.pdf</t>
+        </is>
+      </c>
+      <c r="O84" s="39" t="inlineStr">
+        <is>
+          <t>À discuter</t>
+        </is>
+      </c>
+      <c r="P84" s="39" t="n"/>
       <c r="Q84" s="41" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
     </row>
@@ -64125,7 +64125,7 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>pourvu</t>
+          <t>paie</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
@@ -64135,27 +64135,27 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Consultant AMOA SIRH (Performance &amp; International) - Full remote possible</t>
+          <t>SAP HCM Consultant (French Payroll)</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Cherry Pick (pour client)</t>
+          <t>Movement Group</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>movementgroup.uk</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Freelance (12 mois + extension)</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote (100%)</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -64163,16 +64163,24 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="J85" s="6" t="n"/>
-      <c r="K85" s="6" t="n"/>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>TJM Outside IR35</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>12 mois</t>
+        </is>
+      </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>AMOA SIRH international, lien Group HR et entités locales, évaluation de la performance. Full remote possible. Très bon fit profil L'Oréal mondial.</t>
+          <t>Mission freelance remote, paie française SAP HCM. 3 ans expérience requis. Fit parfait.</t>
         </is>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/consultant-moa-amoa/job-mission/consultant-amoa-sirh-performance-international-full-remote-possible</t>
+          <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -64197,155 +64205,146 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B86" s="39" t="inlineStr">
-        <is>
-          <t>Expiré</t>
-        </is>
-      </c>
-      <c r="C86" s="39" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>pourvu</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Consultant SAP HCM Time senior</t>
+          <t>Consultant AMOA SIRH (Performance &amp; International) - Full remote possible</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Strada (ex-Alight)</t>
+          <t>Cherry Pick (pour client)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>careers.alight.com/strada</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>Colombes (92)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>Oui (depuis toute la France)</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J86" s="6" t="n"/>
       <c r="K86" s="6" t="n"/>
       <c r="L86" s="5" t="inlineStr">
         <is>
+          <t>AMOA SIRH international, lien Group HR et entités locales, évaluation de la performance. Full remote possible. Très bon fit profil L'Oréal mondial.</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/consultant-moa-amoa/job-mission/consultant-amoa-sirh-performance-international-full-remote-possible</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>650-750€/j</t>
+        </is>
+      </c>
+      <c r="Q86" s="41" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="77" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B87" s="39" t="inlineStr">
+        <is>
+          <t>Expiré</t>
+        </is>
+      </c>
+      <c r="C87" s="39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Consultant SAP HCM Time senior</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Strada (ex-Alight)</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>careers.alight.com/strada</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>Colombes (92)</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>Oui (depuis toute la France)</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="n"/>
+      <c r="K87" s="6" t="n"/>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
           <t>Strada 1er partenaire SAP HR. Module Time Management SAP HCM. Remote France confirmé. En complément du poste Paie senior (voir autre entrée).</t>
         </is>
       </c>
-      <c r="M86" s="5" t="inlineStr">
+      <c r="M87" s="5" t="inlineStr">
         <is>
           <t>https://careers.alight.com/strada/us/en/job/ALIGUSR27913STRADAENUS/Consultant-SAP-HCM-Time-senior</t>
         </is>
       </c>
-      <c r="N86" s="39" t="inlineStr">
+      <c r="N87" s="39" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
-      <c r="O86" s="39" t="inlineStr">
+      <c r="O87" s="39" t="inlineStr">
         <is>
           <t>70-85K€</t>
-        </is>
-      </c>
-      <c r="P86" s="39" t="n"/>
-      <c r="Q86" s="41" t="inlineStr">
-        <is>
-          <t>07/05/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="78" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>Technico-Fonctionnel SAP HCM French Payroll</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>Apps IT Limited</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Free-Work</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J87" s="6" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="K87" s="6" t="inlineStr">
-        <is>
-          <t>6 mois renouvelable</t>
-        </is>
-      </c>
-      <c r="L87" s="5" t="inlineStr">
-        <is>
-          <t>100% télétravail, démarrage ASAP. SAP HCM Payroll FR. Profil orienté technique (ABAP) – Gaëtan est fonctionnel mais maîtrise le domaine. À évaluer.</t>
-        </is>
-      </c>
-      <c r="M87" s="5" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/technico-fonctionnel-sap-hcm-french-payroll</t>
-        </is>
-      </c>
-      <c r="N87" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
-        </is>
-      </c>
-      <c r="O87" s="39" t="inlineStr">
-        <is>
-          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P87" s="39" t="n"/>
       <c r="Q87" s="41" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>07/05/2025</t>
         </is>
       </c>
     </row>
@@ -64367,224 +64366,220 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
+          <t>Technico-Fonctionnel SAP HCM French Payroll</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Apps IT Limited</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Free-Work</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>6 mois renouvelable</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>100% télétravail, démarrage ASAP. SAP HCM Payroll FR. Profil orienté technique (ABAP) – Gaëtan est fonctionnel mais maîtrise le domaine. À évaluer.</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-erp-ms-dynamics-oracle-sage-sap/technico-fonctionnel-sap-hcm-french-payroll</t>
+        </is>
+      </c>
+      <c r="N88" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
+        </is>
+      </c>
+      <c r="O88" s="39" t="inlineStr">
+        <is>
+          <t>650-750€/j</t>
+        </is>
+      </c>
+      <c r="P88" s="39" t="n"/>
+      <c r="Q88" s="41" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="78" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>paie</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
           <t>SAP HCM Consultant (French Payroll)</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>Client anonyme (via Movement Group)</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>movementgroup.uk</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I88" s="6" t="inlineStr">
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J88" s="6" t="inlineStr">
+      <c r="J89" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K88" s="6" t="inlineStr">
+      <c r="K89" s="6" t="inlineStr">
         <is>
           <t>12 mois</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr">
+      <c r="L89" s="5" t="inlineStr">
         <is>
           <t>SAP HCM payroll FR config, 100% remote, Outside IR35 — bon fit SAP HR mais spécialisé paie France uniquement (profil Gaetan = SAP HR international L'Oréal 40+ pays)</t>
         </is>
       </c>
-      <c r="M88" s="5" t="inlineStr">
+      <c r="M89" s="5" t="inlineStr">
         <is>
           <t>https://movementgroup.uk/job/sap-hcm-consultant-time-management/</t>
         </is>
       </c>
-      <c r="N88" s="39" t="inlineStr">
+      <c r="N89" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O88" s="39" t="n"/>
-      <c r="P88" s="39" t="n"/>
-      <c r="Q88" s="41" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="82" t="inlineStr">
+      <c r="O89" s="39" t="n"/>
+      <c r="P89" s="39" t="n"/>
+      <c r="Q89" s="41" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="82" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>paie</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D89" s="39" t="inlineStr">
+      <c r="D90" s="39" t="inlineStr">
         <is>
           <t>SAP HCM-Payroll Consultant</t>
         </is>
       </c>
-      <c r="E89" s="39" t="inlineStr">
+      <c r="E90" s="39" t="inlineStr">
         <is>
           <t>N/C (via eursap.eu)</t>
         </is>
       </c>
-      <c r="F89" s="39" t="inlineStr">
+      <c r="F90" s="39" t="inlineStr">
         <is>
           <t>eursap.eu</t>
         </is>
       </c>
-      <c r="G89" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H89" s="39" t="inlineStr">
+      <c r="G90" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H90" s="39" t="inlineStr">
         <is>
           <t>Multiple EU + Remote</t>
         </is>
       </c>
-      <c r="I89" s="39" t="inlineStr">
+      <c r="I90" s="39" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="J89" s="39" t="inlineStr">
+      <c r="J90" s="39" t="inlineStr">
         <is>
           <t>N/C</t>
         </is>
       </c>
-      <c r="K89" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="L89" s="39" t="inlineStr">
+      <c r="K90" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="L90" s="39" t="inlineStr">
         <is>
           <t>SAP HCM Payroll international, remote-friendly ; ref 29132</t>
         </is>
       </c>
-      <c r="M89" s="39" t="inlineStr">
+      <c r="M90" s="39" t="inlineStr">
         <is>
           <t>https://eursap.eu/sap-jobs/france/</t>
         </is>
       </c>
-      <c r="N89" s="39" t="n"/>
-      <c r="O89" s="39" t="n"/>
-      <c r="P89" s="39" t="inlineStr">
+      <c r="N90" s="39" t="n"/>
+      <c r="O90" s="39" t="n"/>
+      <c r="P90" s="39" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="Q89" s="39" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="78" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>paie</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>SAP Payroll Implementation Lead - France</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>Strada Global</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>Strada Global Careers / Remote Rocketship</t>
-        </is>
-      </c>
-      <c r="G90" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>100% remote</t>
-        </is>
-      </c>
-      <c r="J90" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K90" s="6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="L90" s="5" t="inlineStr">
-        <is>
-          <t>Strada = RH/paie globale (SAP, Oracle, Workday). Lead impl SAP Payroll France, 5+ implémentations SAP HCM requises, connaissance paie FR. Profil Gaëtan SAP HR adjacent mais payroll pur = frein partiel.</t>
-        </is>
-      </c>
-      <c r="M90" s="5" t="inlineStr">
-        <is>
-          <t>https://careers.stradaglobal.com/careers/job/1133913392690-sap-payroll-implementation-lead-france-granada-spain</t>
-        </is>
-      </c>
-      <c r="N90" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O90" s="39" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="P90" s="39" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
-      <c r="Q90" s="41" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
+      <c r="Q90" s="39" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="78" t="inlineStr">
@@ -64604,137 +64599,224 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
+          <t>SAP Payroll Implementation Lead - France</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Strada Global</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Strada Global Careers / Remote Rocketship</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>100% remote</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>Strada = RH/paie globale (SAP, Oracle, Workday). Lead impl SAP Payroll France, 5+ implémentations SAP HCM requises, connaissance paie FR. Profil Gaëtan SAP HR adjacent mais payroll pur = frein partiel.</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>https://careers.stradaglobal.com/careers/job/1133913392690-sap-payroll-implementation-lead-france-granada-spain</t>
+        </is>
+      </c>
+      <c r="N91" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O91" s="39" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="P91" s="39" t="inlineStr">
+        <is>
+          <t>07/2026</t>
+        </is>
+      </c>
+      <c r="Q91" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="78" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>paie</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
           <t>Formateur SAP Employee Central &amp; Payroll Integration</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>n.c. (via Freelancer.com)</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>freelancer.com</t>
         </is>
       </c>
-      <c r="G91" s="6" t="inlineStr">
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="H92" s="6" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I91" s="6" t="inlineStr">
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>100% remote</t>
         </is>
       </c>
-      <c r="J91" s="6" t="inlineStr">
+      <c r="J92" s="6" t="inlineStr">
         <is>
           <t>~488 $ (enchère moyenne)</t>
         </is>
       </c>
-      <c r="K91" s="6" t="inlineStr">
+      <c r="K92" s="6" t="inlineStr">
         <is>
           <t>Court, 4 jours restants pour candidater</t>
         </is>
       </c>
-      <c r="L91" s="5" t="inlineStr">
+      <c r="L92" s="5" t="inlineStr">
         <is>
           <t>Le client cherche un praticien SuccessFactors expérimenté pour dispenser une formation sur Employee Central et son intégration paie de bout en bout. C'est exactement le périmètre des go-live OneProfile et OnePayroll ; peu de profils peuvent enseigner cette intégration pour l'avoir livrée en production sur 40 pays. Le budget est faible et la mission courte, mais le format se prête à une première référence de formateur SAP, utile pour ouvrir le segment formation. Date limite proche, à traiter vite.</t>
         </is>
       </c>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="M92" s="5" t="inlineStr">
         <is>
           <t>https://www.freelancer.com/jobs/sap/</t>
         </is>
       </c>
-      <c r="N91" s="39" t="inlineStr">
+      <c r="N92" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH_EN.html</t>
         </is>
       </c>
-      <c r="O91" s="39" t="inlineStr">
+      <c r="O92" s="39" t="inlineStr">
         <is>
           <t>À discuter</t>
         </is>
       </c>
-      <c r="P91" s="39" t="n"/>
-      <c r="Q91" s="41" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="77" t="inlineStr">
+      <c r="P92" s="39" t="n"/>
+      <c r="Q92" s="41" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="77" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="B92" s="39" t="inlineStr">
+      <c r="B93" s="39" t="inlineStr">
         <is>
           <t>pourvu</t>
         </is>
       </c>
-      <c r="C92" s="39" t="inlineStr">
+      <c r="C93" s="39" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Consultant SIRH (H/F) - N2F</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>N2jsoft</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
         <is>
           <t>welcometothejungle.com</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>Montagnat (remote)</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr">
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>100% remote</t>
         </is>
       </c>
-      <c r="J92" s="6" t="n"/>
-      <c r="K92" s="6" t="n"/>
-      <c r="L92" s="5" t="inlineStr">
+      <c r="J93" s="6" t="n"/>
+      <c r="K93" s="6" t="n"/>
+      <c r="L93" s="5" t="inlineStr">
         <is>
           <t>Poste en CDI intégralement remote chez l'éditeur de N2F, avec formation interne sur le produit. Le remote total lève la contrainte principale ; le chef de projet SIRH du même éditeur est déjà suivi dans le tableur. Éditeur de taille moyenne, donc rémunération probablement sous la fourchette cible.</t>
         </is>
       </c>
-      <c r="M92" s="5" t="inlineStr">
+      <c r="M93" s="5" t="inlineStr">
         <is>
           <t>https://www.welcometothejungle.com/en/companies/n2jsoft-fr/jobs/consultant-logiciel-rh-h-f-n2f_montagnat_N2JSO_M2lVjoW</t>
         </is>
       </c>
-      <c r="N92" s="39" t="inlineStr">
+      <c r="N93" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.html</t>
         </is>
       </c>
-      <c r="O92" s="39" t="inlineStr">
+      <c r="O93" s="39" t="inlineStr">
         <is>
           <t>65-75K€</t>
         </is>
       </c>
-      <c r="P92" s="39" t="n"/>
-      <c r="Q92" s="41" t="inlineStr">
+      <c r="P93" s="39" t="n"/>
+      <c r="Q93" s="41" t="inlineStr">
         <is>
           <t>06/10/2026</t>
         </is>

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -35291,7 +35291,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_Constructor_EN.pdf</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -9,13 +9,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres SIRH" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres CSM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres IA" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres PM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fait" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Légende" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Offres SIRH'!$A$1:$O$463</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Offres CSM'!$A$1:$O$295</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Offres IA'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Offres PM'!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +100,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="53">
+  <fills count="54">
     <fill>
       <patternFill/>
     </fill>
@@ -365,6 +367,11 @@
         <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -394,7 +401,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -609,6 +616,8 @@
     <xf numFmtId="0" fontId="7" fillId="51" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -35281,7 +35290,7 @@
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>Encadrement de l'équipe CSM EMEA chez un éditeur search/discovery ecommerce. Points forts : enterprise multi-pays, rôle d'escalade et interface Produit/Engineering (equivalent du role L1/L2/L3 chez L'Oreal), multilinguisme valorisé en bonus, full remote depuis la France. Sephora est client de Constructor : angle beaute/retail a exploiter en LM via L'Oreal et le deploiement Tamigo en magasins. ECART A ASSUMER : ils demandent d'avoir deja manage une equipe de CSM/TAM/Solutions Consulting ; le CV documente du management d'equipe offshore (Inde, 2014-2016), un alternant et le role de CEO cofondateur, pas du line management de CSM. Domaine search/ecommerce inconnu. Remplace l'ancienne annonce Constructor CSM French Speaker, fermee.</t>
+          <t>Encadrement de l'équipe CSM EMEA chez un éditeur search/discovery ecommerce. Points forts : enterprise multi-pays, rôle d'escalade et interface Produit/Engineering (equivalent du role L1/L2/L3 chez L'Oreal), multilinguisme valorisé en bonus, full remote depuis la France. Sephora est client de Constructor : angle beaute/retail a exploiter en LM via L'Oreal et le deploiement Tamigo en magasins. ECART A ASSUMER : ils demandent d'avoir deja manage une equipe de CSM/TAM/Solutions Consulting ; le CV documente du management d'equipe offshore (Inde, 2014-2016), un alternant et le role de cofondateur et Product Manager, pas du line management de CSM. Domaine search/ecommerce inconnu. Remplace l'ancienne annonce Constructor CSM French Speaker, fermee.</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
@@ -60392,6 +60401,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.6640625" customWidth="1" min="1" max="1"/>
+    <col width="10.83203125" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="51.83203125" customWidth="1" min="4" max="4"/>
+    <col width="25.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
+    <col width="14.1640625" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="23.6640625" customWidth="1" min="9" max="9"/>
+    <col width="26.6640625" customWidth="1" min="10" max="10"/>
+    <col width="17.33203125" customWidth="1" min="11" max="11"/>
+    <col width="99.83203125" customWidth="1" min="12" max="12"/>
+    <col width="106.5" customWidth="1" min="13" max="13"/>
+    <col width="31.33203125" customWidth="1" min="14" max="14"/>
+    <col width="9.1640625" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Priorité</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Statut</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Fait</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Poste</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>Entreprise</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>Contrat</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>Localisation</t>
+        </is>
+      </c>
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>Salaire / TJM</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>Durée mission</t>
+        </is>
+      </c>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>Fit / Notes</t>
+        </is>
+      </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="N1" s="102" t="inlineStr">
+        <is>
+          <t>CV à envoyer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Prétention</t>
+        </is>
+      </c>
+      <c r="P1" s="40" t="inlineStr">
+        <is>
+          <t>Date trouvée</t>
+        </is>
+      </c>
+      <c r="Q1" s="40" t="inlineStr">
+        <is>
+          <t>Date publiée</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Product Manager: Customer Onboarding Experience</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Constructor</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>jobs.ashbyhq.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Propriete du parcours d'integration client (SDK, docs, instrumentation de tracking), north star time-to-value. Atouts : propriete produit reelle chez WallOfTraders.com, parcours d'integration L'Oreal sur 40 pays, role de charniere metier/developpeurs, redaction de specifications. LACUNE DURE : ils exigent 3+ ans de PM sur produit oriente developpeurs (SDK, API, tracking) ; Gaetan n'en a pas, c'est un filtre potentiellement eliminatoire. Candidature plus risquee que le poste Regional Manager CS chez le meme employeur.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/constructor/e8fa6194-ef2e-47d3-ab45-a9112d87da24</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>80-100 K€</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -68203,7 +68394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -100,7 +100,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="54">
+  <fills count="56">
     <fill>
       <patternFill/>
     </fill>
@@ -372,6 +372,16 @@
         <fgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF8C00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -401,7 +411,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -618,6 +628,8 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="53" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -60401,7 +60413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.6640625" customWidth="1" min="1" max="1"/>
@@ -60510,64 +60522,1220 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="103" t="inlineStr">
+      <c r="A2" s="104" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - Core Platform (Remote)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Camunda</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>jobs.ashbyhq.com</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Editeur d'orchestration de processus, entreprise remote-first. Gaetan avait deja cible Camunda (CV_GaetanFRANCOIS_Camunda_EN existe), donc le contexte est connu. Poste verifie ouvert par l'API Ashby le 14/08.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/camunda/b771e145-a5cf-4867-ad13-b54830e3b744</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>85-100 K€</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="104" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Senior Product Builder - Connectors Experience - EMEA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Camunda</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>jobs.ashbyhq.com</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Produit centre sur l'experience des connecteurs, donc sur l'integration : c'est l'angle le plus proche du parcours (parcours d'integration L'Oreal, charniere metier/developpeurs). Verifie ouvert par API.</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/camunda/05cb2825-dcd9-40e6-bf92-bda409d99374</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>85-100 K€</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="104" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>360Learning</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>welcometothejungle.com</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Télétravail total</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Plateforme de learning : le domaine recoupe directement l'experience de formation utilisateurs-cles et de transfert de connaissances. Teletravail total, editeur francais bien etabli. Un des meilleurs croisements produit/parcours du lot.</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/360learning/jobs/product-manager_paris_360LE_lGeWWq1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="104" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>welcometothejungle.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Télétravail total</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>55-59 K€</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Teletravail total, plus de 4 ans d'experience demandes, demarrage 31/08/2026. Remuneration sous la cible ; le salaire ne sert pas de filtre.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/side/jobs/product-manager_paris_SIDE_jRLO2Ar</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="104" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inqom</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>welcometothejungle.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Paris / Tours</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Télétravail total</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>50-55 K€</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Teletravail total sur un SaaS comptable. Fourchette sous la cible, a negocier.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/inqom/jobs/product-manager</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="103" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Product Manager: Customer Onboarding Experience</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Constructor</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>jobs.ashbyhq.com</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Propriete du parcours d'integration client (SDK, docs, instrumentation de tracking), north star time-to-value. Atouts : propriete produit reelle chez WallOfTraders.com, parcours d'integration L'Oreal sur 40 pays, role de charniere metier/developpeurs, redaction de specifications. LACUNE DURE : ils exigent 3+ ans de PM sur produit oriente developpeurs (SDK, API, tracking) ; Gaetan n'en a pas, c'est un filtre potentiellement eliminatoire. Candidature plus risquee que le poste Regional Manager CS chez le meme employeur.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/constructor/e8fa6194-ef2e-47d3-ab45-a9112d87da24</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>80-100 K€</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Product Manager, Self Managed Service</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Camunda</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>jobs.ashbyhq.com</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Troisieme poste produit ouvert chez Camunda ; perimetre self-managed, plus technique. Verifie ouvert par API.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/camunda/5652a3f3-e418-4e91-b58b-4be13f36853b</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>80-95 K€</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Product Manager (senior level)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Joko</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>welcometothejungle.com</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Télétravail total</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Niveau senior explicite, teletravail total. Produit B2C, ce qui recoupe l'experience WallOfTraders.com.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/en/companies/joko/jobs/product-manager-senior-level</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Product Manager (full remote avec déplacements)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RISE</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>welcometothejungle.com</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Télétravail total</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Full remote avec deplacements ponctuels, compatible avec une base a Anglet.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/rise/jobs/28b1f52c-1924-40ec-b7e0-18bbdcda6c56</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Follow</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>welcometothejungle.com</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Télétravail total</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Teletravail total, secteur sante. A qualifier sur la seniorite attendue.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/follow-health/jobs/product-manager</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Product Manager, Data Activation</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>n.c. (via Jobgether)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>jobs.lever.co</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Remote depuis la France, verifie ouvert par l'API Lever. Jobgether publie la meme offre par pays ; seule la variante France est retenue ici.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/jobgether/dad5d8dc-4e02-4536-b7f6-8680e1df16ce</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Product Manager, Data Orchestration</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>n.c. (via Jobgether)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>jobs.lever.co</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Remote depuis la France, verifie ouvert par l'API Lever.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/jobgether/5245a149-8431-4452-ab44-50cbb9bafbcf</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>n.c. (via Jobgether)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>jobs.lever.co</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Product Owner en full remote depuis la France, verifie ouvert par l'API Lever.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/jobgether/5405e9ec-8ab3-4075-8f5e-96425e4f11a6</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>B2C Growth Product Manager</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>n.c. (via Jobgether)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>jobs.lever.co</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Produit B2C oriente growth : recoupe directement WallOfTraders.com (acquisition SEO, paid social, boucle de retour utilisateurs).</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/jobgether/bae287fc-687d-48a6-a860-100430cbe25e</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sr. Product Manager, Core Platform</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>n.c. (via Jobgether)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>jobs.lever.co</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>France / Pays-Bas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Full remote</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Poste senior sur plateforme coeur, full remote.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/jobgether/3efb5da5-0c07-4209-a4b6-037ead7571c2</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>80-95 K€</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Senior Product Manager</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pennylane</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>jobs.lever.co</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Remote Europe</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Scale-up francaise, remote depuis n'importe ou en Europe. URL issue de WebSearch : l'API Lever n'a pas repondu sur ce slug, verifier que l'annonce est encore ouverte avant de candidater.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/pennylane/e821e150-f513-4297-86a7-6d2ee25ac50c</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>80-95 K€</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="105" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ITSM Platform Architect / Technical Product Owner</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LeHibou</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>free-work</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Mission freelance</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>650 €/j</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Product Owner technique sur plateforme ITSM. Sur site Paris, donc en retrait sur le critere remote.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/product-owner/itsm-platform-architect-technical-product-owner</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>650 €/j</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="105" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Product Owner (H/F) 69</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Mindquest</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>free-work</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Mission freelance</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>400-550 €/j</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3 mois</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Mission PO courte a Lyon, sur site.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/product-owner/product-owner-h-f-69-1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>550 €/j</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="105" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WIKEYS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>free-work</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Mission freelance</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Bruxelles</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>600-610 €/j</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Mission PO a Bruxelles ; contexte international, mais sur site.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/product-owner/product-owner-1365</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_Constructor_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>610 €/j</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
         </is>
       </c>
     </row>

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -27698,57 +27698,53 @@
       <c r="Q395" s="41" t="n"/>
     </row>
     <row r="396" ht="16" customHeight="1">
-      <c r="A396" s="90" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
+      <c r="A396" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B396" s="39" t="n"/>
       <c r="C396" s="39" t="n"/>
       <c r="D396" s="5" t="inlineStr">
         <is>
-          <t>Senior Consultant HR Transformation Workday</t>
+          <t>Implementation lead - 12 month contract</t>
         </is>
       </c>
       <c r="E396" s="5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Watershed</t>
         </is>
       </c>
       <c r="F396" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>jobs.ashbyhq.com</t>
         </is>
       </c>
       <c r="G396" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>CDD 12 mois</t>
         </is>
       </c>
       <c r="H396" s="6" t="inlineStr">
         <is>
-          <t>La Défense</t>
-        </is>
-      </c>
-      <c r="I396" s="6" t="inlineStr">
-        <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J396" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K396" s="6" t="n"/>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="I396" s="6" t="n"/>
+      <c r="J396" s="6" t="n"/>
+      <c r="K396" s="6" t="inlineStr">
+        <is>
+          <t>12 mois</t>
+        </is>
+      </c>
       <c r="L396" s="5" t="inlineStr">
         <is>
-          <t>Consulting RH ✓ — certification Workday requise, stack différent de SAP</t>
+          <t>Pilotage de deploiement client, exactement le metier exerce pendant quinze ans. Verifie ouvert par API. CDD de 12 mois a Londres.</t>
         </is>
       </c>
       <c r="M396" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4416588225/</t>
+          <t>https://jobs.ashbyhq.com/Watershed/98421ded-d419-4e1b-bb1e-d610d967b17c</t>
         </is>
       </c>
       <c r="N396" s="39" t="inlineStr">
@@ -27758,10 +27754,14 @@
       </c>
       <c r="O396" s="39" t="inlineStr">
         <is>
-          <t>60 K€</t>
-        </is>
-      </c>
-      <c r="P396" s="39" t="n"/>
+          <t>75-90 K€</t>
+        </is>
+      </c>
+      <c r="P396" s="39" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
       <c r="Q396" s="41" t="n"/>
     </row>
     <row r="397" ht="16" customHeight="1">
@@ -27774,32 +27774,32 @@
       <c r="C397" s="39" t="n"/>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>PMO SuccessFactors</t>
+          <t>Senior Consultant HR Transformation Workday</t>
         </is>
       </c>
       <c r="E397" s="5" t="inlineStr">
         <is>
-          <t>Mindquest</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="F397" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G397" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H397" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>La Défense</t>
         </is>
       </c>
       <c r="I397" s="6" t="inlineStr">
         <is>
-          <t>n.p.</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J397" s="6" t="inlineStr">
@@ -27807,37 +27807,29 @@
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K397" s="6" t="inlineStr">
-        <is>
-          <t>3 mois</t>
-        </is>
-      </c>
+      <c r="K397" s="6" t="n"/>
       <c r="L397" s="5" t="inlineStr">
         <is>
-          <t>Coordination projets SF design/build/test, reporting, bilingue EN requis</t>
+          <t>Consulting RH ✓ — certification Workday requise, stack différent de SAP</t>
         </is>
       </c>
       <c r="M397" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/project-management-officer/pmo-successfactors-h-f-75</t>
+          <t>https://www.linkedin.com/jobs/view/4416588225/</t>
         </is>
       </c>
       <c r="N397" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O397" s="39" t="inlineStr">
         <is>
-          <t>650 €/j</t>
+          <t>60 K€</t>
         </is>
       </c>
       <c r="P397" s="39" t="n"/>
-      <c r="Q397" s="41" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q397" s="41" t="n"/>
     </row>
     <row r="398" ht="16" customHeight="1">
       <c r="A398" s="90" t="inlineStr">
@@ -27849,62 +27841,70 @@
       <c r="C398" s="39" t="n"/>
       <c r="D398" s="5" t="inlineStr">
         <is>
-          <t>Global SAP HRIS Manager (SuccessFactors)</t>
+          <t>PMO SuccessFactors</t>
         </is>
       </c>
       <c r="E398" s="5" t="inlineStr">
         <is>
-          <t>Via Eursap</t>
+          <t>Mindquest</t>
         </is>
       </c>
       <c r="F398" s="5" t="inlineStr">
         <is>
-          <t>eursap.eu</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G398" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H398" s="6" t="inlineStr">
         <is>
-          <t>Allemagne</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I398" s="6" t="inlineStr">
         <is>
-          <t>Non précisé</t>
+          <t>n.p.</t>
         </is>
       </c>
       <c r="J398" s="6" t="inlineStr">
         <is>
-          <t>jusqu'à 145 K€</t>
-        </is>
-      </c>
-      <c r="K398" s="6" t="n"/>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K398" s="6" t="inlineStr">
+        <is>
+          <t>3 mois</t>
+        </is>
+      </c>
       <c r="L398" s="5" t="inlineStr">
         <is>
-          <t>Très bon salaire — poste en Allemagne, pas remote confirmé</t>
+          <t>Coordination projets SF design/build/test, reporting, bilingue EN requis</t>
         </is>
       </c>
       <c r="M398" s="5" t="inlineStr">
         <is>
-          <t>https://eursap.eu/jobs/global-sap-hris-manager-successfactors-34522-de</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/project-management-officer/pmo-successfactors-h-f-75</t>
         </is>
       </c>
       <c r="N398" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O398" s="39" t="inlineStr">
         <is>
-          <t>110 K€</t>
+          <t>650 €/j</t>
         </is>
       </c>
       <c r="P398" s="39" t="n"/>
-      <c r="Q398" s="41" t="n"/>
+      <c r="Q398" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="399" ht="32" customHeight="1">
       <c r="A399" s="90" t="inlineStr">
@@ -27916,62 +27916,58 @@
       <c r="C399" s="39" t="n"/>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>Consultant fonctionnel SAP HR/HCM</t>
+          <t>Global SAP HRIS Manager (SuccessFactors)</t>
         </is>
       </c>
       <c r="E399" s="5" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>Via Eursap</t>
         </is>
       </c>
       <c r="F399" s="5" t="inlineStr">
         <is>
-          <t>freelance-informatique.fr</t>
+          <t>eursap.eu</t>
         </is>
       </c>
       <c r="G399" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H399" s="6" t="inlineStr">
         <is>
-          <t>Clermont-Ferrand (63)</t>
+          <t>Allemagne</t>
         </is>
       </c>
       <c r="I399" s="6" t="inlineStr">
         <is>
-          <t>n.p.</t>
+          <t>Non précisé</t>
         </is>
       </c>
       <c r="J399" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K399" s="6" t="inlineStr">
-        <is>
-          <t>9 mois</t>
-        </is>
-      </c>
+          <t>jusqu'à 145 K€</t>
+        </is>
+      </c>
+      <c r="K399" s="6" t="n"/>
       <c r="L399" s="5" t="inlineStr">
         <is>
-          <t>Hors IDF — déplacement nécessaire</t>
+          <t>Très bon salaire — poste en Allemagne, pas remote confirmé</t>
         </is>
       </c>
       <c r="M399" s="5" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/mission-sap-hr-461</t>
+          <t>https://eursap.eu/jobs/global-sap-hris-manager-successfactors-34522-de</t>
         </is>
       </c>
       <c r="N399" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O399" s="39" t="inlineStr">
         <is>
-          <t>700 €/j</t>
+          <t>110 K€</t>
         </is>
       </c>
       <c r="P399" s="39" t="n"/>
@@ -27987,27 +27983,27 @@
       <c r="C400" s="39" t="n"/>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>Consultant(e) Senior SIRH</t>
+          <t>Consultant fonctionnel SAP HR/HCM</t>
         </is>
       </c>
       <c r="E400" s="5" t="inlineStr">
         <is>
-          <t>ALTHEA</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="F400" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>freelance-informatique.fr</t>
         </is>
       </c>
       <c r="G400" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H400" s="6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Clermont-Ferrand (63)</t>
         </is>
       </c>
       <c r="I400" s="6" t="inlineStr">
@@ -28017,18 +28013,22 @@
       </c>
       <c r="J400" s="6" t="inlineStr">
         <is>
-          <t>40-50 K€</t>
-        </is>
-      </c>
-      <c r="K400" s="6" t="n"/>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K400" s="6" t="inlineStr">
+        <is>
+          <t>9 mois</t>
+        </is>
+      </c>
       <c r="L400" s="5" t="inlineStr">
         <is>
-          <t>1-5 ans exp, profil junior/mid — salaire faible, Nantes loin de Biarritz</t>
+          <t>Hors IDF — déplacement nécessaire</t>
         </is>
       </c>
       <c r="M400" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4316255713</t>
+          <t>https://www.freelance-informatique.fr/mission-sap-hr-461</t>
         </is>
       </c>
       <c r="N400" s="39" t="inlineStr">
@@ -28038,7 +28038,7 @@
       </c>
       <c r="O400" s="39" t="inlineStr">
         <is>
-          <t>55 K€</t>
+          <t>700 €/j</t>
         </is>
       </c>
       <c r="P400" s="39" t="n"/>
@@ -28054,12 +28054,12 @@
       <c r="C401" s="39" t="n"/>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>HRIS Specialist SAP SuccessFactors</t>
+          <t>Consultant(e) Senior SIRH</t>
         </is>
       </c>
       <c r="E401" s="5" t="inlineStr">
         <is>
-          <t>Ingenico</t>
+          <t>ALTHEA</t>
         </is>
       </c>
       <c r="F401" s="5" t="inlineStr">
@@ -28074,28 +28074,28 @@
       </c>
       <c r="H401" s="6" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I401" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>n.p.</t>
         </is>
       </c>
       <c r="J401" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>40-50 K€</t>
         </is>
       </c>
       <c r="K401" s="6" t="n"/>
       <c r="L401" s="5" t="inlineStr">
         <is>
-          <t>4+ ans admin SF Employee Central requis — profil trop technique/admin, pas full remote. Gaëtan connait SAP HCM mais pas admin SF.</t>
+          <t>1-5 ans exp, profil junior/mid — salaire faible, Nantes loin de Biarritz</t>
         </is>
       </c>
       <c r="M401" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/hris-specialist-at-ingenico-4427731807</t>
+          <t>https://fr.linkedin.com/jobs/view/4316255713</t>
         </is>
       </c>
       <c r="N401" s="39" t="inlineStr">
@@ -28105,7 +28105,7 @@
       </c>
       <c r="O401" s="39" t="inlineStr">
         <is>
-          <t>65 K€</t>
+          <t>55 K€</t>
         </is>
       </c>
       <c r="P401" s="39" t="n"/>
@@ -28121,12 +28121,12 @@
       <c r="C402" s="39" t="n"/>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>Consultant Senior HR Transformation SAP SuccessFactors F/H</t>
+          <t>HRIS Specialist SAP SuccessFactors</t>
         </is>
       </c>
       <c r="E402" s="5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ingenico</t>
         </is>
       </c>
       <c r="F402" s="5" t="inlineStr">
@@ -28141,7 +28141,7 @@
       </c>
       <c r="H402" s="6" t="inlineStr">
         <is>
-          <t>La Défense</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="I402" s="6" t="inlineStr">
@@ -28157,12 +28157,12 @@
       <c r="K402" s="6" t="n"/>
       <c r="L402" s="5" t="inlineStr">
         <is>
-          <t>2+ ans consulting cabinet requis + expérience SF. Profil consultant Deloitte ≠ profil client-side Gaëtan. Différent du Workday Deloitte déjà en liste.</t>
+          <t>4+ ans admin SF Employee Central requis — profil trop technique/admin, pas full remote. Gaëtan connait SAP HCM mais pas admin SF.</t>
         </is>
       </c>
       <c r="M402" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-senior-hr-transformation-sap-successfactors-f-h-at-deloitte-4072908135</t>
+          <t>https://fr.linkedin.com/jobs/view/hris-specialist-at-ingenico-4427731807</t>
         </is>
       </c>
       <c r="N402" s="39" t="inlineStr">
@@ -28188,27 +28188,27 @@
       <c r="C403" s="39" t="n"/>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>Directeur de Projet SIRH (Freelance)</t>
+          <t>Consultant Senior HR Transformation SAP SuccessFactors F/H</t>
         </is>
       </c>
       <c r="E403" s="5" t="inlineStr">
         <is>
-          <t>EXteam</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="F403" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G403" s="6" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H403" s="6" t="inlineStr">
         <is>
-          <t>Île-de-France</t>
+          <t>La Défense</t>
         </is>
       </c>
       <c r="I403" s="6" t="inlineStr">
@@ -28218,22 +28218,18 @@
       </c>
       <c r="J403" s="6" t="inlineStr">
         <is>
-          <t>630-730 €/j</t>
-        </is>
-      </c>
-      <c r="K403" s="6" t="inlineStr">
-        <is>
-          <t>3 ans</t>
-        </is>
-      </c>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K403" s="6" t="n"/>
       <c r="L403" s="5" t="inlineStr">
         <is>
-          <t>Pilotage projets SIRH, ateliers, conduite du changement. Requiert expertise Pléiades 4you — pas son outil. Secteur audiovisuel public.</t>
+          <t>2+ ans consulting cabinet requis + expérience SF. Profil consultant Deloitte ≠ profil client-side Gaëtan. Différent du Workday Deloitte déjà en liste.</t>
         </is>
       </c>
       <c r="M403" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/directeur-de-projet-sirh-7</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-senior-hr-transformation-sap-successfactors-f-h-at-deloitte-4072908135</t>
         </is>
       </c>
       <c r="N403" s="39" t="inlineStr">
@@ -28243,15 +28239,11 @@
       </c>
       <c r="O403" s="39" t="inlineStr">
         <is>
-          <t>730 €/j</t>
+          <t>65 K€</t>
         </is>
       </c>
       <c r="P403" s="39" t="n"/>
-      <c r="Q403" s="41" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
+      <c r="Q403" s="41" t="n"/>
     </row>
     <row r="404" ht="32" customHeight="1">
       <c r="A404" s="90" t="inlineStr">
@@ -28263,64 +28255,68 @@
       <c r="C404" s="39" t="n"/>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>Solution Advisor Senior Manager</t>
+          <t>Directeur de Projet SIRH (Freelance)</t>
         </is>
       </c>
       <c r="E404" s="5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>EXteam</t>
         </is>
       </c>
       <c r="F404" s="5" t="inlineStr">
         <is>
-          <t>jobs.sap.com</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G404" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H404" s="6" t="inlineStr">
         <is>
-          <t>Levallois-Perret</t>
+          <t>Île-de-France</t>
         </is>
       </c>
       <c r="I404" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="J404" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K404" s="6" t="n"/>
+          <t>630-730 €/j</t>
+        </is>
+      </c>
+      <c r="K404" s="6" t="inlineStr">
+        <is>
+          <t>3 ans</t>
+        </is>
+      </c>
       <c r="L404" s="5" t="inlineStr">
         <is>
-          <t>Management équipe SAs — Supply Chain focus (pas HCM). Requiert expérience leadership SA/CS teams. Mauvais domaine pour Gaëtan.</t>
+          <t>Pilotage projets SIRH, ateliers, conduite du changement. Requiert expertise Pléiades 4you — pas son outil. Secteur audiovisuel public.</t>
         </is>
       </c>
       <c r="M404" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.sap.com/job/Levallois-Perret-Solution-Advisor-Senior-Manager-92300/1385712733/</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/directeur-de-projet-sirh-7</t>
         </is>
       </c>
       <c r="N404" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O404" s="39" t="inlineStr">
         <is>
-          <t>100 K€</t>
+          <t>730 €/j</t>
         </is>
       </c>
       <c r="P404" s="39" t="n"/>
       <c r="Q404" s="41" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
     </row>
@@ -28334,7 +28330,7 @@
       <c r="C405" s="39" t="n"/>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>Client Delivery Manager F/M</t>
+          <t>Solution Advisor Senior Manager</t>
         </is>
       </c>
       <c r="E405" s="5" t="inlineStr">
@@ -28370,12 +28366,12 @@
       <c r="K405" s="6" t="n"/>
       <c r="L405" s="5" t="inlineStr">
         <is>
-          <t>SAP Enterprise Cloud Services — gestion lifecycle client, escalades, renouvellements. Requiert SAP Basis/infra technique. Pas le profil fonctionnel RH de Gaëtan.</t>
+          <t>Management équipe SAs — Supply Chain focus (pas HCM). Requiert expérience leadership SA/CS teams. Mauvais domaine pour Gaëtan.</t>
         </is>
       </c>
       <c r="M405" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.sap.com/job/Levallois-Perret-Client-Delivery-Manager-FM-92300/1379856933/</t>
+          <t>https://jobs.sap.com/job/Levallois-Perret-Solution-Advisor-Senior-Manager-92300/1385712733/</t>
         </is>
       </c>
       <c r="N405" s="39" t="inlineStr">
@@ -28385,11 +28381,15 @@
       </c>
       <c r="O405" s="39" t="inlineStr">
         <is>
-          <t>90 K€</t>
+          <t>100 K€</t>
         </is>
       </c>
       <c r="P405" s="39" t="n"/>
-      <c r="Q405" s="41" t="n"/>
+      <c r="Q405" s="41" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="406" ht="16" customHeight="1">
       <c r="A406" s="90" t="inlineStr">
@@ -28401,7 +28401,7 @@
       <c r="C406" s="39" t="n"/>
       <c r="D406" s="5" t="inlineStr">
         <is>
-          <t>Services Sr. Account Executive F/M</t>
+          <t>Client Delivery Manager F/M</t>
         </is>
       </c>
       <c r="E406" s="5" t="inlineStr">
@@ -28437,12 +28437,12 @@
       <c r="K406" s="6" t="n"/>
       <c r="L406" s="5" t="inlineStr">
         <is>
-          <t>Vente complexe 10+ ans requise, contrats implémentation SAP. Profil hunter/sales pur. Gaëtan est CSM/account management, pas business development.</t>
+          <t>SAP Enterprise Cloud Services — gestion lifecycle client, escalades, renouvellements. Requiert SAP Basis/infra technique. Pas le profil fonctionnel RH de Gaëtan.</t>
         </is>
       </c>
       <c r="M406" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.sap.com/job/Levallois-Perret-Services-Sr_-Account-Executive-FM-92300/1382751433/</t>
+          <t>https://jobs.sap.com/job/Levallois-Perret-Client-Delivery-Manager-FM-92300/1379856933/</t>
         </is>
       </c>
       <c r="N406" s="39" t="inlineStr">
@@ -28452,15 +28452,11 @@
       </c>
       <c r="O406" s="39" t="inlineStr">
         <is>
-          <t>95 K€</t>
+          <t>90 K€</t>
         </is>
       </c>
       <c r="P406" s="39" t="n"/>
-      <c r="Q406" s="41" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q406" s="41" t="n"/>
     </row>
     <row r="407" ht="16" customHeight="1">
       <c r="A407" s="90" t="inlineStr">
@@ -28472,17 +28468,17 @@
       <c r="C407" s="39" t="n"/>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>Managing Consultant - HR Transformation (SuccessFactors)</t>
+          <t>Services Sr. Account Executive F/M</t>
         </is>
       </c>
       <c r="E407" s="5" t="inlineStr">
         <is>
-          <t>Capgemini Invent</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="F407" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>jobs.sap.com</t>
         </is>
       </c>
       <c r="G407" s="6" t="inlineStr">
@@ -28492,7 +28488,7 @@
       </c>
       <c r="H407" s="6" t="inlineStr">
         <is>
-          <t>London (UK)</t>
+          <t>Levallois-Perret</t>
         </is>
       </c>
       <c r="I407" s="6" t="inlineStr">
@@ -28508,12 +28504,12 @@
       <c r="K407" s="6" t="n"/>
       <c r="L407" s="5" t="inlineStr">
         <is>
-          <t>Postée il y a 5 mois — peut être pourvue. 8+ ans HR tech consulting + 4+ ans SF requis. Profil consultant cabinet. London hybride.</t>
+          <t>Vente complexe 10+ ans requise, contrats implémentation SAP. Profil hunter/sales pur. Gaëtan est CSM/account management, pas business development.</t>
         </is>
       </c>
       <c r="M407" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4343035769</t>
+          <t>https://jobs.sap.com/job/Levallois-Perret-Services-Sr_-Account-Executive-FM-92300/1382751433/</t>
         </is>
       </c>
       <c r="N407" s="39" t="inlineStr">
@@ -28523,11 +28519,15 @@
       </c>
       <c r="O407" s="39" t="inlineStr">
         <is>
-          <t>100 K€</t>
+          <t>95 K€</t>
         </is>
       </c>
       <c r="P407" s="39" t="n"/>
-      <c r="Q407" s="41" t="n"/>
+      <c r="Q407" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="408" ht="16" customHeight="1">
       <c r="A408" s="90" t="inlineStr">
@@ -28539,12 +28539,12 @@
       <c r="C408" s="39" t="n"/>
       <c r="D408" s="5" t="inlineStr">
         <is>
-          <t>SAP SuccessFactors Talent Acquisition Consultant</t>
+          <t>Managing Consultant - HR Transformation (SuccessFactors)</t>
         </is>
       </c>
       <c r="E408" s="5" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Capgemini Invent</t>
         </is>
       </c>
       <c r="F408" s="5" t="inlineStr">
@@ -28559,7 +28559,7 @@
       </c>
       <c r="H408" s="6" t="inlineStr">
         <is>
-          <t>London / Birmingham / Manchester (UK)</t>
+          <t>London (UK)</t>
         </is>
       </c>
       <c r="I408" s="6" t="inlineStr">
@@ -28575,12 +28575,12 @@
       <c r="K408" s="6" t="n"/>
       <c r="L408" s="5" t="inlineStr">
         <is>
-          <t>Deadline 31/05/2026 dépassée — vérifier si toujours ouverte. SF Recruiting &amp; Onboarding, 2-3 implémentations full cycle requis. UK offices.</t>
+          <t>Postée il y a 5 mois — peut être pourvue. 8+ ans HR tech consulting + 4+ ans SF requis. Profil consultant cabinet. London hybride.</t>
         </is>
       </c>
       <c r="M408" s="5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4369181135</t>
+          <t>https://www.linkedin.com/jobs/view/4343035769</t>
         </is>
       </c>
       <c r="N408" s="39" t="inlineStr">
@@ -28590,7 +28590,7 @@
       </c>
       <c r="O408" s="39" t="inlineStr">
         <is>
-          <t>90 K€</t>
+          <t>100 K€</t>
         </is>
       </c>
       <c r="P408" s="39" t="n"/>
@@ -28606,12 +28606,12 @@
       <c r="C409" s="39" t="n"/>
       <c r="D409" s="5" t="inlineStr">
         <is>
-          <t>SAP SuccessFactors Consultant</t>
+          <t>SAP SuccessFactors Talent Acquisition Consultant</t>
         </is>
       </c>
       <c r="E409" s="5" t="inlineStr">
         <is>
-          <t>RED Global</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="F409" s="5" t="inlineStr">
@@ -28621,12 +28621,12 @@
       </c>
       <c r="G409" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H409" s="6" t="inlineStr">
         <is>
-          <t>Vitry-le-François</t>
+          <t>London / Birmingham / Manchester (UK)</t>
         </is>
       </c>
       <c r="I409" s="6" t="inlineStr">
@@ -28642,12 +28642,12 @@
       <c r="K409" s="6" t="n"/>
       <c r="L409" s="5" t="inlineStr">
         <is>
-          <t>RED Global (ex-RED Commerce) = réseau SAP utile à activer. Mission Vitry-le-François peu pratique depuis Biarritz, mais RED Global est un contact pertinent pour missions SAP SF.</t>
+          <t>Deadline 31/05/2026 dépassée — vérifier si toujours ouverte. SF Recruiting &amp; Onboarding, 2-3 implémentations full cycle requis. UK offices.</t>
         </is>
       </c>
       <c r="M409" s="5" t="inlineStr">
         <is>
-          <t>https://www.redglobal.com/jobs/</t>
+          <t>https://www.linkedin.com/jobs/view/4369181135</t>
         </is>
       </c>
       <c r="N409" s="39" t="inlineStr">
@@ -28655,7 +28655,11 @@
           <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
-      <c r="O409" s="39" t="n"/>
+      <c r="O409" s="39" t="inlineStr">
+        <is>
+          <t>90 K€</t>
+        </is>
+      </c>
       <c r="P409" s="39" t="n"/>
       <c r="Q409" s="41" t="n"/>
     </row>
@@ -28669,12 +28673,12 @@
       <c r="C410" s="39" t="n"/>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>AMOA SIRH</t>
+          <t>SAP SuccessFactors Consultant</t>
         </is>
       </c>
       <c r="E410" s="5" t="inlineStr">
         <is>
-          <t>Qim info</t>
+          <t>RED Global</t>
         </is>
       </c>
       <c r="F410" s="5" t="inlineStr">
@@ -28684,17 +28688,17 @@
       </c>
       <c r="G410" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H410" s="6" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Vitry-le-François</t>
         </is>
       </c>
       <c r="I410" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J410" s="6" t="inlineStr">
@@ -28705,17 +28709,17 @@
       <c r="K410" s="6" t="n"/>
       <c r="L410" s="5" t="inlineStr">
         <is>
-          <t>Qim info = ESN régionale France. AMOA SIRH Annecy, postée il y a 2 jours. Localisation contraignante depuis Biarritz. Fit fonctionnel correct.</t>
+          <t>RED Global (ex-RED Commerce) = réseau SAP utile à activer. Mission Vitry-le-François peu pratique depuis Biarritz, mais RED Global est un contact pertinent pour missions SAP SF.</t>
         </is>
       </c>
       <c r="M410" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/hris-emplois</t>
+          <t>https://www.redglobal.com/jobs/</t>
         </is>
       </c>
       <c r="N410" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
         </is>
       </c>
       <c r="O410" s="39" t="n"/>
@@ -28732,12 +28736,12 @@
       <c r="C411" s="39" t="n"/>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>Responsable SIRH &amp; Data F/H</t>
+          <t>AMOA SIRH</t>
         </is>
       </c>
       <c r="E411" s="5" t="inlineStr">
         <is>
-          <t>GLS France</t>
+          <t>Qim info</t>
         </is>
       </c>
       <c r="F411" s="5" t="inlineStr">
@@ -28747,12 +28751,12 @@
       </c>
       <c r="G411" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="H411" s="6" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="I411" s="6" t="inlineStr">
@@ -28768,7 +28772,7 @@
       <c r="K411" s="6" t="n"/>
       <c r="L411" s="5" t="inlineStr">
         <is>
-          <t>GLS France = logistique/colis. Toulouse = géographiquement plus proche de Biarritz. Poste Responsable SIRH opérationnel (pas pure consulting). Fit partiel.</t>
+          <t>Qim info = ESN régionale France. AMOA SIRH Annecy, postée il y a 2 jours. Localisation contraignante depuis Biarritz. Fit fonctionnel correct.</t>
         </is>
       </c>
       <c r="M411" s="5" t="inlineStr">
@@ -28781,11 +28785,7 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O411" s="39" t="inlineStr">
-        <is>
-          <t>75 K€</t>
-        </is>
-      </c>
+      <c r="O411" s="39" t="n"/>
       <c r="P411" s="39" t="n"/>
       <c r="Q411" s="41" t="n"/>
     </row>
@@ -28799,12 +28799,12 @@
       <c r="C412" s="39" t="n"/>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>Chef de Projet SIRH H/F</t>
+          <t>Responsable SIRH &amp; Data F/H</t>
         </is>
       </c>
       <c r="E412" s="5" t="inlineStr">
         <is>
-          <t>Groupe Blachère</t>
+          <t>GLS France</t>
         </is>
       </c>
       <c r="F412" s="5" t="inlineStr">
@@ -28819,12 +28819,12 @@
       </c>
       <c r="H412" s="6" t="inlineStr">
         <is>
-          <t>Châteaurenard (13)</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="I412" s="6" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="J412" s="6" t="inlineStr">
@@ -28835,12 +28835,12 @@
       <c r="K412" s="6" t="n"/>
       <c r="L412" s="5" t="inlineStr">
         <is>
-          <t>Groupe Blachère (Marie Blachère). Chef de projet SIRH réseau franchises. Provence, géographiquement accessible depuis Biarritz. Secteur restauration, pas HR Tech. Postée il y a 1 semaine.</t>
+          <t>GLS France = logistique/colis. Toulouse = géographiquement plus proche de Biarritz. Poste Responsable SIRH opérationnel (pas pure consulting). Fit partiel.</t>
         </is>
       </c>
       <c r="M412" s="5" t="inlineStr">
         <is>
-          <t>https://www.groupe-blachere.com/recrutement/</t>
+          <t>https://fr.linkedin.com/jobs/hris-emplois</t>
         </is>
       </c>
       <c r="N412" s="39" t="inlineStr">
@@ -28850,7 +28850,7 @@
       </c>
       <c r="O412" s="39" t="inlineStr">
         <is>
-          <t>70 K€</t>
+          <t>75 K€</t>
         </is>
       </c>
       <c r="P412" s="39" t="n"/>
@@ -28871,7 +28871,7 @@
       </c>
       <c r="E413" s="5" t="inlineStr">
         <is>
-          <t>Paragon France</t>
+          <t>Groupe Blachère</t>
         </is>
       </c>
       <c r="F413" s="5" t="inlineStr">
@@ -28886,7 +28886,7 @@
       </c>
       <c r="H413" s="6" t="inlineStr">
         <is>
-          <t>Nanterre (92)</t>
+          <t>Châteaurenard (13)</t>
         </is>
       </c>
       <c r="I413" s="6" t="inlineStr">
@@ -28902,12 +28902,12 @@
       <c r="K413" s="6" t="n"/>
       <c r="L413" s="5" t="inlineStr">
         <is>
-          <t>Paragon = groupe international services RH et gestion documentaire. Chef de projet SIRH Nanterre. Postée il y a 2 semaines. Présentiel probable = frein.</t>
+          <t>Groupe Blachère (Marie Blachère). Chef de projet SIRH réseau franchises. Provence, géographiquement accessible depuis Biarritz. Secteur restauration, pas HR Tech. Postée il y a 1 semaine.</t>
         </is>
       </c>
       <c r="M413" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/chef-de-projet-sirh-emplois-france</t>
+          <t>https://www.groupe-blachere.com/recrutement/</t>
         </is>
       </c>
       <c r="N413" s="39" t="inlineStr">
@@ -28917,11 +28917,11 @@
       </c>
       <c r="O413" s="39" t="inlineStr">
         <is>
-          <t>72 K€</t>
+          <t>70 K€</t>
         </is>
       </c>
       <c r="P413" s="39" t="n"/>
-      <c r="Q413" s="39" t="n"/>
+      <c r="Q413" s="41" t="n"/>
     </row>
     <row r="414" ht="16" customHeight="1">
       <c r="A414" s="90" t="inlineStr">
@@ -28933,27 +28933,27 @@
       <c r="C414" s="39" t="n"/>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>Directeur de Projet Senior Data &amp; BI RH</t>
+          <t>Chef de Projet SIRH H/F</t>
         </is>
       </c>
       <c r="E414" s="5" t="inlineStr">
         <is>
-          <t>Freelance.com</t>
+          <t>Paragon France</t>
         </is>
       </c>
       <c r="F414" s="5" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G414" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H414" s="6" t="inlineStr">
         <is>
-          <t>Orly (94)</t>
+          <t>Nanterre (92)</t>
         </is>
       </c>
       <c r="I414" s="6" t="inlineStr">
@@ -28963,18 +28963,18 @@
       </c>
       <c r="J414" s="6" t="inlineStr">
         <is>
-          <t>400 - 650 €/jour</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K414" s="6" t="n"/>
       <c r="L414" s="5" t="inlineStr">
         <is>
-          <t>Mission Data/BI RH, adjacente SIRH. TJM en dessous de la cible (400-650€ vs 650-750€). Localisation Orly contraignante. Freelance.com = plateforme recrutement IT.</t>
+          <t>Paragon = groupe international services RH et gestion documentaire. Chef de projet SIRH Nanterre. Postée il y a 2 semaines. Présentiel probable = frein.</t>
         </is>
       </c>
       <c r="M414" s="5" t="inlineStr">
         <is>
-          <t>https://www.freelance.com/missions/sirh</t>
+          <t>https://fr.linkedin.com/jobs/chef-de-projet-sirh-emplois-france</t>
         </is>
       </c>
       <c r="N414" s="39" t="inlineStr">
@@ -28982,7 +28982,11 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O414" s="39" t="n"/>
+      <c r="O414" s="39" t="inlineStr">
+        <is>
+          <t>72 K€</t>
+        </is>
+      </c>
       <c r="P414" s="39" t="n"/>
       <c r="Q414" s="39" t="n"/>
     </row>
@@ -28996,27 +29000,27 @@
       <c r="C415" s="39" t="n"/>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>Chef de Projet SIRH</t>
+          <t>Directeur de Projet Senior Data &amp; BI RH</t>
         </is>
       </c>
       <c r="E415" s="5" t="inlineStr">
         <is>
-          <t>Silae</t>
+          <t>Freelance.com</t>
         </is>
       </c>
       <c r="F415" s="5" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G415" s="6" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H415" s="6" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Orly (94)</t>
         </is>
       </c>
       <c r="I415" s="6" t="inlineStr">
@@ -29026,18 +29030,18 @@
       </c>
       <c r="J415" s="6" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>400 - 650 €/jour</t>
         </is>
       </c>
       <c r="K415" s="6" t="n"/>
       <c r="L415" s="5" t="inlineStr">
         <is>
-          <t>Silae = leader logiciels paie France (éditeur). Rôle Partner Success, onboarding partenaires déployant Silae. Pas full remote, Nantes. Silae adjacent au profil SAP HR (paie).</t>
+          <t>Mission Data/BI RH, adjacente SIRH. TJM en dessous de la cible (400-650€ vs 650-750€). Localisation Orly contraignante. Freelance.com = plateforme recrutement IT.</t>
         </is>
       </c>
       <c r="M415" s="5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/silae/jobs/chef-de-projet-sirh_nantes</t>
+          <t>https://www.freelance.com/missions/sirh</t>
         </is>
       </c>
       <c r="N415" s="39" t="inlineStr">
@@ -29045,11 +29049,7 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O415" s="39" t="inlineStr">
-        <is>
-          <t>70 K€</t>
-        </is>
-      </c>
+      <c r="O415" s="39" t="n"/>
       <c r="P415" s="39" t="n"/>
       <c r="Q415" s="39" t="n"/>
     </row>
@@ -29063,17 +29063,17 @@
       <c r="C416" s="39" t="n"/>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>SAP S/4HANA Project Manager PMO</t>
+          <t>Chef de Projet SIRH</t>
         </is>
       </c>
       <c r="E416" s="5" t="inlineStr">
         <is>
-          <t>Client fabricant industriel (via Eursap)</t>
+          <t>Silae</t>
         </is>
       </c>
       <c r="F416" s="5" t="inlineStr">
         <is>
-          <t>Eursap.eu</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G416" s="6" t="inlineStr">
@@ -29083,38 +29083,38 @@
       </c>
       <c r="H416" s="6" t="inlineStr">
         <is>
-          <t>Paris 8e</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I416" s="6" t="inlineStr">
         <is>
-          <t>Hybride (50%)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J416" s="6" t="inlineStr">
         <is>
-          <t>Jusqu'à 115 000 € + 14% bonus + 11K€ participation</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K416" s="6" t="n"/>
       <c r="L416" s="5" t="inlineStr">
         <is>
-          <t>PMO chef de projet SAP S/4HANA pour fabricant industriel en transformation globale. 10 ans IT requis. Gaëtan a 15 ans SAP mais orienté RH/HCM. Gap S/4HANA non-HR. Salaire excellent. Démarrage sept 2026.</t>
+          <t>Silae = leader logiciels paie France (éditeur). Rôle Partner Success, onboarding partenaires déployant Silae. Pas full remote, Nantes. Silae adjacent au profil SAP HR (paie).</t>
         </is>
       </c>
       <c r="M416" s="5" t="inlineStr">
         <is>
-          <t>https://eursap.eu/jobs/sap-s-4hana-project-manager-pmo-FR-34951</t>
+          <t>https://www.welcometothejungle.com/fr/companies/silae/jobs/chef-de-projet-sirh_nantes</t>
         </is>
       </c>
       <c r="N416" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O416" s="39" t="inlineStr">
         <is>
-          <t>100 K€</t>
+          <t>70 K€</t>
         </is>
       </c>
       <c r="P416" s="39" t="n"/>
@@ -29130,62 +29130,62 @@
       <c r="C417" s="39" t="n"/>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>AMOA RH</t>
+          <t>SAP S/4HANA Project Manager PMO</t>
         </is>
       </c>
       <c r="E417" s="5" t="inlineStr">
         <is>
-          <t>CAT-AMANIA (client assurance)</t>
+          <t>Client fabricant industriel (via Eursap)</t>
         </is>
       </c>
       <c r="F417" s="5" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>Eursap.eu</t>
         </is>
       </c>
       <c r="G417" s="6" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H417" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris 8e</t>
         </is>
       </c>
       <c r="I417" s="6" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride (50%)</t>
         </is>
       </c>
       <c r="J417" s="6" t="inlineStr">
         <is>
-          <t>440-490 €/j</t>
-        </is>
-      </c>
-      <c r="K417" s="6" t="inlineStr">
-        <is>
-          <t>1 an renouvelable</t>
-        </is>
-      </c>
+          <t>Jusqu'à 115 000 € + 14% bonus + 11K€ participation</t>
+        </is>
+      </c>
+      <c r="K417" s="6" t="n"/>
       <c r="L417" s="5" t="inlineStr">
         <is>
-          <t>Grand compte assurance, transformation RH, recette, conduite du changement. Bon fit MOA mais TJM sous cible (440-490€/j).</t>
+          <t>PMO chef de projet SAP S/4HANA pour fabricant industriel en transformation globale. 10 ans IT requis. Gaëtan a 15 ans SAP mais orienté RH/HCM. Gap S/4HANA non-HR. Salaire excellent. Démarrage sept 2026.</t>
         </is>
       </c>
       <c r="M417" s="5" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/amoa-rh-2</t>
-        </is>
-      </c>
-      <c r="N417" s="39" t="n"/>
-      <c r="O417" s="39" t="n"/>
+          <t>https://eursap.eu/jobs/sap-s-4hana-project-manager-pmo-FR-34951</t>
+        </is>
+      </c>
+      <c r="N417" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O417" s="39" t="inlineStr">
+        <is>
+          <t>100 K€</t>
+        </is>
+      </c>
       <c r="P417" s="39" t="n"/>
-      <c r="Q417" s="41" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
+      <c r="Q417" s="39" t="n"/>
     </row>
     <row r="418" ht="16" customHeight="1">
       <c r="A418" s="90" t="inlineStr">
@@ -29195,52 +29195,52 @@
       </c>
       <c r="B418" s="39" t="n"/>
       <c r="C418" s="39" t="n"/>
-      <c r="D418" s="39" t="inlineStr">
+      <c r="D418" s="5" t="inlineStr">
         <is>
           <t>AMOA RH</t>
         </is>
       </c>
-      <c r="E418" s="39" t="inlineStr">
+      <c r="E418" s="5" t="inlineStr">
         <is>
           <t>CAT-AMANIA (client assurance)</t>
         </is>
       </c>
-      <c r="F418" s="39" t="inlineStr">
+      <c r="F418" s="5" t="inlineStr">
         <is>
           <t>free-work.com</t>
         </is>
       </c>
-      <c r="G418" s="39" t="inlineStr">
+      <c r="G418" s="6" t="inlineStr">
         <is>
           <t>Freelance</t>
         </is>
       </c>
-      <c r="H418" s="39" t="inlineStr">
+      <c r="H418" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I418" s="39" t="inlineStr">
+      <c r="I418" s="6" t="inlineStr">
         <is>
           <t>Partiel</t>
         </is>
       </c>
-      <c r="J418" s="39" t="inlineStr">
+      <c r="J418" s="6" t="inlineStr">
         <is>
           <t>440-490 €/j</t>
         </is>
       </c>
-      <c r="K418" s="39" t="inlineStr">
+      <c r="K418" s="6" t="inlineStr">
         <is>
           <t>1 an renouvelable</t>
         </is>
       </c>
-      <c r="L418" s="39" t="inlineStr">
-        <is>
-          <t>Grand compte assurance, transformation RH, recette, conduite du changement. Bon fit MOA mais TJM sous cible.</t>
-        </is>
-      </c>
-      <c r="M418" s="39" t="inlineStr">
+      <c r="L418" s="5" t="inlineStr">
+        <is>
+          <t>Grand compte assurance, transformation RH, recette, conduite du changement. Bon fit MOA mais TJM sous cible (440-490€/j).</t>
+        </is>
+      </c>
+      <c r="M418" s="5" t="inlineStr">
         <is>
           <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/amoa-rh-2</t>
         </is>
@@ -29264,64 +29264,60 @@
       <c r="C419" s="39" t="n"/>
       <c r="D419" s="39" t="inlineStr">
         <is>
-          <t>Consultant Senior SIRH Paie</t>
+          <t>AMOA RH</t>
         </is>
       </c>
       <c r="E419" s="39" t="inlineStr">
         <is>
-          <t>n.c. (Washington Frank)</t>
+          <t>CAT-AMANIA (client assurance)</t>
         </is>
       </c>
       <c r="F419" s="39" t="inlineStr">
         <is>
-          <t>Washington Frank</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G419" s="39" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H419" s="39" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I419" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J419" s="39" t="inlineStr">
         <is>
-          <t>50-60K€/an</t>
-        </is>
-      </c>
-      <c r="K419" s="39" t="n"/>
+          <t>440-490 €/j</t>
+        </is>
+      </c>
+      <c r="K419" s="39" t="inlineStr">
+        <is>
+          <t>1 an renouvelable</t>
+        </is>
+      </c>
       <c r="L419" s="39" t="inlineStr">
         <is>
-          <t>Senior SIRH Paie Lyon CDI. Salaire et localisation sous les critères cibles. Spécialisation paie et compliance.</t>
+          <t>Grand compte assurance, transformation RH, recette, conduite du changement. Bon fit MOA mais TJM sous cible.</t>
         </is>
       </c>
       <c r="M419" s="39" t="inlineStr">
         <is>
-          <t>https://washingtonfrank.com/job/a0M1i00000JW62x.1/consultant-senior-sirh-paie</t>
-        </is>
-      </c>
-      <c r="N419" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_SIRH</t>
-        </is>
-      </c>
-      <c r="O419" s="39" t="inlineStr">
-        <is>
-          <t>70-80K€</t>
-        </is>
-      </c>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-moa-amoa/amoa-rh-2</t>
+        </is>
+      </c>
+      <c r="N419" s="39" t="n"/>
+      <c r="O419" s="39" t="n"/>
       <c r="P419" s="39" t="n"/>
       <c r="Q419" s="41" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
     </row>
@@ -29335,27 +29331,27 @@
       <c r="C420" s="39" t="n"/>
       <c r="D420" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet SIRH confirmé (longue durée)</t>
+          <t>Consultant Senior SIRH Paie</t>
         </is>
       </c>
       <c r="E420" s="39" t="inlineStr">
         <is>
-          <t>n.c. (via Freelance-Informatique)</t>
+          <t>n.c. (Washington Frank)</t>
         </is>
       </c>
       <c r="F420" s="39" t="inlineStr">
         <is>
-          <t>Freelance-Informatique</t>
+          <t>Washington Frank</t>
         </is>
       </c>
       <c r="G420" s="39" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H420" s="39" t="inlineStr">
         <is>
-          <t>Gonesse (95)</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I420" s="39" t="inlineStr">
@@ -29365,18 +29361,18 @@
       </c>
       <c r="J420" s="39" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>50-60K€/an</t>
         </is>
       </c>
       <c r="K420" s="39" t="n"/>
       <c r="L420" s="39" t="inlineStr">
         <is>
-          <t>Mission très longue durée, profil senior chef de projet SIRH. Peu de détails disponibles. Gonesse = déplacements réguliers.</t>
+          <t>Senior SIRH Paie Lyon CDI. Salaire et localisation sous les critères cibles. Spécialisation paie et compliance.</t>
         </is>
       </c>
       <c r="M420" s="39" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/mission-sirh-2293</t>
+          <t>https://washingtonfrank.com/job/a0M1i00000JW62x.1/consultant-senior-sirh-paie</t>
         </is>
       </c>
       <c r="N420" s="39" t="inlineStr">
@@ -29386,13 +29382,13 @@
       </c>
       <c r="O420" s="39" t="inlineStr">
         <is>
-          <t>650-750€/j</t>
+          <t>70-80K€</t>
         </is>
       </c>
       <c r="P420" s="39" t="n"/>
       <c r="Q420" s="41" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
     </row>
@@ -29406,7 +29402,7 @@
       <c r="C421" s="39" t="n"/>
       <c r="D421" s="39" t="inlineStr">
         <is>
-          <t>Consultant SIRH (4 mois)</t>
+          <t>Chef de projet SIRH confirmé (longue durée)</t>
         </is>
       </c>
       <c r="E421" s="39" t="inlineStr">
@@ -29426,7 +29422,7 @@
       </c>
       <c r="H421" s="39" t="inlineStr">
         <is>
-          <t>Archamps (74, frontière Genève)</t>
+          <t>Gonesse (95)</t>
         </is>
       </c>
       <c r="I421" s="39" t="inlineStr">
@@ -29439,14 +29435,10 @@
           <t>N/C</t>
         </is>
       </c>
-      <c r="K421" s="39" t="inlineStr">
-        <is>
-          <t>4 mois (démarrage 01/09/2026)</t>
-        </is>
-      </c>
+      <c r="K421" s="39" t="n"/>
       <c r="L421" s="39" t="inlineStr">
         <is>
-          <t>Démarrage 01/09/2026, Archamps (Haute-Savoie, frontière suisse). Possible si ouvert aux déplacements.</t>
+          <t>Mission très longue durée, profil senior chef de projet SIRH. Peu de détails disponibles. Gonesse = déplacements réguliers.</t>
         </is>
       </c>
       <c r="M421" s="39" t="inlineStr">
@@ -29481,48 +29473,52 @@
       <c r="C422" s="39" t="n"/>
       <c r="D422" s="39" t="inlineStr">
         <is>
-          <t>Manager Technique SIRH H/F</t>
+          <t>Consultant SIRH (4 mois)</t>
         </is>
       </c>
       <c r="E422" s="39" t="inlineStr">
         <is>
-          <t>LCL (Crédit Agricole)</t>
+          <t>n.c. (via Freelance-Informatique)</t>
         </is>
       </c>
       <c r="F422" s="39" t="inlineStr">
         <is>
-          <t>LCL Emploi</t>
+          <t>Freelance-Informatique</t>
         </is>
       </c>
       <c r="G422" s="39" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="H422" s="39" t="inlineStr">
         <is>
-          <t>Villejuif (94)</t>
+          <t>Archamps (74, frontière Genève)</t>
         </is>
       </c>
       <c r="I422" s="39" t="inlineStr">
         <is>
-          <t>Présentiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J422" s="39" t="inlineStr">
         <is>
-          <t>+70K€ estimé</t>
-        </is>
-      </c>
-      <c r="K422" s="39" t="n"/>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K422" s="39" t="inlineStr">
+        <is>
+          <t>4 mois (démarrage 01/09/2026)</t>
+        </is>
+      </c>
       <c r="L422" s="39" t="inlineStr">
         <is>
-          <t>Profil très technique (architecture SIRH, PHP/Symfony, CI/CD, API/ETL). 10-15 ans exp. Secteur bancaire requis. Poste DSI/tech plutôt que consultant fonctionnel — frein pour Gaëtan.</t>
+          <t>Démarrage 01/09/2026, Archamps (Haute-Savoie, frontière suisse). Possible si ouvert aux déplacements.</t>
         </is>
       </c>
       <c r="M422" s="39" t="inlineStr">
         <is>
-          <t>https://offres-emploi.lcl.com/offre-de-emploi/emploi-manager-technique-sirh-h-f_112081.aspx</t>
+          <t>https://www.freelance-informatique.fr/mission-sirh-2293</t>
         </is>
       </c>
       <c r="N422" s="39" t="inlineStr">
@@ -29532,13 +29528,13 @@
       </c>
       <c r="O422" s="39" t="inlineStr">
         <is>
-          <t>80-90K€</t>
+          <t>650-750€/j</t>
         </is>
       </c>
       <c r="P422" s="39" t="n"/>
       <c r="Q422" s="41" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
     </row>
@@ -29552,17 +29548,17 @@
       <c r="C423" s="39" t="n"/>
       <c r="D423" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet / Consultant SIRH H/F</t>
+          <t>Manager Technique SIRH H/F</t>
         </is>
       </c>
       <c r="E423" s="39" t="inlineStr">
         <is>
-          <t>Septeo (Septeo HR Solutions)</t>
+          <t>LCL (Crédit Agricole)</t>
         </is>
       </c>
       <c r="F423" s="39" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LCL Emploi</t>
         </is>
       </c>
       <c r="G423" s="39" t="inlineStr">
@@ -29572,7 +29568,7 @@
       </c>
       <c r="H423" s="39" t="inlineStr">
         <is>
-          <t>Dardilly (69)</t>
+          <t>Villejuif (94)</t>
         </is>
       </c>
       <c r="I423" s="39" t="inlineStr">
@@ -29582,18 +29578,18 @@
       </c>
       <c r="J423" s="39" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>+70K€ estimé</t>
         </is>
       </c>
       <c r="K423" s="39" t="n"/>
       <c r="L423" s="39" t="inlineStr">
         <is>
-          <t>Éditeur SIRH (10e éditeur logiciel FR), accompagnement clients end-to-end. 5 ans exp. min. Localisation Lyon uniquement, pas de remote mentionné. Intéressant si déplacement envisagé.</t>
+          <t>Profil très technique (architecture SIRH, PHP/Symfony, CI/CD, API/ETL). 10-15 ans exp. Secteur bancaire requis. Poste DSI/tech plutôt que consultant fonctionnel — frein pour Gaëtan.</t>
         </is>
       </c>
       <c r="M423" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/septeo/jobs/chef-de-projet-consultant-sirh-h-f_lyon_SEPTE_XKL6GRl</t>
+          <t>https://offres-emploi.lcl.com/offre-de-emploi/emploi-manager-technique-sirh-h-f_112081.aspx</t>
         </is>
       </c>
       <c r="N423" s="39" t="inlineStr">
@@ -29603,11 +29599,15 @@
       </c>
       <c r="O423" s="39" t="inlineStr">
         <is>
-          <t>65-75K€</t>
+          <t>80-90K€</t>
         </is>
       </c>
       <c r="P423" s="39" t="n"/>
-      <c r="Q423" s="39" t="n"/>
+      <c r="Q423" s="41" t="inlineStr">
+        <is>
+          <t>04/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="424" ht="32" customHeight="1">
       <c r="A424" s="90" t="inlineStr">
@@ -29619,7 +29619,7 @@
       <c r="C424" s="39" t="n"/>
       <c r="D424" s="39" t="inlineStr">
         <is>
-          <t>Consultant SIRH Technico-Fonctionnel H/F</t>
+          <t>Chef de projet / Consultant SIRH H/F</t>
         </is>
       </c>
       <c r="E424" s="39" t="inlineStr">
@@ -29655,12 +29655,12 @@
       <c r="K424" s="39" t="n"/>
       <c r="L424" s="39" t="inlineStr">
         <is>
-          <t>Profil technico-fonctionnel, distinct du poste Chef de projet Septeo. Lyon uniquement, pas de remote.</t>
+          <t>Éditeur SIRH (10e éditeur logiciel FR), accompagnement clients end-to-end. 5 ans exp. min. Localisation Lyon uniquement, pas de remote mentionné. Intéressant si déplacement envisagé.</t>
         </is>
       </c>
       <c r="M424" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/septeo/jobs/consultant-technico-fonctionnel-sirh-h-f_lyon</t>
+          <t>https://www.welcometothejungle.com/fr/companies/septeo/jobs/chef-de-projet-consultant-sirh-h-f_lyon_SEPTE_XKL6GRl</t>
         </is>
       </c>
       <c r="N424" s="39" t="inlineStr">
@@ -29670,7 +29670,7 @@
       </c>
       <c r="O424" s="39" t="inlineStr">
         <is>
-          <t>60-70K€</t>
+          <t>65-75K€</t>
         </is>
       </c>
       <c r="P424" s="39" t="n"/>
@@ -29686,12 +29686,12 @@
       <c r="C425" s="39" t="n"/>
       <c r="D425" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet SIRH F/H Workday</t>
+          <t>Consultant SIRH Technico-Fonctionnel H/F</t>
         </is>
       </c>
       <c r="E425" s="39" t="inlineStr">
         <is>
-          <t>IDEX</t>
+          <t>Septeo (Septeo HR Solutions)</t>
         </is>
       </c>
       <c r="F425" s="39" t="inlineStr">
@@ -29706,28 +29706,28 @@
       </c>
       <c r="H425" s="39" t="inlineStr">
         <is>
-          <t>Boulogne-Billancourt (92)</t>
+          <t>Dardilly (69)</t>
         </is>
       </c>
       <c r="I425" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Présentiel</t>
         </is>
       </c>
       <c r="J425" s="39" t="inlineStr">
         <is>
-          <t>43 800 – 56 200 €/an</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K425" s="39" t="n"/>
       <c r="L425" s="39" t="inlineStr">
         <is>
-          <t>Programme Workday Core HR + MDM. 4 ans exp. min. Fourchette salariale modeste (43-56K) pour le profil senior de Gaëtan. Option de repli.</t>
+          <t>Profil technico-fonctionnel, distinct du poste Chef de projet Septeo. Lyon uniquement, pas de remote.</t>
         </is>
       </c>
       <c r="M425" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/idex-1/jobs/chef-de-projet-sirh-f-h_boulogne-billancourt_IDEX_DlyydO0</t>
+          <t>https://www.welcometothejungle.com/fr/companies/septeo/jobs/consultant-technico-fonctionnel-sirh-h-f_lyon</t>
         </is>
       </c>
       <c r="N425" s="39" t="inlineStr">
@@ -29737,7 +29737,7 @@
       </c>
       <c r="O425" s="39" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>60-70K€</t>
         </is>
       </c>
       <c r="P425" s="39" t="n"/>
@@ -29753,12 +29753,12 @@
       <c r="C426" s="39" t="n"/>
       <c r="D426" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet IT SIRH</t>
+          <t>Chef de projet SIRH F/H Workday</t>
         </is>
       </c>
       <c r="E426" s="39" t="inlineStr">
         <is>
-          <t>Objectware</t>
+          <t>IDEX</t>
         </is>
       </c>
       <c r="F426" s="39" t="inlineStr">
@@ -29773,7 +29773,7 @@
       </c>
       <c r="H426" s="39" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Boulogne-Billancourt (92)</t>
         </is>
       </c>
       <c r="I426" s="39" t="inlineStr">
@@ -29783,18 +29783,18 @@
       </c>
       <c r="J426" s="39" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>43 800 – 56 200 €/an</t>
         </is>
       </c>
       <c r="K426" s="39" t="n"/>
       <c r="L426" s="39" t="inlineStr">
         <is>
-          <t>Cabinet de conseil IT. Détails non accessibles (WTJ bloqué). À investiguer directement.</t>
+          <t>Programme Workday Core HR + MDM. 4 ans exp. min. Fourchette salariale modeste (43-56K) pour le profil senior de Gaëtan. Option de repli.</t>
         </is>
       </c>
       <c r="M426" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/objectware/jobs/chef-de-projet-it-sirh_paris</t>
+          <t>https://www.welcometothejungle.com/fr/companies/idex-1/jobs/chef-de-projet-sirh-f-h_boulogne-billancourt_IDEX_DlyydO0</t>
         </is>
       </c>
       <c r="N426" s="39" t="inlineStr">
@@ -29820,12 +29820,12 @@
       <c r="C427" s="39" t="n"/>
       <c r="D427" s="39" t="inlineStr">
         <is>
-          <t>Consultant SIRH Paie H/F</t>
+          <t>Chef de projet IT SIRH</t>
         </is>
       </c>
       <c r="E427" s="39" t="inlineStr">
         <is>
-          <t>Primexis</t>
+          <t>Objectware</t>
         </is>
       </c>
       <c r="F427" s="39" t="inlineStr">
@@ -29840,7 +29840,7 @@
       </c>
       <c r="H427" s="39" t="inlineStr">
         <is>
-          <t>Puteaux (92)</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I427" s="39" t="inlineStr">
@@ -29850,18 +29850,18 @@
       </c>
       <c r="J427" s="39" t="inlineStr">
         <is>
-          <t>40 000 – 55 000 €/an</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K427" s="39" t="n"/>
       <c r="L427" s="39" t="inlineStr">
         <is>
-          <t>Spécialité paie/Silae (pas SAP SF). Cabinet 450 pers. Fourchette basse pour profil senior. Option de repli.</t>
+          <t>Cabinet de conseil IT. Détails non accessibles (WTJ bloqué). À investiguer directement.</t>
         </is>
       </c>
       <c r="M427" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/primexis/jobs/consultant-sirh-paie-h-f_puteaux_PRIME_5AyPM2D</t>
+          <t>https://www.welcometothejungle.com/fr/companies/objectware/jobs/chef-de-projet-it-sirh_paris</t>
         </is>
       </c>
       <c r="N427" s="39" t="inlineStr">
@@ -29871,7 +29871,7 @@
       </c>
       <c r="O427" s="39" t="inlineStr">
         <is>
-          <t>60-70K€</t>
+          <t>70-80K€</t>
         </is>
       </c>
       <c r="P427" s="39" t="n"/>
@@ -29887,17 +29887,17 @@
       <c r="C428" s="39" t="n"/>
       <c r="D428" s="39" t="inlineStr">
         <is>
-          <t>Product Owner IT SIRH CDI F/H/NB</t>
+          <t>Consultant SIRH Paie H/F</t>
         </is>
       </c>
       <c r="E428" s="39" t="inlineStr">
         <is>
-          <t>Disneyland Paris (The Walt Disney Company)</t>
+          <t>Primexis</t>
         </is>
       </c>
       <c r="F428" s="39" t="inlineStr">
         <is>
-          <t>Disney Careers</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G428" s="39" t="inlineStr">
@@ -29907,7 +29907,7 @@
       </c>
       <c r="H428" s="39" t="inlineStr">
         <is>
-          <t>Marne-la-Vallée</t>
+          <t>Puteaux (92)</t>
         </is>
       </c>
       <c r="I428" s="39" t="inlineStr">
@@ -29917,18 +29917,18 @@
       </c>
       <c r="J428" s="39" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>40 000 – 55 000 €/an</t>
         </is>
       </c>
       <c r="K428" s="39" t="n"/>
       <c r="L428" s="39" t="inlineStr">
         <is>
-          <t>Publié 2025 — peut être clôturé. Roadmap RH applications globales Walt Disney Company. Contexte international prestigieux. Vérifier si encore actif avant de postuler.</t>
+          <t>Spécialité paie/Silae (pas SAP SF). Cabinet 450 pers. Fourchette basse pour profil senior. Option de repli.</t>
         </is>
       </c>
       <c r="M428" s="39" t="inlineStr">
         <is>
-          <t>https://emplois.disneycareers.com/emploi/marne-la-vallee/product-owner-it-sirh-cdi-f-h-nb/391/77875747712</t>
+          <t>https://www.welcometothejungle.com/fr/companies/primexis/jobs/consultant-sirh-paie-h-f_puteaux_PRIME_5AyPM2D</t>
         </is>
       </c>
       <c r="N428" s="39" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="O428" s="39" t="inlineStr">
         <is>
-          <t>75-85K€</t>
+          <t>60-70K€</t>
         </is>
       </c>
       <c r="P428" s="39" t="n"/>
@@ -29954,66 +29954,62 @@
       <c r="C429" s="39" t="n"/>
       <c r="D429" s="39" t="inlineStr">
         <is>
-          <t>Chargé de missions SIRH N2 – Workday HCM H/F</t>
+          <t>Product Owner IT SIRH CDI F/H/NB</t>
         </is>
       </c>
       <c r="E429" s="39" t="inlineStr">
         <is>
-          <t>HR DNA</t>
+          <t>Disneyland Paris (The Walt Disney Company)</t>
         </is>
       </c>
       <c r="F429" s="39" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>Disney Careers</t>
         </is>
       </c>
       <c r="G429" s="39" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H429" s="39" t="inlineStr">
         <is>
-          <t>Neuilly-sur-Marne (93)</t>
+          <t>Marne-la-Vallée</t>
         </is>
       </c>
       <c r="I429" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J429" s="39" t="inlineStr">
         <is>
-          <t>250-500€/j</t>
-        </is>
-      </c>
-      <c r="K429" s="39" t="inlineStr">
-        <is>
-          <t>24 mois</t>
-        </is>
-      </c>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K429" s="39" t="n"/>
       <c r="L429" s="39" t="inlineStr">
         <is>
-          <t>MOA SIRH Workday HCM (pas SAP), specs fonctionnelles, recette, TJM bas 250-500€/j, 24 mois — profil AMOA SIRH proche mais mauvais outil et TJM insuffisant</t>
+          <t>Publié 2025 — peut être clôturé. Roadmap RH applications globales Walt Disney Company. Contexte international prestigieux. Vérifier si encore actif avant de postuler.</t>
         </is>
       </c>
       <c r="M429" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/charge-de-missions-sirh-n2-workday-hcm-h-f-23</t>
+          <t>https://emplois.disneycareers.com/emploi/marne-la-vallee/product-owner-it-sirh-cdi-f-h-nb/391/77875747712</t>
         </is>
       </c>
       <c r="N429" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O429" s="39" t="n"/>
+          <t>Resume_GaetanFRANCOIS_SIRH</t>
+        </is>
+      </c>
+      <c r="O429" s="39" t="inlineStr">
+        <is>
+          <t>75-85K€</t>
+        </is>
+      </c>
       <c r="P429" s="39" t="n"/>
-      <c r="Q429" s="41" t="inlineStr">
-        <is>
-          <t>28/06/2026</t>
-        </is>
-      </c>
+      <c r="Q429" s="39" t="n"/>
     </row>
     <row r="430" ht="32" customHeight="1">
       <c r="A430" s="90" t="inlineStr">
@@ -30025,62 +30021,66 @@
       <c r="C430" s="39" t="n"/>
       <c r="D430" s="39" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors</t>
+          <t>Chargé de missions SIRH N2 – Workday HCM H/F</t>
         </is>
       </c>
       <c r="E430" s="39" t="inlineStr">
         <is>
-          <t>CELAD</t>
+          <t>HR DNA</t>
         </is>
       </c>
       <c r="F430" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G430" s="39" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H430" s="39" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Neuilly-sur-Marne (93)</t>
         </is>
       </c>
       <c r="I430" s="39" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J430" s="39" t="inlineStr">
         <is>
-          <t>nc</t>
-        </is>
-      </c>
-      <c r="K430" s="39" t="n"/>
+          <t>250-500€/j</t>
+        </is>
+      </c>
+      <c r="K430" s="39" t="inlineStr">
+        <is>
+          <t>24 mois</t>
+        </is>
+      </c>
       <c r="L430" s="39" t="inlineStr">
         <is>
-          <t>SAP SF + SAP HR ECP</t>
+          <t>MOA SIRH Workday HCM (pas SAP), specs fonctionnelles, recette, TJM bas 250-500€/j, 24 mois — profil AMOA SIRH proche mais mauvais outil et TJM insuffisant</t>
         </is>
       </c>
       <c r="M430" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/consultant-sap-succesfactors-sap-hr-ecp-h-f-at-celad-3275307413</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/charge-de-missions-sirh-n2-workday-hcm-h-f-23</t>
         </is>
       </c>
       <c r="N430" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
-        </is>
-      </c>
-      <c r="O430" s="39" t="inlineStr">
-        <is>
-          <t>70-85K€</t>
-        </is>
-      </c>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O430" s="39" t="n"/>
       <c r="P430" s="39" t="n"/>
-      <c r="Q430" s="39" t="n"/>
+      <c r="Q430" s="41" t="inlineStr">
+        <is>
+          <t>28/06/2026</t>
+        </is>
+      </c>
     </row>
     <row r="431" ht="16" customHeight="1">
       <c r="A431" s="90" t="inlineStr">
@@ -30092,17 +30092,17 @@
       <c r="C431" s="39" t="n"/>
       <c r="D431" s="39" t="inlineStr">
         <is>
-          <t>SIRH and Data RH Manager</t>
+          <t>Consultant SAP SuccessFactors</t>
         </is>
       </c>
       <c r="E431" s="39" t="inlineStr">
         <is>
-          <t>n.c. (Free-Work)</t>
+          <t>CELAD</t>
         </is>
       </c>
       <c r="F431" s="39" t="inlineStr">
         <is>
-          <t>Free-Work</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G431" s="39" t="inlineStr">
@@ -30112,7 +30112,7 @@
       </c>
       <c r="H431" s="39" t="inlineStr">
         <is>
-          <t>Montrouge</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I431" s="39" t="inlineStr">
@@ -30122,18 +30122,18 @@
       </c>
       <c r="J431" s="39" t="inlineStr">
         <is>
-          <t>42-69K€</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="K431" s="39" t="n"/>
       <c r="L431" s="39" t="inlineStr">
         <is>
-          <t>Salaire bas — à vérifier</t>
+          <t>SAP SF + SAP HR ECP</t>
         </is>
       </c>
       <c r="M431" s="39" t="inlineStr">
         <is>
-          <t>https://www.montrouge-emplois.fr/emplois/81020788.html</t>
+          <t>https://fr.linkedin.com/jobs/view/consultant-sap-succesfactors-sap-hr-ecp-h-f-at-celad-3275307413</t>
         </is>
       </c>
       <c r="N431" s="39" t="inlineStr">
@@ -30143,15 +30143,11 @@
       </c>
       <c r="O431" s="39" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>70-85K€</t>
         </is>
       </c>
       <c r="P431" s="39" t="n"/>
-      <c r="Q431" s="41" t="inlineStr">
-        <is>
-          <t>06/07/2026</t>
-        </is>
-      </c>
+      <c r="Q431" s="39" t="n"/>
     </row>
     <row r="432" ht="32" customHeight="1">
       <c r="A432" s="90" t="inlineStr">
@@ -30163,7 +30159,7 @@
       <c r="C432" s="39" t="n"/>
       <c r="D432" s="39" t="inlineStr">
         <is>
-          <t>AMOA RH Consultant</t>
+          <t>SIRH and Data RH Manager</t>
         </is>
       </c>
       <c r="E432" s="39" t="inlineStr">
@@ -30183,7 +30179,7 @@
       </c>
       <c r="H432" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Montrouge</t>
         </is>
       </c>
       <c r="I432" s="39" t="inlineStr">
@@ -30193,7 +30189,7 @@
       </c>
       <c r="J432" s="39" t="inlineStr">
         <is>
-          <t>53-55K€</t>
+          <t>42-69K€</t>
         </is>
       </c>
       <c r="K432" s="39" t="n"/>
@@ -30202,7 +30198,11 @@
           <t>Salaire bas — à vérifier</t>
         </is>
       </c>
-      <c r="M432" s="39" t="n"/>
+      <c r="M432" s="39" t="inlineStr">
+        <is>
+          <t>https://www.montrouge-emplois.fr/emplois/81020788.html</t>
+        </is>
+      </c>
       <c r="N432" s="39" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_SIRH.html</t>
@@ -30230,17 +30230,17 @@
       <c r="C433" s="39" t="n"/>
       <c r="D433" s="39" t="inlineStr">
         <is>
-          <t>Consultant junior IA</t>
+          <t>AMOA RH Consultant</t>
         </is>
       </c>
       <c r="E433" s="39" t="inlineStr">
         <is>
-          <t>MISTER IA</t>
+          <t>n.c. (Free-Work)</t>
         </is>
       </c>
       <c r="F433" s="39" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Free-Work</t>
         </is>
       </c>
       <c r="G433" s="39" t="inlineStr">
@@ -30260,32 +30260,32 @@
       </c>
       <c r="J433" s="39" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>53-55K€</t>
         </is>
       </c>
       <c r="K433" s="39" t="n"/>
       <c r="L433" s="39" t="inlineStr">
         <is>
-          <t>Intitulé "junior" — expérience Gaëtan peut repositionner en senior</t>
-        </is>
-      </c>
-      <c r="M433" s="39" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/fr/companies/mister-ia/jobs/consultant-junior-cdi-des-que-possible_paris</t>
-        </is>
-      </c>
+          <t>Salaire bas — à vérifier</t>
+        </is>
+      </c>
+      <c r="M433" s="39" t="n"/>
       <c r="N433" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS.pdf</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
         </is>
       </c>
       <c r="O433" s="39" t="inlineStr">
         <is>
-          <t>70-85K€</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="P433" s="39" t="n"/>
-      <c r="Q433" s="39" t="n"/>
+      <c r="Q433" s="41" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="434" ht="32" customHeight="1">
       <c r="A434" s="90" t="inlineStr">
@@ -30297,53 +30297,65 @@
       <c r="C434" s="39" t="n"/>
       <c r="D434" s="39" t="inlineStr">
         <is>
-          <t>Group HRIS Specialist</t>
+          <t>Consultant junior IA</t>
         </is>
       </c>
       <c r="E434" s="39" t="inlineStr">
         <is>
-          <t>Lynxeo</t>
+          <t>MISTER IA</t>
         </is>
       </c>
       <c r="F434" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G434" s="39" t="inlineStr">
         <is>
-          <t>CDD 12 mois</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H434" s="39" t="inlineStr">
         <is>
-          <t>Puteaux (La Défense)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I434" s="39" t="inlineStr">
         <is>
-          <t>Non précisé</t>
-        </is>
-      </c>
-      <c r="J434" s="39" t="n"/>
+          <t>nc</t>
+        </is>
+      </c>
+      <c r="J434" s="39" t="inlineStr">
+        <is>
+          <t>nc</t>
+        </is>
+      </c>
       <c r="K434" s="39" t="n"/>
       <c r="L434" s="39" t="inlineStr">
         <is>
-          <t>SAP SF apprécié ; CDD 12 mois + Puteaux sur site = faible</t>
+          <t>Intitulé "junior" — expérience Gaëtan peut repositionner en senior</t>
         </is>
       </c>
       <c r="M434" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/group-hris-specialist-at-lynxeo-4436222526</t>
-        </is>
-      </c>
-      <c r="N434" s="39" t="n"/>
-      <c r="O434" s="39" t="n"/>
+          <t>https://www.welcometothejungle.com/fr/companies/mister-ia/jobs/consultant-junior-cdi-des-que-possible_paris</t>
+        </is>
+      </c>
+      <c r="N434" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS.pdf</t>
+        </is>
+      </c>
+      <c r="O434" s="39" t="inlineStr">
+        <is>
+          <t>70-85K€</t>
+        </is>
+      </c>
       <c r="P434" s="39" t="n"/>
       <c r="Q434" s="39" t="n"/>
     </row>
     <row r="435" ht="32" customHeight="1">
-      <c r="A435" s="99" t="inlineStr">
+      <c r="A435" s="90" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -30352,57 +30364,49 @@
       <c r="C435" s="39" t="n"/>
       <c r="D435" s="39" t="inlineStr">
         <is>
-          <t>Business Analyst TalentSoft / HR Access</t>
+          <t>Group HRIS Specialist</t>
         </is>
       </c>
       <c r="E435" s="39" t="inlineStr">
         <is>
-          <t>CELAD</t>
+          <t>Lynxeo</t>
         </is>
       </c>
       <c r="F435" s="39" t="inlineStr">
         <is>
-          <t>free-work</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G435" s="39" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>CDD 12 mois</t>
         </is>
       </c>
       <c r="H435" s="39" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Puteaux (La Défense)</t>
         </is>
       </c>
       <c r="I435" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J435" s="39" t="inlineStr">
-        <is>
-          <t>450-500€/j</t>
-        </is>
-      </c>
-      <c r="K435" s="39" t="inlineStr">
-        <is>
-          <t>1 an</t>
-        </is>
-      </c>
+          <t>Non précisé</t>
+        </is>
+      </c>
+      <c r="J435" s="39" t="n"/>
+      <c r="K435" s="39" t="n"/>
       <c r="L435" s="39" t="inlineStr">
         <is>
-          <t>TalentSoft / HR Access, hors SF pur</t>
-        </is>
-      </c>
-      <c r="M435" s="39" t="n"/>
+          <t>SAP SF apprécié ; CDD 12 mois + Puteaux sur site = faible</t>
+        </is>
+      </c>
+      <c r="M435" s="39" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/group-hris-specialist-at-lynxeo-4436222526</t>
+        </is>
+      </c>
       <c r="N435" s="39" t="n"/>
       <c r="O435" s="39" t="n"/>
-      <c r="P435" s="39" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
+      <c r="P435" s="39" t="n"/>
       <c r="Q435" s="39" t="n"/>
     </row>
     <row r="436" ht="32" customHeight="1">
@@ -30415,12 +30419,12 @@
       <c r="C436" s="39" t="n"/>
       <c r="D436" s="39" t="inlineStr">
         <is>
-          <t>Consultant SAP SuccessFactors (anglais)</t>
+          <t>Business Analyst TalentSoft / HR Access</t>
         </is>
       </c>
       <c r="E436" s="39" t="inlineStr">
         <is>
-          <t>Intuition IT Solutions</t>
+          <t>CELAD</t>
         </is>
       </c>
       <c r="F436" s="39" t="inlineStr">
@@ -30435,34 +30439,30 @@
       </c>
       <c r="H436" s="39" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I436" s="39" t="inlineStr">
         <is>
-          <t>Hybride 60/40</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J436" s="39" t="inlineStr">
         <is>
-          <t>400-580€/j</t>
+          <t>450-500€/j</t>
         </is>
       </c>
       <c r="K436" s="39" t="inlineStr">
         <is>
-          <t>6 mois</t>
+          <t>1 an</t>
         </is>
       </c>
       <c r="L436" s="39" t="inlineStr">
         <is>
-          <t>Luxembourg, hybride, SF ; 15/05/2026</t>
-        </is>
-      </c>
-      <c r="M436" s="39" t="inlineStr">
-        <is>
-          <t>https://www.free-work.com/fr/tech-it/jobs/sap-successfactors</t>
-        </is>
-      </c>
+          <t>TalentSoft / HR Access, hors SF pur</t>
+        </is>
+      </c>
+      <c r="M436" s="39" t="n"/>
       <c r="N436" s="39" t="n"/>
       <c r="O436" s="39" t="n"/>
       <c r="P436" s="39" t="inlineStr">
@@ -30470,11 +30470,7 @@
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="Q436" s="39" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
+      <c r="Q436" s="39" t="n"/>
     </row>
     <row r="437" ht="16" customHeight="1">
       <c r="A437" s="99" t="inlineStr">
@@ -30486,52 +30482,52 @@
       <c r="C437" s="39" t="n"/>
       <c r="D437" s="39" t="inlineStr">
         <is>
-          <t>SIRH &amp; Data Manager F/H</t>
+          <t>Consultant SAP SuccessFactors (anglais)</t>
         </is>
       </c>
       <c r="E437" s="39" t="inlineStr">
         <is>
-          <t>GLS France</t>
+          <t>Intuition IT Solutions</t>
         </is>
       </c>
       <c r="F437" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G437" s="39" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H437" s="39" t="inlineStr">
         <is>
-          <t>Toulouse (31)</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="I437" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Hybride 60/40</t>
         </is>
       </c>
       <c r="J437" s="39" t="inlineStr">
         <is>
-          <t>N/C</t>
+          <t>400-580€/j</t>
         </is>
       </c>
       <c r="K437" s="39" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>6 mois</t>
         </is>
       </c>
       <c r="L437" s="39" t="inlineStr">
         <is>
-          <t>Data + SIRH Toulouse, hors remote</t>
+          <t>Luxembourg, hybride, SF ; 15/05/2026</t>
         </is>
       </c>
       <c r="M437" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/consultant-sirh-emplois</t>
+          <t>https://www.free-work.com/fr/tech-it/jobs/sap-successfactors</t>
         </is>
       </c>
       <c r="N437" s="39" t="n"/>
@@ -30541,10 +30537,14 @@
           <t>09/07/2026</t>
         </is>
       </c>
-      <c r="Q437" s="39" t="n"/>
+      <c r="Q437" s="39" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
     </row>
     <row r="438" ht="32" customHeight="1">
-      <c r="A438" s="90" t="inlineStr">
+      <c r="A438" s="99" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -30553,65 +30553,65 @@
       <c r="C438" s="39" t="n"/>
       <c r="D438" s="39" t="inlineStr">
         <is>
-          <t>Expert(e) AMOA SIRH – Paie &amp; DSN</t>
+          <t>SIRH &amp; Data Manager F/H</t>
         </is>
       </c>
       <c r="E438" s="39" t="inlineStr">
         <is>
-          <t>BEEZEN</t>
+          <t>GLS France</t>
         </is>
       </c>
       <c r="F438" s="39" t="inlineStr">
         <is>
-          <t>Free-Work</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G438" s="39" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H438" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Toulouse (31)</t>
         </is>
       </c>
       <c r="I438" s="39" t="inlineStr">
         <is>
-          <t>À clarifier</t>
+          <t>Partiel</t>
         </is>
       </c>
       <c r="J438" s="39" t="inlineStr">
         <is>
-          <t>À négocier</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K438" s="39" t="inlineStr">
         <is>
-          <t>3 mois</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="L438" s="39" t="inlineStr">
         <is>
-          <t>Publié 12/07/2026. Focus paie et DSN française, Pléiades apprécié ; hors coeur de ton expertise SF EC. Ne postuler que si mission tampon requise.</t>
+          <t>Data + SIRH Toulouse, hors remote</t>
         </is>
       </c>
       <c r="M438" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/</t>
-        </is>
-      </c>
-      <c r="N438" s="39" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
-        </is>
-      </c>
+          <t>https://fr.linkedin.com/jobs/consultant-sirh-emplois</t>
+        </is>
+      </c>
+      <c r="N438" s="39" t="n"/>
       <c r="O438" s="39" t="n"/>
-      <c r="P438" s="39" t="n"/>
+      <c r="P438" s="39" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="Q438" s="39" t="n"/>
     </row>
     <row r="439" ht="32" customHeight="1">
-      <c r="A439" s="51" t="inlineStr">
+      <c r="A439" s="90" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -30620,61 +30620,65 @@
       <c r="C439" s="39" t="n"/>
       <c r="D439" s="39" t="inlineStr">
         <is>
-          <t>Consultant(e) SIRH Workday (F/H)</t>
+          <t>Expert(e) AMOA SIRH – Paie &amp; DSN</t>
         </is>
       </c>
       <c r="E439" s="39" t="inlineStr">
         <is>
-          <t>ACT-ON HRIS</t>
+          <t>BEEZEN</t>
         </is>
       </c>
       <c r="F439" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Free-Work</t>
         </is>
       </c>
       <c r="G439" s="39" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H439" s="39" t="inlineStr">
         <is>
-          <t>Neuilly-sur-Seine</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I439" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J439" s="39" t="n"/>
-      <c r="K439" s="39" t="n"/>
+          <t>À clarifier</t>
+        </is>
+      </c>
+      <c r="J439" s="39" t="inlineStr">
+        <is>
+          <t>À négocier</t>
+        </is>
+      </c>
+      <c r="K439" s="39" t="inlineStr">
+        <is>
+          <t>3 mois</t>
+        </is>
+      </c>
       <c r="L439" s="39" t="inlineStr">
         <is>
-          <t>Spécialiste Workday (Core HR, Talent, Comp, Learning) — pas d'expérience Workday affichée ; cabinets conseil SIRH déjà bien représentés dans le tableur</t>
+          <t>Publié 12/07/2026. Focus paie et DSN française, Pléiades apprécié ; hors coeur de ton expertise SF EC. Ne postuler que si mission tampon requise.</t>
         </is>
       </c>
       <c r="M439" s="39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4342149906/</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/administrateur-applicatif-erp-crm-sirh/</t>
         </is>
       </c>
       <c r="N439" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
         </is>
       </c>
       <c r="O439" s="39" t="n"/>
-      <c r="P439" s="39" t="inlineStr">
-        <is>
-          <t>13/07/2026</t>
-        </is>
-      </c>
-      <c r="Q439" s="41" t="n"/>
+      <c r="P439" s="39" t="n"/>
+      <c r="Q439" s="39" t="n"/>
     </row>
     <row r="440" ht="16" customHeight="1">
-      <c r="A440" s="90" t="inlineStr">
+      <c r="A440" s="51" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -30683,17 +30687,17 @@
       <c r="C440" s="39" t="n"/>
       <c r="D440" s="39" t="inlineStr">
         <is>
-          <t>Senior Manager SIRH</t>
+          <t>Consultant(e) SIRH Workday (F/H)</t>
         </is>
       </c>
       <c r="E440" s="39" t="inlineStr">
         <is>
-          <t>ALTHEA</t>
+          <t>ACT-ON HRIS</t>
         </is>
       </c>
       <c r="F440" s="39" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G440" s="39" t="inlineStr">
@@ -30703,7 +30707,7 @@
       </c>
       <c r="H440" s="39" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Neuilly-sur-Seine</t>
         </is>
       </c>
       <c r="I440" s="39" t="inlineStr">
@@ -30711,24 +30715,16 @@
           <t>Hybride</t>
         </is>
       </c>
-      <c r="J440" s="39" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K440" s="39" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
+      <c r="J440" s="39" t="n"/>
+      <c r="K440" s="39" t="n"/>
       <c r="L440" s="39" t="inlineStr">
         <is>
-          <t>ALTHEA cabinet conseil SIRH. Senior Manager, Lyon. Frein : Lyon pas remote. Profil senior bien aligné sinon.</t>
+          <t>Spécialiste Workday (Core HR, Talent, Comp, Learning) — pas d'expérience Workday affichée ; cabinets conseil SIRH déjà bien représentés dans le tableur</t>
         </is>
       </c>
       <c r="M440" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/althea/jobs/senior-manager-sirh-lyon-cdi_lyon</t>
+          <t>https://www.linkedin.com/jobs/view/4342149906/</t>
         </is>
       </c>
       <c r="N440" s="39" t="inlineStr">
@@ -30736,21 +30732,13 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O440" s="39" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
+      <c r="O440" s="39" t="n"/>
       <c r="P440" s="39" t="inlineStr">
         <is>
-          <t>07/2026</t>
-        </is>
-      </c>
-      <c r="Q440" s="41" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
+          <t>13/07/2026</t>
+        </is>
+      </c>
+      <c r="Q440" s="41" t="n"/>
     </row>
     <row r="441" ht="32" customHeight="1">
       <c r="A441" s="90" t="inlineStr">
@@ -30762,62 +30750,74 @@
       <c r="C441" s="39" t="n"/>
       <c r="D441" s="39" t="inlineStr">
         <is>
-          <t>Senior SAP HCM Payroll &amp; Time Consultant</t>
+          <t>Senior Manager SIRH</t>
         </is>
       </c>
       <c r="E441" s="39" t="inlineStr">
         <is>
-          <t>Strada Global</t>
+          <t>ALTHEA</t>
         </is>
       </c>
       <c r="F441" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn (il y a 12h)</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G441" s="39" t="inlineStr">
         <is>
-          <t>CDI ou Mission</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H441" s="39" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I441" s="39" t="inlineStr">
         <is>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J441" s="39" t="inlineStr">
+        <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="J441" s="39" t="inlineStr">
+      <c r="K441" s="39" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="K441" s="39" t="n"/>
       <c r="L441" s="39" t="inlineStr">
         <is>
-          <t>Strada Global (ex-Alight) - spécialiste SAP HR France. Très récent (12h). Focus paie/GTA plutôt technique - hors centre de profil mais SAP HR pertinent.</t>
+          <t>ALTHEA cabinet conseil SIRH. Senior Manager, Lyon. Frein : Lyon pas remote. Profil senior bien aligné sinon.</t>
         </is>
       </c>
       <c r="M441" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/sap-hcm-emplois</t>
+          <t>https://www.welcometothejungle.com/fr/companies/althea/jobs/senior-manager-sirh-lyon-cdi_lyon</t>
         </is>
       </c>
       <c r="N441" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
       <c r="O441" s="39" t="inlineStr">
         <is>
-          <t>700 €/j</t>
-        </is>
-      </c>
-      <c r="P441" s="39" t="n"/>
-      <c r="Q441" s="41" t="n"/>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="P441" s="39" t="inlineStr">
+        <is>
+          <t>07/2026</t>
+        </is>
+      </c>
+      <c r="Q441" s="41" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
     </row>
     <row r="442" ht="32" customHeight="1">
       <c r="A442" s="90" t="inlineStr">
@@ -30829,62 +30829,58 @@
       <c r="C442" s="39" t="n"/>
       <c r="D442" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet IA</t>
+          <t>Senior SAP HCM Payroll &amp; Time Consultant</t>
         </is>
       </c>
       <c r="E442" s="39" t="inlineStr">
         <is>
-          <t>HN SERVICES</t>
+          <t>Strada Global</t>
         </is>
       </c>
       <c r="F442" s="39" t="inlineStr">
         <is>
-          <t>free-work.com</t>
+          <t>LinkedIn (il y a 12h)</t>
         </is>
       </c>
       <c r="G442" s="39" t="inlineStr">
         <is>
-          <t>Freelance/CDI</t>
+          <t>CDI ou Mission</t>
         </is>
       </c>
       <c r="H442" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I442" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="J442" s="39" t="inlineStr">
         <is>
-          <t>400-710€/j</t>
-        </is>
-      </c>
-      <c r="K442" s="39" t="inlineStr">
-        <is>
-          <t>6 mois</t>
-        </is>
-      </c>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="K442" s="39" t="n"/>
       <c r="L442" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet IA généraliste. TJM 400-710€/j ou 40-70K€/an. Posté 15/07/2026.</t>
+          <t>Strada Global (ex-Alight) - spécialiste SAP HR France. Très récent (12h). Focus paie/GTA plutôt technique - hors centre de profil mais SAP HR pertinent.</t>
         </is>
       </c>
       <c r="M442" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/ingenieur-ia-16</t>
+          <t>https://fr.linkedin.com/jobs/sap-hcm-emplois</t>
         </is>
       </c>
       <c r="N442" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_IA.html</t>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
         </is>
       </c>
       <c r="O442" s="39" t="inlineStr">
         <is>
-          <t>500-650€/j</t>
+          <t>700 €/j</t>
         </is>
       </c>
       <c r="P442" s="39" t="n"/>
@@ -30900,54 +30896,62 @@
       <c r="C443" s="39" t="n"/>
       <c r="D443" s="39" t="inlineStr">
         <is>
-          <t>Chef de projet SIRH (H/F) / Consultant Paie et SIRH (H/F)</t>
+          <t>Chef de projet IA</t>
         </is>
       </c>
       <c r="E443" s="39" t="inlineStr">
         <is>
-          <t>Ayming</t>
+          <t>HN SERVICES</t>
         </is>
       </c>
       <c r="F443" s="39" t="inlineStr">
         <is>
-          <t>ayming.fr / Glassdoor</t>
+          <t>free-work.com</t>
         </is>
       </c>
       <c r="G443" s="39" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance/CDI</t>
         </is>
       </c>
       <c r="H443" s="39" t="inlineStr">
         <is>
-          <t>France / Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I443" s="39" t="inlineStr">
         <is>
-          <t>Non précisé</t>
-        </is>
-      </c>
-      <c r="J443" s="39" t="n"/>
-      <c r="K443" s="39" t="n"/>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J443" s="39" t="inlineStr">
+        <is>
+          <t>400-710€/j</t>
+        </is>
+      </c>
+      <c r="K443" s="39" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
       <c r="L443" s="39" t="inlineStr">
         <is>
-          <t>Postes trouvés via recherche mais absents de la liste actuelle des offres ouvertes sur le site ; statut incertain (probablement pourvus). À vérifier manuellement avant de postuler.</t>
+          <t>Chef de projet IA généraliste. TJM 400-710€/j ou 40-70K€/an. Posté 15/07/2026.</t>
         </is>
       </c>
       <c r="M443" s="39" t="inlineStr">
         <is>
-          <t>https://www.ayming.fr/jobs/chef-de-projet-sirh-hf/</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/assistant-chef-de-projet/ingenieur-ia-16</t>
         </is>
       </c>
       <c r="N443" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
+          <t>Resume_GaetanFRANCOIS_IA.html</t>
         </is>
       </c>
       <c r="O443" s="39" t="inlineStr">
         <is>
-          <t>70-80K€</t>
+          <t>500-650€/j</t>
         </is>
       </c>
       <c r="P443" s="39" t="n"/>
@@ -30963,17 +30967,17 @@
       <c r="C444" s="39" t="n"/>
       <c r="D444" s="39" t="inlineStr">
         <is>
-          <t>Consultant paramétrage SIRH paie (H/F)</t>
+          <t>Chef de projet SIRH (H/F) / Consultant Paie et SIRH (H/F)</t>
         </is>
       </c>
       <c r="E444" s="39" t="inlineStr">
         <is>
-          <t>Talentia Software</t>
+          <t>Ayming</t>
         </is>
       </c>
       <c r="F444" s="39" t="inlineStr">
         <is>
-          <t>engagement-jeunes.com</t>
+          <t>ayming.fr / Glassdoor</t>
         </is>
       </c>
       <c r="G444" s="39" t="inlineStr">
@@ -30983,7 +30987,7 @@
       </c>
       <c r="H444" s="39" t="inlineStr">
         <is>
-          <t>Puteaux (92)</t>
+          <t>France / Lyon</t>
         </is>
       </c>
       <c r="I444" s="39" t="inlineStr">
@@ -30995,12 +30999,12 @@
       <c r="K444" s="39" t="n"/>
       <c r="L444" s="39" t="inlineStr">
         <is>
-          <t>Éditeur RH/Finance français, poste paramétrage paie SIRH ; source secondaire peu détaillée, à vérifier directement sur le site de l'éditeur.</t>
+          <t>Postes trouvés via recherche mais absents de la liste actuelle des offres ouvertes sur le site ; statut incertain (probablement pourvus). À vérifier manuellement avant de postuler.</t>
         </is>
       </c>
       <c r="M444" s="39" t="inlineStr">
         <is>
-          <t>https://www.engagement-jeunes.com/fr/detail-offre/37016104/cdi-talentia-software-consultant-parametrage-sirh-paie-h-f.html</t>
+          <t>https://www.ayming.fr/jobs/chef-de-projet-sirh-hf/</t>
         </is>
       </c>
       <c r="N444" s="39" t="inlineStr">
@@ -31010,7 +31014,7 @@
       </c>
       <c r="O444" s="39" t="inlineStr">
         <is>
-          <t>65-75K€</t>
+          <t>70-80K€</t>
         </is>
       </c>
       <c r="P444" s="39" t="n"/>
@@ -31026,53 +31030,57 @@
       <c r="C445" s="39" t="n"/>
       <c r="D445" s="39" t="inlineStr">
         <is>
-          <t>Consultant expérimenté en HR Transformation F/H</t>
+          <t>Consultant paramétrage SIRH paie (H/F)</t>
         </is>
       </c>
       <c r="E445" s="39" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Talentia Software</t>
         </is>
       </c>
       <c r="F445" s="39" t="inlineStr">
         <is>
-          <t>Glassdoor</t>
-        </is>
-      </c>
-      <c r="G445" s="39" t="n"/>
+          <t>engagement-jeunes.com</t>
+        </is>
+      </c>
+      <c r="G445" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="H445" s="39" t="inlineStr">
         <is>
-          <t>Neuilly-sur-Seine</t>
-        </is>
-      </c>
-      <c r="I445" s="39" t="n"/>
+          <t>Puteaux (92)</t>
+        </is>
+      </c>
+      <c r="I445" s="39" t="inlineStr">
+        <is>
+          <t>Non précisé</t>
+        </is>
+      </c>
       <c r="J445" s="39" t="n"/>
       <c r="K445" s="39" t="n"/>
       <c r="L445" s="39" t="inlineStr">
         <is>
-          <t>Équipe HR Transformation PwC, diagnostic SIRH ; statut d'activité non confirmé (Glassdoor bloque le fetch direct).</t>
+          <t>Éditeur RH/Finance français, poste paramétrage paie SIRH ; source secondaire peu détaillée, à vérifier directement sur le site de l'éditeur.</t>
         </is>
       </c>
       <c r="M445" s="39" t="inlineStr">
         <is>
-          <t>https://www.glassdoor.fr/job-listing/consultant-exp%C3%A9riment%C3%A9-en-hr-transformation-fh-pwc-JV_IC3041419_KO0,46_KE47,50.htm?jl=1009932776858</t>
+          <t>https://www.engagement-jeunes.com/fr/detail-offre/37016104/cdi-talentia-software-consultant-parametrage-sirh-paie-h-f.html</t>
         </is>
       </c>
       <c r="N445" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
       <c r="O445" s="39" t="inlineStr">
         <is>
-          <t>70-85 K€</t>
-        </is>
-      </c>
-      <c r="P445" s="39" t="inlineStr">
-        <is>
-          <t>09/08/2026</t>
-        </is>
-      </c>
+          <t>65-75K€</t>
+        </is>
+      </c>
+      <c r="P445" s="39" t="n"/>
       <c r="Q445" s="41" t="n"/>
     </row>
     <row r="446" ht="16" customHeight="1">
@@ -31085,27 +31093,23 @@
       <c r="C446" s="39" t="n"/>
       <c r="D446" s="39" t="inlineStr">
         <is>
-          <t>Expert HR Access F/H</t>
+          <t>Consultant expérimenté en HR Transformation F/H</t>
         </is>
       </c>
       <c r="E446" s="39" t="inlineStr">
         <is>
-          <t>La Poste Groupe (i-TEAM)</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="F446" s="39" t="inlineStr">
         <is>
-          <t>laposterecrute.fr</t>
-        </is>
-      </c>
-      <c r="G446" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>Glassdoor</t>
+        </is>
+      </c>
+      <c r="G446" s="39" t="n"/>
       <c r="H446" s="39" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Neuilly-sur-Seine</t>
         </is>
       </c>
       <c r="I446" s="39" t="n"/>
@@ -31113,12 +31117,12 @@
       <c r="K446" s="39" t="n"/>
       <c r="L446" s="39" t="inlineStr">
         <is>
-          <t>Poste très technique (COBOL, développement HR Access), moins aligné avec le profil fonctionnel de Gaëtan.</t>
+          <t>Équipe HR Transformation PwC, diagnostic SIRH ; statut d'activité non confirmé (Glassdoor bloque le fetch direct).</t>
         </is>
       </c>
       <c r="M446" s="39" t="inlineStr">
         <is>
-          <t>https://www.laposterecrute.fr/offre/2026-213570</t>
+          <t>https://www.glassdoor.fr/job-listing/consultant-exp%C3%A9riment%C3%A9-en-hr-transformation-fh-pwc-JV_IC3041419_KO0,46_KE47,50.htm?jl=1009932776858</t>
         </is>
       </c>
       <c r="N446" s="39" t="inlineStr">
@@ -31126,7 +31130,11 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O446" s="39" t="n"/>
+      <c r="O446" s="39" t="inlineStr">
+        <is>
+          <t>70-85 K€</t>
+        </is>
+      </c>
       <c r="P446" s="39" t="inlineStr">
         <is>
           <t>09/08/2026</t>
@@ -31144,17 +31152,17 @@
       <c r="C447" s="39" t="n"/>
       <c r="D447" s="39" t="inlineStr">
         <is>
-          <t>Consultant SIRH Workday</t>
+          <t>Expert HR Access F/H</t>
         </is>
       </c>
       <c r="E447" s="39" t="inlineStr">
         <is>
-          <t>Metaline</t>
+          <t>La Poste Groupe (i-TEAM)</t>
         </is>
       </c>
       <c r="F447" s="39" t="inlineStr">
         <is>
-          <t>Teamtailor</t>
+          <t>laposterecrute.fr</t>
         </is>
       </c>
       <c r="G447" s="39" t="inlineStr">
@@ -31164,7 +31172,7 @@
       </c>
       <c r="H447" s="39" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I447" s="39" t="n"/>
@@ -31172,12 +31180,12 @@
       <c r="K447" s="39" t="n"/>
       <c r="L447" s="39" t="inlineStr">
         <is>
-          <t>Support N2 Workday, niveau plus junior que le profil de Gaëtan.</t>
+          <t>Poste très technique (COBOL, développement HR Access), moins aligné avec le profil fonctionnel de Gaëtan.</t>
         </is>
       </c>
       <c r="M447" s="39" t="inlineStr">
         <is>
-          <t>https://metaline.teamtailor.com/jobs/7315629-consultant-sirh-workday</t>
+          <t>https://www.laposterecrute.fr/offre/2026-213570</t>
         </is>
       </c>
       <c r="N447" s="39" t="inlineStr">
@@ -31191,7 +31199,7 @@
           <t>09/08/2026</t>
         </is>
       </c>
-      <c r="Q447" s="39" t="n"/>
+      <c r="Q447" s="41" t="n"/>
     </row>
     <row r="448" ht="32" customHeight="1">
       <c r="A448" s="90" t="inlineStr">
@@ -31203,48 +31211,40 @@
       <c r="C448" s="39" t="n"/>
       <c r="D448" s="39" t="inlineStr">
         <is>
-          <t>Adjoint(e) Responsable Paie (H/F)</t>
+          <t>Consultant SIRH Workday</t>
         </is>
       </c>
       <c r="E448" s="39" t="inlineStr">
         <is>
-          <t>HR Path</t>
+          <t>Metaline</t>
         </is>
       </c>
       <c r="F448" s="39" t="inlineStr">
         <is>
-          <t>free-work</t>
+          <t>Teamtailor</t>
         </is>
       </c>
       <c r="G448" s="39" t="inlineStr">
         <is>
-          <t>Mission freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H448" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="I448" s="39" t="n"/>
-      <c r="J448" s="39" t="inlineStr">
-        <is>
-          <t>650-700€/j</t>
-        </is>
-      </c>
-      <c r="K448" s="39" t="inlineStr">
-        <is>
-          <t>3 mois</t>
-        </is>
-      </c>
+      <c r="J448" s="39" t="n"/>
+      <c r="K448" s="39" t="n"/>
       <c r="L448" s="39" t="inlineStr">
         <is>
-          <t>HR Path est un partenaire SIRH clé, mais le poste vise l'opérationnel paie plutôt que le conseil SAP HCM/SF.</t>
+          <t>Support N2 Workday, niveau plus junior que le profil de Gaëtan.</t>
         </is>
       </c>
       <c r="M448" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/directeur-de-la-data-cdo/adjoint-e-responsable-paie-h-f</t>
+          <t>https://metaline.teamtailor.com/jobs/7315629-consultant-sirh-workday</t>
         </is>
       </c>
       <c r="N448" s="39" t="inlineStr">
@@ -31252,21 +31252,13 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O448" s="39" t="inlineStr">
-        <is>
-          <t>650-700€/j</t>
-        </is>
-      </c>
+      <c r="O448" s="39" t="n"/>
       <c r="P448" s="39" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
-      <c r="Q448" s="39" t="inlineStr">
-        <is>
-          <t>04/08/2026</t>
-        </is>
-      </c>
+      <c r="Q448" s="39" t="n"/>
     </row>
     <row r="449" ht="32" customHeight="1">
       <c r="A449" s="90" t="inlineStr">
@@ -31278,12 +31270,12 @@
       <c r="C449" s="39" t="n"/>
       <c r="D449" s="39" t="inlineStr">
         <is>
-          <t>Knowledge Manager</t>
+          <t>Adjoint(e) Responsable Paie (H/F)</t>
         </is>
       </c>
       <c r="E449" s="39" t="inlineStr">
         <is>
-          <t>Argain Consulting Innovation</t>
+          <t>HR Path</t>
         </is>
       </c>
       <c r="F449" s="39" t="inlineStr">
@@ -31298,13 +31290,13 @@
       </c>
       <c r="H449" s="39" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I449" s="39" t="n"/>
       <c r="J449" s="39" t="inlineStr">
         <is>
-          <t>350-400€/j</t>
+          <t>650-700€/j</t>
         </is>
       </c>
       <c r="K449" s="39" t="inlineStr">
@@ -31314,12 +31306,12 @@
       </c>
       <c r="L449" s="39" t="inlineStr">
         <is>
-          <t>Accompagnement des usages IA et fiabilisation d'un corpus de connaissances ; rôle plus documentaire que formation.</t>
+          <t>HR Path est un partenaire SIRH clé, mais le poste vise l'opérationnel paie plutôt que le conseil SAP HCM/SF.</t>
         </is>
       </c>
       <c r="M449" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/community-manager-social-media-manager/knowledge-manager-14</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/directeur-de-la-data-cdo/adjoint-e-responsable-paie-h-f</t>
         </is>
       </c>
       <c r="N449" s="39" t="inlineStr">
@@ -31329,7 +31321,7 @@
       </c>
       <c r="O449" s="39" t="inlineStr">
         <is>
-          <t>350-400€/j</t>
+          <t>650-700€/j</t>
         </is>
       </c>
       <c r="P449" s="39" t="inlineStr">
@@ -31339,7 +31331,7 @@
       </c>
       <c r="Q449" s="39" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -31353,58 +31345,70 @@
       <c r="C450" s="39" t="n"/>
       <c r="D450" s="39" t="inlineStr">
         <is>
-          <t>Formateur (H/F) Création de contenus rédactionnels et visuels par de l'IA</t>
+          <t>Knowledge Manager</t>
         </is>
       </c>
       <c r="E450" s="39" t="inlineStr">
         <is>
-          <t>n.c.</t>
+          <t>Argain Consulting Innovation</t>
         </is>
       </c>
       <c r="F450" s="39" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G450" s="39" t="inlineStr">
         <is>
-          <t>Freelance/mission</t>
+          <t>Mission freelance</t>
         </is>
       </c>
       <c r="H450" s="39" t="inlineStr">
         <is>
-          <t>Chartres</t>
-        </is>
-      </c>
-      <c r="I450" s="39" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="J450" s="39" t="n"/>
-      <c r="K450" s="39" t="n"/>
+          <t>Le Mans</t>
+        </is>
+      </c>
+      <c r="I450" s="39" t="n"/>
+      <c r="J450" s="39" t="inlineStr">
+        <is>
+          <t>350-400€/j</t>
+        </is>
+      </c>
+      <c r="K450" s="39" t="inlineStr">
+        <is>
+          <t>3 mois</t>
+        </is>
+      </c>
       <c r="L450" s="39" t="inlineStr">
         <is>
-          <t>Même type de mission que la précédente (ville différente), orientée création de contenu par IA.</t>
+          <t>Accompagnement des usages IA et fiabilisation d'un corpus de connaissances ; rôle plus documentaire que formation.</t>
         </is>
       </c>
       <c r="M450" s="39" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/formateur-h-f-creation-de-contenus-redactionnels-et-visuels-par-de-l-ia-chartres-fc80b0e8/</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/community-manager-social-media-manager/knowledge-manager-14</t>
         </is>
       </c>
       <c r="N450" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_IA.pdf</t>
-        </is>
-      </c>
-      <c r="O450" s="39" t="n"/>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O450" s="39" t="inlineStr">
+        <is>
+          <t>350-400€/j</t>
+        </is>
+      </c>
       <c r="P450" s="39" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
-      <c r="Q450" s="39" t="n"/>
+      <c r="Q450" s="39" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="451" ht="16" customHeight="1">
       <c r="A451" s="90" t="inlineStr">
@@ -31416,7 +31420,7 @@
       <c r="C451" s="39" t="n"/>
       <c r="D451" s="39" t="inlineStr">
         <is>
-          <t>Formateur Indépendant IA</t>
+          <t>Formateur (H/F) Création de contenus rédactionnels et visuels par de l'IA</t>
         </is>
       </c>
       <c r="E451" s="39" t="inlineStr">
@@ -31426,30 +31430,34 @@
       </c>
       <c r="F451" s="39" t="inlineStr">
         <is>
-          <t>infreelancing.com</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G451" s="39" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Freelance/mission</t>
         </is>
       </c>
       <c r="H451" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I451" s="39" t="n"/>
+          <t>Chartres</t>
+        </is>
+      </c>
+      <c r="I451" s="39" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
       <c r="J451" s="39" t="n"/>
       <c r="K451" s="39" t="n"/>
       <c r="L451" s="39" t="inlineStr">
         <is>
-          <t>Nouvelle plateforme freelance non couverte jusqu'ici ; détails non confirmés (fetch direct bloqué).</t>
+          <t>Même type de mission que la précédente (ville différente), orientée création de contenu par IA.</t>
         </is>
       </c>
       <c r="M451" s="39" t="inlineStr">
         <is>
-          <t>https://infreelancing.com/missions-freelance/236811/formateur-independant-ia</t>
+          <t>https://www.mission-freelances.fr/missions/formateur-h-f-creation-de-contenus-redactionnels-et-visuels-par-de-l-ia-chartres-fc80b0e8/</t>
         </is>
       </c>
       <c r="N451" s="39" t="inlineStr">
@@ -31475,7 +31483,7 @@
       <c r="C452" s="39" t="n"/>
       <c r="D452" s="39" t="inlineStr">
         <is>
-          <t>Partenaire Développement &amp; Avant-Vente IA - Lead Business Development</t>
+          <t>Formateur Indépendant IA</t>
         </is>
       </c>
       <c r="E452" s="39" t="inlineStr">
@@ -31485,10 +31493,14 @@
       </c>
       <c r="F452" s="39" t="inlineStr">
         <is>
-          <t>mission-freelances.fr</t>
-        </is>
-      </c>
-      <c r="G452" s="39" t="n"/>
+          <t>infreelancing.com</t>
+        </is>
+      </c>
+      <c r="G452" s="39" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
       <c r="H452" s="39" t="inlineStr">
         <is>
           <t>Paris</t>
@@ -31499,12 +31511,12 @@
       <c r="K452" s="39" t="n"/>
       <c r="L452" s="39" t="inlineStr">
         <is>
-          <t>Avant-vente IA, proche du profil pre-sales mais business dev générique plutôt que HR Tech ; à vérifier en détail.</t>
+          <t>Nouvelle plateforme freelance non couverte jusqu'ici ; détails non confirmés (fetch direct bloqué).</t>
         </is>
       </c>
       <c r="M452" s="39" t="inlineStr">
         <is>
-          <t>https://www.mission-freelances.fr/missions/partenaire-developpement-avant-vente-ia-lead-business-development-paris-ec77a6cc/</t>
+          <t>https://infreelancing.com/missions-freelance/236811/formateur-independant-ia</t>
         </is>
       </c>
       <c r="N452" s="39" t="inlineStr">
@@ -31530,23 +31542,23 @@
       <c r="C453" s="39" t="n"/>
       <c r="D453" s="39" t="inlineStr">
         <is>
-          <t>Consultant SIRH / Oracle HCM Cloud F/H</t>
+          <t>Partenaire Développement &amp; Avant-Vente IA - Lead Business Development</t>
         </is>
       </c>
       <c r="E453" s="39" t="inlineStr">
         <is>
-          <t>n.c. (via APEC)</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="F453" s="39" t="inlineStr">
         <is>
-          <t>apec.fr</t>
+          <t>mission-freelances.fr</t>
         </is>
       </c>
       <c r="G453" s="39" t="n"/>
       <c r="H453" s="39" t="inlineStr">
         <is>
-          <t>Paris 09</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I453" s="39" t="n"/>
@@ -31554,30 +31566,26 @@
       <c r="K453" s="39" t="n"/>
       <c r="L453" s="39" t="inlineStr">
         <is>
-          <t>SIRH mais spécifiquement Oracle HCM (pas SAP, cœur d'expertise) ; APEC bloque le fetch direct, détails à confirmer.</t>
+          <t>Avant-vente IA, proche du profil pre-sales mais business dev générique plutôt que HR Tech ; à vérifier en détail.</t>
         </is>
       </c>
       <c r="M453" s="39" t="inlineStr">
         <is>
-          <t>https://www.apec.fr/candidat/recherche-emploi.html/emploi/detail-offre/177777863W</t>
+          <t>https://www.mission-freelances.fr/missions/partenaire-developpement-avant-vente-ia-lead-business-development-paris-ec77a6cc/</t>
         </is>
       </c>
       <c r="N453" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
-        </is>
-      </c>
-      <c r="O453" s="39" t="inlineStr">
-        <is>
-          <t>70-85 K€</t>
-        </is>
-      </c>
+          <t>Resume_GaetanFRANCOIS_IA.pdf</t>
+        </is>
+      </c>
+      <c r="O453" s="39" t="n"/>
       <c r="P453" s="39" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="Q453" s="41" t="n"/>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="Q453" s="39" t="n"/>
     </row>
     <row r="454" ht="16" customHeight="1">
       <c r="A454" s="90" t="inlineStr">
@@ -31589,27 +31597,23 @@
       <c r="C454" s="39" t="n"/>
       <c r="D454" s="39" t="inlineStr">
         <is>
-          <t>Workday Intégration Consultant (H/F)</t>
+          <t>Consultant SIRH / Oracle HCM Cloud F/H</t>
         </is>
       </c>
       <c r="E454" s="39" t="inlineStr">
         <is>
-          <t>HR Path</t>
+          <t>n.c. (via APEC)</t>
         </is>
       </c>
       <c r="F454" s="39" t="inlineStr">
         <is>
-          <t>jobs.hr-path.com</t>
-        </is>
-      </c>
-      <c r="G454" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>apec.fr</t>
+        </is>
+      </c>
+      <c r="G454" s="39" t="n"/>
       <c r="H454" s="39" t="inlineStr">
         <is>
-          <t>Bègles (33)</t>
+          <t>Paris 09</t>
         </is>
       </c>
       <c r="I454" s="39" t="n"/>
@@ -31617,12 +31621,12 @@
       <c r="K454" s="39" t="n"/>
       <c r="L454" s="39" t="inlineStr">
         <is>
-          <t>SIRH mais Workday, pas d'expérience directe de Gaëtan sur cet outil.</t>
+          <t>SIRH mais spécifiquement Oracle HCM (pas SAP, cœur d'expertise) ; APEC bloque le fetch direct, détails à confirmer.</t>
         </is>
       </c>
       <c r="M454" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/B%C3%A8gles-Workday-Int%C3%A9gration-Consultant-%28HF%29-33-33130/1171326601/</t>
+          <t>https://www.apec.fr/candidat/recherche-emploi.html/emploi/detail-offre/177777863W</t>
         </is>
       </c>
       <c r="N454" s="39" t="inlineStr">
@@ -31630,7 +31634,11 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O454" s="39" t="n"/>
+      <c r="O454" s="39" t="inlineStr">
+        <is>
+          <t>70-85 K€</t>
+        </is>
+      </c>
       <c r="P454" s="39" t="inlineStr">
         <is>
           <t>10/08/2026</t>
@@ -31648,7 +31656,7 @@
       <c r="C455" s="39" t="n"/>
       <c r="D455" s="39" t="inlineStr">
         <is>
-          <t>Consultant Workday HCM - France (H/F)</t>
+          <t>Workday Intégration Consultant (H/F)</t>
         </is>
       </c>
       <c r="E455" s="39" t="inlineStr">
@@ -31668,7 +31676,7 @@
       </c>
       <c r="H455" s="39" t="inlineStr">
         <is>
-          <t>Paris La Défense</t>
+          <t>Bègles (33)</t>
         </is>
       </c>
       <c r="I455" s="39" t="n"/>
@@ -31676,12 +31684,12 @@
       <c r="K455" s="39" t="n"/>
       <c r="L455" s="39" t="inlineStr">
         <is>
-          <t>Idem, Workday hors cœur SAP.</t>
+          <t>SIRH mais Workday, pas d'expérience directe de Gaëtan sur cet outil.</t>
         </is>
       </c>
       <c r="M455" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-Workday-HCM-France-%28HF%29-75-92042/772919601/</t>
+          <t>https://jobs.hr-path.com/job/B%C3%A8gles-Workday-Int%C3%A9gration-Consultant-%28HF%29-33-33130/1171326601/</t>
         </is>
       </c>
       <c r="N455" s="39" t="inlineStr">
@@ -31707,7 +31715,7 @@
       <c r="C456" s="39" t="n"/>
       <c r="D456" s="39" t="inlineStr">
         <is>
-          <t>Oracle HCM Cloud Consultant (H/F)</t>
+          <t>Consultant Workday HCM - France (H/F)</t>
         </is>
       </c>
       <c r="E456" s="39" t="inlineStr">
@@ -31735,12 +31743,12 @@
       <c r="K456" s="39" t="n"/>
       <c r="L456" s="39" t="inlineStr">
         <is>
-          <t>SIRH mais Oracle HCM, hors cœur SAP.</t>
+          <t>Idem, Workday hors cœur SAP.</t>
         </is>
       </c>
       <c r="M456" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Oracle-HCM-Cloud-Consultant-%28HF%29-75-92042/768696101/</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Consultant-Workday-HCM-France-%28HF%29-75-92042/772919601/</t>
         </is>
       </c>
       <c r="N456" s="39" t="inlineStr">
@@ -31766,7 +31774,7 @@
       <c r="C457" s="39" t="n"/>
       <c r="D457" s="39" t="inlineStr">
         <is>
-          <t>Consultant sénior SIRH paie Silae (H/F)</t>
+          <t>Oracle HCM Cloud Consultant (H/F)</t>
         </is>
       </c>
       <c r="E457" s="39" t="inlineStr">
@@ -31786,7 +31794,7 @@
       </c>
       <c r="H457" s="39" t="inlineStr">
         <is>
-          <t>Ifs (14)</t>
+          <t>Paris La Défense</t>
         </is>
       </c>
       <c r="I457" s="39" t="n"/>
@@ -31794,12 +31802,12 @@
       <c r="K457" s="39" t="n"/>
       <c r="L457" s="39" t="inlineStr">
         <is>
-          <t>SIRH paie mais outil Silae, localisation Calvados peu adaptée au remote.</t>
+          <t>SIRH mais Oracle HCM, hors cœur SAP.</t>
         </is>
       </c>
       <c r="M457" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Ifs-Consultant-s%C3%A9nior-SIRH-paie-Silae-%28HF%29-14-14123/1401970133/</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Oracle-HCM-Cloud-Consultant-%28HF%29-75-92042/768696101/</t>
         </is>
       </c>
       <c r="N457" s="39" t="inlineStr">
@@ -31825,7 +31833,7 @@
       <c r="C458" s="39" t="n"/>
       <c r="D458" s="39" t="inlineStr">
         <is>
-          <t>Workday Solution Architect - France</t>
+          <t>Consultant sénior SIRH paie Silae (H/F)</t>
         </is>
       </c>
       <c r="E458" s="39" t="inlineStr">
@@ -31845,7 +31853,7 @@
       </c>
       <c r="H458" s="39" t="inlineStr">
         <is>
-          <t>Paris La Défense</t>
+          <t>Ifs (14)</t>
         </is>
       </c>
       <c r="I458" s="39" t="n"/>
@@ -31853,12 +31861,12 @@
       <c r="K458" s="39" t="n"/>
       <c r="L458" s="39" t="inlineStr">
         <is>
-          <t>Architecte solution, hors cœur SAP.</t>
+          <t>SIRH paie mais outil Silae, localisation Calvados peu adaptée au remote.</t>
         </is>
       </c>
       <c r="M458" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Workday-Solution-Architect-France-75-92042/768697301/</t>
+          <t>https://jobs.hr-path.com/job/Ifs-Consultant-s%C3%A9nior-SIRH-paie-Silae-%28HF%29-14-14123/1401970133/</t>
         </is>
       </c>
       <c r="N458" s="39" t="inlineStr">
@@ -31884,7 +31892,7 @@
       <c r="C459" s="39" t="n"/>
       <c r="D459" s="39" t="inlineStr">
         <is>
-          <t>Workday Lead Consultant (H/F)</t>
+          <t>Workday Solution Architect - France</t>
         </is>
       </c>
       <c r="E459" s="39" t="inlineStr">
@@ -31912,12 +31920,12 @@
       <c r="K459" s="39" t="n"/>
       <c r="L459" s="39" t="inlineStr">
         <is>
-          <t>Idem, Workday hors cœur SAP.</t>
+          <t>Architecte solution, hors cœur SAP.</t>
         </is>
       </c>
       <c r="M459" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Workday-Lead-Consultant-%28HF%29-75-92042/1079681201/</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Workday-Solution-Architect-France-75-92042/768697301/</t>
         </is>
       </c>
       <c r="N459" s="39" t="inlineStr">
@@ -31943,7 +31951,7 @@
       <c r="C460" s="39" t="n"/>
       <c r="D460" s="39" t="inlineStr">
         <is>
-          <t>Workday Talent Lead Consultant</t>
+          <t>Workday Lead Consultant (H/F)</t>
         </is>
       </c>
       <c r="E460" s="39" t="inlineStr">
@@ -31976,7 +31984,7 @@
       </c>
       <c r="M460" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Workday-Talent-Lead-Consultant-75-92042/1079691701/</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Workday-Lead-Consultant-%28HF%29-75-92042/1079681201/</t>
         </is>
       </c>
       <c r="N460" s="39" t="inlineStr">
@@ -32002,17 +32010,17 @@
       <c r="C461" s="39" t="n"/>
       <c r="D461" s="39" t="inlineStr">
         <is>
-          <t>Consultant Technico-Fonctionnel HR Access Paie (H/F)</t>
+          <t>Workday Talent Lead Consultant</t>
         </is>
       </c>
       <c r="E461" s="39" t="inlineStr">
         <is>
-          <t>HR DNA</t>
+          <t>HR Path</t>
         </is>
       </c>
       <c r="F461" s="39" t="inlineStr">
         <is>
-          <t>free-work</t>
+          <t>jobs.hr-path.com</t>
         </is>
       </c>
       <c r="G461" s="39" t="inlineStr">
@@ -32022,24 +32030,20 @@
       </c>
       <c r="H461" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris La Défense</t>
         </is>
       </c>
       <c r="I461" s="39" t="n"/>
-      <c r="J461" s="39" t="inlineStr">
-        <is>
-          <t>60-65 K€</t>
-        </is>
-      </c>
+      <c r="J461" s="39" t="n"/>
       <c r="K461" s="39" t="n"/>
       <c r="L461" s="39" t="inlineStr">
         <is>
-          <t>Poste HR Access orienté paie ; périmètre SIRH mais outil non maîtrisé.</t>
+          <t>Idem, Workday hors cœur SAP.</t>
         </is>
       </c>
       <c r="M461" s="39" t="inlineStr">
         <is>
-          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-fonctionnel/consultant-technico-fonctionnel-hr-access-paie-h-f-6</t>
+          <t>https://jobs.hr-path.com/job/Paris-La-D%C3%A9fense-Cedex-Workday-Talent-Lead-Consultant-75-92042/1079691701/</t>
         </is>
       </c>
       <c r="N461" s="39" t="inlineStr">
@@ -32047,78 +32051,62 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O461" s="39" t="inlineStr">
-        <is>
-          <t>70-85 K€</t>
-        </is>
-      </c>
+      <c r="O461" s="39" t="n"/>
       <c r="P461" s="39" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
-        </is>
-      </c>
-      <c r="Q461" s="41" t="inlineStr">
-        <is>
-          <t>12/08/2026</t>
-        </is>
-      </c>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="Q461" s="41" t="n"/>
     </row>
     <row r="462" ht="16" customHeight="1">
-      <c r="A462" s="33" t="inlineStr">
-        <is>
-          <t>⭐</t>
+      <c r="A462" s="90" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="B462" s="39" t="n"/>
       <c r="C462" s="39" t="n"/>
       <c r="D462" s="39" t="inlineStr">
         <is>
-          <t>Expert HR ACCESS</t>
+          <t>Consultant Technico-Fonctionnel HR Access Paie (H/F)</t>
         </is>
       </c>
       <c r="E462" s="39" t="inlineStr">
         <is>
-          <t>Client anonyme</t>
+          <t>HR DNA</t>
         </is>
       </c>
       <c r="F462" s="39" t="inlineStr">
         <is>
-          <t>freelance-informatique.fr</t>
+          <t>free-work</t>
         </is>
       </c>
       <c r="G462" s="39" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H462" s="39" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
-        </is>
-      </c>
-      <c r="I462" s="39" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I462" s="39" t="n"/>
       <c r="J462" s="39" t="inlineStr">
         <is>
-          <t>n.c.</t>
-        </is>
-      </c>
-      <c r="K462" s="39" t="inlineStr">
-        <is>
-          <t>3 mois</t>
-        </is>
-      </c>
+          <t>60-65 K€</t>
+        </is>
+      </c>
+      <c r="K462" s="39" t="n"/>
       <c r="L462" s="39" t="inlineStr">
         <is>
-          <t>HR Access — hors du cœur SAP/SF de Gaetan, start 14/07/2026</t>
+          <t>Poste HR Access orienté paie ; périmètre SIRH mais outil non maîtrisé.</t>
         </is>
       </c>
       <c r="M462" s="39" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/mission-expert-hr-access-sur-paris-260702C002</t>
+          <t>https://www.free-work.com/fr/tech-it/job-mission/consultant-fonctionnel/consultant-technico-fonctionnel-hr-access-paie-h-f-6</t>
         </is>
       </c>
       <c r="N462" s="39" t="inlineStr">
@@ -32126,16 +32114,24 @@
           <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
         </is>
       </c>
-      <c r="O462" s="39" t="n"/>
-      <c r="P462" s="39" t="n"/>
+      <c r="O462" s="39" t="inlineStr">
+        <is>
+          <t>70-85 K€</t>
+        </is>
+      </c>
+      <c r="P462" s="39" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
+      </c>
       <c r="Q462" s="41" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
     </row>
     <row r="463" ht="16" customHeight="1">
-      <c r="A463" s="75" t="inlineStr">
+      <c r="A463" s="33" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
@@ -32144,17 +32140,17 @@
       <c r="C463" s="39" t="n"/>
       <c r="D463" s="39" t="inlineStr">
         <is>
-          <t>Intégrateur d'application SIRH</t>
+          <t>Expert HR ACCESS</t>
         </is>
       </c>
       <c r="E463" s="39" t="inlineStr">
         <is>
-          <t>n.c. (Freelance-Informatique)</t>
+          <t>Client anonyme</t>
         </is>
       </c>
       <c r="F463" s="39" t="inlineStr">
         <is>
-          <t>Freelance-Informatique</t>
+          <t>freelance-informatique.fr</t>
         </is>
       </c>
       <c r="G463" s="39" t="inlineStr">
@@ -32164,7 +32160,7 @@
       </c>
       <c r="H463" s="39" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I463" s="39" t="inlineStr">
@@ -32174,34 +32170,30 @@
       </c>
       <c r="J463" s="39" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>n.c.</t>
         </is>
       </c>
       <c r="K463" s="39" t="inlineStr">
         <is>
-          <t>6 mois</t>
+          <t>3 mois</t>
         </is>
       </c>
       <c r="L463" s="39" t="inlineStr">
         <is>
-          <t>Pas remote — Rouen</t>
+          <t>HR Access — hors du cœur SAP/SF de Gaetan, start 14/07/2026</t>
         </is>
       </c>
       <c r="M463" s="39" t="inlineStr">
         <is>
-          <t>https://www.freelance-informatique.fr/mission-sirh-2293</t>
+          <t>https://www.freelance-informatique.fr/mission-expert-hr-access-sur-paris-260702C002</t>
         </is>
       </c>
       <c r="N463" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
-        </is>
-      </c>
-      <c r="O463" s="39" t="inlineStr">
-        <is>
-          <t>650€/j</t>
-        </is>
-      </c>
+          <t>Resume_GaetanFRANCOIS_SIRH.pdf</t>
+        </is>
+      </c>
+      <c r="O463" s="39" t="n"/>
       <c r="P463" s="39" t="n"/>
       <c r="Q463" s="41" t="inlineStr">
         <is>
@@ -32210,7 +32202,79 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="90" t="n"/>
+      <c r="A464" s="75" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="B464" s="39" t="n"/>
+      <c r="C464" s="39" t="n"/>
+      <c r="D464" s="39" t="inlineStr">
+        <is>
+          <t>Intégrateur d'application SIRH</t>
+        </is>
+      </c>
+      <c r="E464" s="39" t="inlineStr">
+        <is>
+          <t>n.c. (Freelance-Informatique)</t>
+        </is>
+      </c>
+      <c r="F464" s="39" t="inlineStr">
+        <is>
+          <t>Freelance-Informatique</t>
+        </is>
+      </c>
+      <c r="G464" s="39" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H464" s="39" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="I464" s="39" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="J464" s="39" t="inlineStr">
+        <is>
+          <t>nc</t>
+        </is>
+      </c>
+      <c r="K464" s="39" t="inlineStr">
+        <is>
+          <t>6 mois</t>
+        </is>
+      </c>
+      <c r="L464" s="39" t="inlineStr">
+        <is>
+          <t>Pas remote — Rouen</t>
+        </is>
+      </c>
+      <c r="M464" s="39" t="inlineStr">
+        <is>
+          <t>https://www.freelance-informatique.fr/mission-sirh-2293</t>
+        </is>
+      </c>
+      <c r="N464" s="39" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_SIRH.html</t>
+        </is>
+      </c>
+      <c r="O464" s="39" t="inlineStr">
+        <is>
+          <t>650€/j</t>
+        </is>
+      </c>
+      <c r="P464" s="39" t="n"/>
+      <c r="Q464" s="41" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="90" t="n"/>
@@ -32268,7 +32332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q296"/>
+  <dimension ref="A1:Q298"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="11.1640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -48957,26 +49021,26 @@
       <c r="Q260" s="41" t="n"/>
     </row>
     <row r="261" ht="16" customHeight="1">
-      <c r="A261" s="90" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
+      <c r="A261" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B261" s="6" t="n"/>
       <c r="C261" s="39" t="n"/>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Senior Customer Success Manager France</t>
+          <t>Senior Technical Account Manager (EMEA)</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>Corcentric</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>jobs.ashbyhq.com</t>
         </is>
       </c>
       <c r="G261" s="6" t="inlineStr">
@@ -48986,28 +49050,24 @@
       </c>
       <c r="H261" s="6" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Angleterre</t>
         </is>
       </c>
       <c r="I261" s="6" t="inlineStr">
         <is>
-          <t>n.p.</t>
-        </is>
-      </c>
-      <c r="J261" s="6" t="inlineStr">
-        <is>
-          <t>n.c.</t>
-        </is>
-      </c>
+          <t>Remote-first</t>
+        </is>
+      </c>
+      <c r="J261" s="6" t="n"/>
       <c r="K261" s="6" t="n"/>
       <c r="L261" s="5" t="inlineStr">
         <is>
-          <t>Procure-to-pay/source-to-pay SaaS, 7+ ans, FR+EN, 15% travel — finance/procurement, hors HR Tech</t>
+          <t>Gestion de compte enterprise a composante technique chez un editeur remote-first. Verifie ouvert par API Ashby le 14/08. Base annoncee en Angleterre : verifier la possibilite de travailler depuis la France.</t>
         </is>
       </c>
       <c r="M261" s="5" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/4428735347</t>
+          <t>https://jobs.ashbyhq.com/docker/de4dce34-7643-4c29-9113-230e7a591195</t>
         </is>
       </c>
       <c r="N261" s="39" t="inlineStr">
@@ -49017,33 +49077,37 @@
       </c>
       <c r="O261" s="39" t="inlineStr">
         <is>
-          <t>80 K€</t>
-        </is>
-      </c>
-      <c r="P261" s="39" t="n"/>
+          <t>80-95 K€</t>
+        </is>
+      </c>
+      <c r="P261" s="39" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
       <c r="Q261" s="41" t="n"/>
     </row>
     <row r="262" ht="16" customHeight="1">
-      <c r="A262" s="90" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
+      <c r="A262" s="103" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="B262" s="6" t="n"/>
       <c r="C262" s="39" t="n"/>
       <c r="D262" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager SaaS Transport</t>
+          <t>Manager, Solutions Engineering - EMEA</t>
         </is>
       </c>
       <c r="E262" s="39" t="inlineStr">
         <is>
-          <t>LITY</t>
+          <t>Vanta</t>
         </is>
       </c>
       <c r="F262" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>jobs.ashbyhq.com</t>
         </is>
       </c>
       <c r="G262" s="39" t="inlineStr">
@@ -49053,37 +49117,37 @@
       </c>
       <c r="H262" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I262" s="39" t="inlineStr">
-        <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J262" s="39" t="inlineStr">
-        <is>
-          <t>55 000 - 60 000 €</t>
-        </is>
-      </c>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="I262" s="39" t="n"/>
+      <c r="J262" s="39" t="n"/>
       <c r="K262" s="39" t="n"/>
       <c r="L262" s="39" t="inlineStr">
         <is>
-          <t>Cabinet LITY recrute pour client SaaS transport. Salaire 55-60K trop bas vs cible 80-95K. À creuser pour identifier l'entreprise finale avant de postuler.</t>
+          <t>Encadrement d'une equipe d'avant-vente technique EMEA : croise le management et le pre-sales. Verifie ouvert par API. Poste londonien, question visa a clarifier comme pour Taulia.</t>
         </is>
       </c>
       <c r="M262" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/customer-success-manager-emplois</t>
+          <t>https://jobs.ashbyhq.com/vanta/2daebe8c-69af-44f3-a81f-38fb17da30a0</t>
         </is>
       </c>
       <c r="N262" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
-        </is>
-      </c>
-      <c r="O262" s="39" t="n"/>
-      <c r="P262" s="39" t="n"/>
+          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O262" s="39" t="inlineStr">
+        <is>
+          <t>95-115 K€</t>
+        </is>
+      </c>
+      <c r="P262" s="39" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
       <c r="Q262" s="41" t="n"/>
     </row>
     <row r="263" ht="32" customHeight="1">
@@ -49094,55 +49158,55 @@
       </c>
       <c r="B263" s="6" t="n"/>
       <c r="C263" s="39" t="n"/>
-      <c r="D263" s="39" t="inlineStr">
-        <is>
-          <t>Customer Success Manager RH H/F</t>
-        </is>
-      </c>
-      <c r="E263" s="39" t="inlineStr">
-        <is>
-          <t>Septeo</t>
-        </is>
-      </c>
-      <c r="F263" s="39" t="inlineStr">
-        <is>
-          <t>careers.septeo.com</t>
-        </is>
-      </c>
-      <c r="G263" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H263" s="39" t="inlineStr">
-        <is>
-          <t>Bordeaux (Mérignac)</t>
-        </is>
-      </c>
-      <c r="I263" s="39" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="J263" s="39" t="inlineStr">
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager France</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>Corcentric</t>
+        </is>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G263" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H263" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I263" s="6" t="inlineStr">
+        <is>
+          <t>n.p.</t>
+        </is>
+      </c>
+      <c r="J263" s="6" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K263" s="39" t="n"/>
-      <c r="L263" s="39" t="inlineStr">
-        <is>
-          <t>Septeo = éditeur SaaS RH. CSM avec compréhension enjeux RH/SIRH, pilotage portefeuille clients, upsell. Publié ~11/06/2026. Secteur HR SaaS pertinent mais pas remote = frein depuis Biarritz. Bordeaux géographiquement accessible.</t>
-        </is>
-      </c>
-      <c r="M263" s="39" t="inlineStr">
-        <is>
-          <t>https://careers.septeo.com/j/customer-success-manager-h-f-6836ecba5994894addc2dc4b</t>
+      <c r="K263" s="6" t="n"/>
+      <c r="L263" s="5" t="inlineStr">
+        <is>
+          <t>Procure-to-pay/source-to-pay SaaS, 7+ ans, FR+EN, 15% travel — finance/procurement, hors HR Tech</t>
+        </is>
+      </c>
+      <c r="M263" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/4428735347</t>
         </is>
       </c>
       <c r="N263" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
         </is>
       </c>
       <c r="O263" s="39" t="inlineStr">
@@ -49161,50 +49225,50 @@
       </c>
       <c r="B264" s="6" t="n"/>
       <c r="C264" s="39" t="n"/>
-      <c r="D264" s="5" t="inlineStr">
-        <is>
-          <t>Customer Success Manager Key Accounts H/F/X</t>
-        </is>
-      </c>
-      <c r="E264" s="5" t="inlineStr">
-        <is>
-          <t>Partoo</t>
-        </is>
-      </c>
-      <c r="F264" s="5" t="inlineStr">
-        <is>
-          <t>Welcome to the Jungle</t>
-        </is>
-      </c>
-      <c r="G264" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H264" s="6" t="inlineStr">
+      <c r="D264" s="39" t="inlineStr">
+        <is>
+          <t>Customer Success Manager SaaS Transport</t>
+        </is>
+      </c>
+      <c r="E264" s="39" t="inlineStr">
+        <is>
+          <t>LITY</t>
+        </is>
+      </c>
+      <c r="F264" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G264" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H264" s="39" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I264" s="6" t="inlineStr">
-        <is>
-          <t>Hybride (6 sem/an remote)</t>
-        </is>
-      </c>
-      <c r="J264" s="6" t="inlineStr">
-        <is>
-          <t>44 000 - 59 000 €</t>
-        </is>
-      </c>
-      <c r="K264" s="6" t="n"/>
-      <c r="L264" s="5" t="inlineStr">
-        <is>
-          <t>Partoo = SaaS présence digitale enseignes. ~15 comptes Key Accounts (+1M€ ARR), relation C-level, anti-churn. Pas HR Tech. Salaire sous cible (44-59K vs 80-95K). Peu de remote = frein.</t>
-        </is>
-      </c>
-      <c r="M264" s="5" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/fr/companies/partoo/jobs/customer-success-manager-key-accounts-cdi-paris-h-f-x_paris</t>
+      <c r="I264" s="39" t="inlineStr">
+        <is>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J264" s="39" t="inlineStr">
+        <is>
+          <t>55 000 - 60 000 €</t>
+        </is>
+      </c>
+      <c r="K264" s="39" t="n"/>
+      <c r="L264" s="39" t="inlineStr">
+        <is>
+          <t>Cabinet LITY recrute pour client SaaS transport. Salaire 55-60K trop bas vs cible 80-95K. À creuser pour identifier l'entreprise finale avant de postuler.</t>
+        </is>
+      </c>
+      <c r="M264" s="39" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/customer-success-manager-emplois</t>
         </is>
       </c>
       <c r="N264" s="39" t="inlineStr">
@@ -49214,7 +49278,7 @@
       </c>
       <c r="O264" s="39" t="n"/>
       <c r="P264" s="39" t="n"/>
-      <c r="Q264" s="39" t="n"/>
+      <c r="Q264" s="41" t="n"/>
     </row>
     <row r="265" ht="48" customHeight="1">
       <c r="A265" s="90" t="inlineStr">
@@ -49222,21 +49286,21 @@
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B265" s="39" t="n"/>
+      <c r="B265" s="6" t="n"/>
       <c r="C265" s="39" t="n"/>
       <c r="D265" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager SaaS QVCT &amp; RSE</t>
+          <t>Customer Success Manager RH H/F</t>
         </is>
       </c>
       <c r="E265" s="39" t="inlineStr">
         <is>
-          <t>Windoo</t>
+          <t>Septeo</t>
         </is>
       </c>
       <c r="F265" s="39" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>careers.septeo.com</t>
         </is>
       </c>
       <c r="G265" s="39" t="inlineStr">
@@ -49246,12 +49310,12 @@
       </c>
       <c r="H265" s="39" t="inlineStr">
         <is>
-          <t>Paris (remote étendu)</t>
+          <t>Bordeaux (Mérignac)</t>
         </is>
       </c>
       <c r="I265" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="J265" s="39" t="inlineStr">
@@ -49262,12 +49326,12 @@
       <c r="K265" s="39" t="n"/>
       <c r="L265" s="39" t="inlineStr">
         <is>
-          <t>Windoo = SaaS QVCT/RSE/formation. Remote étendu, début août 2026, 3+ ans requis. Adjacent RH. À vérifier si remote total possible depuis Biarritz.</t>
+          <t>Septeo = éditeur SaaS RH. CSM avec compréhension enjeux RH/SIRH, pilotage portefeuille clients, upsell. Publié ~11/06/2026. Secteur HR SaaS pertinent mais pas remote = frein depuis Biarritz. Bordeaux géographiquement accessible.</t>
         </is>
       </c>
       <c r="M265" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/windoo/jobs/cdi-customer-success-manager-saas-formation-qvct-rse-h-f_paris</t>
+          <t>https://careers.septeo.com/j/customer-success-manager-h-f-6836ecba5994894addc2dc4b</t>
         </is>
       </c>
       <c r="N265" s="39" t="inlineStr">
@@ -49277,7 +49341,7 @@
       </c>
       <c r="O265" s="39" t="inlineStr">
         <is>
-          <t>78 K€</t>
+          <t>80 K€</t>
         </is>
       </c>
       <c r="P265" s="39" t="n"/>
@@ -49289,52 +49353,52 @@
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="B266" s="39" t="n"/>
+      <c r="B266" s="6" t="n"/>
       <c r="C266" s="39" t="n"/>
-      <c r="D266" s="39" t="inlineStr">
-        <is>
-          <t>Customer Success SIRH Grands Comptes</t>
-        </is>
-      </c>
-      <c r="E266" s="39" t="inlineStr">
-        <is>
-          <t>Lucca</t>
-        </is>
-      </c>
-      <c r="F266" s="39" t="inlineStr">
-        <is>
-          <t>Lucca Careers / Welcome to the Jungle</t>
-        </is>
-      </c>
-      <c r="G266" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H266" s="39" t="inlineStr">
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>Customer Success Manager Key Accounts H/F/X</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="inlineStr">
+        <is>
+          <t>Partoo</t>
+        </is>
+      </c>
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H266" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I266" s="39" t="inlineStr">
-        <is>
-          <t>Hybride (2j/sem remote)</t>
-        </is>
-      </c>
-      <c r="J266" s="39" t="inlineStr">
-        <is>
-          <t>45 000 - 55 000 €</t>
-        </is>
-      </c>
-      <c r="K266" s="39" t="n"/>
-      <c r="L266" s="39" t="inlineStr">
-        <is>
-          <t>Lucca = SIRH français (8 700 clients). CSM SIRH Grands Comptes (ARR &gt;14k€, +250 salariés). Excellent fit profil SIRH. Frein : salaire très en dessous cible (45-55K vs 80-95K) et hybride Paris 2j remote seulement. Publié 19/06/2026.</t>
-        </is>
-      </c>
-      <c r="M266" s="39" t="inlineStr">
-        <is>
-          <t>https://jobs.world.luccasoftware.com/lucca/customer-success-sirh-grands-comptes-8d12e285-9f5c-4dcd-ba4c-661c80abe25c</t>
+      <c r="I266" s="6" t="inlineStr">
+        <is>
+          <t>Hybride (6 sem/an remote)</t>
+        </is>
+      </c>
+      <c r="J266" s="6" t="inlineStr">
+        <is>
+          <t>44 000 - 59 000 €</t>
+        </is>
+      </c>
+      <c r="K266" s="6" t="n"/>
+      <c r="L266" s="5" t="inlineStr">
+        <is>
+          <t>Partoo = SaaS présence digitale enseignes. ~15 comptes Key Accounts (+1M€ ARR), relation C-level, anti-churn. Pas HR Tech. Salaire sous cible (44-59K vs 80-95K). Peu de remote = frein.</t>
+        </is>
+      </c>
+      <c r="M266" s="5" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/partoo/jobs/customer-success-manager-key-accounts-cdi-paris-h-f-x_paris</t>
         </is>
       </c>
       <c r="N266" s="39" t="inlineStr">
@@ -49344,11 +49408,7 @@
       </c>
       <c r="O266" s="39" t="n"/>
       <c r="P266" s="39" t="n"/>
-      <c r="Q266" s="41" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
+      <c r="Q266" s="39" t="n"/>
     </row>
     <row r="267" ht="16" customHeight="1">
       <c r="A267" s="90" t="inlineStr">
@@ -49358,50 +49418,50 @@
       </c>
       <c r="B267" s="39" t="n"/>
       <c r="C267" s="39" t="n"/>
-      <c r="D267" s="5" t="inlineStr">
-        <is>
-          <t>Senior Customer Success Manager</t>
-        </is>
-      </c>
-      <c r="E267" s="5" t="inlineStr">
-        <is>
-          <t>Teach Up</t>
-        </is>
-      </c>
-      <c r="F267" s="5" t="inlineStr">
+      <c r="D267" s="39" t="inlineStr">
+        <is>
+          <t>Customer Success Manager SaaS QVCT &amp; RSE</t>
+        </is>
+      </c>
+      <c r="E267" s="39" t="inlineStr">
+        <is>
+          <t>Windoo</t>
+        </is>
+      </c>
+      <c r="F267" s="39" t="inlineStr">
         <is>
           <t>Welcome to the Jungle</t>
         </is>
       </c>
-      <c r="G267" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H267" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I267" s="6" t="inlineStr">
-        <is>
-          <t>Hybride (2j bureau/sem min)</t>
-        </is>
-      </c>
-      <c r="J267" s="6" t="inlineStr">
+      <c r="G267" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H267" s="39" t="inlineStr">
+        <is>
+          <t>Paris (remote étendu)</t>
+        </is>
+      </c>
+      <c r="I267" s="39" t="inlineStr">
+        <is>
+          <t>Hybride</t>
+        </is>
+      </c>
+      <c r="J267" s="39" t="inlineStr">
         <is>
           <t>n.c.</t>
         </is>
       </c>
-      <c r="K267" s="6" t="n"/>
-      <c r="L267" s="5" t="inlineStr">
-        <is>
-          <t>Teach Up = LMS IA adaptatif pour formation entreprise. 4+ ans CSM B2B SaaS exigés. Secteur adjacent HR Tech formation. Gaëtan a expérience formation SAP/transfert de connaissances. Hybride Paris = contrainte.</t>
-        </is>
-      </c>
-      <c r="M267" s="5" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/fr/companies/teach-up/jobs/senior-customer-success-manager-csm-a-paris_paris</t>
+      <c r="K267" s="39" t="n"/>
+      <c r="L267" s="39" t="inlineStr">
+        <is>
+          <t>Windoo = SaaS QVCT/RSE/formation. Remote étendu, début août 2026, 3+ ans requis. Adjacent RH. À vérifier si remote total possible depuis Biarritz.</t>
+        </is>
+      </c>
+      <c r="M267" s="39" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/windoo/jobs/cdi-customer-success-manager-saas-formation-qvct-rse-h-f_paris</t>
         </is>
       </c>
       <c r="N267" s="39" t="inlineStr">
@@ -49411,7 +49471,7 @@
       </c>
       <c r="O267" s="39" t="inlineStr">
         <is>
-          <t>82 K€</t>
+          <t>78 K€</t>
         </is>
       </c>
       <c r="P267" s="39" t="n"/>
@@ -49427,17 +49487,17 @@
       <c r="C268" s="39" t="n"/>
       <c r="D268" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager Senior EMEA</t>
+          <t>Customer Success SIRH Grands Comptes</t>
         </is>
       </c>
       <c r="E268" s="39" t="inlineStr">
         <is>
-          <t>DataDome</t>
+          <t>Lucca</t>
         </is>
       </c>
       <c r="F268" s="39" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Lucca Careers / Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G268" s="39" t="inlineStr">
@@ -49452,27 +49512,35 @@
       </c>
       <c r="I268" s="39" t="inlineStr">
         <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="J268" s="39" t="n"/>
+          <t>Hybride (2j/sem remote)</t>
+        </is>
+      </c>
+      <c r="J268" s="39" t="inlineStr">
+        <is>
+          <t>45 000 - 55 000 €</t>
+        </is>
+      </c>
       <c r="K268" s="39" t="n"/>
       <c r="L268" s="39" t="inlineStr">
         <is>
-          <t>Cybersécurité SaaS (protection bot/fraude), comptes EMEA enterprise. Bon fit secteur — mais poste sur site Paris, incompatible full remote Biarritz.</t>
+          <t>Lucca = SIRH français (8 700 clients). CSM SIRH Grands Comptes (ARR &gt;14k€, +250 salariés). Excellent fit profil SIRH. Frein : salaire très en dessous cible (45-55K vs 80-95K) et hybride Paris 2j remote seulement. Publié 19/06/2026.</t>
         </is>
       </c>
       <c r="M268" s="39" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/ddome</t>
-        </is>
-      </c>
-      <c r="N268" s="39" t="n"/>
+          <t>https://jobs.world.luccasoftware.com/lucca/customer-success-sirh-grands-comptes-8d12e285-9f5c-4dcd-ba4c-661c80abe25c</t>
+        </is>
+      </c>
+      <c r="N268" s="39" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+        </is>
+      </c>
       <c r="O268" s="39" t="n"/>
       <c r="P268" s="39" t="n"/>
       <c r="Q268" s="41" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
     </row>
@@ -49484,52 +49552,64 @@
       </c>
       <c r="B269" s="39" t="n"/>
       <c r="C269" s="39" t="n"/>
-      <c r="D269" s="39" t="inlineStr">
-        <is>
-          <t>Customer Success Manager Mid Market</t>
-        </is>
-      </c>
-      <c r="E269" s="39" t="inlineStr">
-        <is>
-          <t>Modjo</t>
-        </is>
-      </c>
-      <c r="F269" s="39" t="inlineStr">
-        <is>
-          <t>WelcomeToTheJungle</t>
-        </is>
-      </c>
-      <c r="G269" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H269" s="39" t="inlineStr">
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>Teach Up</t>
+        </is>
+      </c>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>Welcome to the Jungle</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H269" s="6" t="inlineStr">
         <is>
           <t>Paris</t>
         </is>
       </c>
-      <c r="I269" s="39" t="inlineStr">
-        <is>
-          <t>Partiel</t>
-        </is>
-      </c>
-      <c r="J269" s="39" t="n"/>
-      <c r="K269" s="39" t="n"/>
-      <c r="L269" s="39" t="inlineStr">
-        <is>
-          <t>IA pour équipes commerciales, portefeuille mid-market (15-60k€ ARR). Gaëtan surqualifié. Startup IA en croissance si pipeline faible.</t>
-        </is>
-      </c>
-      <c r="M269" s="39" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/fr/companies/modjo/jobs/customer-success-manager-mid-market-f-m_paris</t>
-        </is>
-      </c>
-      <c r="N269" s="39" t="n"/>
-      <c r="O269" s="39" t="n"/>
+      <c r="I269" s="6" t="inlineStr">
+        <is>
+          <t>Hybride (2j bureau/sem min)</t>
+        </is>
+      </c>
+      <c r="J269" s="6" t="inlineStr">
+        <is>
+          <t>n.c.</t>
+        </is>
+      </c>
+      <c r="K269" s="6" t="n"/>
+      <c r="L269" s="5" t="inlineStr">
+        <is>
+          <t>Teach Up = LMS IA adaptatif pour formation entreprise. 4+ ans CSM B2B SaaS exigés. Secteur adjacent HR Tech formation. Gaëtan a expérience formation SAP/transfert de connaissances. Hybride Paris = contrainte.</t>
+        </is>
+      </c>
+      <c r="M269" s="5" t="inlineStr">
+        <is>
+          <t>https://www.welcometothejungle.com/fr/companies/teach-up/jobs/senior-customer-success-manager-csm-a-paris_paris</t>
+        </is>
+      </c>
+      <c r="N269" s="39" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="O269" s="39" t="inlineStr">
+        <is>
+          <t>82 K€</t>
+        </is>
+      </c>
       <c r="P269" s="39" t="n"/>
-      <c r="Q269" s="39" t="n"/>
+      <c r="Q269" s="41" t="n"/>
     </row>
     <row r="270" ht="32" customHeight="1">
       <c r="A270" s="90" t="inlineStr">
@@ -49541,17 +49621,17 @@
       <c r="C270" s="39" t="n"/>
       <c r="D270" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager Expansion Mid-Market</t>
+          <t>Customer Success Manager Senior EMEA</t>
         </is>
       </c>
       <c r="E270" s="39" t="inlineStr">
         <is>
-          <t>Riot Security</t>
+          <t>DataDome</t>
         </is>
       </c>
       <c r="F270" s="39" t="inlineStr">
         <is>
-          <t>Lever</t>
+          <t>Greenhouse</t>
         </is>
       </c>
       <c r="G270" s="39" t="inlineStr">
@@ -49566,19 +49646,19 @@
       </c>
       <c r="I270" s="39" t="inlineStr">
         <is>
-          <t>Partiel</t>
+          <t>Non</t>
         </is>
       </c>
       <c r="J270" s="39" t="n"/>
       <c r="K270" s="39" t="n"/>
       <c r="L270" s="39" t="inlineStr">
         <is>
-          <t>Portefeuille ~120 comptes mid-market, rétention/expansion. Plus opérationnel que Enterprise. Même contrainte Paris.</t>
+          <t>Cybersécurité SaaS (protection bot/fraude), comptes EMEA enterprise. Bon fit secteur — mais poste sur site Paris, incompatible full remote Biarritz.</t>
         </is>
       </c>
       <c r="M270" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/tryriot/5fa84b70-04be-4b8f-99fe-338a276a2b7e</t>
+          <t>https://job-boards.greenhouse.io/ddome</t>
         </is>
       </c>
       <c r="N270" s="39" t="n"/>
@@ -49586,7 +49666,7 @@
       <c r="P270" s="39" t="n"/>
       <c r="Q270" s="41" t="inlineStr">
         <is>
-          <t>21/05/2024</t>
+          <t>20/02/2026</t>
         </is>
       </c>
     </row>
@@ -49600,17 +49680,17 @@
       <c r="C271" s="39" t="n"/>
       <c r="D271" s="39" t="inlineStr">
         <is>
-          <t>Senior Customer Success Manager – France</t>
+          <t>Customer Success Manager Mid Market</t>
         </is>
       </c>
       <c r="E271" s="39" t="inlineStr">
         <is>
-          <t>Acast</t>
+          <t>Modjo</t>
         </is>
       </c>
       <c r="F271" s="39" t="inlineStr">
         <is>
-          <t>Lever.co</t>
+          <t>WelcomeToTheJungle</t>
         </is>
       </c>
       <c r="G271" s="39" t="inlineStr">
@@ -49620,40 +49700,28 @@
       </c>
       <c r="H271" s="39" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I271" s="39" t="inlineStr">
         <is>
-          <t>À confirmer</t>
-        </is>
-      </c>
-      <c r="J271" s="39" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J271" s="39" t="n"/>
       <c r="K271" s="39" t="n"/>
       <c r="L271" s="39" t="inlineStr">
         <is>
-          <t>Plateforme podcast/audio. Gestion onboarding et rétention des podcasters partenaires France. Profil moins technique mais moins senior que cible Gaëtan.</t>
+          <t>IA pour équipes commerciales, portefeuille mid-market (15-60k€ ARR). Gaëtan surqualifié. Startup IA en croissance si pipeline faible.</t>
         </is>
       </c>
       <c r="M271" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/acast/92df3678-627e-4123-ae60-d098dd210afb</t>
-        </is>
-      </c>
-      <c r="N271" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS</t>
-        </is>
-      </c>
-      <c r="O271" s="39" t="inlineStr">
-        <is>
-          <t>80-90K€</t>
-        </is>
-      </c>
+          <t>https://www.welcometothejungle.com/fr/companies/modjo/jobs/customer-success-manager-mid-market-f-m_paris</t>
+        </is>
+      </c>
+      <c r="N271" s="39" t="n"/>
+      <c r="O271" s="39" t="n"/>
       <c r="P271" s="39" t="n"/>
       <c r="Q271" s="39" t="n"/>
     </row>
@@ -49667,17 +49735,17 @@
       <c r="C272" s="39" t="n"/>
       <c r="D272" s="39" t="inlineStr">
         <is>
-          <t>Enterprise Customer Success Manager</t>
+          <t>Customer Success Manager Expansion Mid-Market</t>
         </is>
       </c>
       <c r="E272" s="39" t="inlineStr">
         <is>
-          <t>iAdvize</t>
+          <t>Riot Security</t>
         </is>
       </c>
       <c r="F272" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Lever</t>
         </is>
       </c>
       <c r="G272" s="39" t="inlineStr">
@@ -49687,42 +49755,34 @@
       </c>
       <c r="H272" s="39" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I272" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
-        </is>
-      </c>
-      <c r="J272" s="39" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
+          <t>Partiel</t>
+        </is>
+      </c>
+      <c r="J272" s="39" t="n"/>
       <c r="K272" s="39" t="n"/>
       <c r="L272" s="39" t="inlineStr">
         <is>
-          <t>IA conversationnelle B2B (chatbot/live chat e-commerce). Profil enterprise. Nantes — non 100% remote à confirmer. Publié il y a 2 mois (peut être pourvue).</t>
+          <t>Portefeuille ~120 comptes mid-market, rétention/expansion. Plus opérationnel que Enterprise. Même contrainte Paris.</t>
         </is>
       </c>
       <c r="M272" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/customer-success-emplois-france</t>
-        </is>
-      </c>
-      <c r="N272" s="39" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS</t>
-        </is>
-      </c>
-      <c r="O272" s="39" t="inlineStr">
-        <is>
-          <t>80-90K€</t>
-        </is>
-      </c>
+          <t>https://jobs.lever.co/tryriot/5fa84b70-04be-4b8f-99fe-338a276a2b7e</t>
+        </is>
+      </c>
+      <c r="N272" s="39" t="n"/>
+      <c r="O272" s="39" t="n"/>
       <c r="P272" s="39" t="n"/>
-      <c r="Q272" s="39" t="n"/>
+      <c r="Q272" s="41" t="inlineStr">
+        <is>
+          <t>21/05/2024</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="32" customHeight="1">
       <c r="A273" s="90" t="inlineStr">
@@ -49732,50 +49792,50 @@
       </c>
       <c r="B273" s="39" t="n"/>
       <c r="C273" s="39" t="n"/>
-      <c r="D273" s="5" t="inlineStr">
-        <is>
-          <t>Customer Success Manager – Enterprise</t>
-        </is>
-      </c>
-      <c r="E273" s="5" t="inlineStr">
-        <is>
-          <t>Bloomflow</t>
-        </is>
-      </c>
-      <c r="F273" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="G273" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H273" s="6" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I273" s="6" t="inlineStr">
+      <c r="D273" s="39" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Manager – France</t>
+        </is>
+      </c>
+      <c r="E273" s="39" t="inlineStr">
+        <is>
+          <t>Acast</t>
+        </is>
+      </c>
+      <c r="F273" s="39" t="inlineStr">
+        <is>
+          <t>Lever.co</t>
+        </is>
+      </c>
+      <c r="G273" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H273" s="39" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I273" s="39" t="inlineStr">
         <is>
           <t>À confirmer</t>
         </is>
       </c>
-      <c r="J273" s="6" t="inlineStr">
+      <c r="J273" s="39" t="inlineStr">
         <is>
           <t>N/C</t>
         </is>
       </c>
-      <c r="K273" s="6" t="n"/>
-      <c r="L273" s="5" t="inlineStr">
-        <is>
-          <t>Startup innovation management. Publié il y a 2 semaines. Peu de détails disponibles — vérifier directement sur LinkedIn.</t>
-        </is>
-      </c>
-      <c r="M273" s="5" t="inlineStr">
-        <is>
-          <t>https://fr.linkedin.com/jobs/customer-success-manager-emplois</t>
+      <c r="K273" s="39" t="n"/>
+      <c r="L273" s="39" t="inlineStr">
+        <is>
+          <t>Plateforme podcast/audio. Gestion onboarding et rétention des podcasters partenaires France. Profil moins technique mais moins senior que cible Gaëtan.</t>
+        </is>
+      </c>
+      <c r="M273" s="39" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/acast/92df3678-627e-4123-ae60-d098dd210afb</t>
         </is>
       </c>
       <c r="N273" s="39" t="inlineStr">
@@ -49801,17 +49861,17 @@
       <c r="C274" s="39" t="n"/>
       <c r="D274" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager (Automated Touch)</t>
+          <t>Enterprise Customer Success Manager</t>
         </is>
       </c>
       <c r="E274" s="39" t="inlineStr">
         <is>
-          <t>Livestorm</t>
+          <t>iAdvize</t>
         </is>
       </c>
       <c r="F274" s="39" t="inlineStr">
         <is>
-          <t>Livestorm Jobs</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G274" s="39" t="inlineStr">
@@ -49821,12 +49881,12 @@
       </c>
       <c r="H274" s="39" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="I274" s="39" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J274" s="39" t="inlineStr">
@@ -49837,12 +49897,12 @@
       <c r="K274" s="39" t="n"/>
       <c r="L274" s="39" t="inlineStr">
         <is>
-          <t>2e poste Livestorm — profil scale/automation (tech-touch), moins senior. Mentionné car 100% remote France. Moins prioritaire que le poste EMEA Enterprise Livestorm.</t>
+          <t>IA conversationnelle B2B (chatbot/live chat e-commerce). Profil enterprise. Nantes — non 100% remote à confirmer. Publié il y a 2 mois (peut être pourvue).</t>
         </is>
       </c>
       <c r="M274" s="39" t="inlineStr">
         <is>
-          <t>https://jobs.livestorm.co/o/customer-success-manager-automated-touch</t>
+          <t>https://fr.linkedin.com/jobs/customer-success-emplois-france</t>
         </is>
       </c>
       <c r="N274" s="39" t="inlineStr">
@@ -49852,7 +49912,7 @@
       </c>
       <c r="O274" s="39" t="inlineStr">
         <is>
-          <t>75-85K€</t>
+          <t>80-90K€</t>
         </is>
       </c>
       <c r="P274" s="39" t="n"/>
@@ -49866,50 +49926,50 @@
       </c>
       <c r="B275" s="39" t="n"/>
       <c r="C275" s="39" t="n"/>
-      <c r="D275" s="39" t="inlineStr">
-        <is>
-          <t>Customer Success Manager – SaaS (Worldwide Remote)</t>
-        </is>
-      </c>
-      <c r="E275" s="39" t="inlineStr">
-        <is>
-          <t>n.c. (via Goodrecruiter)</t>
-        </is>
-      </c>
-      <c r="F275" s="39" t="inlineStr">
-        <is>
-          <t>Remote Rocketship / Goodrecruiter</t>
-        </is>
-      </c>
-      <c r="G275" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H275" s="39" t="inlineStr">
-        <is>
-          <t>Remote (monde)</t>
-        </is>
-      </c>
-      <c r="I275" s="39" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J275" s="39" t="inlineStr">
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>Customer Success Manager – Enterprise</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>Bloomflow</t>
+        </is>
+      </c>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G275" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H275" s="6" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I275" s="6" t="inlineStr">
+        <is>
+          <t>À confirmer</t>
+        </is>
+      </c>
+      <c r="J275" s="6" t="inlineStr">
         <is>
           <t>N/C</t>
         </is>
       </c>
-      <c r="K275" s="39" t="n"/>
-      <c r="L275" s="39" t="inlineStr">
-        <is>
-          <t>Cabinet recrutement Goodrecruiter — entreprise cliente non révélée. SaaS worldwide remote. À identifier avant de postuler.</t>
-        </is>
-      </c>
-      <c r="M275" s="39" t="inlineStr">
-        <is>
-          <t>https://www.remoterocketship.com/company/goodrecruiter-eu/jobs/customer-success-manager-saas-worldwide-remote/</t>
+      <c r="K275" s="6" t="n"/>
+      <c r="L275" s="5" t="inlineStr">
+        <is>
+          <t>Startup innovation management. Publié il y a 2 semaines. Peu de détails disponibles — vérifier directement sur LinkedIn.</t>
+        </is>
+      </c>
+      <c r="M275" s="5" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/customer-success-manager-emplois</t>
         </is>
       </c>
       <c r="N275" s="39" t="inlineStr">
@@ -49919,7 +49979,7 @@
       </c>
       <c r="O275" s="39" t="inlineStr">
         <is>
-          <t>80-95K€</t>
+          <t>80-90K€</t>
         </is>
       </c>
       <c r="P275" s="39" t="n"/>
@@ -49933,50 +49993,50 @@
       </c>
       <c r="B276" s="39" t="n"/>
       <c r="C276" s="39" t="n"/>
-      <c r="D276" s="5" t="inlineStr">
-        <is>
-          <t>Customer Success Manager EMEA Pooled EU</t>
-        </is>
-      </c>
-      <c r="E276" s="5" t="inlineStr">
-        <is>
-          <t>PandaDoc</t>
-        </is>
-      </c>
-      <c r="F276" s="5" t="inlineStr">
-        <is>
-          <t>PandaDoc Careers</t>
-        </is>
-      </c>
-      <c r="G276" s="6" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H276" s="6" t="inlineStr">
-        <is>
-          <t>Remote (Europe)</t>
-        </is>
-      </c>
-      <c r="I276" s="6" t="inlineStr">
+      <c r="D276" s="39" t="inlineStr">
+        <is>
+          <t>Customer Success Manager (Automated Touch)</t>
+        </is>
+      </c>
+      <c r="E276" s="39" t="inlineStr">
+        <is>
+          <t>Livestorm</t>
+        </is>
+      </c>
+      <c r="F276" s="39" t="inlineStr">
+        <is>
+          <t>Livestorm Jobs</t>
+        </is>
+      </c>
+      <c r="G276" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H276" s="39" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I276" s="39" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J276" s="6" t="inlineStr">
+      <c r="J276" s="39" t="inlineStr">
         <is>
           <t>N/C</t>
         </is>
       </c>
-      <c r="K276" s="6" t="n"/>
-      <c r="L276" s="5" t="inlineStr">
-        <is>
-          <t>2e poste PandaDoc EU (pooled, moins ciblé que French-speaking). 100% remote Europe. Moins prioritaire.</t>
-        </is>
-      </c>
-      <c r="M276" s="5" t="inlineStr">
-        <is>
-          <t>https://www.pandadoc.com/careers/customer-success-manager-pooled-eu/</t>
+      <c r="K276" s="39" t="n"/>
+      <c r="L276" s="39" t="inlineStr">
+        <is>
+          <t>2e poste Livestorm — profil scale/automation (tech-touch), moins senior. Mentionné car 100% remote France. Moins prioritaire que le poste EMEA Enterprise Livestorm.</t>
+        </is>
+      </c>
+      <c r="M276" s="39" t="inlineStr">
+        <is>
+          <t>https://jobs.livestorm.co/o/customer-success-manager-automated-touch</t>
         </is>
       </c>
       <c r="N276" s="39" t="inlineStr">
@@ -49986,7 +50046,7 @@
       </c>
       <c r="O276" s="39" t="inlineStr">
         <is>
-          <t>80-90K€</t>
+          <t>75-85K€</t>
         </is>
       </c>
       <c r="P276" s="39" t="n"/>
@@ -50002,17 +50062,17 @@
       <c r="C277" s="39" t="n"/>
       <c r="D277" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager SaaS B2B</t>
+          <t>Customer Success Manager – SaaS (Worldwide Remote)</t>
         </is>
       </c>
       <c r="E277" s="39" t="inlineStr">
         <is>
-          <t>Padam Mobility</t>
+          <t>n.c. (via Goodrecruiter)</t>
         </is>
       </c>
       <c r="F277" s="39" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Remote Rocketship / Goodrecruiter</t>
         </is>
       </c>
       <c r="G277" s="39" t="inlineStr">
@@ -50022,12 +50082,12 @@
       </c>
       <c r="H277" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote (monde)</t>
         </is>
       </c>
       <c r="I277" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J277" s="39" t="inlineStr">
@@ -50038,12 +50098,12 @@
       <c r="K277" s="39" t="n"/>
       <c r="L277" s="39" t="inlineStr">
         <is>
-          <t>SaaS IA transport à la demande (investisseur Siemens Mobility), clients collectivités. Angle IA + mobilité + secteur public. Paris hybride. Profil PM + client B2B.</t>
+          <t>Cabinet recrutement Goodrecruiter — entreprise cliente non révélée. SaaS worldwide remote. À identifier avant de postuler.</t>
         </is>
       </c>
       <c r="M277" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/padam/jobs/customer-success-manager-saas-b2b_paris</t>
+          <t>https://www.remoterocketship.com/company/goodrecruiter-eu/jobs/customer-success-manager-saas-worldwide-remote/</t>
         </is>
       </c>
       <c r="N277" s="39" t="inlineStr">
@@ -50053,7 +50113,7 @@
       </c>
       <c r="O277" s="39" t="inlineStr">
         <is>
-          <t>75-85K€</t>
+          <t>80-95K€</t>
         </is>
       </c>
       <c r="P277" s="39" t="n"/>
@@ -50067,56 +50127,60 @@
       </c>
       <c r="B278" s="39" t="n"/>
       <c r="C278" s="39" t="n"/>
-      <c r="D278" s="39" t="inlineStr">
-        <is>
-          <t>Customer Success Manager Freelance</t>
-        </is>
-      </c>
-      <c r="E278" s="39" t="inlineStr">
-        <is>
-          <t>Ecair</t>
-        </is>
-      </c>
-      <c r="F278" s="39" t="inlineStr">
-        <is>
-          <t>Welcome to the Jungle</t>
-        </is>
-      </c>
-      <c r="G278" s="39" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-      <c r="H278" s="39" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I278" s="39" t="inlineStr">
-        <is>
-          <t>nc</t>
-        </is>
-      </c>
-      <c r="J278" s="39" t="inlineStr">
-        <is>
-          <t>nc</t>
-        </is>
-      </c>
-      <c r="K278" s="39" t="n"/>
-      <c r="L278" s="39" t="n"/>
-      <c r="M278" s="39" t="inlineStr">
-        <is>
-          <t>https://www.welcometothejungle.com/fr/companies/ecair/jobs/customer-success-manager-freelance_paris</t>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>Customer Success Manager EMEA Pooled EU</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>PandaDoc</t>
+        </is>
+      </c>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>PandaDoc Careers</t>
+        </is>
+      </c>
+      <c r="G278" s="6" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H278" s="6" t="inlineStr">
+        <is>
+          <t>Remote (Europe)</t>
+        </is>
+      </c>
+      <c r="I278" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J278" s="6" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K278" s="6" t="n"/>
+      <c r="L278" s="5" t="inlineStr">
+        <is>
+          <t>2e poste PandaDoc EU (pooled, moins ciblé que French-speaking). 100% remote Europe. Moins prioritaire.</t>
+        </is>
+      </c>
+      <c r="M278" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pandadoc.com/careers/customer-success-manager-pooled-eu/</t>
         </is>
       </c>
       <c r="N278" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
+          <t>Resume_GaetanFRANCOIS</t>
         </is>
       </c>
       <c r="O278" s="39" t="inlineStr">
         <is>
-          <t>650€/j</t>
+          <t>80-90K€</t>
         </is>
       </c>
       <c r="P278" s="39" t="n"/>
@@ -50132,17 +50196,17 @@
       <c r="C279" s="39" t="n"/>
       <c r="D279" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager France</t>
+          <t>Customer Success Manager SaaS B2B</t>
         </is>
       </c>
       <c r="E279" s="39" t="inlineStr">
         <is>
-          <t>Peripass</t>
+          <t>Padam Mobility</t>
         </is>
       </c>
       <c r="F279" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G279" s="39" t="inlineStr">
@@ -50157,33 +50221,33 @@
       </c>
       <c r="I279" s="39" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J279" s="39" t="inlineStr">
         <is>
-          <t>nc</t>
+          <t>N/C</t>
         </is>
       </c>
       <c r="K279" s="39" t="n"/>
       <c r="L279" s="39" t="inlineStr">
         <is>
-          <t>Posté il y a 3 jours</t>
+          <t>SaaS IA transport à la demande (investisseur Siemens Mobility), clients collectivités. Angle IA + mobilité + secteur public. Paris hybride. Profil PM + client B2B.</t>
         </is>
       </c>
       <c r="M279" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-france-at-peripass-4436711714</t>
+          <t>https://www.welcometothejungle.com/fr/companies/padam/jobs/customer-success-manager-saas-b2b_paris</t>
         </is>
       </c>
       <c r="N279" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.html</t>
+          <t>Resume_GaetanFRANCOIS</t>
         </is>
       </c>
       <c r="O279" s="39" t="inlineStr">
         <is>
-          <t>80-95K€</t>
+          <t>75-85K€</t>
         </is>
       </c>
       <c r="P279" s="39" t="n"/>
@@ -50199,22 +50263,22 @@
       <c r="C280" s="39" t="n"/>
       <c r="D280" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager</t>
+          <t>Customer Success Manager Freelance</t>
         </is>
       </c>
       <c r="E280" s="39" t="inlineStr">
         <is>
-          <t>INFINIT</t>
+          <t>Ecair</t>
         </is>
       </c>
       <c r="F280" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G280" s="39" t="inlineStr">
         <is>
-          <t>CDI</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H280" s="39" t="inlineStr">
@@ -50233,14 +50297,10 @@
         </is>
       </c>
       <c r="K280" s="39" t="n"/>
-      <c r="L280" s="39" t="inlineStr">
-        <is>
-          <t>Posté il y a 1 semaine</t>
-        </is>
-      </c>
+      <c r="L280" s="39" t="n"/>
       <c r="M280" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-at-infinit-4429403501</t>
+          <t>https://www.welcometothejungle.com/fr/companies/ecair/jobs/customer-success-manager-freelance_paris</t>
         </is>
       </c>
       <c r="N280" s="39" t="inlineStr">
@@ -50250,14 +50310,14 @@
       </c>
       <c r="O280" s="39" t="inlineStr">
         <is>
-          <t>80-95K€</t>
+          <t>650€/j</t>
         </is>
       </c>
       <c r="P280" s="39" t="n"/>
       <c r="Q280" s="39" t="n"/>
     </row>
     <row r="281" ht="32" customHeight="1">
-      <c r="A281" s="99" t="inlineStr">
+      <c r="A281" s="90" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -50266,17 +50326,17 @@
       <c r="C281" s="39" t="n"/>
       <c r="D281" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager Key Accounts</t>
+          <t>Customer Success Manager France</t>
         </is>
       </c>
       <c r="E281" s="39" t="inlineStr">
         <is>
-          <t>Partoo</t>
+          <t>Peripass</t>
         </is>
       </c>
       <c r="F281" s="39" t="inlineStr">
         <is>
-          <t>welcometothejungle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G281" s="39" t="inlineStr">
@@ -50286,41 +50346,41 @@
       </c>
       <c r="H281" s="39" t="inlineStr">
         <is>
-          <t>Paris (75)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I281" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="J281" s="39" t="inlineStr">
         <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="K281" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>nc</t>
+        </is>
+      </c>
+      <c r="K281" s="39" t="n"/>
       <c r="L281" s="39" t="inlineStr">
         <is>
-          <t>Key Accounts local marketing SaaS, Paris hybride</t>
+          <t>Posté il y a 3 jours</t>
         </is>
       </c>
       <c r="M281" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/partoo/jobs/customer-success-manager-key-accounts-cdi-paris-h-f-x_paris</t>
-        </is>
-      </c>
-      <c r="N281" s="39" t="n"/>
-      <c r="O281" s="39" t="n"/>
-      <c r="P281" s="39" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
+          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-france-at-peripass-4436711714</t>
+        </is>
+      </c>
+      <c r="N281" s="39" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
+        </is>
+      </c>
+      <c r="O281" s="39" t="inlineStr">
+        <is>
+          <t>80-95K€</t>
+        </is>
+      </c>
+      <c r="P281" s="39" t="n"/>
       <c r="Q281" s="39" t="n"/>
     </row>
     <row r="282" ht="16" customHeight="1">
@@ -50338,12 +50398,12 @@
       </c>
       <c r="E282" s="39" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>INFINIT</t>
         </is>
       </c>
       <c r="F282" s="39" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G282" s="39" t="inlineStr">
@@ -50358,52 +50418,40 @@
       </c>
       <c r="I282" s="39" t="inlineStr">
         <is>
-          <t>Hybride</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="J282" s="39" t="inlineStr">
         <is>
-          <t>71-98K€ OTE</t>
-        </is>
-      </c>
-      <c r="K282" s="39" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
+          <t>nc</t>
+        </is>
+      </c>
+      <c r="K282" s="39" t="n"/>
       <c r="L282" s="39" t="inlineStr">
         <is>
-          <t>IAM/SSO, CSM enterprise, OTE 71-98K€. FREIN MAJEUR : français + italien requis (pas de mention anglais seul).</t>
+          <t>Posté il y a 1 semaine</t>
         </is>
       </c>
       <c r="M282" s="39" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/okta/jobs/customer-success-manager_paris_mnpmts4t</t>
+          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-at-infinit-4429403501</t>
         </is>
       </c>
       <c r="N282" s="39" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_CSM_EN.pdf</t>
+          <t>CV_GaetanFRANCOIS_CSM.html</t>
         </is>
       </c>
       <c r="O282" s="39" t="inlineStr">
         <is>
-          <t>71-98K€</t>
-        </is>
-      </c>
-      <c r="P282" s="39" t="inlineStr">
-        <is>
-          <t>07/2026</t>
-        </is>
-      </c>
-      <c r="Q282" s="39" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
+          <t>80-95K€</t>
+        </is>
+      </c>
+      <c r="P282" s="39" t="n"/>
+      <c r="Q282" s="39" t="n"/>
     </row>
     <row r="283" ht="16" customHeight="1">
-      <c r="A283" s="90" t="inlineStr">
+      <c r="A283" s="99" t="inlineStr">
         <is>
           <t>⭐⭐</t>
         </is>
@@ -50412,17 +50460,17 @@
       <c r="C283" s="39" t="n"/>
       <c r="D283" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager, France</t>
+          <t>Customer Success Manager Key Accounts</t>
         </is>
       </c>
       <c r="E283" s="39" t="inlineStr">
         <is>
-          <t>Heidi</t>
+          <t>Partoo</t>
         </is>
       </c>
       <c r="F283" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>welcometothejungle</t>
         </is>
       </c>
       <c r="G283" s="39" t="inlineStr">
@@ -50432,41 +50480,41 @@
       </c>
       <c r="H283" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris (75)</t>
         </is>
       </c>
       <c r="I283" s="39" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J283" s="39" t="inlineStr">
         <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K283" s="39" t="n"/>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="K283" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="L283" s="39" t="inlineStr">
         <is>
-          <t>HealthTech SaaS — déploiements hospitaliers, formation cliniciens, adoption IA médicale. FREIN : profil médical (médecin/infirmier) fortement préféré. Profil Gaëtan = hors cible principale. Publié il y a 2 semaines.</t>
+          <t>Key Accounts local marketing SaaS, Paris hybride</t>
         </is>
       </c>
       <c r="M283" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-france-at-heidi-4437124300</t>
-        </is>
-      </c>
-      <c r="N283" s="39" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O283" s="39" t="inlineStr">
-        <is>
-          <t>80-95K€</t>
-        </is>
-      </c>
-      <c r="P283" s="39" t="n"/>
+          <t>https://www.welcometothejungle.com/fr/companies/partoo/jobs/customer-success-manager-key-accounts-cdi-paris-h-f-x_paris</t>
+        </is>
+      </c>
+      <c r="N283" s="39" t="n"/>
+      <c r="O283" s="39" t="n"/>
+      <c r="P283" s="39" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
       <c r="Q283" s="39" t="n"/>
     </row>
     <row r="284" ht="32" customHeight="1">
@@ -50479,17 +50527,17 @@
       <c r="C284" s="39" t="n"/>
       <c r="D284" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager (m/f/d) - France</t>
+          <t>Customer Success Manager</t>
         </is>
       </c>
       <c r="E284" s="39" t="inlineStr">
         <is>
-          <t>Aras Corporation</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="F284" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G284" s="39" t="inlineStr">
@@ -50499,42 +50547,54 @@
       </c>
       <c r="H284" s="39" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I284" s="39" t="inlineStr">
         <is>
-          <t>Présentiel (20% mobilité)</t>
+          <t>Hybride</t>
         </is>
       </c>
       <c r="J284" s="39" t="inlineStr">
         <is>
+          <t>71-98K€ OTE</t>
+        </is>
+      </c>
+      <c r="K284" s="39" t="inlineStr">
+        <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="K284" s="39" t="n"/>
       <c r="L284" s="39" t="inlineStr">
         <is>
-          <t>Logiciel PLM (gestion cycle de vie produit), secteur manufacturier/industrie, 5+ ans. FREINS : Lyon présentiel, secteur PLM industriel hors SIRH/RH, 20% déplacements. Publié il y a 2 jours.</t>
+          <t>IAM/SSO, CSM enterprise, OTE 71-98K€. FREIN MAJEUR : français + italien requis (pas de mention anglais seul).</t>
         </is>
       </c>
       <c r="M284" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/customer-succes-manager-m-f-d-france-at-aras-corporation-4424777464</t>
+          <t>https://www.welcometothejungle.com/fr/companies/okta/jobs/customer-success-manager_paris_mnpmts4t</t>
         </is>
       </c>
       <c r="N284" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_CSM_EN.pdf</t>
         </is>
       </c>
       <c r="O284" s="39" t="inlineStr">
         <is>
-          <t>80-95K€</t>
-        </is>
-      </c>
-      <c r="P284" s="39" t="n"/>
-      <c r="Q284" s="39" t="n"/>
+          <t>71-98K€</t>
+        </is>
+      </c>
+      <c r="P284" s="39" t="inlineStr">
+        <is>
+          <t>07/2026</t>
+        </is>
+      </c>
+      <c r="Q284" s="39" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="32" customHeight="1">
       <c r="A285" s="90" t="inlineStr">
@@ -50546,12 +50606,12 @@
       <c r="C285" s="39" t="n"/>
       <c r="D285" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager</t>
+          <t>Customer Success Manager, France</t>
         </is>
       </c>
       <c r="E285" s="39" t="inlineStr">
         <is>
-          <t>Steeple</t>
+          <t>Heidi</t>
         </is>
       </c>
       <c r="F285" s="39" t="inlineStr">
@@ -50566,7 +50626,7 @@
       </c>
       <c r="H285" s="39" t="inlineStr">
         <is>
-          <t>Saint-Jacques-de-la-Lande (35)</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I285" s="39" t="inlineStr">
@@ -50576,18 +50636,18 @@
       </c>
       <c r="J285" s="39" t="inlineStr">
         <is>
-          <t>35-50K€</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="K285" s="39" t="n"/>
       <c r="L285" s="39" t="inlineStr">
         <is>
-          <t>SaaS logiciels, onboarding, audits clients, KPI adoption. FREINS : salaire bas (35-50K€), localisation Bretagne (Saint-Jacques-de-la-Lande près Rennes). Publié il y a 3 jours.</t>
+          <t>HealthTech SaaS — déploiements hospitaliers, formation cliniciens, adoption IA médicale. FREIN : profil médical (médecin/infirmier) fortement préféré. Profil Gaëtan = hors cible principale. Publié il y a 2 semaines.</t>
         </is>
       </c>
       <c r="M285" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-at-steeple-4441396209</t>
+          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-france-at-heidi-4437124300</t>
         </is>
       </c>
       <c r="N285" s="39" t="inlineStr">
@@ -50613,17 +50673,17 @@
       <c r="C286" s="39" t="n"/>
       <c r="D286" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager, EU</t>
+          <t>Customer Success Manager (m/f/d) - France</t>
         </is>
       </c>
       <c r="E286" s="39" t="inlineStr">
         <is>
-          <t>Pacvue</t>
+          <t>Aras Corporation</t>
         </is>
       </c>
       <c r="F286" s="39" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G286" s="39" t="inlineStr">
@@ -50633,34 +50693,38 @@
       </c>
       <c r="H286" s="39" t="inlineStr">
         <is>
-          <t>Remote UK ou Allemagne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="I286" s="39" t="inlineStr">
         <is>
-          <t>Oui (zone EU, France non listée explicitement)</t>
-        </is>
-      </c>
-      <c r="J286" s="39" t="n"/>
+          <t>Présentiel (20% mobilité)</t>
+        </is>
+      </c>
+      <c r="J286" s="39" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
       <c r="K286" s="39" t="n"/>
       <c r="L286" s="39" t="inlineStr">
         <is>
-          <t>Zone EU correspond au profil mais la France n'est pas explicitement listée comme éligible ; à vérifier en candidatant.</t>
+          <t>Logiciel PLM (gestion cycle de vie produit), secteur manufacturier/industrie, 5+ ans. FREINS : Lyon présentiel, secteur PLM industriel hors SIRH/RH, 20% déplacements. Publié il y a 2 jours.</t>
         </is>
       </c>
       <c r="M286" s="39" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/pacvue/jobs/4712905004</t>
+          <t>https://fr.linkedin.com/jobs/view/customer-succes-manager-m-f-d-france-at-aras-corporation-4424777464</t>
         </is>
       </c>
       <c r="N286" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
         </is>
       </c>
       <c r="O286" s="39" t="inlineStr">
         <is>
-          <t>75-85K€</t>
+          <t>80-95K€</t>
         </is>
       </c>
       <c r="P286" s="39" t="n"/>
@@ -50676,17 +50740,17 @@
       <c r="C287" s="39" t="n"/>
       <c r="D287" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager (Commercial / Scaled)</t>
+          <t>Customer Success Manager</t>
         </is>
       </c>
       <c r="E287" s="39" t="inlineStr">
         <is>
-          <t>Culture Amp</t>
+          <t>Steeple</t>
         </is>
       </c>
       <c r="F287" s="39" t="inlineStr">
         <is>
-          <t>indexventures.com (portfolio)</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G287" s="39" t="inlineStr">
@@ -50696,34 +50760,38 @@
       </c>
       <c r="H287" s="39" t="inlineStr">
         <is>
-          <t>Bureaux US/UK/Allemagne/Australie</t>
+          <t>Saint-Jacques-de-la-Lande (35)</t>
         </is>
       </c>
       <c r="I287" s="39" t="inlineStr">
         <is>
-          <t>Éligibilité France incertaine</t>
-        </is>
-      </c>
-      <c r="J287" s="39" t="n"/>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="J287" s="39" t="inlineStr">
+        <is>
+          <t>35-50K€</t>
+        </is>
+      </c>
       <c r="K287" s="39" t="n"/>
       <c r="L287" s="39" t="inlineStr">
         <is>
-          <t>Éditeur RH/People Analytics reconnu mais éligibilité remote depuis la France non confirmée ; à clarifier avant de postuler.</t>
+          <t>SaaS logiciels, onboarding, audits clients, KPI adoption. FREINS : salaire bas (35-50K€), localisation Bretagne (Saint-Jacques-de-la-Lande près Rennes). Publié il y a 3 jours.</t>
         </is>
       </c>
       <c r="M287" s="39" t="inlineStr">
         <is>
-          <t>https://www.indexventures.com/startup-jobs/culture-amp/customer-success-manager-commercial-4/</t>
+          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-at-steeple-4441396209</t>
         </is>
       </c>
       <c r="N287" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
+          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
         </is>
       </c>
       <c r="O287" s="39" t="inlineStr">
         <is>
-          <t>75-85K€</t>
+          <t>80-95K€</t>
         </is>
       </c>
       <c r="P287" s="39" t="n"/>
@@ -50739,53 +50807,57 @@
       <c r="C288" s="39" t="n"/>
       <c r="D288" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager F/H</t>
+          <t>Customer Success Manager, EU</t>
         </is>
       </c>
       <c r="E288" s="39" t="inlineStr">
         <is>
-          <t>n.c. (via APEC)</t>
+          <t>Pacvue</t>
         </is>
       </c>
       <c r="F288" s="39" t="inlineStr">
         <is>
-          <t>apec.fr</t>
-        </is>
-      </c>
-      <c r="G288" s="39" t="n"/>
+          <t>job-boards.greenhouse.io</t>
+        </is>
+      </c>
+      <c r="G288" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
       <c r="H288" s="39" t="inlineStr">
         <is>
-          <t>Toulouse (31)</t>
-        </is>
-      </c>
-      <c r="I288" s="39" t="n"/>
+          <t>Remote UK ou Allemagne</t>
+        </is>
+      </c>
+      <c r="I288" s="39" t="inlineStr">
+        <is>
+          <t>Oui (zone EU, France non listée explicitement)</t>
+        </is>
+      </c>
       <c r="J288" s="39" t="n"/>
       <c r="K288" s="39" t="n"/>
       <c r="L288" s="39" t="inlineStr">
         <is>
-          <t>URL d'annonce individuelle réelle issue de WebSearch ; APEC bloque le fetch direct (mur de login), détails à vérifier manuellement.</t>
+          <t>Zone EU correspond au profil mais la France n'est pas explicitement listée comme éligible ; à vérifier en candidatant.</t>
         </is>
       </c>
       <c r="M288" s="39" t="inlineStr">
         <is>
-          <t>https://www.apec.fr/candidat/recherche-emploi.html/emploi/detail-offre/173994098W</t>
+          <t>https://job-boards.greenhouse.io/pacvue/jobs/4712905004</t>
         </is>
       </c>
       <c r="N288" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
       <c r="O288" s="39" t="inlineStr">
         <is>
-          <t>80-95 K€</t>
-        </is>
-      </c>
-      <c r="P288" s="39" t="inlineStr">
-        <is>
-          <t>09/08/2026</t>
-        </is>
-      </c>
+          <t>75-85K€</t>
+        </is>
+      </c>
+      <c r="P288" s="39" t="n"/>
       <c r="Q288" s="39" t="n"/>
     </row>
     <row r="289">
@@ -50798,17 +50870,17 @@
       <c r="C289" s="39" t="n"/>
       <c r="D289" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager, SMB</t>
+          <t>Customer Success Manager (Commercial / Scaled)</t>
         </is>
       </c>
       <c r="E289" s="39" t="inlineStr">
         <is>
-          <t>ZigZag Global</t>
+          <t>Culture Amp</t>
         </is>
       </c>
       <c r="F289" s="39" t="inlineStr">
         <is>
-          <t>RemoteRocketship</t>
+          <t>indexventures.com (portfolio)</t>
         </is>
       </c>
       <c r="G289" s="39" t="inlineStr">
@@ -50818,41 +50890,37 @@
       </c>
       <c r="H289" s="39" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Bureaux US/UK/Allemagne/Australie</t>
         </is>
       </c>
       <c r="I289" s="39" t="inlineStr">
         <is>
-          <t>Oui</t>
+          <t>Éligibilité France incertaine</t>
         </is>
       </c>
       <c r="J289" s="39" t="n"/>
       <c r="K289" s="39" t="n"/>
       <c r="L289" s="39" t="inlineStr">
         <is>
-          <t>Fintech gestion des dépenses ; fetch direct bloqué, détails non confirmés au-delà du titre.</t>
+          <t>Éditeur RH/People Analytics reconnu mais éligibilité remote depuis la France non confirmée ; à clarifier avant de postuler.</t>
         </is>
       </c>
       <c r="M289" s="39" t="inlineStr">
         <is>
-          <t>https://www.remoterocketship.com/company/zigzag-global-global/jobs/customer-success-manager-smb-france-remote/</t>
+          <t>https://www.indexventures.com/startup-jobs/culture-amp/customer-success-manager-commercial-4/</t>
         </is>
       </c>
       <c r="N289" s="39" t="inlineStr">
         <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
+          <t>CV_GaetanFRANCOIS_CSM_EN.html</t>
         </is>
       </c>
       <c r="O289" s="39" t="inlineStr">
         <is>
-          <t>80-95 K€</t>
-        </is>
-      </c>
-      <c r="P289" s="39" t="inlineStr">
-        <is>
-          <t>09/08/2026</t>
-        </is>
-      </c>
+          <t>75-85K€</t>
+        </is>
+      </c>
+      <c r="P289" s="39" t="n"/>
       <c r="Q289" s="39" t="n"/>
     </row>
     <row r="290">
@@ -50861,61 +50929,58 @@
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>Customer Success Manager, French</t>
-        </is>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>Ventrata</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>RemoteRocketship</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="I290" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr">
-        <is>
-          <t>Fetch direct bloqué, détails non confirmés au-delà du titre.</t>
-        </is>
-      </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>https://www.remoterocketship.com/company/ventrata/jobs/customer-success-manager-french-france-remote/</t>
-        </is>
-      </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O290" t="inlineStr">
+      <c r="B290" s="39" t="n"/>
+      <c r="C290" s="39" t="n"/>
+      <c r="D290" s="39" t="inlineStr">
+        <is>
+          <t>Customer Success Manager F/H</t>
+        </is>
+      </c>
+      <c r="E290" s="39" t="inlineStr">
+        <is>
+          <t>n.c. (via APEC)</t>
+        </is>
+      </c>
+      <c r="F290" s="39" t="inlineStr">
+        <is>
+          <t>apec.fr</t>
+        </is>
+      </c>
+      <c r="G290" s="39" t="n"/>
+      <c r="H290" s="39" t="inlineStr">
+        <is>
+          <t>Toulouse (31)</t>
+        </is>
+      </c>
+      <c r="I290" s="39" t="n"/>
+      <c r="J290" s="39" t="n"/>
+      <c r="K290" s="39" t="n"/>
+      <c r="L290" s="39" t="inlineStr">
+        <is>
+          <t>URL d'annonce individuelle réelle issue de WebSearch ; APEC bloque le fetch direct (mur de login), détails à vérifier manuellement.</t>
+        </is>
+      </c>
+      <c r="M290" s="39" t="inlineStr">
+        <is>
+          <t>https://www.apec.fr/candidat/recherche-emploi.html/emploi/detail-offre/173994098W</t>
+        </is>
+      </c>
+      <c r="N290" s="39" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM.pdf</t>
+        </is>
+      </c>
+      <c r="O290" s="39" t="inlineStr">
         <is>
           <t>80-95 K€</t>
         </is>
       </c>
-      <c r="P290" t="inlineStr">
+      <c r="P290" s="39" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
+      <c r="Q290" s="39" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="90" t="inlineStr">
@@ -50923,61 +50988,66 @@
           <t>⭐⭐</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>Customer Success Relationship Manager</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>Fortive</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
+      <c r="B291" s="39" t="n"/>
+      <c r="C291" s="39" t="n"/>
+      <c r="D291" s="39" t="inlineStr">
+        <is>
+          <t>Customer Success Manager, SMB</t>
+        </is>
+      </c>
+      <c r="E291" s="39" t="inlineStr">
+        <is>
+          <t>ZigZag Global</t>
+        </is>
+      </c>
+      <c r="F291" s="39" t="inlineStr">
         <is>
           <t>RemoteRocketship</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr">
+      <c r="G291" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H291" s="39" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr">
+      <c r="I291" s="39" t="inlineStr">
         <is>
           <t>Oui</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr">
-        <is>
-          <t>Gestion de comptes/programmes SaaS (détection gaz) ; fetch direct bloqué.</t>
-        </is>
-      </c>
-      <c r="M291" t="inlineStr">
-        <is>
-          <t>https://www.remoterocketship.com/company/fortive/jobs/customer-success-relationship-manager-france-remote/</t>
-        </is>
-      </c>
-      <c r="N291" t="inlineStr">
+      <c r="J291" s="39" t="n"/>
+      <c r="K291" s="39" t="n"/>
+      <c r="L291" s="39" t="inlineStr">
+        <is>
+          <t>Fintech gestion des dépenses ; fetch direct bloqué, détails non confirmés au-delà du titre.</t>
+        </is>
+      </c>
+      <c r="M291" s="39" t="inlineStr">
+        <is>
+          <t>https://www.remoterocketship.com/company/zigzag-global-global/jobs/customer-success-manager-smb-france-remote/</t>
+        </is>
+      </c>
+      <c r="N291" s="39" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
         </is>
       </c>
-      <c r="O291" t="inlineStr">
+      <c r="O291" s="39" t="inlineStr">
         <is>
           <t>80-95 K€</t>
         </is>
       </c>
-      <c r="P291" t="inlineStr">
+      <c r="P291" s="39" t="inlineStr">
         <is>
           <t>09/08/2026</t>
         </is>
       </c>
+      <c r="Q291" s="39" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="90" t="inlineStr">
@@ -50987,12 +51057,12 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Customer Success Specialist, French-speaking</t>
+          <t>Customer Success Manager, French</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>One Click LCA</t>
+          <t>Ventrata</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -51017,12 +51087,12 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>SaaS décarbonation/construction, société finlandaise ; fetch direct bloqué.</t>
+          <t>Fetch direct bloqué, détails non confirmés au-delà du titre.</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>https://www.remoterocketship.com/company/one-click-lca/jobs/customer-success-specialist-french-speaking-france-remote/</t>
+          <t>https://www.remoterocketship.com/company/ventrata/jobs/customer-success-manager-french-france-remote/</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -51049,17 +51119,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Customer Success Manager - EMEA</t>
+          <t>Customer Success Relationship Manager</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tilla</t>
+          <t>Fortive</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Ashby</t>
+          <t>RemoteRocketship</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -51069,17 +51139,22 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>"Basé en Grèce" (remote)</t>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>Maritime tech (gestion des changements d'équipage) ; l'annonce précise une base en Grèce, éligibilité France incertaine.</t>
+          <t>Gestion de comptes/programmes SaaS (détection gaz) ; fetch direct bloqué.</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/tilla/823e58d1-e986-42d9-9441-47f31bb77a52</t>
+          <t>https://www.remoterocketship.com/company/fortive/jobs/customer-success-relationship-manager-france-remote/</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -51087,9 +51162,14 @@
           <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
         </is>
       </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>80-95 K€</t>
+        </is>
+      </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>09/08/2026</t>
         </is>
       </c>
     </row>
@@ -51103,27 +51183,27 @@
       <c r="C294" s="39" t="n"/>
       <c r="D294" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager (Tech Startup)</t>
+          <t>Customer Success Specialist, French-speaking</t>
         </is>
       </c>
       <c r="E294" s="39" t="inlineStr">
         <is>
-          <t>Rankbreeze</t>
+          <t>One Click LCA</t>
         </is>
       </c>
       <c r="F294" s="39" t="inlineStr">
         <is>
-          <t>weworkremotely.com</t>
+          <t>RemoteRocketship</t>
         </is>
       </c>
       <c r="G294" s="39" t="inlineStr">
         <is>
-          <t>Freelance/contractor long terme</t>
+          <t>CDI</t>
         </is>
       </c>
       <c r="H294" s="39" t="inlineStr">
         <is>
-          <t>Remote monde entier</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I294" s="39" t="inlineStr">
@@ -51131,20 +51211,16 @@
           <t>Oui</t>
         </is>
       </c>
-      <c r="J294" s="39" t="inlineStr">
-        <is>
-          <t>2000-2500 $/mois</t>
-        </is>
-      </c>
+      <c r="J294" s="39" t="n"/>
       <c r="K294" s="39" t="n"/>
       <c r="L294" s="39" t="inlineStr">
         <is>
-          <t>Startup SaaS proptech (vacation rental) ; salaire modeste mais le TJM n'est jamais un critère d'exclusion.</t>
+          <t>SaaS décarbonation/construction, société finlandaise ; fetch direct bloqué.</t>
         </is>
       </c>
       <c r="M294" s="39" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com/remote-jobs/rankbreeze-customer-success-manager-tech-startup</t>
+          <t>https://www.remoterocketship.com/company/one-click-lca/jobs/customer-success-specialist-french-speaking-france-remote/</t>
         </is>
       </c>
       <c r="N294" s="39" t="inlineStr">
@@ -51154,41 +51230,37 @@
       </c>
       <c r="O294" s="39" t="inlineStr">
         <is>
-          <t>2000-2500 $/mois</t>
+          <t>80-95 K€</t>
         </is>
       </c>
       <c r="P294" s="39" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="Q294" s="39" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="Q294" s="39" t="n"/>
     </row>
     <row r="295">
-      <c r="A295" s="53" t="inlineStr">
-        <is>
-          <t>⭐</t>
+      <c r="A295" s="90" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="B295" s="39" t="n"/>
       <c r="C295" s="39" t="n"/>
       <c r="D295" s="39" t="inlineStr">
         <is>
-          <t>Customer Success Manager</t>
+          <t>Customer Success Manager - EMEA</t>
         </is>
       </c>
       <c r="E295" s="39" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Tilla</t>
         </is>
       </c>
       <c r="F295" s="39" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Ashby</t>
         </is>
       </c>
       <c r="G295" s="39" t="inlineStr">
@@ -51198,109 +51270,243 @@
       </c>
       <c r="H295" s="39" t="inlineStr">
         <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="I295" s="39" t="inlineStr">
-        <is>
-          <t>N/C</t>
-        </is>
-      </c>
-      <c r="J295" s="39" t="inlineStr">
-        <is>
-          <t>71-98k€ OTE</t>
-        </is>
-      </c>
-      <c r="K295" s="39" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
+          <t>"Basé en Grèce" (remote)</t>
+        </is>
+      </c>
+      <c r="I295" s="39" t="n"/>
+      <c r="J295" s="39" t="n"/>
+      <c r="K295" s="39" t="n"/>
       <c r="L295" s="39" t="inlineStr">
         <is>
-          <t>Italien courant requis — éliminatoire ; 09/07/2026</t>
+          <t>Maritime tech (gestion des changements d'équipage) ; l'annonce précise une base en Grèce, éligibilité France incertaine.</t>
         </is>
       </c>
       <c r="M295" s="39" t="inlineStr">
         <is>
-          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-at-okta-4434842827</t>
-        </is>
-      </c>
-      <c r="N295" s="39" t="n"/>
+          <t>https://jobs.ashbyhq.com/tilla/823e58d1-e986-42d9-9441-47f31bb77a52</t>
+        </is>
+      </c>
+      <c r="N295" s="39" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
+        </is>
+      </c>
       <c r="O295" s="39" t="n"/>
       <c r="P295" s="39" t="inlineStr">
         <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="Q295" s="39" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="90" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="B296" s="39" t="n"/>
+      <c r="C296" s="39" t="n"/>
+      <c r="D296" s="39" t="inlineStr">
+        <is>
+          <t>Customer Success Manager (Tech Startup)</t>
+        </is>
+      </c>
+      <c r="E296" s="39" t="inlineStr">
+        <is>
+          <t>Rankbreeze</t>
+        </is>
+      </c>
+      <c r="F296" s="39" t="inlineStr">
+        <is>
+          <t>weworkremotely.com</t>
+        </is>
+      </c>
+      <c r="G296" s="39" t="inlineStr">
+        <is>
+          <t>Freelance/contractor long terme</t>
+        </is>
+      </c>
+      <c r="H296" s="39" t="inlineStr">
+        <is>
+          <t>Remote monde entier</t>
+        </is>
+      </c>
+      <c r="I296" s="39" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="J296" s="39" t="inlineStr">
+        <is>
+          <t>2000-2500 $/mois</t>
+        </is>
+      </c>
+      <c r="K296" s="39" t="n"/>
+      <c r="L296" s="39" t="inlineStr">
+        <is>
+          <t>Startup SaaS proptech (vacation rental) ; salaire modeste mais le TJM n'est jamais un critère d'exclusion.</t>
+        </is>
+      </c>
+      <c r="M296" s="39" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/remote-jobs/rankbreeze-customer-success-manager-tech-startup</t>
+        </is>
+      </c>
+      <c r="N296" s="39" t="inlineStr">
+        <is>
+          <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O296" s="39" t="inlineStr">
+        <is>
+          <t>2000-2500 $/mois</t>
+        </is>
+      </c>
+      <c r="P296" s="39" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="Q296" s="39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="53" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="B297" s="39" t="n"/>
+      <c r="C297" s="39" t="n"/>
+      <c r="D297" s="39" t="inlineStr">
+        <is>
+          <t>Customer Success Manager</t>
+        </is>
+      </c>
+      <c r="E297" s="39" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="F297" s="39" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="G297" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H297" s="39" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I297" s="39" t="inlineStr">
+        <is>
+          <t>N/C</t>
+        </is>
+      </c>
+      <c r="J297" s="39" t="inlineStr">
+        <is>
+          <t>71-98k€ OTE</t>
+        </is>
+      </c>
+      <c r="K297" s="39" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="L297" s="39" t="inlineStr">
+        <is>
+          <t>Italien courant requis — éliminatoire ; 09/07/2026</t>
+        </is>
+      </c>
+      <c r="M297" s="39" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/jobs/view/customer-success-manager-at-okta-4434842827</t>
+        </is>
+      </c>
+      <c r="N297" s="39" t="n"/>
+      <c r="O297" s="39" t="n"/>
+      <c r="P297" s="39" t="inlineStr">
+        <is>
           <t>10/07/2026</t>
         </is>
       </c>
-      <c r="Q295" s="39" t="inlineStr">
+      <c r="Q297" s="39" t="inlineStr">
         <is>
           <t>09/07/2026</t>
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" s="75" t="inlineStr">
+    <row r="298">
+      <c r="A298" s="75" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
+      <c r="D298" t="inlineStr">
         <is>
           <t>Customer Success Agent</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
+      <c r="E298" t="inlineStr">
         <is>
           <t>Breezy HR</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
+      <c r="F298" t="inlineStr">
         <is>
           <t>weworkremotely.com</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
         <is>
           <t>USA (horaires 9h-18h EST)</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr">
+      <c r="I298" t="inlineStr">
         <is>
           <t>Oui mais zone US</t>
         </is>
       </c>
-      <c r="J296" t="inlineStr">
+      <c r="J298" t="inlineStr">
         <is>
           <t>~45 K$</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
+      <c r="L298" t="inlineStr">
         <is>
           <t>Éditeur ATS/HR tech (fit sectoriel) mais niveau 'Agent' junior et horaires calés sur l'Est américain (15h-minuit heure FR), peu compatible.</t>
         </is>
       </c>
-      <c r="M296" t="inlineStr">
+      <c r="M298" t="inlineStr">
         <is>
           <t>https://weworkremotely.com/remote-jobs/breezy-hr-customer-success-agent-5</t>
         </is>
       </c>
-      <c r="N296" t="inlineStr">
+      <c r="N298" t="inlineStr">
         <is>
           <t>CV_GaetanFRANCOIS_CSM_EN.pdf</t>
         </is>
       </c>
-      <c r="P296" t="inlineStr">
+      <c r="P298" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="Q296" t="inlineStr">
+      <c r="Q298" t="inlineStr">
         <is>
           <t>2026</t>
         </is>

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -15114,7 +15114,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -15176,7 +15176,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -15074,17 +15074,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Senior Product Manager - Core Platform (Remote)</t>
+          <t>Product Manager</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Camunda</t>
+          <t>360Learning</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com</t>
+          <t>welcometothejungle.com</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -15094,32 +15094,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Full remote</t>
+          <t>Télétravail total</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Editeur d'orchestration de processus, entreprise remote-first. Gaetan avait deja cible Camunda (CV_GaetanFRANCOIS_Camunda_EN existe), donc le contexte est connu. Poste verifie ouvert par l'API Ashby le 14/08.</t>
+          <t>Plateforme de learning : le domaine recoupe directement l'experience de formation utilisateurs-cles et de transfert de connaissances. Teletravail total, editeur francais bien etabli. Un des meilleurs croisements produit/parcours du lot.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/camunda/b771e145-a5cf-4867-ad13-b54830e3b744</t>
+          <t>https://www.welcometothejungle.com/en/companies/360learning/jobs/product-manager_paris_360LE_lGeWWq1</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_FR.pdf</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>85-100 K€</t>
+          <t>75-90 K€</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -15136,17 +15136,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Senior Product Builder - Connectors Experience - EMEA</t>
+          <t>Product Manager</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Camunda</t>
+          <t>Side</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com</t>
+          <t>welcometothejungle.com</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -15156,32 +15156,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>EMEA</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Full remote</t>
+          <t>Télétravail total</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>55-59 K€</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Produit centre sur l'experience des connecteurs, donc sur l'integration : c'est l'angle le plus proche du parcours (parcours d'integration L'Oreal, charniere metier/developpeurs). Verifie ouvert par API.</t>
+          <t>Teletravail total, plus de 4 ans d'experience demandes, demarrage 31/08/2026. Remuneration sous la cible ; le salaire ne sert pas de filtre.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/camunda/05cb2825-dcd9-40e6-bf92-bda409d99374</t>
+          <t>https://www.welcometothejungle.com/fr/companies/side/jobs/product-manager_paris_SIDE_jRLO2Ar</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_FR.pdf</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>85-100 K€</t>
+          <t>75-90 K€</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -15203,7 +15208,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>360Learning</t>
+          <t>Inqom</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -15218,7 +15223,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Paris / Tours</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -15226,14 +15231,19 @@
           <t>Télétravail total</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>50-55 K€</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Plateforme de learning : le domaine recoupe directement l'experience de formation utilisateurs-cles et de transfert de connaissances. Teletravail total, editeur francais bien etabli. Un des meilleurs croisements produit/parcours du lot.</t>
+          <t>Teletravail total sur un SaaS comptable. Fourchette sous la cible, a negocier.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/en/companies/360learning/jobs/product-manager_paris_360LE_lGeWWq1</t>
+          <t>https://www.welcometothejungle.com/fr/companies/inqom/jobs/product-manager</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -15258,19 +15268,24 @@
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>À postuler</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Product Manager</t>
+          <t>Product Manager, Self Managed Service</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Side</t>
+          <t>Camunda</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>welcometothejungle.com</t>
+          <t>jobs.ashbyhq.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -15280,37 +15295,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Télétravail total</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>55-59 K€</t>
+          <t>Full remote</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Teletravail total, plus de 4 ans d'experience demandes, demarrage 31/08/2026. Remuneration sous la cible ; le salaire ne sert pas de filtre.</t>
+          <t>Seule candidature Camunda retenue. Le poste porte sur l'installation, la configuration et l'exploitation de Camunda 8 chez le client (on-premises, configurations enterprise, reduction de la friction de deploiement, travail avec pre-sales et solution architects) ; c'est le parcours SAP HR on-prem vers SuccessFactors. Lacune a concéder en LM : Kubernetes et Helm.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/side/jobs/product-manager_paris_SIDE_jRLO2Ar</t>
+          <t>https://jobs.ashbyhq.com/camunda/5652a3f3-e418-4e91-b58b-4be13f36853b</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_FR.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>75-90 K€</t>
+          <t>80-95 K€</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -15320,24 +15330,24 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="91" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐⭐</t>
+      <c r="A6" s="90" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Product Manager</t>
+          <t>Product Manager: Customer Onboarding Experience</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Inqom</t>
+          <t>Constructor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>welcometothejungle.com</t>
+          <t>jobs.ashbyhq.com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -15347,37 +15357,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paris / Tours</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Télétravail total</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>50-55 K€</t>
+          <t>Full remote</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Teletravail total sur un SaaS comptable. Fourchette sous la cible, a negocier.</t>
+          <t>Propriete du parcours d'integration client (SDK, docs, instrumentation de tracking), north star time-to-value. Atouts : propriete produit reelle chez WallOfTraders.com, parcours d'integration L'Oreal sur 40 pays, role de charniere metier/developpeurs, redaction de specifications. LACUNE DURE : ils exigent 3+ ans de PM sur produit oriente developpeurs (SDK, API, tracking) ; Gaetan n'en a pas, c'est un filtre potentiellement eliminatoire. Candidature plus risquee que le poste Regional Manager CS chez le meme employeur.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/inqom/jobs/product-manager</t>
+          <t>https://jobs.ashbyhq.com/constructor/e8fa6194-ef2e-47d3-ab45-a9112d87da24</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_FR.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>75-90 K€</t>
+          <t>80-100 K€</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -15394,17 +15399,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Product Manager: Customer Onboarding Experience</t>
+          <t>Product Manager (senior level)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Constructor</t>
+          <t>Joko</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com</t>
+          <t>welcometothejungle.com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -15414,32 +15419,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Full remote</t>
+          <t>Télétravail total</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Propriete du parcours d'integration client (SDK, docs, instrumentation de tracking), north star time-to-value. Atouts : propriete produit reelle chez WallOfTraders.com, parcours d'integration L'Oreal sur 40 pays, role de charniere metier/developpeurs, redaction de specifications. LACUNE DURE : ils exigent 3+ ans de PM sur produit oriente developpeurs (SDK, API, tracking) ; Gaetan n'en a pas, c'est un filtre potentiellement eliminatoire. Candidature plus risquee que le poste Regional Manager CS chez le meme employeur.</t>
+          <t>Niveau senior explicite, teletravail total. Produit B2C, ce qui recoupe l'experience WallOfTraders.com.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/constructor/e8fa6194-ef2e-47d3-ab45-a9112d87da24</t>
+          <t>https://www.welcometothejungle.com/en/companies/joko/jobs/product-manager-senior-level</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>80-100 K€</t>
+          <t>75-90 K€</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -15456,17 +15461,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Product Manager, Self Managed Service</t>
+          <t>Product Manager (full remote avec déplacements)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Camunda</t>
+          <t>RISE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com</t>
+          <t>welcometothejungle.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -15476,32 +15481,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Full remote</t>
+          <t>Télétravail total</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Troisieme poste produit ouvert chez Camunda ; perimetre self-managed, plus technique. Verifie ouvert par API.</t>
+          <t>Full remote avec deplacements ponctuels, compatible avec une base a Anglet.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/camunda/5652a3f3-e418-4e91-b58b-4be13f36853b</t>
+          <t>https://www.welcometothejungle.com/fr/companies/rise/jobs/28b1f52c-1924-40ec-b7e0-18bbdcda6c56</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_FR.pdf</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>80-95 K€</t>
+          <t>75-90 K€</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -15518,12 +15523,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Product Manager (senior level)</t>
+          <t>Product Manager</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Joko</t>
+          <t>Follow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -15538,7 +15543,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>France</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -15548,17 +15553,17 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Niveau senior explicite, teletravail total. Produit B2C, ce qui recoupe l'experience WallOfTraders.com.</t>
+          <t>Teletravail total, secteur sante. A qualifier sur la seniorite attendue.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/en/companies/joko/jobs/product-manager-senior-level</t>
+          <t>https://www.welcometothejungle.com/fr/companies/follow-health/jobs/product-manager</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_FR.pdf</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -15580,17 +15585,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Product Manager (full remote avec déplacements)</t>
+          <t>Product Manager, Data Activation</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RISE</t>
+          <t>n.c. (via Jobgether)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>welcometothejungle.com</t>
+          <t>jobs.lever.co</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -15605,22 +15610,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Télétravail total</t>
+          <t>Full remote</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Full remote avec deplacements ponctuels, compatible avec une base a Anglet.</t>
+          <t>Remote depuis la France, verifie ouvert par l'API Lever. Jobgether publie la meme offre par pays ; seule la variante France est retenue ici.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/rise/jobs/28b1f52c-1924-40ec-b7e0-18bbdcda6c56</t>
+          <t>https://jobs.lever.co/jobgether/dad5d8dc-4e02-4536-b7f6-8680e1df16ce</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_FR.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -15642,17 +15647,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Product Manager</t>
+          <t>Product Manager, Data Orchestration</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Follow</t>
+          <t>n.c. (via Jobgether)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>welcometothejungle.com</t>
+          <t>jobs.lever.co</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -15667,22 +15672,22 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Télétravail total</t>
+          <t>Full remote</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Teletravail total, secteur sante. A qualifier sur la seniorite attendue.</t>
+          <t>Remote depuis la France, verifie ouvert par l'API Lever.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.welcometothejungle.com/fr/companies/follow-health/jobs/product-manager</t>
+          <t>https://jobs.lever.co/jobgether/5245a149-8431-4452-ab44-50cbb9bafbcf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_FR.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -15704,7 +15709,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Product Manager, Data Activation</t>
+          <t>Product Owner</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -15734,17 +15739,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Remote depuis la France, verifie ouvert par l'API Lever. Jobgether publie la meme offre par pays ; seule la variante France est retenue ici.</t>
+          <t>Product Owner en full remote depuis la France, verifie ouvert par l'API Lever.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/jobgether/dad5d8dc-4e02-4536-b7f6-8680e1df16ce</t>
+          <t>https://jobs.lever.co/jobgether/5405e9ec-8ab3-4075-8f5e-96425e4f11a6</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -15766,7 +15771,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Product Manager, Data Orchestration</t>
+          <t>B2C Growth Product Manager</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -15796,17 +15801,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Remote depuis la France, verifie ouvert par l'API Lever.</t>
+          <t>Produit B2C oriente growth : recoupe directement WallOfTraders.com (acquisition SEO, paid social, boucle de retour utilisateurs).</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/jobgether/5245a149-8431-4452-ab44-50cbb9bafbcf</t>
+          <t>https://jobs.lever.co/jobgether/bae287fc-687d-48a6-a860-100430cbe25e</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -15828,7 +15833,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>Sr. Product Manager, Core Platform</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -15848,7 +15853,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>France / Pays-Bas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -15858,22 +15863,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Product Owner en full remote depuis la France, verifie ouvert par l'API Lever.</t>
+          <t>Poste senior sur plateforme coeur, full remote.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/jobgether/5405e9ec-8ab3-4075-8f5e-96425e4f11a6</t>
+          <t>https://jobs.lever.co/jobgether/3efb5da5-0c07-4209-a4b6-037ead7571c2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>75-90 K€</t>
+          <t>80-95 K€</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -15890,12 +15895,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B2C Growth Product Manager</t>
+          <t>Senior Product Manager</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>n.c. (via Jobgether)</t>
+          <t>Pennylane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -15910,156 +15915,166 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>Remote Europe</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Scale-up francaise, remote depuis n'importe ou en Europe. URL issue de WebSearch : l'API Lever n'a pas repondu sur ce slug, verifier que l'annonce est encore ouverte avant de candidater.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/pennylane/e821e150-f513-4297-86a7-6d2ee25ac50c</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>80-95 K€</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="69" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hors profil</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Senior Product Manager - Core Platform (Remote)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Camunda</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>jobs.ashbyhq.com</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Produit B2C oriente growth : recoupe directement WallOfTraders.com (acquisition SEO, paid social, boucle de retour utilisateurs).</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/jobgether/bae287fc-687d-48a6-a860-100430cbe25e</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>75-90 K€</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Ecarte : moteur Zeebe, systemes distribues, scalabilite et fiabilite ; expertise non couverte. Une seule candidature Camunda, celle sur Self Managed Service.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/camunda/b771e145-a5cf-4867-ad13-b54830e3b744</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>85-100 K€</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="90" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Sr. Product Manager, Core Platform</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>n.c. (via Jobgether)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>jobs.lever.co</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>France / Pays-Bas</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="69" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Hors profil</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Senior Product Builder - Connectors Experience - EMEA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Camunda</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>jobs.ashbyhq.com</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CDI</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>EMEA</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>Full remote</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Poste senior sur plateforme coeur, full remote.</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/jobgether/3efb5da5-0c07-4209-a4b6-037ead7571c2</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Ecarte : annonce dupliquee par Camunda (version generique + version EMEA) et role de builder hands-on (prototype, build, ship, relecture de code). Une seule candidature Camunda, celle sur Self Managed Service.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/camunda/05cb2825-dcd9-40e6-bf92-bda409d99374</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Resume_GaetanFRANCOIS_PM_Platform_EN.pdf</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>80-95 K€</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="90" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Senior Product Manager</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Pennylane</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>jobs.lever.co</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CDI</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Remote Europe</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Scale-up francaise, remote depuis n'importe ou en Europe. URL issue de WebSearch : l'API Lever n'a pas repondu sur ce slug, verifier que l'annonce est encore ouverte avant de candidater.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/pennylane/e821e150-f513-4297-86a7-6d2ee25ac50c</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Resume_GaetanFRANCOIS_PM_EN.pdf</t>
-        </is>
-      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>80-95 K€</t>
+          <t>85-100 K€</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -15303,9 +15303,14 @@
           <t>Full remote</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Total Target Cash (base + variable) : US 143,8-231,9 K$ / UK 90,3-148,5 K£ / SG 178,6-267,9 KS$ / CA 152,7-251,2 KC$. Fourchette du mini marche Standard au maxi marche Major. Hors ces pays : embauche via Remote.com, calculateur personnalise apres le 1er entretien. VSOP (equity) en plus.</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Seule candidature Camunda retenue. Le poste porte sur l'installation, la configuration et l'exploitation de Camunda 8 chez le client (on-premises, configurations enterprise, reduction de la friction de deploiement, travail avec pre-sales et solution architects) ; c'est le parcours SAP HR on-prem vers SuccessFactors. Lacune a concéder en LM : Kubernetes et Helm.</t>
+          <t>Seule candidature Camunda retenue. Le poste porte sur l'installation, la configuration et l'exploitation de Camunda 8 chez le client (on-premises, configurations enterprise, reduction de la friction de deploiement, travail avec pre-sales et solution architects) ; c'est le parcours SAP HR on-prem vers SuccessFactors. Lacune a concéder en LM : Kubernetes et Helm. Salaire : viser 100-115 K€ TTC ; la France compte comme marche Standard, donc bas de fourchette des marches Standard (UK mini ~106 K€), et ils annoncent recruter dans la premiere moitie de la fourchette.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -15320,7 +15325,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>80-95 K€</t>
+          <t>100-115 K€</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17540" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offres SIRH" sheetId="1" state="visible" r:id="rId1"/>

--- a/offres_emploi.xlsx
+++ b/offres_emploi.xlsx
@@ -1421,6 +1421,11 @@
           <t>Full remote</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>OTE 110-146 K€ (grille France) + equity</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>Encadrement d'une equipe de deploiement client sur l'EMEA, chez un editeur d'ATS. Quinze ans de deploiement SIRH multi-pays plus l'encadrement d'equipe : c'est le poste le plus proche du parcours reel dans cette relance. Full remote depuis l'Union europeenne.</t>
@@ -1433,12 +1438,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Resume_GaetanFRANCOIS_SIRH_EN.pdf</t>
+          <t>Resume_GaetanFRANCOIS_Ashby_EN.pdf</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>90-110 K€</t>
+          <t>110-146 K€ (OTE)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
